--- a/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
+++ b/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarashan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25BD85DA-7875-EF40-8948-12E63B8AEB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8FEB08-DE0C-E44D-B295-D6C844FD0FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="WCu/6944McHvHyNK2onvg6JRC0bml1GLhisApHsn1DjCTkOjvjd5Bi7ovaPAo2yvWdxJpoVq3+3HJlZ/+nApuw==" workbookSaltValue="zKo6aCdJBNVkW2e5aPCnBA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-20" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="317">
   <si>
     <t>Source Note</t>
   </si>
@@ -807,9 +807,6 @@
     <t>2026E Consolidated Sales Revenue (forward-looking)</t>
   </si>
   <si>
-    <t>Bolt Technology OÜ - Draft Valuation Model</t>
-  </si>
-  <si>
     <t>Mid-year discounting convention (period offset)</t>
   </si>
   <si>
@@ -984,9 +981,6 @@
     <t>Discounted Unlevered FCF</t>
   </si>
   <si>
-    <t>Disounted Cashflow</t>
-  </si>
-  <si>
     <t>Blended pre-money enterprise and equity valuations &amp; IPO pricing analysis</t>
   </si>
   <si>
@@ -994,6 +988,15 @@
   </si>
   <si>
     <t>Matrix showing Pre-Money Implied Share Price at varying EV/ Sales multiples.</t>
+  </si>
+  <si>
+    <t>Discounted Cashflow</t>
+  </si>
+  <si>
+    <t>Any unauthorized reproduction, distribution, dissemination, or disclosure of these materials to third parties without prior written consent is strictly prohibited.</t>
+  </si>
+  <si>
+    <t>Bolt Technology OÜ - Pre-IPO Equity Valuation Model</t>
   </si>
 </sst>
 </file>
@@ -8627,7 +8630,7 @@
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.83203125" customWidth="1"/>
@@ -8638,7 +8641,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>253</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -8717,7 +8720,7 @@
         <v>248</v>
       </c>
       <c r="D25" s="95" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -8738,7 +8741,7 @@
     </row>
     <row r="28" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="250" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C28" s="95"/>
       <c r="D28" s="95"/>
@@ -8750,7 +8753,7 @@
     </row>
     <row r="30" spans="1:12" ht="86" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="276" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C30" s="276"/>
       <c r="D30" s="276"/>
@@ -8763,18 +8766,34 @@
       <c r="K30" s="276"/>
       <c r="L30" s="276"/>
     </row>
-    <row r="32" spans="1:12" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A32" s="127" t="s">
+    <row r="31" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="276" t="s">
+        <v>315</v>
+      </c>
+      <c r="C31" s="276"/>
+      <c r="D31" s="276"/>
+      <c r="E31" s="276"/>
+      <c r="F31" s="276"/>
+      <c r="G31" s="276"/>
+      <c r="H31" s="276"/>
+      <c r="I31" s="276"/>
+      <c r="J31" s="276"/>
+      <c r="K31" s="276"/>
+      <c r="L31" s="276"/>
+    </row>
+    <row r="33" spans="1:2" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A33" s="127" t="s">
         <v>122</v>
       </c>
-      <c r="B32" s="125" t="s">
+      <c r="B33" s="125" t="s">
         <v>124</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="pYNSFFgIN885Fwxqwp0dL/RBi4CAGSGUa//j0NAc8b+JuJ+7SOGoUTTJWQSN/hYeQ38ZMq4jQFrtaVE/Hnnnvw==" saltValue="pBHB/2stMvkYuJYjbMVEWw==" spinCount="100000" sheet="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <mergeCells count="1">
+  <sheetProtection algorithmName="SHA-512" hashValue="ewXWeb1Xe8czjAyha3VgZJOk4X9YB2YMJwuY/PtH+hzuQPR4EXmmF+bEFvbcMgD4cOHllqDD0+BrS9DNBZ6rxQ==" saltValue="MG57gZMn+33HKghB9USjPA==" spinCount="100000" sheet="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
+  <mergeCells count="2">
     <mergeCell ref="B30:L30"/>
+    <mergeCell ref="B31:L31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8803,7 +8822,7 @@
     <row r="1" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="str">
         <f>Contents!$A1</f>
-        <v>Bolt Technology OÜ - Draft Valuation Model</v>
+        <v>Bolt Technology OÜ - Pre-IPO Equity Valuation Model</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -10267,7 +10286,7 @@
     <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="249" t="str">
         <f>Contents!$A1</f>
-        <v>Bolt Technology OÜ - Draft Valuation Model</v>
+        <v>Bolt Technology OÜ - Pre-IPO Equity Valuation Model</v>
       </c>
       <c r="B1" s="90"/>
     </row>
@@ -10825,7 +10844,7 @@
     <row r="1" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="str">
         <f>Contents!$A1</f>
-        <v>Bolt Technology OÜ - Draft Valuation Model</v>
+        <v>Bolt Technology OÜ - Pre-IPO Equity Valuation Model</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -10845,7 +10864,7 @@
         <v>122</v>
       </c>
       <c r="B5" s="125" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C5" s="204"/>
     </row>
@@ -10856,7 +10875,7 @@
     </row>
     <row r="7" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B7" s="160" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C7" s="206" t="s">
         <v>58</v>
@@ -10869,7 +10888,7 @@
     </row>
     <row r="8" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B8" s="160" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C8" s="206" t="s">
         <v>69</v>
@@ -10882,7 +10901,7 @@
     </row>
     <row r="9" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B9" s="160" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C9" s="206" t="s">
         <v>58</v>
@@ -10895,7 +10914,7 @@
     </row>
     <row r="10" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" s="160" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C10" s="206" t="s">
         <v>58</v>
@@ -10908,7 +10927,7 @@
     </row>
     <row r="11" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" s="160" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C11" s="206" t="s">
         <v>69</v>
@@ -10921,7 +10940,7 @@
     </row>
     <row r="12" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B12" s="160" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C12" s="206" t="s">
         <v>58</v>
@@ -10940,7 +10959,7 @@
     </row>
     <row r="14" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="160" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C14" s="206" t="s">
         <v>69</v>
@@ -10953,7 +10972,7 @@
     </row>
     <row r="15" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B15" s="160" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C15" s="206" t="s">
         <v>58</v>
@@ -10966,7 +10985,7 @@
     </row>
     <row r="16" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="160" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C16" s="206" t="s">
         <v>58</v>
@@ -10979,7 +10998,7 @@
     </row>
     <row r="17" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B17" s="160" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C17" s="206" t="s">
         <v>58</v>
@@ -10992,7 +11011,7 @@
     </row>
     <row r="18" spans="1:9" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="166" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C18" s="207" t="s">
         <v>58</v>
@@ -11011,7 +11030,7 @@
     </row>
     <row r="20" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B20" s="160" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C20" s="206" t="s">
         <v>58</v>
@@ -11024,7 +11043,7 @@
     </row>
     <row r="21" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B21" s="160" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C21" s="206" t="s">
         <v>58</v>
@@ -11037,7 +11056,7 @@
     </row>
     <row r="22" spans="1:9" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B22" s="270" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C22" s="271" t="s">
         <v>58</v>
@@ -11056,7 +11075,7 @@
     </row>
     <row r="24" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B24" s="160" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C24" s="206" t="s">
         <v>58</v>
@@ -11069,10 +11088,10 @@
     </row>
     <row r="25" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B25" s="160" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C25" s="206" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D25" s="168">
         <f>i_Inputs!$D$78</f>
@@ -11082,7 +11101,7 @@
     </row>
     <row r="26" spans="1:9" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="273" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C26" s="274" t="s">
         <v>58</v>
@@ -11114,7 +11133,7 @@
     </row>
     <row r="30" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B30" s="160" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C30" s="206" t="s">
         <v>58</v>
@@ -11148,7 +11167,7 @@
     </row>
     <row r="32" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B32" s="160" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C32" s="206" t="s">
         <v>226</v>
@@ -11175,7 +11194,7 @@
     </row>
     <row r="34" spans="2:9" s="52" customFormat="1" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B34" s="218" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C34" s="219"/>
       <c r="D34" s="220"/>
@@ -11202,10 +11221,10 @@
     </row>
     <row r="35" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B35" s="160" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C35" s="211" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D35" s="172"/>
       <c r="E35" s="173">
@@ -11231,7 +11250,7 @@
     </row>
     <row r="36" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B36" s="160" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C36" s="206" t="s">
         <v>226</v>
@@ -11260,10 +11279,10 @@
     </row>
     <row r="37" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="160" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C37" s="211" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D37" s="172"/>
       <c r="E37" s="173">
@@ -11299,7 +11318,7 @@
     </row>
     <row r="39" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B39" s="160" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C39" s="206" t="s">
         <v>8</v>
@@ -11328,7 +11347,7 @@
     </row>
     <row r="40" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B40" s="160" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C40" s="206" t="s">
         <v>69</v>
@@ -11357,7 +11376,7 @@
     </row>
     <row r="41" spans="2:9" s="52" customFormat="1" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B41" s="199" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C41" s="209" t="s">
         <v>8</v>
@@ -11396,7 +11415,7 @@
     </row>
     <row r="43" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B43" s="160" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C43" s="206" t="s">
         <v>8</v>
@@ -11413,7 +11432,7 @@
     </row>
     <row r="44" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B44" s="160" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C44" s="206" t="s">
         <v>8</v>
@@ -11845,7 +11864,7 @@
     </row>
     <row r="80" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B80" s="253" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C80" s="254" t="s">
         <v>108</v>
@@ -11870,7 +11889,7 @@
     </row>
     <row r="83" spans="1:8" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B83" s="187" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="84" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
@@ -11997,7 +12016,7 @@
       <c r="C90" s="210"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="hCXB8rW3zrCC8gVKh75B+GccbSIDBL1Z5zkfda2YpKdmJtk22ND44MAPu09n9yvL+q5BrCPfysCHOUb9eXm5Bw==" saltValue="vDdGpalC0CN+39GTdlChYQ==" spinCount="100000" sheet="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="XuVaUcrAzULq9PL4q9TTlVrpSY08DtX2gh5PXiEH7kLA4xErEUtlowd7nZNBbL9pjq2a+Eizdb17fI7HL82bKg==" saltValue="wGtr3wTUCBvC4Oeqfo7XaA==" spinCount="100000" sheet="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
@@ -12021,7 +12040,7 @@
     <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="str">
         <f>Contents!$A1</f>
-        <v>Bolt Technology OÜ - Draft Valuation Model</v>
+        <v>Bolt Technology OÜ - Pre-IPO Equity Valuation Model</v>
       </c>
       <c r="B1" s="3"/>
     </row>
@@ -12985,7 +13004,7 @@
     <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="str">
         <f>Contents!$A1</f>
-        <v>Bolt Technology OÜ - Draft Valuation Model</v>
+        <v>Bolt Technology OÜ - Pre-IPO Equity Valuation Model</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -14080,7 +14099,7 @@
     <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="str">
         <f>Contents!$A1</f>
-        <v>Bolt Technology OÜ - Draft Valuation Model</v>
+        <v>Bolt Technology OÜ - Pre-IPO Equity Valuation Model</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -14120,7 +14139,7 @@
         <v>2028E</v>
       </c>
       <c r="J4" s="128" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="131" customFormat="1" ht="19" x14ac:dyDescent="0.2">
@@ -14280,7 +14299,7 @@
         <v>0.4</v>
       </c>
       <c r="J16" s="116" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14475,7 +14494,7 @@
     </row>
     <row r="29" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B29" s="34" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>58</v>
@@ -14816,12 +14835,12 @@
       <c r="H54" s="19"/>
       <c r="I54" s="19"/>
       <c r="J54" s="116" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="55" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B55" s="34" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C55" s="33" t="s">
         <v>58</v>
@@ -14840,7 +14859,7 @@
     </row>
     <row r="56" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B56" s="34" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C56" s="33" t="s">
         <v>69</v>
@@ -14859,7 +14878,7 @@
     </row>
     <row r="57" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B57" s="34" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C57" s="33" t="s">
         <v>69</v>
@@ -14977,7 +14996,7 @@
     </row>
     <row r="64" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B64" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C64" s="33" t="s">
         <v>226</v>
@@ -14991,12 +15010,12 @@
       <c r="H64" s="19"/>
       <c r="I64" s="19"/>
       <c r="J64" s="116" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="65" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B65" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C65" s="33" t="s">
         <v>58</v>
@@ -15010,7 +15029,7 @@
       <c r="H65" s="19"/>
       <c r="I65" s="19"/>
       <c r="J65" s="116" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="67" spans="1:10" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
@@ -15018,7 +15037,7 @@
         <v>122</v>
       </c>
       <c r="B67" s="125" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="68" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -15027,7 +15046,7 @@
     </row>
     <row r="69" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B69" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C69" s="33" t="s">
         <v>58</v>
@@ -15041,12 +15060,12 @@
       <c r="H69" s="19"/>
       <c r="I69" s="19"/>
       <c r="J69" s="116" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="70" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B70" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C70" s="33" t="s">
         <v>58</v>
@@ -15060,12 +15079,12 @@
       <c r="H70" s="19"/>
       <c r="I70" s="19"/>
       <c r="J70" s="116" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="71" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B71" s="34" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C71" s="33" t="s">
         <v>58</v>
@@ -15079,12 +15098,12 @@
       <c r="H71" s="19"/>
       <c r="I71" s="19"/>
       <c r="J71" s="116" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="72" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B72" s="34" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C72" s="33" t="s">
         <v>69</v>
@@ -15098,12 +15117,12 @@
       <c r="H72" s="19"/>
       <c r="I72" s="19"/>
       <c r="J72" s="116" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="73" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B73" s="34" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C73" s="33" t="s">
         <v>58</v>
@@ -15117,12 +15136,12 @@
       <c r="H73" s="19"/>
       <c r="I73" s="19"/>
       <c r="J73" s="116" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="74" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B74" s="34" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C74" s="33" t="s">
         <v>58</v>
@@ -15137,12 +15156,12 @@
       <c r="H74" s="19"/>
       <c r="I74" s="19"/>
       <c r="J74" s="116" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="75" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B75" s="34" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C75" s="33" t="s">
         <v>58</v>
@@ -15157,12 +15176,12 @@
       <c r="H75" s="19"/>
       <c r="I75" s="19"/>
       <c r="J75" s="116" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="76" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B76" s="34" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C76" s="33" t="s">
         <v>58</v>
@@ -15176,12 +15195,12 @@
       <c r="H76" s="19"/>
       <c r="I76" s="19"/>
       <c r="J76" s="116" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="77" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B77" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C77" s="33" t="s">
         <v>58</v>
@@ -15196,15 +15215,15 @@
       <c r="H77" s="19"/>
       <c r="I77" s="19"/>
       <c r="J77" s="116" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="78" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B78" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C78" s="33" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D78" s="120">
         <v>1</v>
@@ -15215,7 +15234,7 @@
       <c r="H78" s="19"/>
       <c r="I78" s="19"/>
       <c r="J78" s="116" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">

--- a/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
+++ b/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarashan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8FEB08-DE0C-E44D-B295-D6C844FD0FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8A98D7-D1ED-D44C-9611-F44F5B17AA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="WCu/6944McHvHyNK2onvg6JRC0bml1GLhisApHsn1DjCTkOjvjd5Bi7ovaPAo2yvWdxJpoVq3+3HJlZ/+nApuw==" workbookSaltValue="zKo6aCdJBNVkW2e5aPCnBA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contents" sheetId="6" r:id="rId1"/>
@@ -423,9 +423,6 @@
     <t>End of Worksheet</t>
   </si>
   <si>
-    <t>Source: Bolt Technology OÜ Consolidated Annual Report 2025 (AS PricewaterhouseCoopers audit)</t>
-  </si>
-  <si>
     <t>Sensitivity Analysis: Implied IPO Share Price (EUR)</t>
   </si>
   <si>
@@ -993,10 +990,13 @@
     <t>Discounted Cashflow</t>
   </si>
   <si>
-    <t>Any unauthorized reproduction, distribution, dissemination, or disclosure of these materials to third parties without prior written consent is strictly prohibited.</t>
-  </si>
-  <si>
     <t>Bolt Technology OÜ - Pre-IPO Equity Valuation Model</t>
+  </si>
+  <si>
+    <t>Confidentiality: Any unauthorized reproduction, distribution, dissemination, or disclosure of these materials to third parties without prior written consent is strictly prohibited.</t>
+  </si>
+  <si>
+    <t>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</t>
   </si>
 </sst>
 </file>
@@ -1018,7 +1018,7 @@
     <numFmt numFmtId="174" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="175" formatCode="0.00\x"/>
   </numFmts>
-  <fonts count="86" x14ac:knownFonts="1">
+  <fonts count="84" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1495,24 +1495,6 @@
       <name val="Calibri (Body)"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri (Body)"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri (Body)"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="14"/>
       <color rgb="FF595959"/>
@@ -1628,6 +1610,13 @@
       <i/>
       <sz val="12"/>
       <color rgb="FF595959"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -2096,7 +2085,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="277">
+  <cellXfs count="275">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2547,33 +2536,12 @@
     <xf numFmtId="3" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="69" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="49" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="167" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="50" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2614,87 +2582,84 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="74" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="71" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="17" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="17" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="173" fontId="64" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="72" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="69" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="72" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="69" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="71" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="68" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="71" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="68" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="72" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="69" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="72" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="69" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2716,39 +2681,39 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="81" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="72" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="69" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="72" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="69" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2760,7 +2725,7 @@
     <xf numFmtId="0" fontId="67" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="64" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2772,16 +2737,10 @@
     <xf numFmtId="167" fontId="64" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="70" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="67" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="64" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2790,7 +2749,7 @@
     <xf numFmtId="0" fontId="67" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="64" fillId="13" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2799,7 +2758,7 @@
     <xf numFmtId="0" fontId="67" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="64" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2811,7 +2770,7 @@
     <xf numFmtId="0" fontId="67" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="64" fillId="4" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2820,14 +2779,38 @@
     <xf numFmtId="0" fontId="67" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="64" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="67" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -8641,12 +8624,12 @@
   <sheetData>
     <row r="1" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="51" t="s">
-        <v>125</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="134" customFormat="1" ht="21" x14ac:dyDescent="0.25">
@@ -8684,7 +8667,7 @@
         <v>122</v>
       </c>
       <c r="B21" s="133" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
@@ -8692,46 +8675,46 @@
     </row>
     <row r="23" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="122" t="s">
+        <v>230</v>
+      </c>
+      <c r="C23" s="94" t="s">
         <v>231</v>
       </c>
-      <c r="C23" s="94" t="s">
+      <c r="D23" s="95" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="243" t="s">
         <v>232</v>
       </c>
-      <c r="D23" s="95" t="s">
+      <c r="C24" s="94" t="s">
+        <v>233</v>
+      </c>
+      <c r="D24" s="95" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="251" t="s">
-        <v>233</v>
-      </c>
-      <c r="C24" s="94" t="s">
+    <row r="25" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="244" t="s">
         <v>234</v>
       </c>
-      <c r="D24" s="95" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="252" t="s">
-        <v>235</v>
-      </c>
       <c r="C25" s="94" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D25" s="95" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="117" t="s">
+        <v>235</v>
+      </c>
+      <c r="C26" s="94" t="s">
         <v>236</v>
       </c>
-      <c r="C26" s="94" t="s">
-        <v>237</v>
-      </c>
       <c r="D26" s="95" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
@@ -8740,8 +8723,8 @@
       <c r="D27" s="95"/>
     </row>
     <row r="28" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="250" t="s">
-        <v>309</v>
+      <c r="B28" s="242" t="s">
+        <v>308</v>
       </c>
       <c r="C28" s="95"/>
       <c r="D28" s="95"/>
@@ -8752,34 +8735,34 @@
       <c r="D29" s="95"/>
     </row>
     <row r="30" spans="1:12" ht="86" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="276" t="s">
-        <v>266</v>
-      </c>
-      <c r="C30" s="276"/>
-      <c r="D30" s="276"/>
-      <c r="E30" s="276"/>
-      <c r="F30" s="276"/>
-      <c r="G30" s="276"/>
-      <c r="H30" s="276"/>
-      <c r="I30" s="276"/>
-      <c r="J30" s="276"/>
-      <c r="K30" s="276"/>
-      <c r="L30" s="276"/>
+      <c r="B30" s="274" t="s">
+        <v>265</v>
+      </c>
+      <c r="C30" s="274"/>
+      <c r="D30" s="274"/>
+      <c r="E30" s="274"/>
+      <c r="F30" s="274"/>
+      <c r="G30" s="274"/>
+      <c r="H30" s="274"/>
+      <c r="I30" s="274"/>
+      <c r="J30" s="274"/>
+      <c r="K30" s="274"/>
+      <c r="L30" s="274"/>
     </row>
     <row r="31" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="276" t="s">
+      <c r="B31" s="274" t="s">
         <v>315</v>
       </c>
-      <c r="C31" s="276"/>
-      <c r="D31" s="276"/>
-      <c r="E31" s="276"/>
-      <c r="F31" s="276"/>
-      <c r="G31" s="276"/>
-      <c r="H31" s="276"/>
-      <c r="I31" s="276"/>
-      <c r="J31" s="276"/>
-      <c r="K31" s="276"/>
-      <c r="L31" s="276"/>
+      <c r="C31" s="274"/>
+      <c r="D31" s="274"/>
+      <c r="E31" s="274"/>
+      <c r="F31" s="274"/>
+      <c r="G31" s="274"/>
+      <c r="H31" s="274"/>
+      <c r="I31" s="274"/>
+      <c r="J31" s="274"/>
+      <c r="K31" s="274"/>
+      <c r="L31" s="274"/>
     </row>
     <row r="33" spans="1:2" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A33" s="127" t="s">
@@ -8790,7 +8773,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ewXWeb1Xe8czjAyha3VgZJOk4X9YB2YMJwuY/PtH+hzuQPR4EXmmF+bEFvbcMgD4cOHllqDD0+BrS9DNBZ6rxQ==" saltValue="MG57gZMn+33HKghB9USjPA==" spinCount="100000" sheet="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="FBXcg9zOmLJvlDD+hDK/7RsDSvIVYkwoG+2tePihf411y9xfjC6lrnbClopsGOIMi7y91CBdU1HM262zTPXHfg==" saltValue="TjfBOK78XWHbIzVDb02vqg==" spinCount="100000" sheet="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="B30:L30"/>
     <mergeCell ref="B31:L31"/>
@@ -8828,7 +8811,7 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="51" t="str">
         <f>Contents!$A2</f>
-        <v>Source: Bolt Technology OÜ Consolidated Annual Report 2025 (AS PricewaterhouseCoopers audit)</v>
+        <v>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="138" customFormat="1" ht="19" x14ac:dyDescent="0.2">
@@ -8887,15 +8870,15 @@
         <v>122</v>
       </c>
       <c r="B6" s="140" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="142" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A8" s="142" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B8" s="143" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C8" s="144"/>
       <c r="D8" s="144"/>
@@ -9034,7 +9017,7 @@
     </row>
     <row r="14" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>8</v>
@@ -9431,7 +9414,7 @@
     </row>
     <row r="28" spans="1:13" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A28" s="127" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B28" s="143" t="s">
         <v>34</v>
@@ -9473,7 +9456,7 @@
     </row>
     <row r="31" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B31" s="47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>8</v>
@@ -9498,12 +9481,12 @@
         <v>0.26540721915577969</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B32" s="47" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>8</v>
@@ -9572,7 +9555,7 @@
     </row>
     <row r="34" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B34" s="47" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>8</v>
@@ -9597,12 +9580,12 @@
         <v>-4.8687499340849406E-2</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B35" s="47" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>8</v>
@@ -9641,7 +9624,7 @@
     </row>
     <row r="36" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B36" s="73" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C36" s="74" t="s">
         <v>8</v>
@@ -9726,7 +9709,7 @@
         <v>0.38280512524056581</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -9761,7 +9744,7 @@
     </row>
     <row r="40" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B40" s="47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>8</v>
@@ -9791,7 +9774,7 @@
     </row>
     <row r="41" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B41" s="47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>8</v>
@@ -9821,7 +9804,7 @@
     </row>
     <row r="42" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B42" s="47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>8</v>
@@ -9924,10 +9907,10 @@
         <v>OK</v>
       </c>
       <c r="B45" s="63" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D45" s="64"/>
       <c r="E45" s="65">
@@ -10062,7 +10045,7 @@
     <row r="50" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="51" spans="1:13" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A51" s="127" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B51" s="143" t="s">
         <v>51</v>
@@ -10131,7 +10114,7 @@
     </row>
     <row r="54" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B54" s="47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>8</v>
@@ -10284,7 +10267,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="249" t="str">
+      <c r="A1" s="241" t="str">
         <f>Contents!$A1</f>
         <v>Bolt Technology OÜ - Pre-IPO Equity Valuation Model</v>
       </c>
@@ -10293,13 +10276,13 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="89" t="str">
         <f>Contents!$A2</f>
-        <v>Source: Bolt Technology OÜ Consolidated Annual Report 2025 (AS PricewaterhouseCoopers audit)</v>
+        <v>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</v>
       </c>
       <c r="B2" s="89"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="91" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B3" s="91"/>
     </row>
@@ -10308,7 +10291,7 @@
         <v>122</v>
       </c>
       <c r="B5" s="125" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="8" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -10316,7 +10299,7 @@
       <c r="B6" s="61"/>
     </row>
     <row r="7" spans="1:7" ht="42" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="248" t="str">
+      <c r="B7" s="240" t="str">
         <f>o_Valuation!B80</f>
         <v>Target Price post IPO Discount</v>
       </c>
@@ -10333,7 +10316,7 @@
     </row>
     <row r="9" spans="1:7" ht="8" customHeight="1" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="248" t="str">
+      <c r="B10" s="240" t="str">
         <f>o_Valuation!B74</f>
         <v>Blended Target Pre-Money Equity Value</v>
       </c>
@@ -10360,7 +10343,7 @@
         <v>122</v>
       </c>
       <c r="B13" s="125" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -10369,7 +10352,7 @@
     </row>
     <row r="15" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B15" s="146" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C15" s="126" t="str">
         <f>o_FS!E4</f>
@@ -10393,360 +10376,360 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B16" s="237"/>
-      <c r="C16" s="238" t="str">
+      <c r="B16" s="229"/>
+      <c r="C16" s="230" t="str">
         <f>o_FS!E5</f>
         <v>Actual</v>
       </c>
-      <c r="D16" s="238" t="str">
+      <c r="D16" s="230" t="str">
         <f>o_FS!F5</f>
         <v>Actual</v>
       </c>
-      <c r="E16" s="238" t="str">
+      <c r="E16" s="230" t="str">
         <f>o_FS!G5</f>
         <v>Estimate</v>
       </c>
-      <c r="F16" s="238" t="str">
+      <c r="F16" s="230" t="str">
         <f>o_FS!H5</f>
         <v>Estimate</v>
       </c>
-      <c r="G16" s="238" t="str">
+      <c r="G16" s="230" t="str">
         <f>o_FS!I5</f>
         <v>Estimate</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B17" s="222" t="str">
+      <c r="B17" s="214" t="str">
         <f>o_FS!B8</f>
         <v>Sales revenue</v>
       </c>
-      <c r="C17" s="223">
+      <c r="C17" s="215">
         <f>o_FS!E8</f>
         <v>1992054</v>
       </c>
-      <c r="D17" s="223">
+      <c r="D17" s="215">
         <f>o_FS!F8</f>
         <v>2270854</v>
       </c>
-      <c r="E17" s="224">
+      <c r="E17" s="216">
         <f>o_FS!G8</f>
         <v>2563281.25</v>
       </c>
-      <c r="F17" s="224">
+      <c r="F17" s="216">
         <f>o_FS!H8</f>
         <v>2867849.1805000002</v>
       </c>
-      <c r="G17" s="224">
+      <c r="G17" s="216">
         <f>o_FS!I8</f>
         <v>3172646.9490240002</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B18" s="225" t="str">
+      <c r="B18" s="217" t="str">
         <f>c_FS!B12</f>
         <v xml:space="preserve">  YoY revenue growth rate (%)</v>
       </c>
-      <c r="C18" s="226">
+      <c r="C18" s="218">
         <f>c_FS!E12</f>
         <v>0</v>
       </c>
-      <c r="D18" s="226">
+      <c r="D18" s="218">
         <f>c_FS!F12</f>
         <v>0.13995604536824802</v>
       </c>
-      <c r="E18" s="227">
+      <c r="E18" s="219">
         <f>c_FS!G12</f>
         <v>0.12877413078956201</v>
       </c>
-      <c r="F18" s="227">
+      <c r="F18" s="219">
         <f>c_FS!H12</f>
         <v>0.1188195522828408</v>
       </c>
-      <c r="G18" s="227">
+      <c r="G18" s="219">
         <f>c_FS!I12</f>
         <v>0.10628096156397571</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B19" s="225" t="str">
+      <c r="B19" s="217" t="str">
         <f>o_FS!B11</f>
         <v xml:space="preserve">  Gross Margin %</v>
       </c>
-      <c r="C19" s="226">
+      <c r="C19" s="218">
         <f>o_FS!E11</f>
         <v>0.56603736645693337</v>
       </c>
-      <c r="D19" s="226">
+      <c r="D19" s="218">
         <f>o_FS!F11</f>
         <v>0.63395268916451697</v>
       </c>
-      <c r="E19" s="227">
+      <c r="E19" s="219">
         <f>o_FS!G11</f>
         <v>0.64500000000000002</v>
       </c>
-      <c r="F19" s="227">
+      <c r="F19" s="219">
         <f>o_FS!H11</f>
         <v>0.65</v>
       </c>
-      <c r="G19" s="227">
+      <c r="G19" s="219">
         <f>o_FS!I11</f>
         <v>0.65500000000000003</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B20" s="228" t="str">
+      <c r="B20" s="220" t="str">
         <f>o_FS!B20</f>
         <v>EBITDA</v>
       </c>
-      <c r="C20" s="229">
+      <c r="C20" s="221">
         <f>o_FS!E20</f>
         <v>-30298</v>
       </c>
-      <c r="D20" s="229">
+      <c r="D20" s="221">
         <f>o_FS!F20</f>
         <v>76672</v>
       </c>
-      <c r="E20" s="230">
+      <c r="E20" s="222">
         <f>o_FS!G20</f>
         <v>92570.71875</v>
       </c>
-      <c r="F20" s="230">
+      <c r="F20" s="222">
         <f>o_FS!H20</f>
         <v>183438.2631225001</v>
       </c>
-      <c r="G20" s="230">
+      <c r="G20" s="222">
         <f>o_FS!I20</f>
         <v>292518.0561768004</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B21" s="225" t="str">
+      <c r="B21" s="217" t="str">
         <f>o_FS!B21</f>
         <v xml:space="preserve">  EBITDA Margin %</v>
       </c>
-      <c r="C21" s="226">
+      <c r="C21" s="218">
         <f>o_FS!E21</f>
         <v>-1.5209427053684287E-2</v>
       </c>
-      <c r="D21" s="226">
+      <c r="D21" s="218">
         <f>o_FS!F21</f>
         <v>3.3763509234851732E-2</v>
       </c>
-      <c r="E21" s="227">
+      <c r="E21" s="219">
         <f>o_FS!G21</f>
         <v>3.6114148125571476E-2</v>
       </c>
-      <c r="F21" s="227">
+      <c r="F21" s="219">
         <f>o_FS!H21</f>
         <v>6.3963706449346208E-2</v>
       </c>
-      <c r="G21" s="227">
+      <c r="G21" s="219">
         <f>o_FS!I21</f>
         <v>9.2200002356640276E-2</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B22" s="231" t="str">
+      <c r="B22" s="223" t="str">
         <f>o_FS!B17</f>
         <v>Operating Profit / (Loss) (EBIT)</v>
       </c>
-      <c r="C22" s="232">
+      <c r="C22" s="224">
         <f>o_FS!E17</f>
         <v>-87735</v>
       </c>
-      <c r="D22" s="232">
+      <c r="D22" s="224">
         <f>o_FS!F17</f>
         <v>19454</v>
       </c>
-      <c r="E22" s="233">
+      <c r="E22" s="225">
         <f>o_FS!G17</f>
         <v>38449.21875</v>
       </c>
-      <c r="F22" s="233">
+      <c r="F22" s="225">
         <f>o_FS!H17</f>
         <v>129053.21312250011</v>
       </c>
-      <c r="G22" s="233">
+      <c r="G22" s="225">
         <f>o_FS!I17</f>
         <v>237948.52117680036</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B23" s="231" t="str">
+      <c r="B23" s="223" t="str">
         <f>o_FS!B26</f>
         <v>Net Profit / (Loss) for the Period</v>
       </c>
-      <c r="C23" s="232">
+      <c r="C23" s="224">
         <f>o_FS!E26</f>
         <v>-102594</v>
       </c>
-      <c r="D23" s="232">
+      <c r="D23" s="224">
         <f>o_FS!F26</f>
         <v>920</v>
       </c>
-      <c r="E23" s="233">
+      <c r="E23" s="225">
         <f>o_FS!G26</f>
         <v>29347.712276999999</v>
       </c>
-      <c r="F23" s="233">
+      <c r="F23" s="225">
         <f>o_FS!H26</f>
         <v>101054.30998760104</v>
       </c>
-      <c r="G23" s="233">
+      <c r="G23" s="225">
         <f>o_FS!I26</f>
         <v>187892.75760187401</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B24" s="228" t="str">
+      <c r="B24" s="220" t="str">
         <f>o_FS!B35</f>
         <v>Free Cash Flow to Firm (FCFF)</v>
       </c>
-      <c r="C24" s="229">
+      <c r="C24" s="221">
         <f>o_FS!E35</f>
         <v>-34486.300000000003</v>
       </c>
-      <c r="D24" s="229">
+      <c r="D24" s="221">
         <f>o_FS!F35</f>
         <v>48622.119999999995</v>
       </c>
-      <c r="E24" s="230">
+      <c r="E24" s="222">
         <f>o_FS!G35</f>
         <v>39064.744648972614</v>
       </c>
-      <c r="F24" s="230">
+      <c r="F24" s="222">
         <f>o_FS!H35</f>
         <v>91447.670551303483</v>
       </c>
-      <c r="G24" s="230">
+      <c r="G24" s="222">
         <f>o_FS!I35</f>
         <v>188373.00718525331</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B25" s="231" t="str">
+      <c r="B25" s="223" t="str">
         <f>o_FS!B39</f>
         <v>Closing cash &amp; cash equivalents</v>
       </c>
-      <c r="C25" s="232">
+      <c r="C25" s="224">
         <f>o_FS!E39</f>
         <v>342247</v>
       </c>
-      <c r="D25" s="232">
+      <c r="D25" s="224">
         <f>o_FS!F39</f>
         <v>357038</v>
       </c>
-      <c r="E25" s="233">
+      <c r="E25" s="225">
         <f>o_FS!G39</f>
         <v>384660.83190148778</v>
       </c>
-      <c r="F25" s="233">
+      <c r="F25" s="225">
         <f>o_FS!H39</f>
         <v>465465.84478947567</v>
       </c>
-      <c r="G25" s="233">
+      <c r="G25" s="225">
         <f>o_FS!I39</f>
         <v>644276.36686017038</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B26" s="234" t="str">
+      <c r="B26" s="226" t="str">
         <f>o_FS!B42</f>
         <v>Net Cash / (Net Debt) Position</v>
       </c>
-      <c r="C26" s="235">
+      <c r="C26" s="227">
         <f>o_FS!E42</f>
         <v>104873</v>
       </c>
-      <c r="D26" s="235">
+      <c r="D26" s="227">
         <f>o_FS!F42</f>
         <v>249474</v>
       </c>
-      <c r="E26" s="236">
+      <c r="E26" s="228">
         <f>o_FS!G42</f>
         <v>287896.0663009726</v>
       </c>
-      <c r="F26" s="236">
+      <c r="F26" s="228">
         <f>o_FS!H42</f>
         <v>379736.54060432699</v>
       </c>
-      <c r="G26" s="236">
+      <c r="G26" s="228">
         <f>o_FS!I42</f>
         <v>570402.45887354994</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B28" s="239" t="s">
-        <v>242</v>
-      </c>
-      <c r="C28" s="239"/>
+      <c r="B28" s="231" t="s">
+        <v>241</v>
+      </c>
+      <c r="C28" s="231"/>
     </row>
     <row r="29" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B29" s="240" t="str">
+      <c r="B29" s="232" t="str">
         <f>i_Inputs!B54</f>
         <v>Weighted Average Cost of Capital (WACC)</v>
       </c>
-      <c r="C29" s="241">
+      <c r="C29" s="233">
         <f>o_Valuation!D26</f>
         <v>0.10201850000000001</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B30" s="242" t="str">
+      <c r="B30" s="234" t="str">
         <f>i_Inputs!B55</f>
         <v>Terminal Growth Rate</v>
       </c>
-      <c r="C30" s="241">
+      <c r="C30" s="233">
         <f>i_Inputs!D55</f>
         <v>0.04</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B31" s="242" t="str">
+      <c r="B31" s="234" t="str">
         <f>i_Inputs!B56</f>
         <v>Target EV / Sales Multiple</v>
       </c>
-      <c r="C31" s="243">
+      <c r="C31" s="235">
         <f>i_Inputs!D56</f>
         <v>2.5</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B32" s="242" t="str">
+      <c r="B32" s="234" t="str">
         <f>i_Inputs!B57</f>
         <v>Target EV / EBITDA Multiple</v>
       </c>
-      <c r="C32" s="243">
+      <c r="C32" s="235">
         <f>i_Inputs!D57</f>
         <v>20</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B33" s="242" t="str">
+      <c r="B33" s="234" t="str">
         <f>i_Inputs!B49</f>
         <v>Effective corporate tax rate</v>
       </c>
-      <c r="C33" s="241">
+      <c r="C33" s="233">
         <f>i_Inputs!D49</f>
         <v>0.22</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B34" s="244" t="str">
+      <c r="B34" s="236" t="str">
         <f>i_Inputs!B60</f>
         <v>IPO Underwriter Discount / Spread</v>
       </c>
-      <c r="C34" s="241">
+      <c r="C34" s="233">
         <f>i_Inputs!D60</f>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B35" s="242" t="str">
+      <c r="B35" s="234" t="str">
         <f>i_Inputs!B61</f>
         <v>Target Primary Capital Raised at IPO</v>
       </c>
-      <c r="C35" s="245">
+      <c r="C35" s="237">
         <f>i_Inputs!D61</f>
         <v>500000</v>
       </c>
@@ -10756,52 +10739,52 @@
       <c r="C36" s="169"/>
     </row>
     <row r="37" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B37" s="239" t="s">
-        <v>244</v>
-      </c>
-      <c r="C37" s="239"/>
+      <c r="B37" s="231" t="s">
+        <v>243</v>
+      </c>
+      <c r="C37" s="231"/>
     </row>
     <row r="38" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B38" s="242" t="s">
-        <v>243</v>
-      </c>
-      <c r="C38" s="246">
+      <c r="B38" s="234" t="s">
+        <v>242</v>
+      </c>
+      <c r="C38" s="238">
         <f>i_Historical!F49</f>
         <v>31223</v>
       </c>
     </row>
     <row r="39" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B39" s="242" t="s">
-        <v>245</v>
-      </c>
-      <c r="C39" s="247">
+      <c r="B39" s="234" t="s">
+        <v>244</v>
+      </c>
+      <c r="C39" s="239">
         <f>o_FS!F39</f>
         <v>357038</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B40" s="242" t="s">
-        <v>246</v>
-      </c>
-      <c r="C40" s="246">
+      <c r="B40" s="234" t="s">
+        <v>245</v>
+      </c>
+      <c r="C40" s="238">
         <f>o_FS!F40</f>
         <v>-527</v>
       </c>
     </row>
     <row r="41" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B41" s="242" t="s">
-        <v>247</v>
-      </c>
-      <c r="C41" s="246">
+      <c r="B41" s="234" t="s">
+        <v>246</v>
+      </c>
+      <c r="C41" s="238">
         <f>o_FS!F41</f>
         <v>-107037</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B42" s="242" t="s">
+      <c r="B42" s="234" t="s">
         <v>56</v>
       </c>
-      <c r="C42" s="246">
+      <c r="C42" s="238">
         <f>i_Historical!F55</f>
         <v>220000</v>
       </c>
@@ -10835,8 +10818,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="52.83203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="202" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.5" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="195" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5" bestFit="1" customWidth="1"/>
     <col min="5" max="9" width="14.33203125" customWidth="1"/>
   </cols>
@@ -10850,34 +10833,34 @@
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="51" t="str">
         <f>Contents!$A2</f>
-        <v>Source: Bolt Technology OÜ Consolidated Annual Report 2025 (AS PricewaterhouseCoopers audit)</v>
+        <v>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
     </row>
     <row r="4" spans="1:5" s="123" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C4" s="203"/>
+      <c r="C4" s="196"/>
     </row>
     <row r="5" spans="1:5" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A5" s="124" t="s">
         <v>122</v>
       </c>
       <c r="B5" s="125" t="s">
-        <v>267</v>
-      </c>
-      <c r="C5" s="204"/>
+        <v>266</v>
+      </c>
+      <c r="C5" s="197"/>
     </row>
     <row r="6" spans="1:5" s="102" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="C6" s="205"/>
+      <c r="C6" s="198"/>
       <c r="D6" s="103"/>
       <c r="E6" s="103"/>
     </row>
     <row r="7" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B7" s="160" t="s">
-        <v>268</v>
-      </c>
-      <c r="C7" s="206" t="s">
+        <v>267</v>
+      </c>
+      <c r="C7" s="199" t="s">
         <v>58</v>
       </c>
       <c r="D7" s="161">
@@ -10888,9 +10871,9 @@
     </row>
     <row r="8" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B8" s="160" t="s">
-        <v>288</v>
-      </c>
-      <c r="C8" s="206" t="s">
+        <v>287</v>
+      </c>
+      <c r="C8" s="199" t="s">
         <v>69</v>
       </c>
       <c r="D8" s="162">
@@ -10901,9 +10884,9 @@
     </row>
     <row r="9" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B9" s="160" t="s">
-        <v>289</v>
-      </c>
-      <c r="C9" s="206" t="s">
+        <v>288</v>
+      </c>
+      <c r="C9" s="199" t="s">
         <v>58</v>
       </c>
       <c r="D9" s="161">
@@ -10914,9 +10897,9 @@
     </row>
     <row r="10" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" s="160" t="s">
-        <v>276</v>
-      </c>
-      <c r="C10" s="206" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10" s="199" t="s">
         <v>58</v>
       </c>
       <c r="D10" s="161">
@@ -10927,9 +10910,9 @@
     </row>
     <row r="11" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" s="160" t="s">
-        <v>290</v>
-      </c>
-      <c r="C11" s="206" t="s">
+        <v>289</v>
+      </c>
+      <c r="C11" s="199" t="s">
         <v>69</v>
       </c>
       <c r="D11" s="162">
@@ -10940,9 +10923,9 @@
     </row>
     <row r="12" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B12" s="160" t="s">
-        <v>291</v>
-      </c>
-      <c r="C12" s="206" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" s="199" t="s">
         <v>58</v>
       </c>
       <c r="D12" s="161">
@@ -10953,15 +10936,15 @@
     </row>
     <row r="13" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B13" s="160"/>
-      <c r="C13" s="206"/>
+      <c r="C13" s="199"/>
       <c r="D13" s="161"/>
       <c r="E13" s="109"/>
     </row>
     <row r="14" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="160" t="s">
-        <v>292</v>
-      </c>
-      <c r="C14" s="206" t="s">
+        <v>291</v>
+      </c>
+      <c r="C14" s="199" t="s">
         <v>69</v>
       </c>
       <c r="D14" s="162">
@@ -10972,9 +10955,9 @@
     </row>
     <row r="15" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B15" s="160" t="s">
-        <v>269</v>
-      </c>
-      <c r="C15" s="206" t="s">
+        <v>268</v>
+      </c>
+      <c r="C15" s="199" t="s">
         <v>58</v>
       </c>
       <c r="D15" s="161">
@@ -10985,9 +10968,9 @@
     </row>
     <row r="16" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="160" t="s">
-        <v>270</v>
-      </c>
-      <c r="C16" s="206" t="s">
+        <v>269</v>
+      </c>
+      <c r="C16" s="199" t="s">
         <v>58</v>
       </c>
       <c r="D16" s="161">
@@ -10998,9 +10981,9 @@
     </row>
     <row r="17" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B17" s="160" t="s">
-        <v>293</v>
-      </c>
-      <c r="C17" s="206" t="s">
+        <v>292</v>
+      </c>
+      <c r="C17" s="199" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="161">
@@ -11011,9 +10994,9 @@
     </row>
     <row r="18" spans="1:9" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="166" t="s">
-        <v>294</v>
-      </c>
-      <c r="C18" s="207" t="s">
+        <v>293</v>
+      </c>
+      <c r="C18" s="200" t="s">
         <v>58</v>
       </c>
       <c r="D18" s="167">
@@ -11024,15 +11007,15 @@
     </row>
     <row r="19" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B19" s="163"/>
-      <c r="C19" s="208"/>
+      <c r="C19" s="201"/>
       <c r="D19" s="165"/>
       <c r="E19" s="109"/>
     </row>
     <row r="20" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B20" s="160" t="s">
-        <v>295</v>
-      </c>
-      <c r="C20" s="206" t="s">
+        <v>294</v>
+      </c>
+      <c r="C20" s="199" t="s">
         <v>58</v>
       </c>
       <c r="D20" s="161">
@@ -11043,9 +11026,9 @@
     </row>
     <row r="21" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B21" s="160" t="s">
-        <v>296</v>
-      </c>
-      <c r="C21" s="206" t="s">
+        <v>295</v>
+      </c>
+      <c r="C21" s="199" t="s">
         <v>58</v>
       </c>
       <c r="D21" s="161">
@@ -11055,13 +11038,13 @@
       <c r="E21" s="109"/>
     </row>
     <row r="22" spans="1:9" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="270" t="s">
-        <v>297</v>
-      </c>
-      <c r="C22" s="271" t="s">
+      <c r="B22" s="260" t="s">
+        <v>296</v>
+      </c>
+      <c r="C22" s="261" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="272">
+      <c r="D22" s="262">
         <f>D10*D18+D9*D21</f>
         <v>0.10201850000000001</v>
       </c>
@@ -11069,15 +11052,15 @@
     </row>
     <row r="23" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B23" s="163"/>
-      <c r="C23" s="208"/>
+      <c r="C23" s="201"/>
       <c r="D23" s="165"/>
       <c r="E23" s="109"/>
     </row>
     <row r="24" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B24" s="160" t="s">
-        <v>298</v>
-      </c>
-      <c r="C24" s="206" t="s">
+        <v>297</v>
+      </c>
+      <c r="C24" s="199" t="s">
         <v>58</v>
       </c>
       <c r="D24" s="161">
@@ -11088,10 +11071,10 @@
     </row>
     <row r="25" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B25" s="160" t="s">
-        <v>299</v>
-      </c>
-      <c r="C25" s="206" t="s">
-        <v>261</v>
+        <v>298</v>
+      </c>
+      <c r="C25" s="199" t="s">
+        <v>260</v>
       </c>
       <c r="D25" s="168">
         <f>i_Inputs!$D$78</f>
@@ -11100,20 +11083,20 @@
       <c r="E25" s="109"/>
     </row>
     <row r="26" spans="1:9" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="273" t="s">
-        <v>300</v>
-      </c>
-      <c r="C26" s="274" t="s">
+      <c r="B26" s="263" t="s">
+        <v>299</v>
+      </c>
+      <c r="C26" s="264" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="275">
+      <c r="D26" s="265">
         <f>IF(D25=1,D22,D24)</f>
         <v>0.10201850000000001</v>
       </c>
       <c r="E26" s="109"/>
     </row>
     <row r="27" spans="1:9" s="102" customFormat="1" ht="18" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="C27" s="205"/>
+      <c r="C27" s="198"/>
       <c r="D27" s="103"/>
       <c r="E27" s="103"/>
     </row>
@@ -11122,20 +11105,20 @@
         <v>122</v>
       </c>
       <c r="B28" s="125" t="s">
-        <v>129</v>
-      </c>
-      <c r="C28" s="210"/>
+        <v>128</v>
+      </c>
+      <c r="C28" s="203"/>
     </row>
     <row r="29" spans="1:9" s="102" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="C29" s="205"/>
+      <c r="C29" s="198"/>
       <c r="D29" s="103"/>
       <c r="E29" s="103"/>
     </row>
     <row r="30" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B30" s="160" t="s">
-        <v>301</v>
-      </c>
-      <c r="C30" s="206" t="s">
+        <v>300</v>
+      </c>
+      <c r="C30" s="199" t="s">
         <v>58</v>
       </c>
       <c r="D30" s="161">
@@ -11152,7 +11135,7 @@
       <c r="B31" s="160" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="206" t="s">
+      <c r="C31" s="199" t="s">
         <v>58</v>
       </c>
       <c r="D31" s="161">
@@ -11167,10 +11150,10 @@
     </row>
     <row r="32" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B32" s="160" t="s">
-        <v>255</v>
-      </c>
-      <c r="C32" s="206" t="s">
-        <v>226</v>
+        <v>254</v>
+      </c>
+      <c r="C32" s="199" t="s">
+        <v>225</v>
       </c>
       <c r="D32" s="170">
         <f>i_Inputs!$D$64</f>
@@ -11184,7 +11167,7 @@
     </row>
     <row r="33" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B33" s="160"/>
-      <c r="C33" s="206"/>
+      <c r="C33" s="199"/>
       <c r="D33" s="171"/>
       <c r="E33" s="153"/>
       <c r="F33" s="169"/>
@@ -11193,38 +11176,38 @@
       <c r="I33" s="169"/>
     </row>
     <row r="34" spans="2:9" s="52" customFormat="1" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="218" t="s">
-        <v>314</v>
-      </c>
-      <c r="C34" s="219"/>
-      <c r="D34" s="220"/>
-      <c r="E34" s="221" t="str">
+      <c r="B34" s="210" t="s">
+        <v>313</v>
+      </c>
+      <c r="C34" s="211"/>
+      <c r="D34" s="212"/>
+      <c r="E34" s="213" t="str">
         <f>o_FS!E4</f>
         <v>2024A</v>
       </c>
-      <c r="F34" s="221" t="str">
+      <c r="F34" s="213" t="str">
         <f>o_FS!F4</f>
         <v>2025A</v>
       </c>
-      <c r="G34" s="221" t="str">
+      <c r="G34" s="213" t="str">
         <f>o_FS!G4</f>
         <v>2026E</v>
       </c>
-      <c r="H34" s="221" t="str">
+      <c r="H34" s="213" t="str">
         <f>o_FS!H4</f>
         <v>2027E</v>
       </c>
-      <c r="I34" s="221" t="str">
+      <c r="I34" s="213" t="str">
         <f>o_FS!I4</f>
         <v>2028E</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B35" s="160" t="s">
-        <v>256</v>
-      </c>
-      <c r="C35" s="211" t="s">
-        <v>261</v>
+        <v>255</v>
+      </c>
+      <c r="C35" s="204" t="s">
+        <v>260</v>
       </c>
       <c r="D35" s="172"/>
       <c r="E35" s="173">
@@ -11250,10 +11233,10 @@
     </row>
     <row r="36" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B36" s="160" t="s">
-        <v>257</v>
-      </c>
-      <c r="C36" s="206" t="s">
-        <v>226</v>
+        <v>256</v>
+      </c>
+      <c r="C36" s="199" t="s">
+        <v>225</v>
       </c>
       <c r="D36" s="172"/>
       <c r="E36" s="170">
@@ -11279,10 +11262,10 @@
     </row>
     <row r="37" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="160" t="s">
-        <v>258</v>
-      </c>
-      <c r="C37" s="211" t="s">
-        <v>261</v>
+        <v>257</v>
+      </c>
+      <c r="C37" s="204" t="s">
+        <v>260</v>
       </c>
       <c r="D37" s="172"/>
       <c r="E37" s="173">
@@ -11308,7 +11291,7 @@
     </row>
     <row r="38" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B38" s="160"/>
-      <c r="C38" s="211"/>
+      <c r="C38" s="204"/>
       <c r="D38" s="172"/>
       <c r="E38" s="173"/>
       <c r="F38" s="173"/>
@@ -11318,9 +11301,9 @@
     </row>
     <row r="39" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B39" s="160" t="s">
-        <v>262</v>
-      </c>
-      <c r="C39" s="206" t="s">
+        <v>261</v>
+      </c>
+      <c r="C39" s="199" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="172"/>
@@ -11347,9 +11330,9 @@
     </row>
     <row r="40" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B40" s="160" t="s">
-        <v>259</v>
-      </c>
-      <c r="C40" s="206" t="s">
+        <v>258</v>
+      </c>
+      <c r="C40" s="199" t="s">
         <v>69</v>
       </c>
       <c r="D40" s="172"/>
@@ -11375,37 +11358,37 @@
       </c>
     </row>
     <row r="41" spans="2:9" s="52" customFormat="1" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="199" t="s">
-        <v>310</v>
-      </c>
-      <c r="C41" s="209" t="s">
+      <c r="B41" s="192" t="s">
+        <v>309</v>
+      </c>
+      <c r="C41" s="202" t="s">
         <v>8</v>
       </c>
-      <c r="D41" s="201"/>
-      <c r="E41" s="200">
+      <c r="D41" s="194"/>
+      <c r="E41" s="193">
         <f>E39*E40</f>
         <v>0</v>
       </c>
-      <c r="F41" s="200">
+      <c r="F41" s="193">
         <f t="shared" ref="F41:I41" si="2">F39*F40</f>
         <v>0</v>
       </c>
-      <c r="G41" s="200">
+      <c r="G41" s="193">
         <f t="shared" si="2"/>
         <v>37212.645627428727</v>
       </c>
-      <c r="H41" s="200">
+      <c r="H41" s="193">
         <f t="shared" si="2"/>
         <v>79047.714785199423</v>
       </c>
-      <c r="I41" s="200">
+      <c r="I41" s="193">
         <f t="shared" si="2"/>
         <v>147756.45327084191</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="20" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B42" s="160"/>
-      <c r="C42" s="206"/>
+      <c r="C42" s="199"/>
       <c r="D42" s="172"/>
       <c r="E42" s="174"/>
       <c r="F42" s="174"/>
@@ -11415,9 +11398,9 @@
     </row>
     <row r="43" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B43" s="160" t="s">
-        <v>263</v>
-      </c>
-      <c r="C43" s="206" t="s">
+        <v>262</v>
+      </c>
+      <c r="C43" s="199" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="175">
@@ -11432,9 +11415,9 @@
     </row>
     <row r="44" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B44" s="160" t="s">
-        <v>260</v>
-      </c>
-      <c r="C44" s="206" t="s">
+        <v>259</v>
+      </c>
+      <c r="C44" s="199" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="175">
@@ -11451,7 +11434,7 @@
       <c r="B45" s="160" t="s">
         <v>100</v>
       </c>
-      <c r="C45" s="206" t="s">
+      <c r="C45" s="199" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="175">
@@ -11468,7 +11451,7 @@
       <c r="B46" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="C46" s="206" t="s">
+      <c r="C46" s="199" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="175">
@@ -11482,13 +11465,13 @@
       <c r="I46" s="169"/>
     </row>
     <row r="47" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="253" t="s">
+      <c r="B47" s="245" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="254" t="s">
+      <c r="C47" s="246" t="s">
         <v>8</v>
       </c>
-      <c r="D47" s="255">
+      <c r="D47" s="247">
         <f>D43+D46</f>
         <v>2741772.8284480255</v>
       </c>
@@ -11500,9 +11483,9 @@
     </row>
     <row r="48" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B48" s="160" t="s">
-        <v>180</v>
-      </c>
-      <c r="C48" s="206" t="s">
+        <v>179</v>
+      </c>
+      <c r="C48" s="199" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="174">
@@ -11519,7 +11502,7 @@
       <c r="B49" s="160" t="s">
         <v>103</v>
       </c>
-      <c r="C49" s="206" t="s">
+      <c r="C49" s="199" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="174">
@@ -11536,7 +11519,7 @@
       <c r="B50" s="160" t="s">
         <v>104</v>
       </c>
-      <c r="C50" s="206" t="s">
+      <c r="C50" s="199" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="174">
@@ -11550,13 +11533,13 @@
       <c r="I50" s="169"/>
     </row>
     <row r="51" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="253" t="s">
+      <c r="B51" s="245" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="254" t="s">
+      <c r="C51" s="246" t="s">
         <v>8</v>
       </c>
-      <c r="D51" s="256">
+      <c r="D51" s="248">
         <f>D47+D48+D49+D50</f>
         <v>2991246.8284480255</v>
       </c>
@@ -11570,7 +11553,7 @@
       <c r="B52" s="160" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="206" t="s">
+      <c r="C52" s="199" t="s">
         <v>48</v>
       </c>
       <c r="D52" s="176">
@@ -11584,13 +11567,13 @@
       <c r="I52" s="169"/>
     </row>
     <row r="53" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="253" t="s">
+      <c r="B53" s="245" t="s">
         <v>107</v>
       </c>
-      <c r="C53" s="254" t="s">
+      <c r="C53" s="246" t="s">
         <v>108</v>
       </c>
-      <c r="D53" s="257">
+      <c r="D53" s="249">
         <f>D51/D52</f>
         <v>95.802672018961204</v>
       </c>
@@ -11605,145 +11588,145 @@
         <v>122</v>
       </c>
       <c r="B55" s="125" t="s">
-        <v>130</v>
-      </c>
-      <c r="C55" s="210"/>
+        <v>129</v>
+      </c>
+      <c r="C55" s="203"/>
     </row>
     <row r="56" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A56" s="41"/>
       <c r="B56" s="61"/>
     </row>
-    <row r="57" spans="1:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="177" t="s">
-        <v>252</v>
-      </c>
-      <c r="C57" s="206" t="s">
+    <row r="57" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="160" t="s">
+        <v>251</v>
+      </c>
+      <c r="C57" s="266" t="s">
         <v>8</v>
       </c>
-      <c r="D57" s="178">
+      <c r="D57" s="267">
         <f>o_FS!G8</f>
         <v>2563281.25</v>
       </c>
       <c r="E57" s="5"/>
     </row>
-    <row r="58" spans="1:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="177" t="s">
+    <row r="58" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="160" t="s">
         <v>109</v>
       </c>
-      <c r="C58" s="206" t="s">
+      <c r="C58" s="266" t="s">
         <v>69</v>
       </c>
-      <c r="D58" s="179">
+      <c r="D58" s="268">
         <f>i_Inputs!$D$56</f>
         <v>2.5</v>
       </c>
       <c r="E58" s="5"/>
     </row>
-    <row r="59" spans="1:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="180" t="s">
+    <row r="59" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="269" t="s">
         <v>110</v>
       </c>
-      <c r="C59" s="212" t="s">
+      <c r="C59" s="270" t="s">
         <v>8</v>
       </c>
-      <c r="D59" s="181">
+      <c r="D59" s="271">
         <f>D57*D58</f>
         <v>6408203.125</v>
       </c>
       <c r="E59" s="5"/>
     </row>
-    <row r="60" spans="1:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="180" t="s">
+    <row r="60" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="269" t="s">
         <v>111</v>
       </c>
-      <c r="C60" s="212" t="s">
+      <c r="C60" s="270" t="s">
         <v>8</v>
       </c>
-      <c r="D60" s="181">
+      <c r="D60" s="271">
         <f>D59+D48+D49+D50</f>
         <v>6657677.125</v>
       </c>
       <c r="E60" s="5"/>
     </row>
-    <row r="61" spans="1:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="258" t="s">
+    <row r="61" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="C61" s="254" t="s">
+      <c r="C61" s="272" t="s">
         <v>108</v>
       </c>
-      <c r="D61" s="259">
+      <c r="D61" s="249">
         <f>D60/D52</f>
         <v>213.22989863241841</v>
       </c>
       <c r="E61" s="5"/>
     </row>
-    <row r="62" spans="1:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="182"/>
-      <c r="C62" s="208"/>
-      <c r="D62" s="183"/>
+    <row r="62" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="163"/>
+      <c r="C62" s="273"/>
+      <c r="D62" s="164"/>
       <c r="E62" s="5"/>
     </row>
-    <row r="63" spans="1:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="177" t="s">
-        <v>251</v>
-      </c>
-      <c r="C63" s="206" t="s">
+    <row r="63" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="160" t="s">
+        <v>250</v>
+      </c>
+      <c r="C63" s="266" t="s">
         <v>8</v>
       </c>
-      <c r="D63" s="178">
+      <c r="D63" s="267">
         <f>o_FS!G20</f>
         <v>92570.71875</v>
       </c>
       <c r="E63" s="5"/>
     </row>
-    <row r="64" spans="1:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="177" t="s">
+    <row r="64" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C64" s="206" t="s">
+      <c r="C64" s="266" t="s">
         <v>69</v>
       </c>
-      <c r="D64" s="179">
+      <c r="D64" s="268">
         <f>i_Inputs!$D$57</f>
         <v>20</v>
       </c>
       <c r="E64" s="5"/>
     </row>
-    <row r="65" spans="1:5" ht="21" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="180" t="s">
+    <row r="65" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="269" t="s">
         <v>114</v>
       </c>
-      <c r="C65" s="212" t="s">
+      <c r="C65" s="270" t="s">
         <v>8</v>
       </c>
-      <c r="D65" s="181">
+      <c r="D65" s="271">
         <f>D63*D64</f>
         <v>1851414.375</v>
       </c>
       <c r="E65" s="5"/>
     </row>
-    <row r="66" spans="1:5" ht="21" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="180" t="s">
+    <row r="66" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="269" t="s">
         <v>115</v>
       </c>
-      <c r="C66" s="212" t="s">
+      <c r="C66" s="270" t="s">
         <v>8</v>
       </c>
-      <c r="D66" s="181">
+      <c r="D66" s="271">
         <f>D65+D48+D49+D50</f>
         <v>2100888.375</v>
       </c>
       <c r="E66" s="5"/>
     </row>
-    <row r="67" spans="1:5" ht="21" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="258" t="s">
+    <row r="67" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="245" t="s">
         <v>116</v>
       </c>
-      <c r="C67" s="254" t="s">
+      <c r="C67" s="272" t="s">
         <v>108</v>
       </c>
-      <c r="D67" s="259">
+      <c r="D67" s="249">
         <f>D66/D52</f>
         <v>67.286563590942578</v>
       </c>
@@ -11757,9 +11740,9 @@
         <v>122</v>
       </c>
       <c r="B69" s="125" t="s">
-        <v>131</v>
-      </c>
-      <c r="C69" s="210"/>
+        <v>130</v>
+      </c>
+      <c r="C69" s="203"/>
     </row>
     <row r="70" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A70" s="41"/>
@@ -11771,41 +11754,41 @@
         <f>i_Inputs!B63</f>
         <v>DCF Weight</v>
       </c>
-      <c r="C71" s="213" t="str">
+      <c r="C71" s="205" t="str">
         <f>i_Inputs!C63</f>
         <v>%</v>
       </c>
-      <c r="D71" s="184">
+      <c r="D71" s="177">
         <f>i_Inputs!D63</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A72" s="41"/>
-      <c r="B72" s="185"/>
+      <c r="B72" s="178"/>
       <c r="D72" s="169"/>
     </row>
     <row r="73" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="260" t="s">
+      <c r="B73" s="250" t="s">
         <v>117</v>
       </c>
-      <c r="C73" s="261" t="s">
+      <c r="C73" s="251" t="s">
         <v>8</v>
       </c>
-      <c r="D73" s="262">
+      <c r="D73" s="252">
         <f>D47*$D$71+D59*(1-$D$71)</f>
         <v>4574987.9767240128</v>
       </c>
       <c r="E73" s="15"/>
     </row>
     <row r="74" spans="1:5" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="263" t="s">
+      <c r="B74" s="253" t="s">
         <v>118</v>
       </c>
-      <c r="C74" s="264" t="s">
+      <c r="C74" s="254" t="s">
         <v>8</v>
       </c>
-      <c r="D74" s="265">
+      <c r="D74" s="255">
         <f>D73+D48+D49+D50</f>
         <v>4824461.9767240128</v>
       </c>
@@ -11813,7 +11796,7 @@
     </row>
     <row r="75" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B75" s="163"/>
-      <c r="C75" s="208"/>
+      <c r="C75" s="201"/>
       <c r="D75" s="164"/>
       <c r="E75" s="15"/>
     </row>
@@ -11821,7 +11804,7 @@
       <c r="B76" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="206" t="s">
+      <c r="C76" s="199" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="174">
@@ -11831,13 +11814,13 @@
       <c r="E76" s="15"/>
     </row>
     <row r="77" spans="1:5" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="266" t="s">
+      <c r="B77" s="256" t="s">
         <v>119</v>
       </c>
-      <c r="C77" s="267" t="s">
+      <c r="C77" s="257" t="s">
         <v>8</v>
       </c>
-      <c r="D77" s="268">
+      <c r="D77" s="258">
         <f>D74+D76</f>
         <v>5324461.9767240128</v>
       </c>
@@ -11845,7 +11828,7 @@
     </row>
     <row r="78" spans="1:5" ht="20" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B78" s="163"/>
-      <c r="C78" s="208"/>
+      <c r="C78" s="201"/>
       <c r="D78" s="164"/>
       <c r="E78" s="15"/>
     </row>
@@ -11853,23 +11836,23 @@
       <c r="B79" s="160" t="s">
         <v>120</v>
       </c>
-      <c r="C79" s="206" t="s">
+      <c r="C79" s="199" t="s">
         <v>108</v>
       </c>
-      <c r="D79" s="186">
+      <c r="D79" s="179">
         <f>D74/D52</f>
         <v>154.51628532568981</v>
       </c>
       <c r="E79" s="15"/>
     </row>
     <row r="80" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="253" t="s">
-        <v>312</v>
-      </c>
-      <c r="C80" s="254" t="s">
+      <c r="B80" s="245" t="s">
+        <v>311</v>
+      </c>
+      <c r="C80" s="246" t="s">
         <v>108</v>
       </c>
-      <c r="D80" s="257">
+      <c r="D80" s="249">
         <f>D79*(1-i_Inputs!$D$60)</f>
         <v>143.70014535289152</v>
       </c>
@@ -11883,125 +11866,125 @@
         <v>122</v>
       </c>
       <c r="B82" s="125" t="s">
-        <v>126</v>
-      </c>
-      <c r="C82" s="210"/>
+        <v>125</v>
+      </c>
+      <c r="C82" s="203"/>
     </row>
     <row r="83" spans="1:8" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="187" t="s">
-        <v>313</v>
+      <c r="B83" s="180" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="84" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
     <row r="85" spans="1:8" s="88" customFormat="1" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A85"/>
-      <c r="B85" s="188" t="s">
+      <c r="B85" s="181" t="s">
         <v>121</v>
       </c>
-      <c r="C85" s="214"/>
-      <c r="D85" s="189">
+      <c r="C85" s="206"/>
+      <c r="D85" s="182">
         <f>$F$85-1</f>
         <v>1.5</v>
       </c>
-      <c r="E85" s="189">
+      <c r="E85" s="182">
         <f>$F$85-0.5</f>
         <v>2</v>
       </c>
-      <c r="F85" s="189">
+      <c r="F85" s="182">
         <f>i_Inputs!$D$56</f>
         <v>2.5</v>
       </c>
-      <c r="G85" s="189">
+      <c r="G85" s="182">
         <f>$F$85+0.5</f>
         <v>3</v>
       </c>
-      <c r="H85" s="189">
+      <c r="H85" s="182">
         <f>F85+1</f>
         <v>3.5</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="190">
+      <c r="B86" s="183">
         <f>-i_Inputs!$D$65</f>
         <v>-0.05</v>
       </c>
-      <c r="C86" s="215" t="s">
+      <c r="C86" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="D86" s="191">
+      <c r="D86" s="184">
         <f>(o_FS!$G$8*(1+$B86)*D$85+$D$48+$D$49+$D$50)/$D$52</f>
         <v>124.97677293181309</v>
       </c>
-      <c r="E86" s="191">
+      <c r="E86" s="184">
         <f>(o_FS!$G$8*(1+$B86)*E$85+$D$48+$D$49+$D$50)/$D$52</f>
         <v>163.972340101848</v>
       </c>
-      <c r="F86" s="191">
+      <c r="F86" s="184">
         <f>(o_FS!$G$8*(1+$B86)*F$85+$D$48+$D$49+$D$50)/$D$52</f>
         <v>202.96790727188289</v>
       </c>
-      <c r="G86" s="191">
+      <c r="G86" s="184">
         <f>(o_FS!$G$8*(1+$B86)*G$85+$D$48+$D$49+$D$50)/$D$52</f>
         <v>241.96347444191781</v>
       </c>
-      <c r="H86" s="192">
+      <c r="H86" s="185">
         <f>(o_FS!$G$8*(1+$B86)*H$85+$D$48+$D$49+$D$50)/$D$52</f>
         <v>280.95904161195273</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="193">
+      <c r="B87" s="186">
         <v>0</v>
       </c>
-      <c r="C87" s="216" t="s">
+      <c r="C87" s="208" t="s">
         <v>108</v>
       </c>
-      <c r="D87" s="194">
+      <c r="D87" s="187">
         <f>(o_FS!$G$8*(1+$B87)*D$85+$D$48+$D$49+$D$50)/$D$52</f>
         <v>131.13396774813438</v>
       </c>
-      <c r="E87" s="194">
+      <c r="E87" s="187">
         <f>(o_FS!$G$8*(1+$B87)*E$85+$D$48+$D$49+$D$50)/$D$52</f>
         <v>172.1819331902764</v>
       </c>
-      <c r="F87" s="269">
+      <c r="F87" s="259">
         <f>(o_FS!$G$8*(1+$B87)*F$85+$D$48+$D$49+$D$50)/$D$52</f>
         <v>213.22989863241841</v>
       </c>
-      <c r="G87" s="194">
+      <c r="G87" s="187">
         <f>(o_FS!$G$8*(1+$B87)*G$85+$D$48+$D$49+$D$50)/$D$52</f>
         <v>254.27786407456043</v>
       </c>
-      <c r="H87" s="195">
+      <c r="H87" s="188">
         <f>(o_FS!$G$8*(1+$B87)*H$85+$D$48+$D$49+$D$50)/$D$52</f>
         <v>295.32582951670241</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="196">
+      <c r="B88" s="189">
         <f>i_Inputs!$D$65</f>
         <v>0.05</v>
       </c>
-      <c r="C88" s="217" t="s">
+      <c r="C88" s="209" t="s">
         <v>108</v>
       </c>
-      <c r="D88" s="197">
+      <c r="D88" s="190">
         <f>(o_FS!$G$8*(1+$B88)*D$85+$D$48+$D$49+$D$50)/$D$52</f>
         <v>137.2911625644557</v>
       </c>
-      <c r="E88" s="197">
+      <c r="E88" s="190">
         <f>(o_FS!$G$8*(1+$B88)*E$85+$D$48+$D$49+$D$50)/$D$52</f>
         <v>180.39152627870479</v>
       </c>
-      <c r="F88" s="197">
+      <c r="F88" s="190">
         <f>(o_FS!$G$8*(1+$B88)*F$85+$D$48+$D$49+$D$50)/$D$52</f>
         <v>223.4918899929539</v>
       </c>
-      <c r="G88" s="197">
+      <c r="G88" s="190">
         <f>(o_FS!$G$8*(1+$B88)*G$85+$D$48+$D$49+$D$50)/$D$52</f>
         <v>266.59225370720304</v>
       </c>
-      <c r="H88" s="198">
+      <c r="H88" s="191">
         <f>(o_FS!$G$8*(1+$B88)*H$85+$D$48+$D$49+$D$50)/$D$52</f>
         <v>309.69261742145216</v>
       </c>
@@ -12013,10 +11996,10 @@
       <c r="B90" s="125" t="s">
         <v>124</v>
       </c>
-      <c r="C90" s="210"/>
+      <c r="C90" s="203"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="XuVaUcrAzULq9PL4q9TTlVrpSY08DtX2gh5PXiEH7kLA4xErEUtlowd7nZNBbL9pjq2a+Eizdb17fI7HL82bKg==" saltValue="wGtr3wTUCBvC4Oeqfo7XaA==" spinCount="100000" sheet="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="7ca7Z/GnO1w8lJyDwibbYdCmAJKT/G0FpqLaly/bRC5Y0cV/5oQQnqGf7K6iembmmhK3ZRSp4tD0AnFK+d8vuA==" saltValue="JfvJ8wVyweAALfxtILsK2A==" spinCount="100000" sheet="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
@@ -12047,7 +12030,7 @@
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="51" t="str">
         <f>Contents!$A2</f>
-        <v>Source: Bolt Technology OÜ Consolidated Annual Report 2025 (AS PricewaterhouseCoopers audit)</v>
+        <v>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</v>
       </c>
       <c r="B2" s="3"/>
     </row>
@@ -12056,7 +12039,7 @@
     </row>
     <row r="4" spans="1:10" s="128" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="B4" s="129" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" s="130"/>
       <c r="E4" s="130" t="str">
@@ -12108,7 +12091,7 @@
         <v>122</v>
       </c>
       <c r="B6" s="125" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -12142,7 +12125,7 @@
     </row>
     <row r="9" spans="1:10" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B9" s="153" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="147">
@@ -12405,7 +12388,7 @@
     </row>
     <row r="19" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B19" s="153" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="150">
@@ -12645,7 +12628,7 @@
         <v>122</v>
       </c>
       <c r="B29" s="125" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -12679,7 +12662,7 @@
     </row>
     <row r="32" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B32" s="153" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="147">
@@ -12705,7 +12688,7 @@
     </row>
     <row r="33" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B33" s="153" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="150">
@@ -12731,7 +12714,7 @@
     </row>
     <row r="34" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B34" s="153" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="150">
@@ -12793,7 +12776,7 @@
     </row>
     <row r="37" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="153" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="150">
@@ -12819,7 +12802,7 @@
     </row>
     <row r="38" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B38" s="153" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="150">
@@ -12845,7 +12828,7 @@
     </row>
     <row r="39" spans="1:9" s="52" customFormat="1" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B39" s="154" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C39" s="53"/>
       <c r="D39" s="159">
@@ -12875,7 +12858,7 @@
     </row>
     <row r="40" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B40" s="153" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="150">
@@ -12901,7 +12884,7 @@
     </row>
     <row r="41" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B41" s="153" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="150">
@@ -13010,12 +12993,12 @@
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="51" t="str">
         <f>Contents!$A2</f>
-        <v>Source: Bolt Technology OÜ Consolidated Annual Report 2025 (AS PricewaterhouseCoopers audit)</v>
+        <v>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="128" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="B4" s="129" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" s="130"/>
       <c r="E4" s="130" t="str">
@@ -13067,7 +13050,7 @@
         <v>122</v>
       </c>
       <c r="B6" s="125" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2"/>
@@ -13181,7 +13164,7 @@
     </row>
     <row r="12" spans="1:10" s="41" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B12" s="84" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D12" s="85"/>
       <c r="E12" s="86">
@@ -13211,13 +13194,13 @@
         <v>122</v>
       </c>
       <c r="B14" s="136" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="1:10" s="52" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="59" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E16" s="17">
         <f>IF(E$5="Actual",i_Historical!E14,-E$11*i_Inputs!E14)</f>
@@ -13368,7 +13351,7 @@
     </row>
     <row r="23" spans="1:9" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B23" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="39"/>
@@ -13395,7 +13378,7 @@
     </row>
     <row r="24" spans="1:9" s="41" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B24" s="84" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D24" s="85"/>
       <c r="E24" s="86">
@@ -13425,7 +13408,7 @@
         <v>122</v>
       </c>
       <c r="B26" s="136" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2"/>
@@ -13513,7 +13496,7 @@
     </row>
     <row r="31" spans="1:9" ht="17" hidden="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B31" s="34" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="54">
@@ -13551,13 +13534,13 @@
         <v>122</v>
       </c>
       <c r="B33" s="136" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B35" s="34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="54">
@@ -13583,7 +13566,7 @@
     </row>
     <row r="36" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B36" s="34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="7">
@@ -13609,7 +13592,7 @@
     </row>
     <row r="37" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="34" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="7">
@@ -13635,7 +13618,7 @@
     </row>
     <row r="38" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B38" s="34" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="54">
@@ -13661,7 +13644,7 @@
     </row>
     <row r="39" spans="1:9" s="52" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B39" s="37" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C39" s="56"/>
       <c r="D39" s="66">
@@ -13701,13 +13684,13 @@
         <v>122</v>
       </c>
       <c r="B41" s="136" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2"/>
     <row r="43" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B43" s="34" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="54">
@@ -13733,7 +13716,7 @@
     </row>
     <row r="44" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B44" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E44" s="54">
         <f>IF(E$5="Actual",0,MAX(0,N(i_Inputs!E36)))</f>
@@ -13758,7 +13741,7 @@
     </row>
     <row r="45" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B45" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E45" s="54">
         <f>IF(E$5="Actual",i_Historical!E39-SUM(E43:E44), MIN(0,N(i_Inputs!E36)))</f>
@@ -13783,7 +13766,7 @@
     </row>
     <row r="46" spans="1:9" s="52" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B46" s="67" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C46" s="56"/>
       <c r="D46" s="66">
@@ -13814,7 +13797,7 @@
     <row r="47" spans="1:9" ht="17" hidden="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="48" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B48" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="54">
@@ -13840,7 +13823,7 @@
     </row>
     <row r="49" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B49" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E49" s="54">
         <f>E38</f>
@@ -13865,7 +13848,7 @@
     </row>
     <row r="50" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B50" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E50" s="54">
         <f>-E55</f>
@@ -13890,7 +13873,7 @@
     </row>
     <row r="51" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B51" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E51" s="54">
         <f>IF(E$5="Actual",i_Historical!E40-SUM(E48:E50),-i_Inputs!E41)</f>
@@ -13915,7 +13898,7 @@
     </row>
     <row r="52" spans="1:9" s="52" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B52" s="67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C52" s="56"/>
       <c r="D52" s="66">
@@ -13946,7 +13929,7 @@
     <row r="53" spans="1:9" ht="17" hidden="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="54" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B54" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E54" s="54">
         <f>-AVERAGE(E43,E46)*i_Inputs!$D$35</f>
@@ -13971,7 +13954,7 @@
     </row>
     <row r="55" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B55" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E55" s="54">
         <f>-E48*i_Inputs!$D$39</f>
@@ -13996,7 +13979,7 @@
     </row>
     <row r="56" spans="1:9" s="52" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B56" s="67" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C56" s="56"/>
       <c r="D56" s="56"/>
@@ -14105,7 +14088,7 @@
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="51" t="str">
         <f>Contents!$A2</f>
-        <v>Source: Bolt Technology OÜ Consolidated Annual Report 2025 (AS PricewaterhouseCoopers audit)</v>
+        <v>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -14139,7 +14122,7 @@
         <v>2028E</v>
       </c>
       <c r="J4" s="128" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="131" customFormat="1" ht="19" x14ac:dyDescent="0.2">
@@ -14170,7 +14153,7 @@
         <v>122</v>
       </c>
       <c r="B6" s="125" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2"/>
@@ -14198,7 +14181,7 @@
     </row>
     <row r="9" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B9" s="34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>58</v>
@@ -14220,7 +14203,7 @@
     </row>
     <row r="10" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" s="34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>58</v>
@@ -14248,7 +14231,7 @@
         <v>122</v>
       </c>
       <c r="B12" s="125" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14256,7 +14239,7 @@
     </row>
     <row r="14" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>58</v>
@@ -14282,7 +14265,7 @@
     </row>
     <row r="16" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="34" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>58</v>
@@ -14299,12 +14282,12 @@
         <v>0.4</v>
       </c>
       <c r="J16" s="116" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B17" s="34" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>58</v>
@@ -14326,7 +14309,7 @@
     </row>
     <row r="18" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B18" s="34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>58</v>
@@ -14387,7 +14370,7 @@
         <v>0.01</v>
       </c>
       <c r="J20" s="116" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -14398,7 +14381,7 @@
         <v>122</v>
       </c>
       <c r="B22" s="125" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14406,10 +14389,10 @@
     </row>
     <row r="24" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B24" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
@@ -14428,10 +14411,10 @@
     </row>
     <row r="25" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B25" s="34" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
@@ -14450,7 +14433,7 @@
     </row>
     <row r="26" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B26" s="34" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>8</v>
@@ -14464,7 +14447,7 @@
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
       <c r="J26" s="116" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14472,7 +14455,7 @@
     </row>
     <row r="28" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B28" s="34" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>8</v>
@@ -14489,12 +14472,12 @@
         <v>55000</v>
       </c>
       <c r="J28" s="116" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B29" s="34" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>58</v>
@@ -14513,7 +14496,7 @@
     </row>
     <row r="30" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B30" s="34" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>8</v>
@@ -14527,12 +14510,12 @@
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
       <c r="J30" s="116" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B31" s="34" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>8</v>
@@ -14543,7 +14526,7 @@
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="116" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
@@ -14554,7 +14537,7 @@
         <v>122</v>
       </c>
       <c r="B33" s="125" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14562,7 +14545,7 @@
     </row>
     <row r="35" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B35" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>58</v>
@@ -14576,12 +14559,12 @@
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="116" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B36" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>8</v>
@@ -14595,12 +14578,12 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="116" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>8</v>
@@ -14614,7 +14597,7 @@
       <c r="H37" s="19"/>
       <c r="I37" s="19"/>
       <c r="J37" s="116" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14630,7 +14613,7 @@
     </row>
     <row r="39" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B39" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>58</v>
@@ -14644,12 +14627,12 @@
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
       <c r="J39" s="116" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B40" s="34" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>8</v>
@@ -14663,12 +14646,12 @@
       <c r="H40" s="19"/>
       <c r="I40" s="19"/>
       <c r="J40" s="116" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B41" s="34" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>8</v>
@@ -14688,15 +14671,15 @@
         <v>18225.083499484805</v>
       </c>
       <c r="J41" s="116" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B42" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="D42" s="112">
         <v>8</v>
@@ -14711,7 +14694,7 @@
         <v>122</v>
       </c>
       <c r="B44" s="125" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="45" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14719,7 +14702,7 @@
     </row>
     <row r="46" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B46" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>58</v>
@@ -14733,12 +14716,12 @@
       <c r="H46" s="19"/>
       <c r="I46" s="19"/>
       <c r="J46" s="116" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B47" s="34" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>8</v>
@@ -14752,7 +14735,7 @@
       <c r="H47" s="19"/>
       <c r="I47" s="19"/>
       <c r="J47" s="116" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14768,7 +14751,7 @@
     </row>
     <row r="49" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B49" s="34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>58</v>
@@ -14785,7 +14768,7 @@
     </row>
     <row r="50" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B50" s="34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>8</v>
@@ -14812,7 +14795,7 @@
         <v>122</v>
       </c>
       <c r="B52" s="125" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="53" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14835,12 +14818,12 @@
       <c r="H54" s="19"/>
       <c r="I54" s="19"/>
       <c r="J54" s="116" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="55" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B55" s="34" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C55" s="33" t="s">
         <v>58</v>
@@ -14854,12 +14837,12 @@
       <c r="H55" s="19"/>
       <c r="I55" s="19"/>
       <c r="J55" s="116" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="56" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B56" s="34" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C56" s="33" t="s">
         <v>69</v>
@@ -14878,7 +14861,7 @@
     </row>
     <row r="57" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B57" s="34" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C57" s="33" t="s">
         <v>69</v>
@@ -14908,7 +14891,7 @@
     </row>
     <row r="59" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B59" s="34" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C59" s="33" t="s">
         <v>48</v>
@@ -14977,7 +14960,7 @@
     </row>
     <row r="63" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B63" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C63" s="33" t="s">
         <v>58</v>
@@ -14991,15 +14974,15 @@
       <c r="H63" s="19"/>
       <c r="I63" s="19"/>
       <c r="J63" s="116" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="64" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B64" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C64" s="33" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D64" s="115">
         <v>0.5</v>
@@ -15010,12 +14993,12 @@
       <c r="H64" s="19"/>
       <c r="I64" s="19"/>
       <c r="J64" s="116" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="65" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B65" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C65" s="33" t="s">
         <v>58</v>
@@ -15029,7 +15012,7 @@
       <c r="H65" s="19"/>
       <c r="I65" s="19"/>
       <c r="J65" s="116" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="67" spans="1:10" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
@@ -15037,7 +15020,7 @@
         <v>122</v>
       </c>
       <c r="B67" s="125" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="68" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -15046,7 +15029,7 @@
     </row>
     <row r="69" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B69" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C69" s="33" t="s">
         <v>58</v>
@@ -15060,12 +15043,12 @@
       <c r="H69" s="19"/>
       <c r="I69" s="19"/>
       <c r="J69" s="116" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="70" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B70" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C70" s="33" t="s">
         <v>58</v>
@@ -15079,12 +15062,12 @@
       <c r="H70" s="19"/>
       <c r="I70" s="19"/>
       <c r="J70" s="116" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="71" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B71" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C71" s="33" t="s">
         <v>58</v>
@@ -15098,12 +15081,12 @@
       <c r="H71" s="19"/>
       <c r="I71" s="19"/>
       <c r="J71" s="116" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="72" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B72" s="34" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C72" s="33" t="s">
         <v>69</v>
@@ -15117,12 +15100,12 @@
       <c r="H72" s="19"/>
       <c r="I72" s="19"/>
       <c r="J72" s="116" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="73" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B73" s="34" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C73" s="33" t="s">
         <v>58</v>
@@ -15136,12 +15119,12 @@
       <c r="H73" s="19"/>
       <c r="I73" s="19"/>
       <c r="J73" s="116" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="74" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B74" s="34" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C74" s="33" t="s">
         <v>58</v>
@@ -15156,12 +15139,12 @@
       <c r="H74" s="19"/>
       <c r="I74" s="19"/>
       <c r="J74" s="116" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="75" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B75" s="34" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C75" s="33" t="s">
         <v>58</v>
@@ -15176,12 +15159,12 @@
       <c r="H75" s="19"/>
       <c r="I75" s="19"/>
       <c r="J75" s="116" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="76" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B76" s="34" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C76" s="33" t="s">
         <v>58</v>
@@ -15195,12 +15178,12 @@
       <c r="H76" s="19"/>
       <c r="I76" s="19"/>
       <c r="J76" s="116" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="77" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B77" s="34" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C77" s="33" t="s">
         <v>58</v>
@@ -15215,15 +15198,15 @@
       <c r="H77" s="19"/>
       <c r="I77" s="19"/>
       <c r="J77" s="116" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="78" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B78" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C78" s="33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D78" s="120">
         <v>1</v>
@@ -15234,7 +15217,7 @@
       <c r="H78" s="19"/>
       <c r="I78" s="19"/>
       <c r="J78" s="116" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">

--- a/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
+++ b/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarashan/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarashan/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8A98D7-D1ED-D44C-9611-F44F5B17AA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B7A57C-5978-3446-AE04-250C7F00F5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="WCu/6944McHvHyNK2onvg6JRC0bml1GLhisApHsn1DjCTkOjvjd5Bi7ovaPAo2yvWdxJpoVq3+3HJlZ/+nApuw==" workbookSaltValue="zKo6aCdJBNVkW2e5aPCnBA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="321">
   <si>
     <t>Source Note</t>
   </si>
@@ -450,9 +450,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Grown Drivers</t>
-  </si>
-  <si>
     <t>Valuation and IPO Capital Market Assumptions</t>
   </si>
   <si>
@@ -997,6 +994,21 @@
   </si>
   <si>
     <t>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</t>
+  </si>
+  <si>
+    <t>Selection</t>
+  </si>
+  <si>
+    <t>Selected Multiple</t>
+  </si>
+  <si>
+    <t>Dropdown selection for blended valuation</t>
+  </si>
+  <si>
+    <t>Growth Drivers</t>
+  </si>
+  <si>
+    <t>Selected Multiple for Blended Valuation</t>
   </si>
 </sst>
 </file>
@@ -1018,9 +1030,16 @@
     <numFmt numFmtId="174" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="175" formatCode="0.00\x"/>
   </numFmts>
-  <fonts count="84" x14ac:knownFonts="1">
+  <fonts count="91" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1620,8 +1639,48 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="13"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1699,8 +1758,20 @@
         <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="33">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -2078,51 +2149,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="275">
+  <cellXfs count="284">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2132,688 +2189,747 @@
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="30" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="38" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="38" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="45" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="37" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="37" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="44" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="44" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="173" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="175" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="47" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="48" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="49" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="50" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="52" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="51" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="52" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="55" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="56" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="47" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="51" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="54" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="55" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="46" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="47" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="49" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="50" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="57" fillId="10" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="58" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="59" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="48" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="59" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="49" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="48" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="60" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="58" fillId="10" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="59" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="60" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="49" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="60" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="50" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="49" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="61" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="61" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="62" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="60" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="61" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="61" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="62" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="61" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="62" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="62" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="62" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="61" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="61" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="63" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="63" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="64" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="64" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="64" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="65" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="63" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="174" fontId="64" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="63" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="64" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="63" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="49" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="51" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="52" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="68" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="64" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="50" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="64" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="68" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="51" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="64" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="68" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="64" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="64" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="65" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="72" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="67" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="63" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="63" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="67" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="63" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="63" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="67" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="63" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="63" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="64" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="71" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="17" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="17" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="64" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="65" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="69" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="70" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="69" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="68" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="68" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="70" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="69" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="69" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="69" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="69" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="49" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="70" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="49" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="70" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="49" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="50" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="49" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="50" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="78" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="50" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="50" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="79" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="69" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="70" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="69" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="70" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="43" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="64" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="65" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="64" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="65" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="64" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="65" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="64" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="65" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="64" fillId="13" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="65" fillId="13" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="64" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="65" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="64" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="65" fillId="4" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="64" fillId="4" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="65" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="64" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="68" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="89" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="67" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="65" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="65" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="90" fillId="15" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="64" fillId="15" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="64" fillId="15" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="64" fillId="15" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="50" fillId="15" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="64" fillId="15" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
+    <cellStyle name="20% - Accent3" xfId="4" builtinId="38"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2864,6 +2980,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFBE6"/>
+      <color rgb="FFECFFDC"/>
       <color rgb="FF0432FF"/>
       <color rgb="FF0F182C"/>
     </mruColors>
@@ -3727,7 +3845,7 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>o_Valuation!$D$79</c:f>
+              <c:f>o_Valuation!$D$80</c:f>
               <c:numCache>
                 <c:formatCode>\€#,##0.00</c:formatCode>
                 <c:ptCount val="1"/>
@@ -3821,7 +3939,7 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>o_Valuation!$D$80</c:f>
+              <c:f>o_Valuation!$D$81</c:f>
               <c:numCache>
                 <c:formatCode>\€#,##0.00</c:formatCode>
                 <c:ptCount val="1"/>
@@ -8624,12 +8742,12 @@
   <sheetData>
     <row r="1" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="51" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="134" customFormat="1" ht="21" x14ac:dyDescent="0.25">
@@ -8667,7 +8785,7 @@
         <v>122</v>
       </c>
       <c r="B21" s="133" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
@@ -8675,46 +8793,46 @@
     </row>
     <row r="23" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="122" t="s">
+        <v>229</v>
+      </c>
+      <c r="C23" s="94" t="s">
         <v>230</v>
       </c>
-      <c r="C23" s="94" t="s">
+      <c r="D23" s="95" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="240" t="s">
         <v>231</v>
       </c>
-      <c r="D23" s="95" t="s">
+      <c r="C24" s="94" t="s">
+        <v>232</v>
+      </c>
+      <c r="D24" s="95" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="243" t="s">
-        <v>232</v>
-      </c>
-      <c r="C24" s="94" t="s">
+    <row r="25" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="241" t="s">
         <v>233</v>
       </c>
-      <c r="D24" s="95" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="244" t="s">
-        <v>234</v>
-      </c>
       <c r="C25" s="94" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D25" s="95" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="117" t="s">
+        <v>234</v>
+      </c>
+      <c r="C26" s="94" t="s">
         <v>235</v>
       </c>
-      <c r="C26" s="94" t="s">
-        <v>236</v>
-      </c>
       <c r="D26" s="95" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
@@ -8723,8 +8841,8 @@
       <c r="D27" s="95"/>
     </row>
     <row r="28" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="242" t="s">
-        <v>308</v>
+      <c r="B28" s="239" t="s">
+        <v>307</v>
       </c>
       <c r="C28" s="95"/>
       <c r="D28" s="95"/>
@@ -8735,34 +8853,34 @@
       <c r="D29" s="95"/>
     </row>
     <row r="30" spans="1:12" ht="86" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="274" t="s">
-        <v>265</v>
-      </c>
-      <c r="C30" s="274"/>
-      <c r="D30" s="274"/>
-      <c r="E30" s="274"/>
-      <c r="F30" s="274"/>
-      <c r="G30" s="274"/>
-      <c r="H30" s="274"/>
-      <c r="I30" s="274"/>
-      <c r="J30" s="274"/>
-      <c r="K30" s="274"/>
-      <c r="L30" s="274"/>
+      <c r="B30" s="269" t="s">
+        <v>264</v>
+      </c>
+      <c r="C30" s="269"/>
+      <c r="D30" s="269"/>
+      <c r="E30" s="269"/>
+      <c r="F30" s="269"/>
+      <c r="G30" s="269"/>
+      <c r="H30" s="269"/>
+      <c r="I30" s="269"/>
+      <c r="J30" s="269"/>
+      <c r="K30" s="269"/>
+      <c r="L30" s="269"/>
     </row>
     <row r="31" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="274" t="s">
-        <v>315</v>
-      </c>
-      <c r="C31" s="274"/>
-      <c r="D31" s="274"/>
-      <c r="E31" s="274"/>
-      <c r="F31" s="274"/>
-      <c r="G31" s="274"/>
-      <c r="H31" s="274"/>
-      <c r="I31" s="274"/>
-      <c r="J31" s="274"/>
-      <c r="K31" s="274"/>
-      <c r="L31" s="274"/>
+      <c r="B31" s="269" t="s">
+        <v>314</v>
+      </c>
+      <c r="C31" s="269"/>
+      <c r="D31" s="269"/>
+      <c r="E31" s="269"/>
+      <c r="F31" s="269"/>
+      <c r="G31" s="269"/>
+      <c r="H31" s="269"/>
+      <c r="I31" s="269"/>
+      <c r="J31" s="269"/>
+      <c r="K31" s="269"/>
+      <c r="L31" s="269"/>
     </row>
     <row r="33" spans="1:2" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A33" s="127" t="s">
@@ -8870,7 +8988,7 @@
         <v>122</v>
       </c>
       <c r="B6" s="140" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="142" customFormat="1" ht="19" x14ac:dyDescent="0.25">
@@ -9017,7 +9135,7 @@
     </row>
     <row r="14" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>8</v>
@@ -9456,7 +9574,7 @@
     </row>
     <row r="31" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B31" s="47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>8</v>
@@ -9481,12 +9599,12 @@
         <v>0.26540721915577969</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B32" s="47" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>8</v>
@@ -9555,7 +9673,7 @@
     </row>
     <row r="34" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B34" s="47" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>8</v>
@@ -9580,12 +9698,12 @@
         <v>-4.8687499340849406E-2</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B35" s="47" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>8</v>
@@ -9624,7 +9742,7 @@
     </row>
     <row r="36" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B36" s="73" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C36" s="74" t="s">
         <v>8</v>
@@ -9709,7 +9827,7 @@
         <v>0.38280512524056581</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -9744,7 +9862,7 @@
     </row>
     <row r="40" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B40" s="47" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>8</v>
@@ -9774,7 +9892,7 @@
     </row>
     <row r="41" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B41" s="47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>8</v>
@@ -9804,7 +9922,7 @@
     </row>
     <row r="42" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B42" s="47" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>8</v>
@@ -9907,10 +10025,10 @@
         <v>OK</v>
       </c>
       <c r="B45" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D45" s="64"/>
       <c r="E45" s="65">
@@ -10114,7 +10232,7 @@
     </row>
     <row r="54" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B54" s="47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>8</v>
@@ -10267,7 +10385,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="241" t="str">
+      <c r="A1" s="238" t="str">
         <f>Contents!$A1</f>
         <v>Bolt Technology OÜ - Pre-IPO Equity Valuation Model</v>
       </c>
@@ -10282,7 +10400,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="91" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B3" s="91"/>
     </row>
@@ -10291,7 +10409,7 @@
         <v>122</v>
       </c>
       <c r="B5" s="125" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="8" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -10299,8 +10417,8 @@
       <c r="B6" s="61"/>
     </row>
     <row r="7" spans="1:7" ht="42" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="240" t="str">
-        <f>o_Valuation!B80</f>
+      <c r="B7" s="237" t="str">
+        <f>o_Valuation!B81</f>
         <v>Target Price post IPO Discount</v>
       </c>
       <c r="C7" s="108"/>
@@ -10308,7 +10426,7 @@
     </row>
     <row r="8" spans="1:7" ht="34" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="106">
-        <f>o_Valuation!D80</f>
+        <f>o_Valuation!D81</f>
         <v>143.70014535289152</v>
       </c>
       <c r="C8" s="105"/>
@@ -10316,8 +10434,8 @@
     </row>
     <row r="9" spans="1:7" ht="8" customHeight="1" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="240" t="str">
-        <f>o_Valuation!B74</f>
+      <c r="B10" s="237" t="str">
+        <f>o_Valuation!B75</f>
         <v>Blended Target Pre-Money Equity Value</v>
       </c>
       <c r="C10" s="98"/>
@@ -10328,7 +10446,7 @@
     </row>
     <row r="11" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="107">
-        <f>o_Valuation!D74</f>
+        <f>o_Valuation!D75</f>
         <v>4824461.9767240128</v>
       </c>
       <c r="C11" s="96"/>
@@ -10343,7 +10461,7 @@
         <v>122</v>
       </c>
       <c r="B13" s="125" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -10352,7 +10470,7 @@
     </row>
     <row r="15" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B15" s="146" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C15" s="126" t="str">
         <f>o_FS!E4</f>
@@ -10376,415 +10494,415 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B16" s="229"/>
-      <c r="C16" s="230" t="str">
+      <c r="B16" s="226"/>
+      <c r="C16" s="227" t="str">
         <f>o_FS!E5</f>
         <v>Actual</v>
       </c>
-      <c r="D16" s="230" t="str">
+      <c r="D16" s="227" t="str">
         <f>o_FS!F5</f>
         <v>Actual</v>
       </c>
-      <c r="E16" s="230" t="str">
+      <c r="E16" s="227" t="str">
         <f>o_FS!G5</f>
         <v>Estimate</v>
       </c>
-      <c r="F16" s="230" t="str">
+      <c r="F16" s="227" t="str">
         <f>o_FS!H5</f>
         <v>Estimate</v>
       </c>
-      <c r="G16" s="230" t="str">
+      <c r="G16" s="227" t="str">
         <f>o_FS!I5</f>
         <v>Estimate</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B17" s="214" t="str">
+      <c r="B17" s="211" t="str">
         <f>o_FS!B8</f>
         <v>Sales revenue</v>
       </c>
-      <c r="C17" s="215">
+      <c r="C17" s="212">
         <f>o_FS!E8</f>
         <v>1992054</v>
       </c>
-      <c r="D17" s="215">
+      <c r="D17" s="212">
         <f>o_FS!F8</f>
         <v>2270854</v>
       </c>
-      <c r="E17" s="216">
+      <c r="E17" s="213">
         <f>o_FS!G8</f>
         <v>2563281.25</v>
       </c>
-      <c r="F17" s="216">
+      <c r="F17" s="213">
         <f>o_FS!H8</f>
         <v>2867849.1805000002</v>
       </c>
-      <c r="G17" s="216">
+      <c r="G17" s="213">
         <f>o_FS!I8</f>
         <v>3172646.9490240002</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B18" s="217" t="str">
+      <c r="B18" s="214" t="str">
         <f>c_FS!B12</f>
         <v xml:space="preserve">  YoY revenue growth rate (%)</v>
       </c>
-      <c r="C18" s="218">
+      <c r="C18" s="215">
         <f>c_FS!E12</f>
         <v>0</v>
       </c>
-      <c r="D18" s="218">
+      <c r="D18" s="215">
         <f>c_FS!F12</f>
         <v>0.13995604536824802</v>
       </c>
-      <c r="E18" s="219">
+      <c r="E18" s="216">
         <f>c_FS!G12</f>
         <v>0.12877413078956201</v>
       </c>
-      <c r="F18" s="219">
+      <c r="F18" s="216">
         <f>c_FS!H12</f>
         <v>0.1188195522828408</v>
       </c>
-      <c r="G18" s="219">
+      <c r="G18" s="216">
         <f>c_FS!I12</f>
         <v>0.10628096156397571</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B19" s="217" t="str">
+      <c r="B19" s="214" t="str">
         <f>o_FS!B11</f>
         <v xml:space="preserve">  Gross Margin %</v>
       </c>
-      <c r="C19" s="218">
+      <c r="C19" s="215">
         <f>o_FS!E11</f>
         <v>0.56603736645693337</v>
       </c>
-      <c r="D19" s="218">
+      <c r="D19" s="215">
         <f>o_FS!F11</f>
         <v>0.63395268916451697</v>
       </c>
-      <c r="E19" s="219">
+      <c r="E19" s="216">
         <f>o_FS!G11</f>
         <v>0.64500000000000002</v>
       </c>
-      <c r="F19" s="219">
+      <c r="F19" s="216">
         <f>o_FS!H11</f>
         <v>0.65</v>
       </c>
-      <c r="G19" s="219">
+      <c r="G19" s="216">
         <f>o_FS!I11</f>
         <v>0.65500000000000003</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B20" s="220" t="str">
+      <c r="B20" s="217" t="str">
         <f>o_FS!B20</f>
         <v>EBITDA</v>
       </c>
-      <c r="C20" s="221">
+      <c r="C20" s="218">
         <f>o_FS!E20</f>
         <v>-30298</v>
       </c>
-      <c r="D20" s="221">
+      <c r="D20" s="218">
         <f>o_FS!F20</f>
         <v>76672</v>
       </c>
-      <c r="E20" s="222">
+      <c r="E20" s="219">
         <f>o_FS!G20</f>
         <v>92570.71875</v>
       </c>
-      <c r="F20" s="222">
+      <c r="F20" s="219">
         <f>o_FS!H20</f>
         <v>183438.2631225001</v>
       </c>
-      <c r="G20" s="222">
+      <c r="G20" s="219">
         <f>o_FS!I20</f>
         <v>292518.0561768004</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B21" s="217" t="str">
+      <c r="B21" s="214" t="str">
         <f>o_FS!B21</f>
         <v xml:space="preserve">  EBITDA Margin %</v>
       </c>
-      <c r="C21" s="218">
+      <c r="C21" s="215">
         <f>o_FS!E21</f>
         <v>-1.5209427053684287E-2</v>
       </c>
-      <c r="D21" s="218">
+      <c r="D21" s="215">
         <f>o_FS!F21</f>
         <v>3.3763509234851732E-2</v>
       </c>
-      <c r="E21" s="219">
+      <c r="E21" s="216">
         <f>o_FS!G21</f>
         <v>3.6114148125571476E-2</v>
       </c>
-      <c r="F21" s="219">
+      <c r="F21" s="216">
         <f>o_FS!H21</f>
         <v>6.3963706449346208E-2</v>
       </c>
-      <c r="G21" s="219">
+      <c r="G21" s="216">
         <f>o_FS!I21</f>
         <v>9.2200002356640276E-2</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B22" s="223" t="str">
+      <c r="B22" s="220" t="str">
         <f>o_FS!B17</f>
         <v>Operating Profit / (Loss) (EBIT)</v>
       </c>
-      <c r="C22" s="224">
+      <c r="C22" s="221">
         <f>o_FS!E17</f>
         <v>-87735</v>
       </c>
-      <c r="D22" s="224">
+      <c r="D22" s="221">
         <f>o_FS!F17</f>
         <v>19454</v>
       </c>
-      <c r="E22" s="225">
+      <c r="E22" s="222">
         <f>o_FS!G17</f>
         <v>38449.21875</v>
       </c>
-      <c r="F22" s="225">
+      <c r="F22" s="222">
         <f>o_FS!H17</f>
         <v>129053.21312250011</v>
       </c>
-      <c r="G22" s="225">
+      <c r="G22" s="222">
         <f>o_FS!I17</f>
         <v>237948.52117680036</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B23" s="223" t="str">
+      <c r="B23" s="220" t="str">
         <f>o_FS!B26</f>
         <v>Net Profit / (Loss) for the Period</v>
       </c>
-      <c r="C23" s="224">
+      <c r="C23" s="221">
         <f>o_FS!E26</f>
         <v>-102594</v>
       </c>
-      <c r="D23" s="224">
+      <c r="D23" s="221">
         <f>o_FS!F26</f>
         <v>920</v>
       </c>
-      <c r="E23" s="225">
+      <c r="E23" s="222">
         <f>o_FS!G26</f>
         <v>29347.712276999999</v>
       </c>
-      <c r="F23" s="225">
+      <c r="F23" s="222">
         <f>o_FS!H26</f>
         <v>101054.30998760104</v>
       </c>
-      <c r="G23" s="225">
+      <c r="G23" s="222">
         <f>o_FS!I26</f>
         <v>187892.75760187401</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B24" s="220" t="str">
+      <c r="B24" s="217" t="str">
         <f>o_FS!B35</f>
         <v>Free Cash Flow to Firm (FCFF)</v>
       </c>
-      <c r="C24" s="221">
+      <c r="C24" s="218">
         <f>o_FS!E35</f>
         <v>-34486.300000000003</v>
       </c>
-      <c r="D24" s="221">
+      <c r="D24" s="218">
         <f>o_FS!F35</f>
         <v>48622.119999999995</v>
       </c>
-      <c r="E24" s="222">
+      <c r="E24" s="219">
         <f>o_FS!G35</f>
         <v>39064.744648972614</v>
       </c>
-      <c r="F24" s="222">
+      <c r="F24" s="219">
         <f>o_FS!H35</f>
         <v>91447.670551303483</v>
       </c>
-      <c r="G24" s="222">
+      <c r="G24" s="219">
         <f>o_FS!I35</f>
         <v>188373.00718525331</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B25" s="223" t="str">
+      <c r="B25" s="220" t="str">
         <f>o_FS!B39</f>
         <v>Closing cash &amp; cash equivalents</v>
       </c>
-      <c r="C25" s="224">
+      <c r="C25" s="221">
         <f>o_FS!E39</f>
         <v>342247</v>
       </c>
-      <c r="D25" s="224">
+      <c r="D25" s="221">
         <f>o_FS!F39</f>
         <v>357038</v>
       </c>
-      <c r="E25" s="225">
+      <c r="E25" s="222">
         <f>o_FS!G39</f>
         <v>384660.83190148778</v>
       </c>
-      <c r="F25" s="225">
+      <c r="F25" s="222">
         <f>o_FS!H39</f>
         <v>465465.84478947567</v>
       </c>
-      <c r="G25" s="225">
+      <c r="G25" s="222">
         <f>o_FS!I39</f>
         <v>644276.36686017038</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B26" s="226" t="str">
+      <c r="B26" s="223" t="str">
         <f>o_FS!B42</f>
         <v>Net Cash / (Net Debt) Position</v>
       </c>
-      <c r="C26" s="227">
+      <c r="C26" s="224">
         <f>o_FS!E42</f>
         <v>104873</v>
       </c>
-      <c r="D26" s="227">
+      <c r="D26" s="224">
         <f>o_FS!F42</f>
         <v>249474</v>
       </c>
-      <c r="E26" s="228">
+      <c r="E26" s="225">
         <f>o_FS!G42</f>
         <v>287896.0663009726</v>
       </c>
-      <c r="F26" s="228">
+      <c r="F26" s="225">
         <f>o_FS!H42</f>
         <v>379736.54060432699</v>
       </c>
-      <c r="G26" s="228">
+      <c r="G26" s="225">
         <f>o_FS!I42</f>
         <v>570402.45887354994</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B28" s="231" t="s">
-        <v>241</v>
-      </c>
-      <c r="C28" s="231"/>
+      <c r="B28" s="228" t="s">
+        <v>240</v>
+      </c>
+      <c r="C28" s="228"/>
     </row>
     <row r="29" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B29" s="232" t="str">
+      <c r="B29" s="229" t="str">
         <f>i_Inputs!B54</f>
         <v>Weighted Average Cost of Capital (WACC)</v>
       </c>
-      <c r="C29" s="233">
+      <c r="C29" s="230">
         <f>o_Valuation!D26</f>
         <v>0.10201850000000001</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B30" s="234" t="str">
+      <c r="B30" s="231" t="str">
         <f>i_Inputs!B55</f>
         <v>Terminal Growth Rate</v>
       </c>
-      <c r="C30" s="233">
+      <c r="C30" s="230">
         <f>i_Inputs!D55</f>
         <v>0.04</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B31" s="234" t="str">
+      <c r="B31" s="231" t="str">
         <f>i_Inputs!B56</f>
         <v>Target EV / Sales Multiple</v>
       </c>
-      <c r="C31" s="235">
+      <c r="C31" s="232">
         <f>i_Inputs!D56</f>
         <v>2.5</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B32" s="234" t="str">
+      <c r="B32" s="231" t="str">
         <f>i_Inputs!B57</f>
         <v>Target EV / EBITDA Multiple</v>
       </c>
-      <c r="C32" s="235">
+      <c r="C32" s="232">
         <f>i_Inputs!D57</f>
         <v>20</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B33" s="234" t="str">
+      <c r="B33" s="231" t="str">
         <f>i_Inputs!B49</f>
         <v>Effective corporate tax rate</v>
       </c>
-      <c r="C33" s="233">
+      <c r="C33" s="230">
         <f>i_Inputs!D49</f>
         <v>0.22</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B34" s="236" t="str">
+      <c r="B34" s="233" t="str">
         <f>i_Inputs!B60</f>
         <v>IPO Underwriter Discount / Spread</v>
       </c>
-      <c r="C34" s="233">
+      <c r="C34" s="230">
         <f>i_Inputs!D60</f>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B35" s="234" t="str">
+      <c r="B35" s="231" t="str">
         <f>i_Inputs!B61</f>
         <v>Target Primary Capital Raised at IPO</v>
       </c>
-      <c r="C35" s="237">
+      <c r="C35" s="234">
         <f>i_Inputs!D61</f>
         <v>500000</v>
       </c>
     </row>
     <row r="36" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B36" s="169"/>
-      <c r="C36" s="169"/>
+      <c r="B36" s="167"/>
+      <c r="C36" s="167"/>
     </row>
     <row r="37" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B37" s="231" t="s">
-        <v>243</v>
-      </c>
-      <c r="C37" s="231"/>
+      <c r="B37" s="228" t="s">
+        <v>242</v>
+      </c>
+      <c r="C37" s="228"/>
     </row>
     <row r="38" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B38" s="234" t="s">
-        <v>242</v>
-      </c>
-      <c r="C38" s="238">
+      <c r="B38" s="231" t="s">
+        <v>241</v>
+      </c>
+      <c r="C38" s="235">
         <f>i_Historical!F49</f>
         <v>31223</v>
       </c>
     </row>
     <row r="39" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B39" s="234" t="s">
-        <v>244</v>
-      </c>
-      <c r="C39" s="239">
+      <c r="B39" s="231" t="s">
+        <v>243</v>
+      </c>
+      <c r="C39" s="236">
         <f>o_FS!F39</f>
         <v>357038</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B40" s="234" t="s">
-        <v>245</v>
-      </c>
-      <c r="C40" s="238">
+      <c r="B40" s="231" t="s">
+        <v>244</v>
+      </c>
+      <c r="C40" s="235">
         <f>o_FS!F40</f>
         <v>-527</v>
       </c>
     </row>
     <row r="41" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B41" s="234" t="s">
-        <v>246</v>
-      </c>
-      <c r="C41" s="238">
+      <c r="B41" s="231" t="s">
+        <v>245</v>
+      </c>
+      <c r="C41" s="235">
         <f>o_FS!F41</f>
         <v>-107037</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="B42" s="234" t="s">
+      <c r="B42" s="231" t="s">
         <v>56</v>
       </c>
-      <c r="C42" s="238">
+      <c r="C42" s="235">
         <f>i_Historical!F55</f>
         <v>220000</v>
       </c>
@@ -10814,14 +10932,13 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="57.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="195" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="192" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="29" x14ac:dyDescent="0.35">
@@ -10840,79 +10957,79 @@
       <c r="A3" s="1"/>
     </row>
     <row r="4" spans="1:5" s="123" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C4" s="196"/>
+      <c r="C4" s="193"/>
     </row>
     <row r="5" spans="1:5" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A5" s="124" t="s">
         <v>122</v>
       </c>
       <c r="B5" s="125" t="s">
-        <v>266</v>
-      </c>
-      <c r="C5" s="197"/>
+        <v>265</v>
+      </c>
+      <c r="C5" s="194"/>
     </row>
     <row r="6" spans="1:5" s="102" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="C6" s="198"/>
+      <c r="C6" s="195"/>
       <c r="D6" s="103"/>
       <c r="E6" s="103"/>
     </row>
     <row r="7" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B7" s="160" t="s">
-        <v>267</v>
-      </c>
-      <c r="C7" s="199" t="s">
+        <v>266</v>
+      </c>
+      <c r="C7" s="196" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="161">
-        <f>i_Inputs!$D$69</f>
+      <c r="D7" s="278">
+        <f>i_Inputs!$D$70</f>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="E7" s="109"/>
     </row>
     <row r="8" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B8" s="160" t="s">
-        <v>287</v>
-      </c>
-      <c r="C8" s="199" t="s">
+        <v>286</v>
+      </c>
+      <c r="C8" s="196" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="162">
-        <f>i_Inputs!$D$72</f>
+      <c r="D8" s="279">
+        <f>i_Inputs!$D$73</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="E8" s="109"/>
     </row>
     <row r="9" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B9" s="160" t="s">
-        <v>288</v>
-      </c>
-      <c r="C9" s="199" t="s">
+        <v>287</v>
+      </c>
+      <c r="C9" s="196" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="161">
-        <f>i_Inputs!$D$76</f>
+      <c r="D9" s="278">
+        <f>i_Inputs!$D$77</f>
         <v>0.15</v>
       </c>
       <c r="E9" s="109"/>
     </row>
     <row r="10" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" s="160" t="s">
-        <v>275</v>
-      </c>
-      <c r="C10" s="199" t="s">
+        <v>274</v>
+      </c>
+      <c r="C10" s="196" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="161">
-        <f>i_Inputs!$D$77</f>
+      <c r="D10" s="278">
+        <f>i_Inputs!$D$78</f>
         <v>0.85</v>
       </c>
       <c r="E10" s="109"/>
     </row>
     <row r="11" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" s="160" t="s">
-        <v>289</v>
-      </c>
-      <c r="C11" s="199" t="s">
+        <v>288</v>
+      </c>
+      <c r="C11" s="196" t="s">
         <v>69</v>
       </c>
       <c r="D11" s="162">
@@ -10923,28 +11040,28 @@
     </row>
     <row r="12" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B12" s="160" t="s">
-        <v>290</v>
-      </c>
-      <c r="C12" s="199" t="s">
+        <v>289</v>
+      </c>
+      <c r="C12" s="196" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="161">
-        <f>i_Inputs!$D$75</f>
+      <c r="D12" s="278">
+        <f>i_Inputs!$D$76</f>
         <v>0.22</v>
       </c>
       <c r="E12" s="109"/>
     </row>
     <row r="13" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B13" s="160"/>
-      <c r="C13" s="199"/>
+      <c r="C13" s="196"/>
       <c r="D13" s="161"/>
       <c r="E13" s="109"/>
     </row>
     <row r="14" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="160" t="s">
-        <v>291</v>
-      </c>
-      <c r="C14" s="199" t="s">
+        <v>290</v>
+      </c>
+      <c r="C14" s="196" t="s">
         <v>69</v>
       </c>
       <c r="D14" s="162">
@@ -10955,51 +11072,51 @@
     </row>
     <row r="15" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B15" s="160" t="s">
-        <v>268</v>
-      </c>
-      <c r="C15" s="199" t="s">
+        <v>267</v>
+      </c>
+      <c r="C15" s="196" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="161">
-        <f>i_Inputs!$D$70</f>
+      <c r="D15" s="278">
+        <f>i_Inputs!$D$71</f>
         <v>5.5E-2</v>
       </c>
       <c r="E15" s="109"/>
     </row>
     <row r="16" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="160" t="s">
-        <v>269</v>
-      </c>
-      <c r="C16" s="199" t="s">
+        <v>268</v>
+      </c>
+      <c r="C16" s="196" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="161">
-        <f>i_Inputs!$D$71</f>
+      <c r="D16" s="278">
+        <f>i_Inputs!$D$72</f>
         <v>0.01</v>
       </c>
       <c r="E16" s="109"/>
     </row>
     <row r="17" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B17" s="160" t="s">
-        <v>292</v>
-      </c>
-      <c r="C17" s="199" t="s">
+        <v>291</v>
+      </c>
+      <c r="C17" s="196" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="161">
-        <f>i_Inputs!$D$73</f>
+      <c r="D17" s="278">
+        <f>i_Inputs!$D$74</f>
         <v>0.01</v>
       </c>
       <c r="E17" s="109"/>
     </row>
     <row r="18" spans="1:9" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="166" t="s">
-        <v>293</v>
-      </c>
-      <c r="C18" s="200" t="s">
+        <v>292</v>
+      </c>
+      <c r="C18" s="197" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="167">
+      <c r="D18" s="276">
         <f>D7+D14*D15+D16+D17</f>
         <v>0.11382764705882353</v>
       </c>
@@ -11007,28 +11124,28 @@
     </row>
     <row r="19" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B19" s="163"/>
-      <c r="C19" s="201"/>
+      <c r="C19" s="198"/>
       <c r="D19" s="165"/>
       <c r="E19" s="109"/>
     </row>
     <row r="20" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B20" s="160" t="s">
-        <v>294</v>
-      </c>
-      <c r="C20" s="199" t="s">
+        <v>293</v>
+      </c>
+      <c r="C20" s="196" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="161">
-        <f>i_Inputs!$D$74</f>
+      <c r="D20" s="278">
+        <f>i_Inputs!$D$75</f>
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="E20" s="109"/>
     </row>
     <row r="21" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B21" s="160" t="s">
-        <v>295</v>
-      </c>
-      <c r="C21" s="199" t="s">
+        <v>294</v>
+      </c>
+      <c r="C21" s="196" t="s">
         <v>58</v>
       </c>
       <c r="D21" s="161">
@@ -11038,13 +11155,13 @@
       <c r="E21" s="109"/>
     </row>
     <row r="22" spans="1:9" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="260" t="s">
-        <v>296</v>
-      </c>
-      <c r="C22" s="261" t="s">
+      <c r="B22" s="256" t="s">
+        <v>295</v>
+      </c>
+      <c r="C22" s="257" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="262">
+      <c r="D22" s="258">
         <f>D10*D18+D9*D21</f>
         <v>0.10201850000000001</v>
       </c>
@@ -11052,51 +11169,51 @@
     </row>
     <row r="23" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B23" s="163"/>
-      <c r="C23" s="201"/>
+      <c r="C23" s="198"/>
       <c r="D23" s="165"/>
       <c r="E23" s="109"/>
     </row>
     <row r="24" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B24" s="160" t="s">
-        <v>297</v>
-      </c>
-      <c r="C24" s="199" t="s">
+        <v>296</v>
+      </c>
+      <c r="C24" s="196" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="161">
+      <c r="D24" s="278">
         <f>i_Inputs!$D$54</f>
         <v>0.105</v>
       </c>
       <c r="E24" s="109"/>
     </row>
     <row r="25" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="160" t="s">
+      <c r="B25" s="271" t="s">
+        <v>297</v>
+      </c>
+      <c r="C25" s="273" t="s">
+        <v>259</v>
+      </c>
+      <c r="D25" s="274">
+        <f>i_Inputs!$D$79</f>
+        <v>1</v>
+      </c>
+      <c r="E25" s="109"/>
+    </row>
+    <row r="26" spans="1:9" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="259" t="s">
         <v>298</v>
       </c>
-      <c r="C25" s="199" t="s">
-        <v>260</v>
-      </c>
-      <c r="D25" s="168">
-        <f>i_Inputs!$D$78</f>
-        <v>1</v>
-      </c>
-      <c r="E25" s="109"/>
-    </row>
-    <row r="26" spans="1:9" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="263" t="s">
-        <v>299</v>
-      </c>
-      <c r="C26" s="264" t="s">
+      <c r="C26" s="260" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="265">
+      <c r="D26" s="261">
         <f>IF(D25=1,D22,D24)</f>
         <v>0.10201850000000001</v>
       </c>
       <c r="E26" s="109"/>
     </row>
     <row r="27" spans="1:9" s="102" customFormat="1" ht="18" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="C27" s="198"/>
+      <c r="C27" s="195"/>
       <c r="D27" s="103"/>
       <c r="E27" s="103"/>
     </row>
@@ -11107,18 +11224,18 @@
       <c r="B28" s="125" t="s">
         <v>128</v>
       </c>
-      <c r="C28" s="203"/>
+      <c r="C28" s="200"/>
     </row>
     <row r="29" spans="1:9" s="102" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="C29" s="198"/>
+      <c r="C29" s="195"/>
       <c r="D29" s="103"/>
       <c r="E29" s="103"/>
     </row>
     <row r="30" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B30" s="160" t="s">
-        <v>300</v>
-      </c>
-      <c r="C30" s="199" t="s">
+        <v>299</v>
+      </c>
+      <c r="C30" s="196" t="s">
         <v>58</v>
       </c>
       <c r="D30" s="161">
@@ -11126,462 +11243,462 @@
         <v>0.10201850000000001</v>
       </c>
       <c r="E30" s="153"/>
-      <c r="F30" s="169"/>
-      <c r="G30" s="169"/>
-      <c r="H30" s="169"/>
-      <c r="I30" s="169"/>
+      <c r="F30" s="167"/>
+      <c r="G30" s="167"/>
+      <c r="H30" s="167"/>
+      <c r="I30" s="167"/>
     </row>
     <row r="31" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B31" s="160" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="199" t="s">
+      <c r="C31" s="196" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="161">
+      <c r="D31" s="278">
         <f>i_Inputs!$D$55</f>
         <v>0.04</v>
       </c>
       <c r="E31" s="153"/>
-      <c r="F31" s="169"/>
-      <c r="G31" s="169"/>
-      <c r="H31" s="169"/>
-      <c r="I31" s="169"/>
+      <c r="F31" s="167"/>
+      <c r="G31" s="167"/>
+      <c r="H31" s="167"/>
+      <c r="I31" s="167"/>
     </row>
     <row r="32" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B32" s="160" t="s">
-        <v>254</v>
-      </c>
-      <c r="C32" s="199" t="s">
-        <v>225</v>
-      </c>
-      <c r="D32" s="170">
-        <f>i_Inputs!$D$64</f>
+        <v>253</v>
+      </c>
+      <c r="C32" s="196" t="s">
+        <v>224</v>
+      </c>
+      <c r="D32" s="280">
+        <f>i_Inputs!$D$65</f>
         <v>0.5</v>
       </c>
       <c r="E32" s="153"/>
-      <c r="F32" s="169"/>
-      <c r="G32" s="169"/>
-      <c r="H32" s="169"/>
-      <c r="I32" s="169"/>
+      <c r="F32" s="167"/>
+      <c r="G32" s="167"/>
+      <c r="H32" s="167"/>
+      <c r="I32" s="167"/>
     </row>
     <row r="33" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B33" s="160"/>
-      <c r="C33" s="199"/>
-      <c r="D33" s="171"/>
+      <c r="C33" s="196"/>
+      <c r="D33" s="169"/>
       <c r="E33" s="153"/>
-      <c r="F33" s="169"/>
-      <c r="G33" s="169"/>
-      <c r="H33" s="169"/>
-      <c r="I33" s="169"/>
+      <c r="F33" s="167"/>
+      <c r="G33" s="167"/>
+      <c r="H33" s="167"/>
+      <c r="I33" s="167"/>
     </row>
     <row r="34" spans="2:9" s="52" customFormat="1" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="210" t="s">
-        <v>313</v>
-      </c>
-      <c r="C34" s="211"/>
-      <c r="D34" s="212"/>
-      <c r="E34" s="213" t="str">
+      <c r="B34" s="207" t="s">
+        <v>312</v>
+      </c>
+      <c r="C34" s="208"/>
+      <c r="D34" s="209"/>
+      <c r="E34" s="210" t="str">
         <f>o_FS!E4</f>
         <v>2024A</v>
       </c>
-      <c r="F34" s="213" t="str">
+      <c r="F34" s="210" t="str">
         <f>o_FS!F4</f>
         <v>2025A</v>
       </c>
-      <c r="G34" s="213" t="str">
+      <c r="G34" s="210" t="str">
         <f>o_FS!G4</f>
         <v>2026E</v>
       </c>
-      <c r="H34" s="213" t="str">
+      <c r="H34" s="210" t="str">
         <f>o_FS!H4</f>
         <v>2027E</v>
       </c>
-      <c r="I34" s="213" t="str">
+      <c r="I34" s="210" t="str">
         <f>o_FS!I4</f>
         <v>2028E</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B35" s="160" t="s">
-        <v>255</v>
-      </c>
-      <c r="C35" s="204" t="s">
-        <v>260</v>
-      </c>
-      <c r="D35" s="172"/>
-      <c r="E35" s="173">
+        <v>254</v>
+      </c>
+      <c r="C35" s="201" t="s">
+        <v>259</v>
+      </c>
+      <c r="D35" s="170"/>
+      <c r="E35" s="171">
         <f>IF(RIGHT(E$34,1)="E",1,0)</f>
         <v>0</v>
       </c>
-      <c r="F35" s="173">
+      <c r="F35" s="171">
         <f>IF(RIGHT(F$34,1)="E",1,0)</f>
         <v>0</v>
       </c>
-      <c r="G35" s="173">
+      <c r="G35" s="171">
         <f>IF(RIGHT(G$34,1)="E",1,0)</f>
         <v>1</v>
       </c>
-      <c r="H35" s="173">
+      <c r="H35" s="171">
         <f>IF(RIGHT(H$34,1)="E",1,0)</f>
         <v>1</v>
       </c>
-      <c r="I35" s="173">
+      <c r="I35" s="171">
         <f>IF(RIGHT(I$34,1)="E",1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B36" s="160" t="s">
-        <v>256</v>
-      </c>
-      <c r="C36" s="199" t="s">
-        <v>225</v>
-      </c>
-      <c r="D36" s="172"/>
-      <c r="E36" s="170">
+        <v>255</v>
+      </c>
+      <c r="C36" s="196" t="s">
+        <v>224</v>
+      </c>
+      <c r="D36" s="170"/>
+      <c r="E36" s="168">
         <f>IF(E35=1,SUM($E35:E35)-$D$32,0)</f>
         <v>0</v>
       </c>
-      <c r="F36" s="170">
+      <c r="F36" s="168">
         <f>IF(F35=1,SUM($E35:F35)-$D$32,0)</f>
         <v>0</v>
       </c>
-      <c r="G36" s="170">
+      <c r="G36" s="168">
         <f>IF(G35=1,SUM($E35:G35)-$D$32,0)</f>
         <v>0.5</v>
       </c>
-      <c r="H36" s="170">
+      <c r="H36" s="168">
         <f>IF(H35=1,SUM($E35:H35)-$D$32,0)</f>
         <v>1.5</v>
       </c>
-      <c r="I36" s="170">
+      <c r="I36" s="168">
         <f>IF(I35=1,SUM($E35:I35)-$D$32,0)</f>
         <v>2.5</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="160" t="s">
-        <v>257</v>
-      </c>
-      <c r="C37" s="204" t="s">
-        <v>260</v>
-      </c>
-      <c r="D37" s="172"/>
-      <c r="E37" s="173">
+        <v>256</v>
+      </c>
+      <c r="C37" s="201" t="s">
+        <v>259</v>
+      </c>
+      <c r="D37" s="170"/>
+      <c r="E37" s="171">
         <f>IF(AND(E35=1,E36=MAX($E$36:$I$36)),1,0)</f>
         <v>0</v>
       </c>
-      <c r="F37" s="173">
+      <c r="F37" s="171">
         <f t="shared" ref="F37:I37" si="0">IF(AND(F35=1,F36=MAX($E$36:$I$36)),1,0)</f>
         <v>0</v>
       </c>
-      <c r="G37" s="173">
+      <c r="G37" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H37" s="173">
+      <c r="H37" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I37" s="173">
+      <c r="I37" s="171">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B38" s="160"/>
-      <c r="C38" s="204"/>
-      <c r="D38" s="172"/>
-      <c r="E38" s="173"/>
-      <c r="F38" s="173"/>
-      <c r="G38" s="173"/>
-      <c r="H38" s="173"/>
-      <c r="I38" s="173"/>
+      <c r="C38" s="201"/>
+      <c r="D38" s="170"/>
+      <c r="E38" s="171"/>
+      <c r="F38" s="171"/>
+      <c r="G38" s="171"/>
+      <c r="H38" s="171"/>
+      <c r="I38" s="171"/>
     </row>
     <row r="39" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B39" s="160" t="s">
-        <v>261</v>
-      </c>
-      <c r="C39" s="199" t="s">
+        <v>260</v>
+      </c>
+      <c r="C39" s="196" t="s">
         <v>8</v>
       </c>
-      <c r="D39" s="172"/>
-      <c r="E39" s="173">
+      <c r="D39" s="170"/>
+      <c r="E39" s="171">
         <f>o_FS!E35</f>
         <v>-34486.300000000003</v>
       </c>
-      <c r="F39" s="173">
+      <c r="F39" s="171">
         <f>o_FS!F35</f>
         <v>48622.119999999995</v>
       </c>
-      <c r="G39" s="173">
+      <c r="G39" s="171">
         <f>o_FS!G35</f>
         <v>39064.744648972614</v>
       </c>
-      <c r="H39" s="173">
+      <c r="H39" s="171">
         <f>o_FS!H35</f>
         <v>91447.670551303483</v>
       </c>
-      <c r="I39" s="173">
+      <c r="I39" s="171">
         <f>o_FS!I35</f>
         <v>188373.00718525331</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B40" s="160" t="s">
-        <v>258</v>
-      </c>
-      <c r="C40" s="199" t="s">
+        <v>257</v>
+      </c>
+      <c r="C40" s="196" t="s">
         <v>69</v>
       </c>
-      <c r="D40" s="172"/>
-      <c r="E40" s="170">
+      <c r="D40" s="170"/>
+      <c r="E40" s="168">
         <f>IF(E35=1,1/(1+$D$30)^E36,0)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="170">
+      <c r="F40" s="168">
         <f t="shared" ref="F40:I40" si="1">IF(F35=1,1/(1+$D$30)^F36,0)</f>
         <v>0</v>
       </c>
-      <c r="G40" s="170">
+      <c r="G40" s="168">
         <f t="shared" si="1"/>
         <v>0.9525889894280265</v>
       </c>
-      <c r="H40" s="170">
+      <c r="H40" s="168">
         <f t="shared" si="1"/>
         <v>0.86440380939886807</v>
       </c>
-      <c r="I40" s="170">
+      <c r="I40" s="168">
         <f t="shared" si="1"/>
         <v>0.78438230338135706</v>
       </c>
     </row>
     <row r="41" spans="2:9" s="52" customFormat="1" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="192" t="s">
-        <v>309</v>
-      </c>
-      <c r="C41" s="202" t="s">
+      <c r="B41" s="189" t="s">
+        <v>308</v>
+      </c>
+      <c r="C41" s="199" t="s">
         <v>8</v>
       </c>
-      <c r="D41" s="194"/>
-      <c r="E41" s="193">
+      <c r="D41" s="191"/>
+      <c r="E41" s="190">
         <f>E39*E40</f>
         <v>0</v>
       </c>
-      <c r="F41" s="193">
+      <c r="F41" s="190">
         <f t="shared" ref="F41:I41" si="2">F39*F40</f>
         <v>0</v>
       </c>
-      <c r="G41" s="193">
+      <c r="G41" s="190">
         <f t="shared" si="2"/>
         <v>37212.645627428727</v>
       </c>
-      <c r="H41" s="193">
+      <c r="H41" s="190">
         <f t="shared" si="2"/>
         <v>79047.714785199423</v>
       </c>
-      <c r="I41" s="193">
+      <c r="I41" s="190">
         <f t="shared" si="2"/>
         <v>147756.45327084191</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="20" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B42" s="160"/>
-      <c r="C42" s="199"/>
-      <c r="D42" s="172"/>
-      <c r="E42" s="174"/>
-      <c r="F42" s="174"/>
-      <c r="G42" s="174"/>
-      <c r="H42" s="174"/>
-      <c r="I42" s="174"/>
+      <c r="C42" s="196"/>
+      <c r="D42" s="170"/>
+      <c r="E42" s="172"/>
+      <c r="F42" s="172"/>
+      <c r="G42" s="172"/>
+      <c r="H42" s="172"/>
+      <c r="I42" s="172"/>
     </row>
     <row r="43" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B43" s="160" t="s">
-        <v>262</v>
-      </c>
-      <c r="C43" s="199" t="s">
+        <v>261</v>
+      </c>
+      <c r="C43" s="196" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="175">
+      <c r="D43" s="173">
         <f>SUM(E41:I41)</f>
         <v>264016.81368347007</v>
       </c>
-      <c r="E43" s="174"/>
-      <c r="F43" s="174"/>
-      <c r="G43" s="174"/>
-      <c r="H43" s="174"/>
-      <c r="I43" s="174"/>
+      <c r="E43" s="172"/>
+      <c r="F43" s="172"/>
+      <c r="G43" s="172"/>
+      <c r="H43" s="172"/>
+      <c r="I43" s="172"/>
     </row>
     <row r="44" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B44" s="160" t="s">
-        <v>259</v>
-      </c>
-      <c r="C44" s="199" t="s">
+        <v>258</v>
+      </c>
+      <c r="C44" s="196" t="s">
         <v>8</v>
       </c>
-      <c r="D44" s="175">
+      <c r="D44" s="173">
         <f>SUMPRODUCT(E37:I37,E39:I39)</f>
         <v>188373.00718525331</v>
       </c>
       <c r="E44" s="153"/>
-      <c r="F44" s="169"/>
-      <c r="G44" s="169"/>
-      <c r="H44" s="169"/>
-      <c r="I44" s="169"/>
+      <c r="F44" s="167"/>
+      <c r="G44" s="167"/>
+      <c r="H44" s="167"/>
+      <c r="I44" s="167"/>
     </row>
     <row r="45" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B45" s="160" t="s">
         <v>100</v>
       </c>
-      <c r="C45" s="199" t="s">
+      <c r="C45" s="196" t="s">
         <v>8</v>
       </c>
-      <c r="D45" s="175">
+      <c r="D45" s="173">
         <f>D44*(1+D31)/(D30-D31)</f>
         <v>3158862.7179416372</v>
       </c>
       <c r="E45" s="153"/>
-      <c r="F45" s="169"/>
-      <c r="G45" s="169"/>
-      <c r="H45" s="169"/>
-      <c r="I45" s="169"/>
+      <c r="F45" s="167"/>
+      <c r="G45" s="167"/>
+      <c r="H45" s="167"/>
+      <c r="I45" s="167"/>
     </row>
     <row r="46" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B46" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="C46" s="199" t="s">
+      <c r="C46" s="196" t="s">
         <v>8</v>
       </c>
-      <c r="D46" s="175">
+      <c r="D46" s="173">
         <f>D45*SUMPRODUCT(E37:I37,E40:I40)</f>
         <v>2477756.0147645553</v>
       </c>
       <c r="E46" s="153"/>
-      <c r="F46" s="169"/>
-      <c r="G46" s="169"/>
-      <c r="H46" s="169"/>
-      <c r="I46" s="169"/>
+      <c r="F46" s="167"/>
+      <c r="G46" s="167"/>
+      <c r="H46" s="167"/>
+      <c r="I46" s="167"/>
     </row>
     <row r="47" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="245" t="s">
+      <c r="B47" s="242" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="246" t="s">
+      <c r="C47" s="243" t="s">
         <v>8</v>
       </c>
-      <c r="D47" s="247">
+      <c r="D47" s="244">
         <f>D43+D46</f>
         <v>2741772.8284480255</v>
       </c>
       <c r="E47" s="153"/>
-      <c r="F47" s="169"/>
-      <c r="G47" s="169"/>
-      <c r="H47" s="169"/>
-      <c r="I47" s="169"/>
+      <c r="F47" s="167"/>
+      <c r="G47" s="167"/>
+      <c r="H47" s="167"/>
+      <c r="I47" s="167"/>
     </row>
     <row r="48" spans="2:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B48" s="160" t="s">
-        <v>179</v>
-      </c>
-      <c r="C48" s="199" t="s">
+        <v>178</v>
+      </c>
+      <c r="C48" s="196" t="s">
         <v>8</v>
       </c>
-      <c r="D48" s="174">
+      <c r="D48" s="172">
         <f>i_Historical!F30</f>
         <v>357038</v>
       </c>
       <c r="E48" s="153"/>
-      <c r="F48" s="169"/>
-      <c r="G48" s="169"/>
-      <c r="H48" s="169"/>
-      <c r="I48" s="169"/>
+      <c r="F48" s="167"/>
+      <c r="G48" s="167"/>
+      <c r="H48" s="167"/>
+      <c r="I48" s="167"/>
     </row>
     <row r="49" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B49" s="160" t="s">
         <v>103</v>
       </c>
-      <c r="C49" s="199" t="s">
+      <c r="C49" s="196" t="s">
         <v>8</v>
       </c>
-      <c r="D49" s="174">
+      <c r="D49" s="172">
         <f>-i_Historical!F39</f>
         <v>-527</v>
       </c>
       <c r="E49" s="153"/>
-      <c r="F49" s="169"/>
-      <c r="G49" s="169"/>
-      <c r="H49" s="169"/>
-      <c r="I49" s="169"/>
+      <c r="F49" s="167"/>
+      <c r="G49" s="167"/>
+      <c r="H49" s="167"/>
+      <c r="I49" s="167"/>
     </row>
     <row r="50" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B50" s="160" t="s">
         <v>104</v>
       </c>
-      <c r="C50" s="199" t="s">
+      <c r="C50" s="196" t="s">
         <v>8</v>
       </c>
-      <c r="D50" s="174">
+      <c r="D50" s="172">
         <f>-i_Historical!F40</f>
         <v>-107037</v>
       </c>
       <c r="E50" s="153"/>
-      <c r="F50" s="169"/>
-      <c r="G50" s="169"/>
-      <c r="H50" s="169"/>
-      <c r="I50" s="169"/>
+      <c r="F50" s="167"/>
+      <c r="G50" s="167"/>
+      <c r="H50" s="167"/>
+      <c r="I50" s="167"/>
     </row>
     <row r="51" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="245" t="s">
+      <c r="B51" s="242" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="246" t="s">
+      <c r="C51" s="243" t="s">
         <v>8</v>
       </c>
-      <c r="D51" s="248">
+      <c r="D51" s="245">
         <f>D47+D48+D49+D50</f>
         <v>2991246.8284480255</v>
       </c>
       <c r="E51" s="153"/>
-      <c r="F51" s="169"/>
-      <c r="G51" s="169"/>
-      <c r="H51" s="169"/>
-      <c r="I51" s="169"/>
+      <c r="F51" s="167"/>
+      <c r="G51" s="167"/>
+      <c r="H51" s="167"/>
+      <c r="I51" s="167"/>
     </row>
     <row r="52" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B52" s="160" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="199" t="s">
+      <c r="C52" s="196" t="s">
         <v>48</v>
       </c>
-      <c r="D52" s="176">
+      <c r="D52" s="174">
         <f>i_Inputs!$D$59</f>
         <v>31223</v>
       </c>
       <c r="E52" s="153"/>
-      <c r="F52" s="169"/>
-      <c r="G52" s="169"/>
-      <c r="H52" s="169"/>
-      <c r="I52" s="169"/>
+      <c r="F52" s="167"/>
+      <c r="G52" s="167"/>
+      <c r="H52" s="167"/>
+      <c r="I52" s="167"/>
     </row>
     <row r="53" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="245" t="s">
+      <c r="B53" s="242" t="s">
         <v>107</v>
       </c>
-      <c r="C53" s="246" t="s">
+      <c r="C53" s="243" t="s">
         <v>108</v>
       </c>
-      <c r="D53" s="249">
+      <c r="D53" s="246">
         <f>D51/D52</f>
         <v>95.802672018961204</v>
       </c>
       <c r="E53" s="153"/>
-      <c r="F53" s="169"/>
-      <c r="G53" s="169"/>
-      <c r="H53" s="169"/>
-      <c r="I53" s="169"/>
+      <c r="F53" s="167"/>
+      <c r="G53" s="167"/>
+      <c r="H53" s="167"/>
+      <c r="I53" s="167"/>
     </row>
     <row r="55" spans="1:9" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A55" s="124" t="s">
@@ -11590,7 +11707,7 @@
       <c r="B55" s="125" t="s">
         <v>129</v>
       </c>
-      <c r="C55" s="203"/>
+      <c r="C55" s="200"/>
     </row>
     <row r="56" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A56" s="41"/>
@@ -11598,64 +11715,64 @@
     </row>
     <row r="57" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B57" s="160" t="s">
-        <v>251</v>
-      </c>
-      <c r="C57" s="266" t="s">
+        <v>250</v>
+      </c>
+      <c r="C57" s="262" t="s">
         <v>8</v>
       </c>
-      <c r="D57" s="267">
+      <c r="D57" s="263">
         <f>o_FS!G8</f>
         <v>2563281.25</v>
       </c>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="160" t="s">
+      <c r="B58" s="271" t="s">
         <v>109</v>
       </c>
-      <c r="C58" s="266" t="s">
+      <c r="C58" s="272" t="s">
         <v>69</v>
       </c>
-      <c r="D58" s="268">
+      <c r="D58" s="270">
         <f>i_Inputs!$D$56</f>
         <v>2.5</v>
       </c>
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="269" t="s">
+      <c r="B59" s="264" t="s">
         <v>110</v>
       </c>
-      <c r="C59" s="270" t="s">
+      <c r="C59" s="265" t="s">
         <v>8</v>
       </c>
-      <c r="D59" s="271">
+      <c r="D59" s="266">
         <f>D57*D58</f>
         <v>6408203.125</v>
       </c>
       <c r="E59" s="5"/>
     </row>
     <row r="60" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="269" t="s">
+      <c r="B60" s="264" t="s">
         <v>111</v>
       </c>
-      <c r="C60" s="270" t="s">
+      <c r="C60" s="265" t="s">
         <v>8</v>
       </c>
-      <c r="D60" s="271">
+      <c r="D60" s="266">
         <f>D59+D48+D49+D50</f>
         <v>6657677.125</v>
       </c>
       <c r="E60" s="5"/>
     </row>
     <row r="61" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="245" t="s">
+      <c r="B61" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="C61" s="272" t="s">
+      <c r="C61" s="267" t="s">
         <v>108</v>
       </c>
-      <c r="D61" s="249">
+      <c r="D61" s="246">
         <f>D60/D52</f>
         <v>213.22989863241841</v>
       </c>
@@ -11663,70 +11780,70 @@
     </row>
     <row r="62" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B62" s="163"/>
-      <c r="C62" s="273"/>
+      <c r="C62" s="268"/>
       <c r="D62" s="164"/>
       <c r="E62" s="5"/>
     </row>
     <row r="63" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B63" s="160" t="s">
-        <v>250</v>
-      </c>
-      <c r="C63" s="266" t="s">
+        <v>249</v>
+      </c>
+      <c r="C63" s="262" t="s">
         <v>8</v>
       </c>
-      <c r="D63" s="267">
+      <c r="D63" s="263">
         <f>o_FS!G20</f>
         <v>92570.71875</v>
       </c>
       <c r="E63" s="5"/>
     </row>
     <row r="64" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="160" t="s">
+      <c r="B64" s="271" t="s">
         <v>113</v>
       </c>
-      <c r="C64" s="266" t="s">
+      <c r="C64" s="272" t="s">
         <v>69</v>
       </c>
-      <c r="D64" s="268">
+      <c r="D64" s="270">
         <f>i_Inputs!$D$57</f>
         <v>20</v>
       </c>
       <c r="E64" s="5"/>
     </row>
     <row r="65" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="269" t="s">
+      <c r="B65" s="264" t="s">
         <v>114</v>
       </c>
-      <c r="C65" s="270" t="s">
+      <c r="C65" s="265" t="s">
         <v>8</v>
       </c>
-      <c r="D65" s="271">
+      <c r="D65" s="266">
         <f>D63*D64</f>
         <v>1851414.375</v>
       </c>
       <c r="E65" s="5"/>
     </row>
     <row r="66" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="269" t="s">
+      <c r="B66" s="264" t="s">
         <v>115</v>
       </c>
-      <c r="C66" s="270" t="s">
+      <c r="C66" s="265" t="s">
         <v>8</v>
       </c>
-      <c r="D66" s="271">
+      <c r="D66" s="266">
         <f>D65+D48+D49+D50</f>
         <v>2100888.375</v>
       </c>
       <c r="E66" s="5"/>
     </row>
     <row r="67" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="245" t="s">
+      <c r="B67" s="242" t="s">
         <v>116</v>
       </c>
-      <c r="C67" s="272" t="s">
+      <c r="C67" s="267" t="s">
         <v>108</v>
       </c>
-      <c r="D67" s="249">
+      <c r="D67" s="246">
         <f>D66/D52</f>
         <v>67.286563590942578</v>
       </c>
@@ -11742,7 +11859,7 @@
       <c r="B69" s="125" t="s">
         <v>130</v>
       </c>
-      <c r="C69" s="203"/>
+      <c r="C69" s="200"/>
     </row>
     <row r="70" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A70" s="41"/>
@@ -11750,256 +11867,269 @@
     </row>
     <row r="71" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A71" s="41"/>
-      <c r="B71" s="169" t="str">
+      <c r="B71" s="167" t="str">
         <f>i_Inputs!B63</f>
         <v>DCF Weight</v>
       </c>
-      <c r="C71" s="205" t="str">
+      <c r="C71" s="202" t="str">
         <f>i_Inputs!C63</f>
         <v>%</v>
       </c>
-      <c r="D71" s="177">
+      <c r="D71" s="281">
         <f>i_Inputs!D63</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A72" s="41"/>
-      <c r="B72" s="178"/>
-      <c r="D72" s="169"/>
-    </row>
-    <row r="73" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="250" t="s">
+      <c r="B72" s="167" t="s">
+        <v>317</v>
+      </c>
+      <c r="C72" s="202" t="s">
+        <v>316</v>
+      </c>
+      <c r="D72" s="282" t="str">
+        <f>i_Inputs!D64</f>
+        <v>Target EV / Sales Multiple</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="41"/>
+      <c r="B73" s="175"/>
+      <c r="D73" s="167"/>
+    </row>
+    <row r="74" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="247" t="s">
         <v>117</v>
       </c>
-      <c r="C73" s="251" t="s">
+      <c r="C74" s="248" t="s">
         <v>8</v>
       </c>
-      <c r="D73" s="252">
-        <f>D47*$D$71+D59*(1-$D$71)</f>
+      <c r="D74" s="249">
+        <f>D47*$D$71 + IF($D$72 = i_Inputs!$B$56, D59, IF($D$72 = i_Inputs!$B$57, D65, D47))*(1-$D$71)</f>
         <v>4574987.9767240128</v>
       </c>
-      <c r="E73" s="15"/>
-    </row>
-    <row r="74" spans="1:5" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="253" t="s">
+      <c r="E74" s="15"/>
+    </row>
+    <row r="75" spans="1:5" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="C74" s="254" t="s">
+      <c r="C75" s="251" t="s">
         <v>8</v>
       </c>
-      <c r="D74" s="255">
-        <f>D73+D48+D49+D50</f>
+      <c r="D75" s="252">
+        <f>D74+D48+D49+D50</f>
         <v>4824461.9767240128</v>
       </c>
-      <c r="E74" s="15"/>
-    </row>
-    <row r="75" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="163"/>
-      <c r="C75" s="201"/>
-      <c r="D75" s="164"/>
       <c r="E75" s="15"/>
     </row>
     <row r="76" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="160" t="s">
+      <c r="B76" s="163"/>
+      <c r="C76" s="198"/>
+      <c r="D76" s="164"/>
+      <c r="E76" s="15"/>
+    </row>
+    <row r="77" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="199" t="s">
+      <c r="C77" s="196" t="s">
         <v>8</v>
       </c>
-      <c r="D76" s="174">
+      <c r="D77" s="283">
         <f>i_Inputs!$D$61</f>
         <v>500000</v>
       </c>
-      <c r="E76" s="15"/>
-    </row>
-    <row r="77" spans="1:5" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="256" t="s">
+      <c r="E77" s="15"/>
+    </row>
+    <row r="78" spans="1:5" ht="20" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="253" t="s">
         <v>119</v>
       </c>
-      <c r="C77" s="257" t="s">
+      <c r="C78" s="254" t="s">
         <v>8</v>
       </c>
-      <c r="D77" s="258">
-        <f>D74+D76</f>
+      <c r="D78" s="275">
+        <f>D75+D77</f>
         <v>5324461.9767240128</v>
       </c>
-      <c r="E77" s="15"/>
-    </row>
-    <row r="78" spans="1:5" ht="20" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="163"/>
-      <c r="C78" s="201"/>
-      <c r="D78" s="164"/>
       <c r="E78" s="15"/>
     </row>
-    <row r="79" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="160" t="s">
+    <row r="79" spans="1:5" ht="20" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="163"/>
+      <c r="C79" s="198"/>
+      <c r="D79" s="164"/>
+      <c r="E79" s="15"/>
+    </row>
+    <row r="80" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="160" t="s">
         <v>120</v>
       </c>
-      <c r="C79" s="199" t="s">
+      <c r="C80" s="196" t="s">
         <v>108</v>
       </c>
-      <c r="D79" s="179">
-        <f>D74/D52</f>
+      <c r="D80" s="176">
+        <f>D75/D52</f>
         <v>154.51628532568981</v>
       </c>
-      <c r="E79" s="15"/>
-    </row>
-    <row r="80" spans="1:5" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="245" t="s">
+      <c r="E80" s="15"/>
+    </row>
+    <row r="81" spans="1:8" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="242" t="s">
+        <v>310</v>
+      </c>
+      <c r="C81" s="243" t="s">
+        <v>108</v>
+      </c>
+      <c r="D81" s="246">
+        <f>D80*(1-i_Inputs!$D$60)</f>
+        <v>143.70014535289152</v>
+      </c>
+      <c r="E81" s="15"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E82" s="15"/>
+    </row>
+    <row r="83" spans="1:8" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A83" s="124" t="s">
+        <v>122</v>
+      </c>
+      <c r="B83" s="125" t="s">
+        <v>125</v>
+      </c>
+      <c r="C83" s="200"/>
+    </row>
+    <row r="84" spans="1:8" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="177" t="s">
         <v>311</v>
       </c>
-      <c r="C80" s="246" t="s">
-        <v>108</v>
-      </c>
-      <c r="D80" s="249">
-        <f>D79*(1-i_Inputs!$D$60)</f>
-        <v>143.70014535289152</v>
-      </c>
-      <c r="E80" s="15"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="E81" s="15"/>
-    </row>
-    <row r="82" spans="1:8" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A82" s="124" t="s">
-        <v>122</v>
-      </c>
-      <c r="B82" s="125" t="s">
-        <v>125</v>
-      </c>
-      <c r="C82" s="203"/>
-    </row>
-    <row r="83" spans="1:8" ht="19" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="180" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="85" spans="1:8" s="88" customFormat="1" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A85"/>
-      <c r="B85" s="181" t="s">
+    </row>
+    <row r="85" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="86" spans="1:8" s="88" customFormat="1" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A86"/>
+      <c r="B86" s="178" t="s">
         <v>121</v>
       </c>
-      <c r="C85" s="206"/>
-      <c r="D85" s="182">
-        <f>$F$85-1</f>
+      <c r="C86" s="203"/>
+      <c r="D86" s="179">
+        <f>$F$86-1</f>
         <v>1.5</v>
       </c>
-      <c r="E85" s="182">
-        <f>$F$85-0.5</f>
+      <c r="E86" s="179">
+        <f>$F$86-0.5</f>
         <v>2</v>
       </c>
-      <c r="F85" s="182">
+      <c r="F86" s="179">
         <f>i_Inputs!$D$56</f>
         <v>2.5</v>
       </c>
-      <c r="G85" s="182">
-        <f>$F$85+0.5</f>
+      <c r="G86" s="179">
+        <f>$F$86+0.5</f>
         <v>3</v>
       </c>
-      <c r="H85" s="182">
-        <f>F85+1</f>
+      <c r="H86" s="179">
+        <f>F86+1</f>
         <v>3.5</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="183">
-        <f>-i_Inputs!$D$65</f>
+    <row r="87" spans="1:8" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B87" s="180">
+        <f>-i_Inputs!$D$66</f>
         <v>-0.05</v>
       </c>
-      <c r="C86" s="207" t="s">
+      <c r="C87" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="D86" s="184">
-        <f>(o_FS!$G$8*(1+$B86)*D$85+$D$48+$D$49+$D$50)/$D$52</f>
+      <c r="D87" s="181">
+        <f>(o_FS!$G$8*(1+$B87)*D$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>124.97677293181309</v>
       </c>
-      <c r="E86" s="184">
-        <f>(o_FS!$G$8*(1+$B86)*E$85+$D$48+$D$49+$D$50)/$D$52</f>
+      <c r="E87" s="181">
+        <f>(o_FS!$G$8*(1+$B87)*E$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>163.972340101848</v>
       </c>
-      <c r="F86" s="184">
-        <f>(o_FS!$G$8*(1+$B86)*F$85+$D$48+$D$49+$D$50)/$D$52</f>
+      <c r="F87" s="181">
+        <f>(o_FS!$G$8*(1+$B87)*F$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>202.96790727188289</v>
       </c>
-      <c r="G86" s="184">
-        <f>(o_FS!$G$8*(1+$B86)*G$85+$D$48+$D$49+$D$50)/$D$52</f>
+      <c r="G87" s="181">
+        <f>(o_FS!$G$8*(1+$B87)*G$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>241.96347444191781</v>
       </c>
-      <c r="H86" s="185">
-        <f>(o_FS!$G$8*(1+$B86)*H$85+$D$48+$D$49+$D$50)/$D$52</f>
+      <c r="H87" s="182">
+        <f>(o_FS!$G$8*(1+$B87)*H$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>280.95904161195273</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="186">
+    <row r="88" spans="1:8" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B88" s="183">
         <v>0</v>
       </c>
-      <c r="C87" s="208" t="s">
+      <c r="C88" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="D87" s="187">
-        <f>(o_FS!$G$8*(1+$B87)*D$85+$D$48+$D$49+$D$50)/$D$52</f>
+      <c r="D88" s="184">
+        <f>(o_FS!$G$8*(1+$B88)*D$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>131.13396774813438</v>
       </c>
-      <c r="E87" s="187">
-        <f>(o_FS!$G$8*(1+$B87)*E$85+$D$48+$D$49+$D$50)/$D$52</f>
+      <c r="E88" s="184">
+        <f>(o_FS!$G$8*(1+$B88)*E$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>172.1819331902764</v>
       </c>
-      <c r="F87" s="259">
-        <f>(o_FS!$G$8*(1+$B87)*F$85+$D$48+$D$49+$D$50)/$D$52</f>
+      <c r="F88" s="255">
+        <f>(o_FS!$G$8*(1+$B88)*F$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>213.22989863241841</v>
       </c>
-      <c r="G87" s="187">
-        <f>(o_FS!$G$8*(1+$B87)*G$85+$D$48+$D$49+$D$50)/$D$52</f>
+      <c r="G88" s="184">
+        <f>(o_FS!$G$8*(1+$B88)*G$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>254.27786407456043</v>
       </c>
-      <c r="H87" s="188">
-        <f>(o_FS!$G$8*(1+$B87)*H$85+$D$48+$D$49+$D$50)/$D$52</f>
+      <c r="H88" s="185">
+        <f>(o_FS!$G$8*(1+$B88)*H$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>295.32582951670241</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="189">
-        <f>i_Inputs!$D$65</f>
+    <row r="89" spans="1:8" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B89" s="186">
+        <f>i_Inputs!$D$66</f>
         <v>0.05</v>
       </c>
-      <c r="C88" s="209" t="s">
+      <c r="C89" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="D88" s="190">
-        <f>(o_FS!$G$8*(1+$B88)*D$85+$D$48+$D$49+$D$50)/$D$52</f>
+      <c r="D89" s="187">
+        <f>(o_FS!$G$8*(1+$B89)*D$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>137.2911625644557</v>
       </c>
-      <c r="E88" s="190">
-        <f>(o_FS!$G$8*(1+$B88)*E$85+$D$48+$D$49+$D$50)/$D$52</f>
+      <c r="E89" s="187">
+        <f>(o_FS!$G$8*(1+$B89)*E$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>180.39152627870479</v>
       </c>
-      <c r="F88" s="190">
-        <f>(o_FS!$G$8*(1+$B88)*F$85+$D$48+$D$49+$D$50)/$D$52</f>
+      <c r="F89" s="187">
+        <f>(o_FS!$G$8*(1+$B89)*F$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>223.4918899929539</v>
       </c>
-      <c r="G88" s="190">
-        <f>(o_FS!$G$8*(1+$B88)*G$85+$D$48+$D$49+$D$50)/$D$52</f>
+      <c r="G89" s="187">
+        <f>(o_FS!$G$8*(1+$B89)*G$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>266.59225370720304</v>
       </c>
-      <c r="H88" s="191">
-        <f>(o_FS!$G$8*(1+$B88)*H$85+$D$48+$D$49+$D$50)/$D$52</f>
+      <c r="H89" s="188">
+        <f>(o_FS!$G$8*(1+$B89)*H$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>309.69261742145216</v>
       </c>
     </row>
-    <row r="90" spans="1:8" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A90" s="124" t="s">
+    <row r="91" spans="1:8" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A91" s="124" t="s">
         <v>122</v>
       </c>
-      <c r="B90" s="125" t="s">
+      <c r="B91" s="125" t="s">
         <v>124</v>
       </c>
-      <c r="C90" s="203"/>
+      <c r="C91" s="200"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7ca7Z/GnO1w8lJyDwibbYdCmAJKT/G0FpqLaly/bRC5Y0cV/5oQQnqGf7K6iembmmhK3ZRSp4tD0AnFK+d8vuA==" saltValue="JfvJ8wVyweAALfxtILsK2A==" spinCount="100000" sheet="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ZApRvT0RGVqCbRQYC1cOiJ8qK0v0vLgbcw2EEyhH5YajmJw3eQrg6y4c4m0DPvznRhgv4qzz+ldBNHQUrbPutA==" saltValue="nIbY1gAJ8li9DtUIoOHIJg==" spinCount="100000" sheet="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
@@ -12039,7 +12169,7 @@
     </row>
     <row r="4" spans="1:10" s="128" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="B4" s="129" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C4" s="130"/>
       <c r="E4" s="130" t="str">
@@ -12125,7 +12255,7 @@
     </row>
     <row r="9" spans="1:10" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B9" s="153" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="147">
@@ -12388,7 +12518,7 @@
     </row>
     <row r="19" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B19" s="153" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="150">
@@ -12662,7 +12792,7 @@
     </row>
     <row r="32" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B32" s="153" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="147">
@@ -12688,7 +12818,7 @@
     </row>
     <row r="33" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B33" s="153" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="150">
@@ -12714,7 +12844,7 @@
     </row>
     <row r="34" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B34" s="153" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="150">
@@ -12776,7 +12906,7 @@
     </row>
     <row r="37" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="153" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="150">
@@ -12802,7 +12932,7 @@
     </row>
     <row r="38" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B38" s="153" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="150">
@@ -12828,7 +12958,7 @@
     </row>
     <row r="39" spans="1:9" s="52" customFormat="1" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B39" s="154" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C39" s="53"/>
       <c r="D39" s="159">
@@ -12858,7 +12988,7 @@
     </row>
     <row r="40" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B40" s="153" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="150">
@@ -12884,7 +13014,7 @@
     </row>
     <row r="41" spans="1:9" ht="19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B41" s="153" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="150">
@@ -12998,7 +13128,7 @@
     </row>
     <row r="4" spans="1:10" s="128" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="B4" s="129" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C4" s="130"/>
       <c r="E4" s="130" t="str">
@@ -13164,7 +13294,7 @@
     </row>
     <row r="12" spans="1:10" s="41" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B12" s="84" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D12" s="85"/>
       <c r="E12" s="86">
@@ -13194,13 +13324,13 @@
         <v>122</v>
       </c>
       <c r="B14" s="136" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="1:10" s="52" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="59" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E16" s="17">
         <f>IF(E$5="Actual",i_Historical!E14,-E$11*i_Inputs!E14)</f>
@@ -13351,7 +13481,7 @@
     </row>
     <row r="23" spans="1:9" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B23" s="37" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="39"/>
@@ -13378,7 +13508,7 @@
     </row>
     <row r="24" spans="1:9" s="41" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B24" s="84" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D24" s="85"/>
       <c r="E24" s="86">
@@ -13408,7 +13538,7 @@
         <v>122</v>
       </c>
       <c r="B26" s="136" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2"/>
@@ -13496,7 +13626,7 @@
     </row>
     <row r="31" spans="1:9" ht="17" hidden="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B31" s="34" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="54">
@@ -13534,13 +13664,13 @@
         <v>122</v>
       </c>
       <c r="B33" s="136" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B35" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="54">
@@ -13566,7 +13696,7 @@
     </row>
     <row r="36" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B36" s="34" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="7">
@@ -13592,7 +13722,7 @@
     </row>
     <row r="37" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="7">
@@ -13618,7 +13748,7 @@
     </row>
     <row r="38" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B38" s="34" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="54">
@@ -13644,7 +13774,7 @@
     </row>
     <row r="39" spans="1:9" s="52" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B39" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C39" s="56"/>
       <c r="D39" s="66">
@@ -13684,13 +13814,13 @@
         <v>122</v>
       </c>
       <c r="B41" s="136" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2"/>
     <row r="43" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B43" s="34" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="54">
@@ -13716,7 +13846,7 @@
     </row>
     <row r="44" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B44" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E44" s="54">
         <f>IF(E$5="Actual",0,MAX(0,N(i_Inputs!E36)))</f>
@@ -13741,7 +13871,7 @@
     </row>
     <row r="45" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B45" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E45" s="54">
         <f>IF(E$5="Actual",i_Historical!E39-SUM(E43:E44), MIN(0,N(i_Inputs!E36)))</f>
@@ -13766,7 +13896,7 @@
     </row>
     <row r="46" spans="1:9" s="52" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B46" s="67" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C46" s="56"/>
       <c r="D46" s="66">
@@ -13797,7 +13927,7 @@
     <row r="47" spans="1:9" ht="17" hidden="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="48" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B48" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="54">
@@ -13823,7 +13953,7 @@
     </row>
     <row r="49" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B49" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E49" s="54">
         <f>E38</f>
@@ -13848,7 +13978,7 @@
     </row>
     <row r="50" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B50" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E50" s="54">
         <f>-E55</f>
@@ -13873,7 +14003,7 @@
     </row>
     <row r="51" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B51" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E51" s="54">
         <f>IF(E$5="Actual",i_Historical!E40-SUM(E48:E50),-i_Inputs!E41)</f>
@@ -13898,7 +14028,7 @@
     </row>
     <row r="52" spans="1:9" s="52" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B52" s="67" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C52" s="56"/>
       <c r="D52" s="66">
@@ -13929,7 +14059,7 @@
     <row r="53" spans="1:9" ht="17" hidden="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="54" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B54" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E54" s="54">
         <f>-AVERAGE(E43,E46)*i_Inputs!$D$35</f>
@@ -13954,7 +14084,7 @@
     </row>
     <row r="55" spans="1:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B55" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E55" s="54">
         <f>-E48*i_Inputs!$D$39</f>
@@ -13979,7 +14109,7 @@
     </row>
     <row r="56" spans="1:9" s="52" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B56" s="67" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C56" s="56"/>
       <c r="D56" s="56"/>
@@ -14069,13 +14199,14 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.83203125" customWidth="1"/>
     <col min="2" max="2" width="76" style="3" customWidth="1"/>
     <col min="3" max="3" width="11.6640625" customWidth="1"/>
-    <col min="4" max="9" width="12" customWidth="1"/>
+    <col min="4" max="4" width="23.1640625" customWidth="1"/>
+    <col min="5" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="46.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14122,7 +14253,7 @@
         <v>2028E</v>
       </c>
       <c r="J4" s="128" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="131" customFormat="1" ht="19" x14ac:dyDescent="0.2">
@@ -14153,7 +14284,7 @@
         <v>122</v>
       </c>
       <c r="B6" s="125" t="s">
-        <v>134</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2"/>
@@ -14181,7 +14312,7 @@
     </row>
     <row r="9" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B9" s="34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>58</v>
@@ -14203,7 +14334,7 @@
     </row>
     <row r="10" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" s="34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>58</v>
@@ -14231,7 +14362,7 @@
         <v>122</v>
       </c>
       <c r="B12" s="125" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14239,7 +14370,7 @@
     </row>
     <row r="14" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>58</v>
@@ -14265,7 +14396,7 @@
     </row>
     <row r="16" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="34" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>58</v>
@@ -14282,12 +14413,12 @@
         <v>0.4</v>
       </c>
       <c r="J16" s="116" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B17" s="34" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>58</v>
@@ -14309,7 +14440,7 @@
     </row>
     <row r="18" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B18" s="34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>58</v>
@@ -14370,7 +14501,7 @@
         <v>0.01</v>
       </c>
       <c r="J20" s="116" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -14381,7 +14512,7 @@
         <v>122</v>
       </c>
       <c r="B22" s="125" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14389,10 +14520,10 @@
     </row>
     <row r="24" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B24" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
@@ -14411,10 +14542,10 @@
     </row>
     <row r="25" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B25" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
@@ -14433,7 +14564,7 @@
     </row>
     <row r="26" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B26" s="34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>8</v>
@@ -14447,7 +14578,7 @@
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
       <c r="J26" s="116" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14455,7 +14586,7 @@
     </row>
     <row r="28" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B28" s="34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>8</v>
@@ -14472,12 +14603,12 @@
         <v>55000</v>
       </c>
       <c r="J28" s="116" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B29" s="34" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>58</v>
@@ -14496,7 +14627,7 @@
     </row>
     <row r="30" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B30" s="34" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>8</v>
@@ -14510,12 +14641,12 @@
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
       <c r="J30" s="116" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B31" s="34" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>8</v>
@@ -14526,7 +14657,7 @@
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="116" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
@@ -14537,7 +14668,7 @@
         <v>122</v>
       </c>
       <c r="B33" s="125" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14545,7 +14676,7 @@
     </row>
     <row r="35" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B35" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>58</v>
@@ -14559,12 +14690,12 @@
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="116" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B36" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>8</v>
@@ -14578,12 +14709,12 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="116" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>8</v>
@@ -14597,7 +14728,7 @@
       <c r="H37" s="19"/>
       <c r="I37" s="19"/>
       <c r="J37" s="116" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14613,7 +14744,7 @@
     </row>
     <row r="39" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B39" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>58</v>
@@ -14627,12 +14758,12 @@
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
       <c r="J39" s="116" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B40" s="34" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>8</v>
@@ -14646,12 +14777,12 @@
       <c r="H40" s="19"/>
       <c r="I40" s="19"/>
       <c r="J40" s="116" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B41" s="34" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>8</v>
@@ -14671,15 +14802,15 @@
         <v>18225.083499484805</v>
       </c>
       <c r="J41" s="116" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B42" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="D42" s="112">
         <v>8</v>
@@ -14694,7 +14825,7 @@
         <v>122</v>
       </c>
       <c r="B44" s="125" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14702,7 +14833,7 @@
     </row>
     <row r="46" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B46" s="34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>58</v>
@@ -14716,12 +14847,12 @@
       <c r="H46" s="19"/>
       <c r="I46" s="19"/>
       <c r="J46" s="116" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B47" s="34" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>8</v>
@@ -14735,7 +14866,7 @@
       <c r="H47" s="19"/>
       <c r="I47" s="19"/>
       <c r="J47" s="116" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14751,7 +14882,7 @@
     </row>
     <row r="49" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B49" s="34" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>58</v>
@@ -14768,7 +14899,7 @@
     </row>
     <row r="50" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B50" s="34" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>8</v>
@@ -14795,7 +14926,7 @@
         <v>122</v>
       </c>
       <c r="B52" s="125" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14818,12 +14949,12 @@
       <c r="H54" s="19"/>
       <c r="I54" s="19"/>
       <c r="J54" s="116" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="55" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B55" s="34" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C55" s="33" t="s">
         <v>58</v>
@@ -14837,12 +14968,12 @@
       <c r="H55" s="19"/>
       <c r="I55" s="19"/>
       <c r="J55" s="116" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="56" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B56" s="34" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C56" s="33" t="s">
         <v>69</v>
@@ -14861,7 +14992,7 @@
     </row>
     <row r="57" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B57" s="34" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C57" s="33" t="s">
         <v>69</v>
@@ -14891,7 +15022,7 @@
     </row>
     <row r="59" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B59" s="34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C59" s="33" t="s">
         <v>48</v>
@@ -14960,7 +15091,7 @@
     </row>
     <row r="63" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B63" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C63" s="33" t="s">
         <v>58</v>
@@ -14974,18 +15105,18 @@
       <c r="H63" s="19"/>
       <c r="I63" s="19"/>
       <c r="J63" s="116" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="64" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B64" s="3" t="s">
-        <v>252</v>
+        <v>320</v>
       </c>
       <c r="C64" s="33" t="s">
-        <v>225</v>
-      </c>
-      <c r="D64" s="115">
-        <v>0.5</v>
+        <v>316</v>
+      </c>
+      <c r="D64" s="277" t="s">
+        <v>302</v>
       </c>
       <c r="E64" s="19"/>
       <c r="F64" s="19"/>
@@ -14993,18 +15124,18 @@
       <c r="H64" s="19"/>
       <c r="I64" s="19"/>
       <c r="J64" s="116" t="s">
-        <v>253</v>
+        <v>318</v>
       </c>
     </row>
     <row r="65" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B65" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="C65" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="D65" s="111">
-        <v>0.05</v>
+        <v>224</v>
+      </c>
+      <c r="D65" s="115">
+        <v>0.5</v>
       </c>
       <c r="E65" s="19"/>
       <c r="F65" s="19"/>
@@ -15012,49 +15143,49 @@
       <c r="H65" s="19"/>
       <c r="I65" s="19"/>
       <c r="J65" s="116" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A67" s="124" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C66" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="D66" s="111">
+        <v>0.05</v>
+      </c>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="116" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A68" s="124" t="s">
         <v>122</v>
       </c>
-      <c r="B67" s="125" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="35"/>
-      <c r="J68" s="104"/>
+      <c r="B68" s="125" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="69" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="C69" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="D69" s="111">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="E69" s="19"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="19"/>
-      <c r="I69" s="19"/>
-      <c r="J69" s="116" t="s">
-        <v>277</v>
-      </c>
+      <c r="B69" s="35"/>
+      <c r="J69" s="104"/>
     </row>
     <row r="70" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B70" s="34" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C70" s="33" t="s">
         <v>58</v>
       </c>
       <c r="D70" s="111">
-        <v>5.5E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="E70" s="19"/>
       <c r="F70" s="19"/>
@@ -15062,18 +15193,18 @@
       <c r="H70" s="19"/>
       <c r="I70" s="19"/>
       <c r="J70" s="116" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="71" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B71" s="34" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C71" s="33" t="s">
         <v>58</v>
       </c>
       <c r="D71" s="111">
-        <v>0.01</v>
+        <v>5.5E-2</v>
       </c>
       <c r="E71" s="19"/>
       <c r="F71" s="19"/>
@@ -15081,18 +15212,18 @@
       <c r="H71" s="19"/>
       <c r="I71" s="19"/>
       <c r="J71" s="116" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="72" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B72" s="34" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C72" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="D72" s="119">
-        <v>1.1000000000000001</v>
+        <v>58</v>
+      </c>
+      <c r="D72" s="111">
+        <v>0.01</v>
       </c>
       <c r="E72" s="19"/>
       <c r="F72" s="19"/>
@@ -15100,18 +15231,18 @@
       <c r="H72" s="19"/>
       <c r="I72" s="19"/>
       <c r="J72" s="116" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="73" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B73" s="34" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C73" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="D73" s="111">
-        <v>0.01</v>
+        <v>69</v>
+      </c>
+      <c r="D73" s="119">
+        <v>1.1000000000000001</v>
       </c>
       <c r="E73" s="19"/>
       <c r="F73" s="19"/>
@@ -15119,19 +15250,18 @@
       <c r="H73" s="19"/>
       <c r="I73" s="19"/>
       <c r="J73" s="116" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="74" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B74" s="34" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C74" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D74" s="121">
-        <f>$D$35</f>
-        <v>4.4999999999999998E-2</v>
+      <c r="D74" s="111">
+        <v>0.01</v>
       </c>
       <c r="E74" s="19"/>
       <c r="F74" s="19"/>
@@ -15139,19 +15269,19 @@
       <c r="H74" s="19"/>
       <c r="I74" s="19"/>
       <c r="J74" s="116" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="75" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B75" s="34" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C75" s="33" t="s">
         <v>58</v>
       </c>
       <c r="D75" s="121">
-        <f>$D$49</f>
-        <v>0.22</v>
+        <f>$D$35</f>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="E75" s="19"/>
       <c r="F75" s="19"/>
@@ -15159,18 +15289,19 @@
       <c r="H75" s="19"/>
       <c r="I75" s="19"/>
       <c r="J75" s="116" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="76" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B76" s="34" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C76" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D76" s="111">
-        <v>0.15</v>
+      <c r="D76" s="121">
+        <f>$D$49</f>
+        <v>0.22</v>
       </c>
       <c r="E76" s="19"/>
       <c r="F76" s="19"/>
@@ -15178,19 +15309,18 @@
       <c r="H76" s="19"/>
       <c r="I76" s="19"/>
       <c r="J76" s="116" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="77" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B77" s="34" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C77" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D77" s="121">
-        <f>1-$D$76</f>
-        <v>0.85</v>
+      <c r="D77" s="111">
+        <v>0.15</v>
       </c>
       <c r="E77" s="19"/>
       <c r="F77" s="19"/>
@@ -15198,18 +15328,19 @@
       <c r="H77" s="19"/>
       <c r="I77" s="19"/>
       <c r="J77" s="116" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="78" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B78" s="34" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C78" s="33" t="s">
-        <v>260</v>
-      </c>
-      <c r="D78" s="120">
-        <v>1</v>
+        <v>58</v>
+      </c>
+      <c r="D78" s="121">
+        <f>1-$D$77</f>
+        <v>0.85</v>
       </c>
       <c r="E78" s="19"/>
       <c r="F78" s="19"/>
@@ -15217,37 +15348,59 @@
       <c r="H78" s="19"/>
       <c r="I78" s="19"/>
       <c r="J78" s="116" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B79" s="35"/>
-      <c r="J79" s="104"/>
-    </row>
-    <row r="80" spans="1:10" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A80" s="124" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="34" t="s">
+        <v>275</v>
+      </c>
+      <c r="C79" s="33" t="s">
+        <v>259</v>
+      </c>
+      <c r="D79" s="120">
+        <v>1</v>
+      </c>
+      <c r="E79" s="19"/>
+      <c r="F79" s="19"/>
+      <c r="G79" s="19"/>
+      <c r="H79" s="19"/>
+      <c r="I79" s="19"/>
+      <c r="J79" s="116" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B80" s="35"/>
+      <c r="J80" s="104"/>
+    </row>
+    <row r="81" spans="1:2" s="127" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A81" s="124" t="s">
         <v>122</v>
       </c>
-      <c r="B80" s="125" t="s">
+      <c r="B81" s="125" t="s">
         <v>124</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <dataValidations count="2">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid input" error="Enter a percentage between -100% and 100%." promptTitle="Assumption" prompt="Editable input (percentage)." sqref="G8:I10 G14:I14 G16:I20 D29 D35 D39 D46 D49 D54:D55 D60 D63 D65" xr:uid="{C66B3575-E215-F140-83A7-553D0605393D}">
+  <dataValidations count="3">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid input" error="Enter a percentage between -100% and 100%." promptTitle="Assumption" prompt="Editable input (percentage)." sqref="G8:I10 G14:I14 G16:I20 D29 D35 D39 D46 D49 D54:D55 D60 D66 D63" xr:uid="{C66B3575-E215-F140-83A7-553D0605393D}">
       <formula1>-1</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid input" error="Enter a numeric value." promptTitle="Assumption" prompt="Editable input (number)." sqref="G24:I25 D26 G28:I28 D30 G36 D37 D40 D42 D47 G50:I50 D64:D65 D56:D57 D61" xr:uid="{DE2D9CA4-BF5C-AC40-B123-6B481F9687B8}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid input" error="Enter a numeric value." promptTitle="Assumption" prompt="Editable input (number)." sqref="G24:I25 D26 G28:I28 D30 G36 D37 D40 D42 D47 G50:I50 D65:D66 D56:D57 D61" xr:uid="{DE2D9CA4-BF5C-AC40-B123-6B481F9687B8}">
       <formula1>-1000000000000</formula1>
       <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D64" xr:uid="{8494F2A8-6436-B44A-B9CA-D836660514D4}">
+      <formula1>$B$56:$B$57</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
-    <ignoredError sqref="D74:D75 D77" unlockedFormula="1"/>
+    <ignoredError sqref="D75:D76 D78" unlockedFormula="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
+++ b/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarashan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA9F737-5881-944B-8981-9F28FA4F62E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="gf9yq7wNGRf1LU1tYhmeB2WcDNkKfd4fJZX47NNJod6VHHo2RiH0WooOj2f1ubYFKaN6hoN75hPtI8QGbPx5Lg==" workbookSaltValue="YFQSL0nS//I4UqZMZx8plQ==" workbookSpinCount="100000" lockStructure="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF24F888-DFB9-1B42-BB49-DAB17E69E69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Z44C3UyMEVL96bB2AOb31YihuRAWn+WK0XNOKqNiH22qQvOGTrSBUlxcpAHwsliaRiFi7c92lVZkujb1M09ogg==" workbookSaltValue="3kyWm35AZS5dfiT25bcycw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contents" sheetId="6" r:id="rId1"/>
@@ -28,10 +28,6 @@
     <sheet name="i_Historical" sheetId="2" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">c_FS!$E$10:$I$10</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">c_FS!$E$4:$I$4</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">c_FS!$E$8:$I$8</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">c_FS!$E$9:$I$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">o_Dashboard!$A$1:$H$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -52,7 +48,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -823,9 +819,6 @@
     <t>Drives Bear (-step) and Bull (+step) rows in o_Valuation sensitivity matrix</t>
   </si>
   <si>
-    <t>Disclaimer: This model is a draft prepared for illustrative and analytical purposes only. Forward-looking figures (2026E-2028E), valuation multiples, and implied share prices are based on assumptions and estimates that are inherently uncertain and may differ materially from actual results. Historical figures are extracted from the Bolt Technology OÜ Consolidated Annual Report 2025 and have not been independently verified. Nothing in this model constitutes investment, financial, legal or tax advice, an offer or solicitation to buy or sell any security, or a recommendation regarding any IPO. No output should be relied upon for any investment decision. The author accepts no liability for any loss arising from use of, or reliance on, this model.</t>
-  </si>
-  <si>
     <t>CAPM &amp; WACC Build-up</t>
   </si>
   <si>
@@ -1077,6 +1070,9 @@
   </si>
   <si>
     <t>Produces a ground-up DCF (using mid-year discounting) paired with market trading multiple benchmarks to determine implied Enterprise Value, equity dilution parameters, and target share value.</t>
+  </si>
+  <si>
+    <t>Disclaimer: This model is a draft prepared for illustrative and analytical purposes only. Forward-looking figures (2026E-2028E), valuation multiples, and implied share prices are based on assumptions and estimates that are inherently uncertain and may differ materially from actual results. Historical figures are extracted from the Bolt Technology OÜ Consolidated Annual Reports 2024-25 and have not been independently verified. Nothing in this model constitutes investment, financial, legal or tax advice, an offer or solicitation to buy or sell any security, or a recommendation regarding any IPO. No output should be relied upon for any investment decision. The author accepts no liability for any loss arising from use of, or reliance on, this model.</t>
   </si>
 </sst>
 </file>
@@ -1097,10 +1093,10 @@
     <numFmt numFmtId="173" formatCode="0.0"/>
     <numFmt numFmtId="174" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="175" formatCode="0.00\x"/>
-    <numFmt numFmtId="178" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="179" formatCode="&quot;Case&quot;\ General"/>
+    <numFmt numFmtId="176" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="177" formatCode="&quot;Case&quot;\ General"/>
   </numFmts>
-  <fonts count="51" x14ac:knownFonts="1">
+  <fonts count="50" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1400,13 +1396,6 @@
     <font>
       <sz val="12"/>
       <color rgb="FF404040"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FF0563C1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1846,7 +1835,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="261">
+  <cellXfs count="246">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1978,7 +1967,6 @@
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1994,9 +1982,6 @@
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2092,7 +2077,7 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2137,7 +2122,6 @@
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2295,22 +2279,16 @@
     <xf numFmtId="165" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="34" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="34" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="34" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2362,19 +2340,18 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="19" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="44" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="44" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2399,18 +2376,6 @@
     <xf numFmtId="3" fontId="6" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2429,22 +2394,22 @@
     <xf numFmtId="167" fontId="10" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="47" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="47" fillId="15" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="15" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2459,29 +2424,19 @@
     <xf numFmtId="170" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
-    <xf numFmtId="178" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="179" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2502,10 +2457,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2514,16 +2466,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2532,7 +2486,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="lightUp"/>
@@ -2572,21 +2526,6 @@
       <font>
         <color rgb="FF9C0006"/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightDown"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightDown"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightDown"/>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -6303,24 +6242,24 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>279400</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
+      <xdr:colOff>1231900</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="Input&gt;&gt;">
+        <xdr:cNvPr id="23" name="Contents">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96837579-7A80-0A4C-9F42-A2E5E16B24B0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EA38E50-0841-534C-9BD0-51F72D69A9C6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6328,245 +6267,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="279400" y="1206500"/>
-          <a:ext cx="2171700" cy="812800"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Input&gt;&gt;</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>279400</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>28222</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="Calcs&gt;&gt;">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF3FF2CA-6CFC-E446-BD2B-80CDC1BF883A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="279400" y="2171700"/>
-          <a:ext cx="2171700" cy="790222"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Calcs&gt;&gt;</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>279400</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="Ouput&gt;&gt;">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C5B21E8-324E-604E-A402-6B14E07DBF60}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="279400" y="3124200"/>
-          <a:ext cx="2171700" cy="812800"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Output&gt;&gt;</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>671805</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2186669</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="i_Historical">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CB7B654-4C1B-174C-912A-E5D863D61E0A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2602205" y="1206500"/>
-          <a:ext cx="3419864" cy="812800"/>
+          <a:off x="292100" y="1066800"/>
+          <a:ext cx="2870200" cy="838200"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
+          <a:srgbClr val="000000"/>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
@@ -6596,55 +6304,14 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1">
+            <a:rPr lang="en-US" sz="1000" b="1">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>i_Historical</a:t>
+            <a:t>Contents</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="en-US" sz="1050" b="1">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>includes audited actuals</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> for FY24-25</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1050" b="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -6652,24 +6319,24 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1231900</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="i_Inputs">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        <xdr:cNvPr id="24" name="How To">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7671F14C-A985-A845-B48C-515761AB5EC1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7359BEF-4CF7-E64E-9959-94EB5E87BA25}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6677,17 +6344,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6756400" y="1206500"/>
-          <a:ext cx="3441700" cy="812800"/>
+          <a:off x="292100" y="2032000"/>
+          <a:ext cx="2870200" cy="838200"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
+          <a:srgbClr val="000000"/>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
@@ -6717,21 +6381,20 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1">
+            <a:rPr lang="en-US" sz="1000" b="1">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>i_Inputs</a:t>
+            <a:t>How To</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="en-US" sz="1050" b="1">
+          <a:endParaRPr lang="en-US" sz="1000" b="0">
             <a:solidFill>
-              <a:srgbClr val="000000"/>
+              <a:srgbClr val="FFFFFF"/>
             </a:solidFill>
             <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
@@ -6740,28 +6403,28 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0">
+            <a:rPr lang="en-US" sz="1000" b="0">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
               <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
-            <a:t>includes forecast drivers &amp; model</a:t>
+            <a:t>contains model key and roll-forward user</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="0" baseline="0">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
               <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
-            <a:t> assumptions</a:t>
+            <a:t> manual</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1050" b="0">
+          <a:endParaRPr lang="en-US" sz="1000" b="0">
             <a:solidFill>
-              <a:srgbClr val="000000"/>
+              <a:srgbClr val="FFFFFF"/>
             </a:solidFill>
             <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
@@ -6774,23 +6437,23 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>661291</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>40341</xdr:rowOff>
+      <xdr:colOff>1392767</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2184400</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>43165</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>46567</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="c_FS">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        <xdr:cNvPr id="25" name="Output&gt;&gt;">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB058F4D-F58B-2349-B474-07B0AB7BD248}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87387414-D9B0-1F4A-BBF6-521DA5AB26C6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6798,14 +6461,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2591691" y="2186641"/>
-          <a:ext cx="3428109" cy="790224"/>
+          <a:off x="3323167" y="1066800"/>
+          <a:ext cx="2870200" cy="838200"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6"/>
+          <a:srgbClr val="000000"/>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
@@ -6835,57 +6498,13 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1">
+            <a:rPr lang="en-US" sz="1000" b="1">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>c_FS</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="en-US" sz="1050" b="1">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>comprises calculation schedules including</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>revenue, opex, NWC, fixed assets, debt, and leases</a:t>
+            <a:t>Output&gt;&gt;</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -6895,23 +6514,23 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
+      <xdr:colOff>207434</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>190501</xdr:rowOff>
+      <xdr:colOff>601134</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="o_Valuation">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        <xdr:cNvPr id="26" name="Calcs&gt;&gt;">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BEA691D-7613-8A40-8DAF-FE8C0B10DC2E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FF67CA1-B509-014C-9417-1560284BA3FE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6919,16 +6538,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6719046" y="3124199"/>
-          <a:ext cx="3440954" cy="812802"/>
+          <a:off x="6354234" y="1066800"/>
+          <a:ext cx="2870200" cy="838200"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
+          <a:srgbClr val="000000"/>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
@@ -6958,67 +6575,13 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1">
+            <a:rPr lang="en-US" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>o_Valuation</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="en-US" sz="1050" b="1">
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF"/>
-            </a:solidFill>
-            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>produces</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> blended enterprise and equity </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>valuations</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> along with pricing sensitivity matrix </a:t>
+            <a:t>Calcs&gt;&gt;</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -7027,24 +6590,24 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2183825</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="o_FS">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        <xdr:cNvPr id="27" name="Input&gt;&gt;">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7E2B63D-2EE3-0D49-B77E-CFDDD771C2E5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{315B7E51-C298-4A41-84BF-254D9C2F3C5D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7052,16 +6615,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2590800" y="3124200"/>
-          <a:ext cx="3428425" cy="812800"/>
+          <a:off x="9385300" y="1066800"/>
+          <a:ext cx="2870200" cy="838200"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
+          <a:srgbClr val="000000"/>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
@@ -7091,37 +6652,13 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1">
+            <a:rPr lang="en-US" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>o_FS</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="en-US" sz="1050" b="1">
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF"/>
-            </a:solidFill>
-            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>produces income statement, FCFF, cash &amp; net debt profiles</a:t>
+            <a:t>Input&gt;&gt;</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -7130,24 +6667,24 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1388533</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>143933</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>240554</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>190502</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>42333</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>169333</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="o_Valuation">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        <xdr:cNvPr id="28" name="o_Dashboard">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A86F8839-027E-AA46-B199-4E0BA012C928}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C61FD7DB-5174-E848-B618-54A271F7B7F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7155,16 +6692,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9550400" y="3124200"/>
-          <a:ext cx="3440954" cy="812802"/>
+          <a:off x="3318933" y="2036233"/>
+          <a:ext cx="2870200" cy="838200"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
+          <a:srgbClr val="F79646"/>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
@@ -7194,21 +6729,524 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1">
+            <a:rPr lang="en-US" sz="1000" b="1">
               <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>o_Dashboard</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="en-US" sz="1050" b="1">
+          <a:endParaRPr lang="en-US" sz="1000" b="1">
             <a:solidFill>
-              <a:srgbClr val="FFFFFF"/>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>comprises </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>executive summary and charts</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1384300</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>97366</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>122766</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="o_Valuation">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CDA1294-AD59-C749-8814-85D3AF2BC014}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3314700" y="3005666"/>
+          <a:ext cx="2870200" cy="838200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F79646"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>o_Valuation</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="1000" b="1">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>produces</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t> blended enterprise and equity </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>valuations</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t> along with pricing sensitivity matrix </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1384300</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="o_FS">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0617FBD-4289-774B-B140-759E015D77C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3314700" y="3975100"/>
+          <a:ext cx="2870200" cy="838200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F79646"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>o_FS</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="1000" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>produces income statement, FCFF, cash &amp; net debt profiles</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>198966</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>592666</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="c_FS">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CFC2F54-0510-A740-ABBE-60391C6D8118}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6345766" y="2044700"/>
+          <a:ext cx="2870200" cy="838200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FABF8F"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>c_FS</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="1000" b="1">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>comprises calculation schedules including</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>revenue, opex, NWC, fixed assets, debt, and leases</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>749300</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>143933</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>169333</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="i_Scenario_Manager">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56FE930E-2A34-5749-8D5B-6001D9B0FCF6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9372600" y="2036233"/>
+          <a:ext cx="2870200" cy="838200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FDE9D9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>i_Scenario_Manager</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="1000" b="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
@@ -7217,25 +7255,299 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="0">
               <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
-            <a:t>comprises </a:t>
+            <a:t>contains scenario overlays</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0">
+            <a:rPr lang="en-US" sz="1000" b="0" baseline="0">
               <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
-            <a:t>executive summary and charts</a:t>
+            <a:t> used to stress-test free cashflow and valuation outputs</a:t>
           </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>749300</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>97366</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>122766</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="i_Inputs">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDA4DCD3-A00F-EE43-912F-35AE682D3C29}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9372600" y="3005666"/>
+          <a:ext cx="2870200" cy="838200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FDE9D9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>i_Inputs</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="1000" b="1">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>includes forecast drivers &amp; model</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t> assumptions</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>749300</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="i_Historical">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0380BB58-0459-C041-946A-2D5476EDEDEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9372600" y="3975100"/>
+          <a:ext cx="2870200" cy="838200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FDE9D9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>i_Historical</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="1000" b="1">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>includes audited actuals</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t> for FY24-25</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8581,7 +8893,7 @@
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.83203125" style="1" customWidth="1"/>
@@ -8591,89 +8903,363 @@
     <col min="5" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="198" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="107" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="69" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="196" t="s">
+    <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="192" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" s="105" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="67" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="191" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="195" t="s">
+      <c r="B4" s="190" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="51"/>
+      <c r="B5" s="52"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="51"/>
       <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B7" s="197"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B8" s="197"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B9" s="197"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B10" s="197"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B11" s="197"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B12" s="197"/>
-    </row>
-    <row r="21" spans="1:12" ht="86" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="57" t="s">
-        <v>249</v>
-      </c>
-      <c r="C21" s="57"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="57"/>
-    </row>
-    <row r="22" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="57" t="s">
-        <v>294</v>
-      </c>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="57"/>
-    </row>
-    <row r="24" spans="1:12" s="69" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="69" t="s">
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="51"/>
+      <c r="B7" s="52"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="51"/>
+      <c r="B8" s="52"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="51"/>
+      <c r="B9" s="52"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="51"/>
+      <c r="B10" s="52"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="51"/>
+      <c r="B11" s="52"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="51"/>
+      <c r="B12" s="52"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13"/>
+      <c r="N13"/>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="51"/>
+      <c r="B14" s="52"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="51"/>
+      <c r="B15" s="52"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="51"/>
+      <c r="B16" s="52"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A17" s="51"/>
+      <c r="B17" s="52"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A18" s="51"/>
+      <c r="B18" s="52"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19" s="51"/>
+      <c r="B19" s="52"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A20" s="51"/>
+      <c r="B20" s="52"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A21" s="51"/>
+      <c r="B21" s="52"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A22" s="51"/>
+      <c r="B22" s="52"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A23" s="51"/>
+      <c r="B23" s="52"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A24" s="51"/>
+      <c r="B24" s="52"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+      <c r="P24"/>
+      <c r="Q24"/>
+    </row>
+    <row r="25" spans="1:17" ht="71" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="245" t="s">
+        <v>333</v>
+      </c>
+      <c r="C25" s="245"/>
+      <c r="D25" s="245"/>
+      <c r="E25" s="245"/>
+      <c r="F25" s="245"/>
+      <c r="G25" s="245"/>
+      <c r="H25" s="245"/>
+      <c r="I25" s="245"/>
+      <c r="J25" s="245"/>
+      <c r="K25" s="245"/>
+      <c r="L25" s="245"/>
+    </row>
+    <row r="26" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="245" t="s">
+        <v>293</v>
+      </c>
+      <c r="C26" s="245"/>
+      <c r="D26" s="245"/>
+      <c r="E26" s="245"/>
+      <c r="F26" s="245"/>
+      <c r="G26" s="245"/>
+      <c r="H26" s="245"/>
+      <c r="I26" s="245"/>
+      <c r="J26" s="245"/>
+      <c r="K26" s="245"/>
+      <c r="L26" s="245"/>
+    </row>
+    <row r="28" spans="1:17" s="67" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="B24" s="195" t="s">
+      <c r="B28" s="190" t="s">
         <v>118</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="aqN7MSLwzkDCAP1XDAnjmlhyCEoXPWdpj3ZsTve5+rb48jmKWnvi3zgCLabteDxPv9X81xB+kbGzHtuyGelFpw==" saltValue="Og+PB9lQF04tdaQ/pf1VmA==" spinCount="100000" sheet="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="cjrqWurdRXbDN3J94aXSzH9Oradoec+3PtvkqHW2KkKP4Bn3okgq27BrS0M8dN1Y5oClnChMVNwuRYiGekM4ag==" saltValue="VxgFtFKQl2JXeM/oKegIgg==" spinCount="100000" sheet="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="2">
-    <mergeCell ref="B21:L21"/>
-    <mergeCell ref="B22:L22"/>
+    <mergeCell ref="B25:L25"/>
+    <mergeCell ref="B26:L26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8689,484 +9275,483 @@
   <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.5" style="187" customWidth="1"/>
-    <col min="2" max="2" width="56.6640625" style="187" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" style="241" customWidth="1"/>
-    <col min="4" max="4" width="16" style="187" customWidth="1"/>
-    <col min="5" max="9" width="14.33203125" style="187" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="187"/>
+    <col min="1" max="1" width="4.5" style="182" customWidth="1"/>
+    <col min="2" max="2" width="56.6640625" style="182" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" style="227" customWidth="1"/>
+    <col min="4" max="4" width="16" style="182" customWidth="1"/>
+    <col min="5" max="9" width="14.33203125" style="182" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="182"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="199" t="str">
+      <c r="A1" s="193" t="str">
         <f>Contents!$A1</f>
         <v>Bolt Technology OÜ|Pre-IPO Equity Valuation Model</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="107" t="str">
+      <c r="A2" s="105" t="str">
         <f>Contents!$A2</f>
         <v>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="113"/>
-      <c r="D3" s="258"/>
-    </row>
-    <row r="4" spans="1:10" s="256" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:10" s="240" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="253"/>
+      <c r="A3" s="110"/>
+    </row>
+    <row r="4" spans="1:10" s="241" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:10" s="58" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="238"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B6" s="235" t="s">
-        <v>315</v>
-      </c>
-      <c r="C6" s="257">
+      <c r="B6" s="224" t="s">
+        <v>314</v>
+      </c>
+      <c r="C6" s="242">
         <v>3</v>
       </c>
-      <c r="E6" s="243">
+      <c r="E6" s="229">
         <f>D6+1</f>
         <v>1</v>
       </c>
-      <c r="F6" s="243">
+      <c r="F6" s="229">
         <f t="shared" ref="F6:I6" si="0">E6+1</f>
         <v>2</v>
       </c>
-      <c r="G6" s="243">
+      <c r="G6" s="229">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H6" s="243">
+      <c r="H6" s="229">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I6" s="243">
+      <c r="I6" s="229">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J6" s="73"/>
-    </row>
-    <row r="7" spans="1:10" s="240" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="253"/>
-    </row>
-    <row r="8" spans="1:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="90" t="s">
+      <c r="J6" s="71"/>
+    </row>
+    <row r="7" spans="1:10" s="58" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="238"/>
+    </row>
+    <row r="8" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B8" s="112" t="s">
-        <v>309</v>
-      </c>
-      <c r="C8" s="244"/>
+      <c r="B8" s="109" t="s">
+        <v>308</v>
+      </c>
+      <c r="C8" s="230"/>
     </row>
     <row r="9" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="187" t="s">
+      <c r="B10" s="182" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="241" t="s">
-        <v>314</v>
-      </c>
-      <c r="D10" s="248" cm="1">
+      <c r="C10" s="227" t="s">
+        <v>313</v>
+      </c>
+      <c r="D10" s="234" cm="1">
         <f t="array" ref="D10">INDEX(E10:J10,$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="81">
+      <c r="E10" s="79">
         <v>-0.05</v>
       </c>
-      <c r="F10" s="81">
+      <c r="F10" s="79">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="G10" s="81">
+      <c r="G10" s="79">
         <v>0</v>
       </c>
-      <c r="H10" s="81">
+      <c r="H10" s="79">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I10" s="81">
+      <c r="I10" s="79">
         <v>0.05</v>
       </c>
-      <c r="J10" s="73"/>
+      <c r="J10" s="71"/>
     </row>
     <row r="11" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="187" t="s">
+      <c r="B11" s="182" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="241" t="s">
-        <v>314</v>
-      </c>
-      <c r="D11" s="248" cm="1">
+      <c r="C11" s="227" t="s">
+        <v>313</v>
+      </c>
+      <c r="D11" s="234" cm="1">
         <f t="array" ref="D11">INDEX(E11:J11,$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="81">
+      <c r="E11" s="79">
         <v>-0.05</v>
       </c>
-      <c r="F11" s="81">
+      <c r="F11" s="79">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="G11" s="81">
+      <c r="G11" s="79">
         <v>0</v>
       </c>
-      <c r="H11" s="81">
+      <c r="H11" s="79">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I11" s="81">
+      <c r="I11" s="79">
         <v>0.05</v>
       </c>
-      <c r="J11" s="73"/>
+      <c r="J11" s="71"/>
     </row>
     <row r="12" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="187" t="s">
+      <c r="B12" s="182" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="241" t="s">
-        <v>314</v>
-      </c>
-      <c r="D12" s="248" cm="1">
+      <c r="C12" s="227" t="s">
+        <v>313</v>
+      </c>
+      <c r="D12" s="234" cm="1">
         <f t="array" ref="D12">INDEX(E12:J12,$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="81">
+      <c r="E12" s="79">
         <v>-0.05</v>
       </c>
-      <c r="F12" s="81">
+      <c r="F12" s="79">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="G12" s="81">
+      <c r="G12" s="79">
         <v>0</v>
       </c>
-      <c r="H12" s="81">
+      <c r="H12" s="79">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I12" s="81">
+      <c r="I12" s="79">
         <v>0.05</v>
       </c>
-      <c r="J12" s="73"/>
+      <c r="J12" s="71"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="D13" s="248"/>
-      <c r="E13" s="246"/>
-      <c r="F13" s="246"/>
-      <c r="G13" s="246"/>
-      <c r="H13" s="246"/>
-      <c r="I13" s="246"/>
-    </row>
-    <row r="14" spans="1:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="90" t="s">
+      <c r="D13" s="234"/>
+      <c r="E13" s="232"/>
+      <c r="F13" s="232"/>
+      <c r="G13" s="232"/>
+      <c r="H13" s="232"/>
+      <c r="I13" s="232"/>
+    </row>
+    <row r="14" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B14" s="112" t="s">
-        <v>310</v>
-      </c>
-      <c r="C14" s="244"/>
-      <c r="D14" s="249"/>
-      <c r="E14" s="247"/>
-      <c r="F14" s="247"/>
-      <c r="G14" s="247"/>
-      <c r="H14" s="247"/>
-      <c r="I14" s="247"/>
+      <c r="B14" s="109" t="s">
+        <v>309</v>
+      </c>
+      <c r="C14" s="230"/>
+      <c r="D14" s="235"/>
+      <c r="E14" s="233"/>
+      <c r="F14" s="233"/>
+      <c r="G14" s="233"/>
+      <c r="H14" s="233"/>
+      <c r="I14" s="233"/>
     </row>
     <row r="15" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="248"/>
-      <c r="E15" s="246"/>
-      <c r="F15" s="246"/>
-      <c r="G15" s="246"/>
-      <c r="H15" s="246"/>
-      <c r="I15" s="246"/>
+      <c r="D15" s="234"/>
+      <c r="E15" s="232"/>
+      <c r="F15" s="232"/>
+      <c r="G15" s="232"/>
+      <c r="H15" s="232"/>
+      <c r="I15" s="232"/>
     </row>
     <row r="16" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="187" t="s">
+      <c r="B16" s="182" t="s">
         <v>161</v>
       </c>
-      <c r="C16" s="241" t="s">
-        <v>314</v>
-      </c>
-      <c r="D16" s="248" cm="1">
+      <c r="C16" s="227" t="s">
+        <v>313</v>
+      </c>
+      <c r="D16" s="234" cm="1">
         <f t="array" ref="D16">INDEX(E16:J16,$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="81">
+      <c r="E16" s="79">
         <v>-0.05</v>
       </c>
-      <c r="F16" s="81">
+      <c r="F16" s="79">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="G16" s="81">
+      <c r="G16" s="79">
         <v>0</v>
       </c>
-      <c r="H16" s="81">
+      <c r="H16" s="79">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I16" s="81">
+      <c r="I16" s="79">
         <v>0.05</v>
       </c>
-      <c r="J16" s="73"/>
+      <c r="J16" s="71"/>
     </row>
     <row r="17" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="242"/>
-      <c r="C17" s="245"/>
-      <c r="D17" s="248"/>
-      <c r="E17" s="246"/>
-      <c r="F17" s="246"/>
-      <c r="G17" s="246"/>
-      <c r="H17" s="246"/>
-      <c r="I17" s="246"/>
+      <c r="B17" s="228"/>
+      <c r="C17" s="231"/>
+      <c r="D17" s="234"/>
+      <c r="E17" s="232"/>
+      <c r="F17" s="232"/>
+      <c r="G17" s="232"/>
+      <c r="H17" s="232"/>
+      <c r="I17" s="232"/>
     </row>
     <row r="18" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="187" t="s">
+      <c r="B18" s="182" t="s">
         <v>153</v>
       </c>
-      <c r="C18" s="241" t="s">
-        <v>314</v>
-      </c>
-      <c r="D18" s="248" cm="1">
+      <c r="C18" s="227" t="s">
+        <v>313</v>
+      </c>
+      <c r="D18" s="234" cm="1">
         <f t="array" ref="D18">INDEX(E18:J18,$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="81">
+      <c r="E18" s="79">
         <v>-0.05</v>
       </c>
-      <c r="F18" s="81">
+      <c r="F18" s="79">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="G18" s="81">
+      <c r="G18" s="79">
         <v>0</v>
       </c>
-      <c r="H18" s="81">
+      <c r="H18" s="79">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I18" s="81">
+      <c r="I18" s="79">
         <v>0.05</v>
       </c>
-      <c r="J18" s="73"/>
+      <c r="J18" s="71"/>
     </row>
     <row r="19" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="187" t="s">
+      <c r="B19" s="182" t="s">
         <v>154</v>
       </c>
-      <c r="C19" s="241" t="s">
-        <v>314</v>
-      </c>
-      <c r="D19" s="248" cm="1">
+      <c r="C19" s="227" t="s">
+        <v>313</v>
+      </c>
+      <c r="D19" s="234" cm="1">
         <f t="array" ref="D19">INDEX(E19:J19,$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="81">
+      <c r="E19" s="79">
         <v>-0.05</v>
       </c>
-      <c r="F19" s="81">
+      <c r="F19" s="79">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="G19" s="81">
+      <c r="G19" s="79">
         <v>0</v>
       </c>
-      <c r="H19" s="81">
+      <c r="H19" s="79">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I19" s="81">
+      <c r="I19" s="79">
         <v>0.05</v>
       </c>
-      <c r="J19" s="73"/>
+      <c r="J19" s="71"/>
     </row>
     <row r="20" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="187" t="s">
+      <c r="B20" s="182" t="s">
         <v>128</v>
       </c>
-      <c r="C20" s="241" t="s">
-        <v>314</v>
-      </c>
-      <c r="D20" s="248" cm="1">
+      <c r="C20" s="227" t="s">
+        <v>313</v>
+      </c>
+      <c r="D20" s="234" cm="1">
         <f t="array" ref="D20">INDEX(E20:J20,$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="81">
+      <c r="E20" s="79">
         <v>-0.05</v>
       </c>
-      <c r="F20" s="81">
+      <c r="F20" s="79">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="G20" s="81">
+      <c r="G20" s="79">
         <v>0</v>
       </c>
-      <c r="H20" s="81">
+      <c r="H20" s="79">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I20" s="81">
+      <c r="I20" s="79">
         <v>0.05</v>
       </c>
-      <c r="J20" s="73"/>
+      <c r="J20" s="71"/>
     </row>
     <row r="21" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="187" t="s">
+      <c r="B21" s="182" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="241" t="s">
-        <v>314</v>
-      </c>
-      <c r="D21" s="248" cm="1">
+      <c r="C21" s="227" t="s">
+        <v>313</v>
+      </c>
+      <c r="D21" s="234" cm="1">
         <f t="array" ref="D21">INDEX(E21:J21,$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E21" s="81">
+      <c r="E21" s="79">
         <v>-0.05</v>
       </c>
-      <c r="F21" s="81">
+      <c r="F21" s="79">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="G21" s="81">
+      <c r="G21" s="79">
         <v>0</v>
       </c>
-      <c r="H21" s="81">
+      <c r="H21" s="79">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I21" s="81">
+      <c r="I21" s="79">
         <v>0.05</v>
       </c>
-      <c r="J21" s="73"/>
+      <c r="J21" s="71"/>
     </row>
     <row r="22" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="187" t="s">
+      <c r="B22" s="182" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="241" t="s">
-        <v>314</v>
-      </c>
-      <c r="D22" s="248" cm="1">
+      <c r="C22" s="227" t="s">
+        <v>313</v>
+      </c>
+      <c r="D22" s="234" cm="1">
         <f t="array" ref="D22">INDEX(E22:J22,$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="81">
+      <c r="E22" s="79">
         <v>-0.05</v>
       </c>
-      <c r="F22" s="81">
+      <c r="F22" s="79">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="G22" s="81">
+      <c r="G22" s="79">
         <v>0</v>
       </c>
-      <c r="H22" s="81">
+      <c r="H22" s="79">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I22" s="81">
+      <c r="I22" s="79">
         <v>0.05</v>
       </c>
-      <c r="J22" s="73"/>
-    </row>
-    <row r="24" spans="1:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="90" t="s">
+      <c r="J22" s="71"/>
+    </row>
+    <row r="24" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="112" t="s">
-        <v>312</v>
-      </c>
-      <c r="C24" s="244"/>
+      <c r="B24" s="109" t="s">
+        <v>311</v>
+      </c>
+      <c r="C24" s="230"/>
     </row>
     <row r="25" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="241" t="s">
-        <v>314</v>
-      </c>
-      <c r="D26" s="248" cm="1">
+      <c r="C26" s="227" t="s">
+        <v>313</v>
+      </c>
+      <c r="D26" s="234" cm="1">
         <f t="array" ref="D26">INDEX(E26:J26,$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="81">
+      <c r="E26" s="79">
         <v>-0.05</v>
       </c>
-      <c r="F26" s="81">
+      <c r="F26" s="79">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="G26" s="81">
+      <c r="G26" s="79">
         <v>0</v>
       </c>
-      <c r="H26" s="81">
+      <c r="H26" s="79">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I26" s="81">
+      <c r="I26" s="79">
         <v>0.05</v>
       </c>
-      <c r="J26" s="73"/>
+      <c r="J26" s="71"/>
     </row>
     <row r="27" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B27" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="241" t="s">
-        <v>314</v>
-      </c>
-      <c r="D27" s="248" cm="1">
+      <c r="C27" s="227" t="s">
+        <v>313</v>
+      </c>
+      <c r="D27" s="234" cm="1">
         <f t="array" ref="D27">INDEX(E27:J27,$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="81">
+      <c r="E27" s="79">
         <v>-0.05</v>
       </c>
-      <c r="F27" s="81">
+      <c r="F27" s="79">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="G27" s="81">
+      <c r="G27" s="79">
         <v>0</v>
       </c>
-      <c r="H27" s="81">
+      <c r="H27" s="79">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I27" s="81">
+      <c r="I27" s="79">
         <v>0.05</v>
       </c>
-      <c r="J27" s="73"/>
-    </row>
-    <row r="29" spans="1:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="90" t="s">
+      <c r="J27" s="71"/>
+    </row>
+    <row r="29" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B29" s="112" t="s">
-        <v>313</v>
-      </c>
-      <c r="C29" s="244"/>
+      <c r="B29" s="109" t="s">
+        <v>312</v>
+      </c>
+      <c r="C29" s="230"/>
     </row>
     <row r="30" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2"/>
     <row r="31" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="239" t="s">
+      <c r="B31" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="241" t="s">
-        <v>314</v>
-      </c>
-      <c r="D31" s="248" cm="1">
+      <c r="C31" s="227" t="s">
+        <v>313</v>
+      </c>
+      <c r="D31" s="234" cm="1">
         <f t="array" ref="D31">INDEX(E31:J31,$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E31" s="81">
+      <c r="E31" s="79">
         <v>-0.05</v>
       </c>
-      <c r="F31" s="81">
+      <c r="F31" s="79">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="G31" s="81">
+      <c r="G31" s="79">
         <v>0</v>
       </c>
-      <c r="H31" s="81">
+      <c r="H31" s="79">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I31" s="81">
+      <c r="I31" s="79">
         <v>0.05</v>
       </c>
-      <c r="J31" s="73"/>
-    </row>
-    <row r="33" spans="1:3" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="90" t="s">
+      <c r="J31" s="71"/>
+    </row>
+    <row r="33" spans="1:3" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="112" t="s">
+      <c r="B33" s="109" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="244"/>
+      <c r="C33" s="230"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="50" type="noConversion"/>
+  <phoneticPr fontId="49" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6" xr:uid="{170547D3-ECA6-9D43-A65D-1CBD8E5AA951}">
       <formula1>$E$6:$J$6</formula1>
@@ -9190,86 +9775,86 @@
     <col min="3" max="3" width="11.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="23.1640625" style="1" customWidth="1"/>
     <col min="5" max="9" width="12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="46.83203125" style="87" customWidth="1"/>
+    <col min="10" max="10" width="46.83203125" style="85" customWidth="1"/>
     <col min="11" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="199" t="str">
+      <c r="A1" s="193" t="str">
         <f>Contents!$A1</f>
         <v>Bolt Technology OÜ|Pre-IPO Equity Valuation Model</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="107" t="str">
+      <c r="A2" s="105" t="str">
         <f>Contents!$A2</f>
         <v>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="113"/>
+      <c r="A3" s="110"/>
       <c r="E3" s="47"/>
       <c r="F3" s="47"/>
     </row>
-    <row r="4" spans="1:10" s="70" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C4" s="70" t="s">
+    <row r="4" spans="1:10" s="68" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C4" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="70" t="str">
+      <c r="E4" s="68" t="str">
         <f>i_Historical!E4</f>
         <v>2024A</v>
       </c>
-      <c r="F4" s="70" t="str">
+      <c r="F4" s="68" t="str">
         <f>i_Historical!F4</f>
         <v>2025A</v>
       </c>
-      <c r="G4" s="70" t="str">
+      <c r="G4" s="68" t="str">
         <f>i_Historical!G4</f>
         <v>2026E</v>
       </c>
-      <c r="H4" s="70" t="str">
+      <c r="H4" s="68" t="str">
         <f>i_Historical!H4</f>
         <v>2027E</v>
       </c>
-      <c r="I4" s="70" t="str">
+      <c r="I4" s="68" t="str">
         <f>i_Historical!I4</f>
         <v>2028E</v>
       </c>
-      <c r="J4" s="85" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="70" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E5" s="70" t="str">
+      <c r="J4" s="83" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="68" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="68" t="str">
         <f>i_Historical!E5</f>
         <v>Actual</v>
       </c>
-      <c r="F5" s="70" t="str">
+      <c r="F5" s="68" t="str">
         <f>i_Historical!F5</f>
         <v>Actual</v>
       </c>
-      <c r="G5" s="70" t="str">
+      <c r="G5" s="68" t="str">
         <f>i_Historical!G5</f>
         <v>Estimate</v>
       </c>
-      <c r="H5" s="70" t="str">
+      <c r="H5" s="68" t="str">
         <f>i_Historical!H5</f>
         <v>Estimate</v>
       </c>
-      <c r="I5" s="70" t="str">
+      <c r="I5" s="68" t="str">
         <f>i_Historical!I5</f>
         <v>Estimate</v>
       </c>
-      <c r="J5" s="86"/>
-    </row>
-    <row r="6" spans="1:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="90" t="s">
+      <c r="J5" s="84"/>
+    </row>
+    <row r="6" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="112" t="s">
-        <v>299</v>
-      </c>
-      <c r="J6" s="90"/>
+      <c r="B6" s="109" t="s">
+        <v>298</v>
+      </c>
+      <c r="J6" s="88"/>
     </row>
     <row r="7" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -9279,18 +9864,18 @@
       <c r="C8" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="81">
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="79">
         <v>0.12</v>
       </c>
-      <c r="H8" s="81">
+      <c r="H8" s="79">
         <v>0.11</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="79">
         <v>0.1</v>
       </c>
-      <c r="J8" s="98" t="s">
+      <c r="J8" s="96" t="s">
         <v>57</v>
       </c>
     </row>
@@ -9301,18 +9886,18 @@
       <c r="C9" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="81">
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="79">
         <v>0.18</v>
       </c>
-      <c r="H9" s="81">
+      <c r="H9" s="79">
         <v>0.16</v>
       </c>
-      <c r="I9" s="81">
+      <c r="I9" s="79">
         <v>0.14000000000000001</v>
       </c>
-      <c r="J9" s="98" t="s">
+      <c r="J9" s="96" t="s">
         <v>58</v>
       </c>
     </row>
@@ -9323,37 +9908,37 @@
       <c r="C10" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="81">
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="79">
         <v>0.15</v>
       </c>
-      <c r="H10" s="81">
+      <c r="H10" s="79">
         <v>0.15</v>
       </c>
-      <c r="I10" s="81">
+      <c r="I10" s="79">
         <v>0.12</v>
       </c>
-      <c r="J10" s="98" t="s">
+      <c r="J10" s="96" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B11" s="2"/>
-      <c r="J11" s="99"/>
-    </row>
-    <row r="12" spans="1:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="90" t="s">
+      <c r="J11" s="97"/>
+    </row>
+    <row r="12" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B12" s="112" t="s">
+      <c r="B12" s="109" t="s">
         <v>163</v>
       </c>
-      <c r="J12" s="100"/>
+      <c r="J12" s="98"/>
     </row>
     <row r="13" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B13" s="2"/>
-      <c r="J13" s="99"/>
+      <c r="J13" s="97"/>
     </row>
     <row r="14" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
@@ -9362,25 +9947,25 @@
       <c r="C14" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="81">
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="79">
         <v>0.35499999999999998</v>
       </c>
-      <c r="H14" s="81">
+      <c r="H14" s="79">
         <v>0.35</v>
       </c>
-      <c r="I14" s="81">
+      <c r="I14" s="79">
         <v>0.34499999999999997</v>
       </c>
-      <c r="J14" s="98" t="s">
+      <c r="J14" s="96" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B15" s="3"/>
       <c r="C15" s="14"/>
-      <c r="J15" s="101"/>
+      <c r="J15" s="99"/>
     </row>
     <row r="16" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
@@ -9389,19 +9974,19 @@
       <c r="C16" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="73"/>
-      <c r="F16" s="73"/>
-      <c r="G16" s="81">
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="79">
         <v>0.45</v>
       </c>
-      <c r="H16" s="81">
+      <c r="H16" s="79">
         <v>0.42499999999999999</v>
       </c>
-      <c r="I16" s="81">
+      <c r="I16" s="79">
         <v>0.4</v>
       </c>
-      <c r="J16" s="98" t="s">
-        <v>284</v>
+      <c r="J16" s="96" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -9411,18 +9996,18 @@
       <c r="C17" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="81">
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="79">
         <v>0.05</v>
       </c>
-      <c r="H17" s="81">
+      <c r="H17" s="79">
         <v>0.05</v>
       </c>
-      <c r="I17" s="81">
+      <c r="I17" s="79">
         <v>0.05</v>
       </c>
-      <c r="J17" s="98" t="s">
+      <c r="J17" s="96" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9433,18 +10018,18 @@
       <c r="C18" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="81">
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="79">
         <v>0.12</v>
       </c>
-      <c r="H18" s="81">
+      <c r="H18" s="79">
         <v>0.12</v>
       </c>
-      <c r="I18" s="81">
+      <c r="I18" s="79">
         <v>0.12</v>
       </c>
-      <c r="J18" s="98" t="s">
+      <c r="J18" s="96" t="s">
         <v>62</v>
       </c>
     </row>
@@ -9455,18 +10040,18 @@
       <c r="C19" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="81">
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="79">
         <v>0.02</v>
       </c>
-      <c r="H19" s="81">
+      <c r="H19" s="79">
         <v>0.02</v>
       </c>
-      <c r="I19" s="81">
+      <c r="I19" s="79">
         <v>0.02</v>
       </c>
-      <c r="J19" s="98" t="s">
+      <c r="J19" s="96" t="s">
         <v>78</v>
       </c>
     </row>
@@ -9477,37 +10062,37 @@
       <c r="C20" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="81">
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="79">
         <v>0.01</v>
       </c>
-      <c r="H20" s="81">
+      <c r="H20" s="79">
         <v>0.01</v>
       </c>
-      <c r="I20" s="81">
+      <c r="I20" s="79">
         <v>0.01</v>
       </c>
-      <c r="J20" s="98" t="s">
+      <c r="J20" s="96" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B21" s="2"/>
-      <c r="J21" s="99"/>
-    </row>
-    <row r="22" spans="1:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="90" t="s">
+      <c r="J21" s="97"/>
+    </row>
+    <row r="22" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B22" s="112" t="s">
+      <c r="B22" s="109" t="s">
         <v>162</v>
       </c>
-      <c r="J22" s="100"/>
+      <c r="J22" s="98"/>
     </row>
     <row r="23" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B23" s="2"/>
-      <c r="J23" s="99"/>
+      <c r="J23" s="97"/>
     </row>
     <row r="24" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B24" s="3" t="s">
@@ -9516,18 +10101,18 @@
       <c r="C24" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E24" s="73"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="83">
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="81">
         <v>20</v>
       </c>
-      <c r="H24" s="83">
+      <c r="H24" s="81">
         <v>20</v>
       </c>
-      <c r="I24" s="83">
+      <c r="I24" s="81">
         <v>20</v>
       </c>
-      <c r="J24" s="98" t="s">
+      <c r="J24" s="96" t="s">
         <v>63</v>
       </c>
     </row>
@@ -9538,44 +10123,44 @@
       <c r="C25" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E25" s="73"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="83">
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="81">
         <v>85</v>
       </c>
-      <c r="H25" s="83">
+      <c r="H25" s="81">
         <v>80</v>
       </c>
-      <c r="I25" s="83">
+      <c r="I25" s="81">
         <v>80</v>
       </c>
-      <c r="J25" s="98" t="s">
+      <c r="J25" s="96" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="239" t="str">
+      <c r="B26" s="3" t="str">
         <f>"Closing working capital balance as of " &amp; TEXT(i_Historical!$C$7 - 1, "dd-mm-yyyy")</f>
         <v>Closing working capital balance as of 31-12-2023</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="82">
+      <c r="D26" s="80">
         <v>-34555</v>
       </c>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="73"/>
-      <c r="J26" s="98" t="s">
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="96" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B27" s="2"/>
-      <c r="J27" s="99"/>
+      <c r="J27" s="97"/>
     </row>
     <row r="28" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B28" s="3" t="s">
@@ -9584,57 +10169,57 @@
       <c r="C28" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="73"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="83">
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="81">
         <v>55000</v>
       </c>
-      <c r="H28" s="83">
+      <c r="H28" s="81">
         <v>55000</v>
       </c>
-      <c r="I28" s="83">
+      <c r="I28" s="81">
         <v>55000</v>
       </c>
-      <c r="J28" s="98" t="s">
+      <c r="J28" s="96" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B29" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D29" s="81">
+      <c r="D29" s="79">
         <v>0.3</v>
       </c>
-      <c r="E29" s="73"/>
-      <c r="F29" s="73"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73"/>
-      <c r="J29" s="98" t="s">
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="96" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="239" t="str">
+      <c r="B30" s="3" t="str">
         <f>"Closing PPE and ROU balance as of " &amp; TEXT(i_Historical!$C$7 - 1, "dd-mm-yyyy")</f>
         <v>Closing PPE and ROU balance as of 31-12-2023</v>
       </c>
       <c r="C30" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="82">
+      <c r="D30" s="80">
         <v>209987</v>
       </c>
-      <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="98" t="s">
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="96" t="s">
         <v>152</v>
       </c>
     </row>
@@ -9645,31 +10230,31 @@
       <c r="C31" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="83"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="83"/>
-      <c r="J31" s="98" t="s">
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
+      <c r="I31" s="81"/>
+      <c r="J31" s="96" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B32" s="2"/>
-      <c r="J32" s="99"/>
-    </row>
-    <row r="33" spans="1:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="90" t="s">
+      <c r="J32" s="97"/>
+    </row>
+    <row r="33" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="112" t="s">
+      <c r="B33" s="109" t="s">
         <v>160</v>
       </c>
-      <c r="J33" s="100"/>
+      <c r="J33" s="98"/>
     </row>
     <row r="34" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B34" s="2"/>
-      <c r="J34" s="99"/>
+      <c r="J34" s="97"/>
     </row>
     <row r="35" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
@@ -9678,15 +10263,15 @@
       <c r="C35" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D35" s="81">
+      <c r="D35" s="79">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
-      <c r="G35" s="73"/>
-      <c r="H35" s="73"/>
-      <c r="I35" s="73"/>
-      <c r="J35" s="98" t="s">
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="96" t="s">
         <v>157</v>
       </c>
     </row>
@@ -9698,34 +10283,34 @@
         <v>6</v>
       </c>
       <c r="D36" s="14"/>
-      <c r="E36" s="73"/>
-      <c r="F36" s="73"/>
-      <c r="G36" s="83">
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="81">
         <v>-527</v>
       </c>
-      <c r="H36" s="83"/>
-      <c r="I36" s="83"/>
-      <c r="J36" s="98" t="s">
-        <v>305</v>
+      <c r="H36" s="81"/>
+      <c r="I36" s="81"/>
+      <c r="J36" s="96" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="37" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="239" t="str">
+      <c r="B37" s="3" t="str">
         <f>"Closing debt balance as of "&amp; TEXT(i_Historical!$C$7 - 1, "dd-mm-yyyy")</f>
         <v>Closing debt balance as of 31-12-2023</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D37" s="82">
+      <c r="D37" s="80">
         <v>139715</v>
       </c>
-      <c r="E37" s="73"/>
-      <c r="F37" s="73"/>
-      <c r="G37" s="73"/>
-      <c r="H37" s="73"/>
-      <c r="I37" s="73"/>
-      <c r="J37" s="98" t="s">
+      <c r="E37" s="71"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="71"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="96" t="s">
         <v>152</v>
       </c>
     </row>
@@ -9738,7 +10323,7 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="102"/>
+      <c r="J38" s="100"/>
     </row>
     <row r="39" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
@@ -9747,35 +10332,35 @@
       <c r="C39" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D39" s="81">
+      <c r="D39" s="79">
         <v>7.4300000000000005E-2</v>
       </c>
-      <c r="E39" s="73"/>
-      <c r="F39" s="73"/>
-      <c r="G39" s="73"/>
-      <c r="H39" s="73"/>
-      <c r="I39" s="73"/>
-      <c r="J39" s="98" t="s">
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="96" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="239" t="str">
+      <c r="B40" s="3" t="str">
         <f>"Closing lease liabilities as of "&amp; TEXT(i_Historical!$C$7 - 1, "dd-mm-yyyy")</f>
         <v>Closing lease liabilities as of 31-12-2023</v>
       </c>
       <c r="C40" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D40" s="82">
+      <c r="D40" s="80">
         <v>96820</v>
       </c>
-      <c r="E40" s="73"/>
-      <c r="F40" s="73"/>
-      <c r="G40" s="73"/>
-      <c r="H40" s="73"/>
-      <c r="I40" s="73"/>
-      <c r="J40" s="98" t="s">
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="96" t="s">
         <v>152</v>
       </c>
     </row>
@@ -9786,21 +10371,21 @@
       <c r="C41" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E41" s="73"/>
-      <c r="F41" s="73"/>
-      <c r="G41" s="83">
+      <c r="E41" s="71"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="81">
         <f>PMT($D$39,$D$42,-c_FS!$F$52)</f>
         <v>18225.083499484805</v>
       </c>
-      <c r="H41" s="83">
+      <c r="H41" s="81">
         <f>PMT($D$39,$D$42,-c_FS!$F$52)</f>
         <v>18225.083499484805</v>
       </c>
-      <c r="I41" s="83">
+      <c r="I41" s="81">
         <f>PMT($D$39,$D$42,-c_FS!$F$52)</f>
         <v>18225.083499484805</v>
       </c>
-      <c r="J41" s="98" t="s">
+      <c r="J41" s="96" t="s">
         <v>211</v>
       </c>
     </row>
@@ -9811,27 +10396,27 @@
       <c r="C42" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="D42" s="82">
+      <c r="D42" s="80">
         <v>8</v>
       </c>
-      <c r="J42" s="99"/>
+      <c r="J42" s="97"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C43" s="14"/>
-      <c r="J43" s="67"/>
-    </row>
-    <row r="44" spans="1:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="90" t="s">
+      <c r="J43" s="65"/>
+    </row>
+    <row r="44" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B44" s="112" t="s">
+      <c r="B44" s="109" t="s">
         <v>143</v>
       </c>
-      <c r="J44" s="100"/>
+      <c r="J44" s="98"/>
     </row>
     <row r="45" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B45" s="2"/>
-      <c r="J45" s="99"/>
+      <c r="J45" s="97"/>
     </row>
     <row r="46" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B46" s="3" t="s">
@@ -9840,35 +10425,35 @@
       <c r="C46" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D46" s="81">
+      <c r="D46" s="79">
         <v>0.02</v>
       </c>
-      <c r="E46" s="73"/>
-      <c r="F46" s="73"/>
-      <c r="G46" s="73"/>
-      <c r="H46" s="73"/>
-      <c r="I46" s="73"/>
-      <c r="J46" s="98" t="s">
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="96" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="239" t="str">
+      <c r="B47" s="3" t="str">
         <f>"Closing cash balance as of "&amp; TEXT(i_Historical!$C$7 - 1, "dd-mm-yyyy")</f>
         <v>Closing cash balance as of 31-12-2023</v>
       </c>
       <c r="C47" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D47" s="82">
+      <c r="D47" s="80">
         <v>325013</v>
       </c>
-      <c r="E47" s="73"/>
-      <c r="F47" s="73"/>
-      <c r="G47" s="73"/>
-      <c r="H47" s="73"/>
-      <c r="I47" s="73"/>
-      <c r="J47" s="98" t="s">
+      <c r="E47" s="71"/>
+      <c r="F47" s="71"/>
+      <c r="G47" s="71"/>
+      <c r="H47" s="71"/>
+      <c r="I47" s="71"/>
+      <c r="J47" s="96" t="s">
         <v>152</v>
       </c>
     </row>
@@ -9881,7 +10466,7 @@
       <c r="G48" s="14"/>
       <c r="H48" s="14"/>
       <c r="I48" s="14"/>
-      <c r="J48" s="103"/>
+      <c r="J48" s="101"/>
     </row>
     <row r="49" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B49" s="3" t="s">
@@ -9890,15 +10475,15 @@
       <c r="C49" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D49" s="81">
+      <c r="D49" s="79">
         <v>0.22</v>
       </c>
-      <c r="E49" s="73"/>
-      <c r="F49" s="73"/>
-      <c r="G49" s="73"/>
-      <c r="H49" s="73"/>
-      <c r="I49" s="73"/>
-      <c r="J49" s="67"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="65"/>
     </row>
     <row r="50" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B50" s="3" t="s">
@@ -9908,72 +10493,72 @@
         <v>6</v>
       </c>
       <c r="D50" s="14"/>
-      <c r="E50" s="73"/>
-      <c r="F50" s="73"/>
-      <c r="G50" s="83">
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="81">
         <v>0</v>
       </c>
-      <c r="H50" s="83">
+      <c r="H50" s="81">
         <v>0</v>
       </c>
-      <c r="I50" s="83">
+      <c r="I50" s="81">
         <v>0</v>
       </c>
-      <c r="J50" s="67"/>
+      <c r="J50" s="65"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B51" s="2"/>
-      <c r="J51" s="99"/>
-    </row>
-    <row r="52" spans="1:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="90" t="s">
+      <c r="J51" s="97"/>
+    </row>
+    <row r="52" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B52" s="112" t="s">
+      <c r="B52" s="109" t="s">
         <v>127</v>
       </c>
-      <c r="J52" s="100"/>
+      <c r="J52" s="98"/>
     </row>
     <row r="53" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B53" s="2"/>
-      <c r="J53" s="104"/>
+      <c r="J53" s="102"/>
     </row>
     <row r="54" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B54" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C54" s="71" t="s">
+      <c r="C54" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D54" s="72">
+      <c r="D54" s="70">
         <v>0.105</v>
       </c>
-      <c r="E54" s="73"/>
-      <c r="F54" s="73"/>
-      <c r="G54" s="73"/>
-      <c r="H54" s="73"/>
-      <c r="I54" s="73"/>
-      <c r="J54" s="98" t="s">
-        <v>304</v>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="96" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="55" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B55" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C55" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="C55" s="69" t="s">
         <v>244</v>
       </c>
-      <c r="D55" s="76">
+      <c r="D55" s="74">
         <v>1</v>
       </c>
-      <c r="E55" s="73"/>
-      <c r="F55" s="73"/>
-      <c r="G55" s="73"/>
-      <c r="H55" s="73"/>
-      <c r="I55" s="73"/>
-      <c r="J55" s="105" t="s">
-        <v>270</v>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="103" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="56" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -9985,62 +10570,62 @@
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
-      <c r="J56" s="61"/>
+      <c r="J56" s="59"/>
     </row>
     <row r="57" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B57" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C57" s="71" t="s">
+        <v>286</v>
+      </c>
+      <c r="C57" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D57" s="72">
+      <c r="D57" s="70">
         <v>0.04</v>
       </c>
-      <c r="E57" s="73"/>
-      <c r="F57" s="73"/>
-      <c r="G57" s="73"/>
-      <c r="H57" s="73"/>
-      <c r="I57" s="73"/>
-      <c r="J57" s="98" t="s">
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="96" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="58" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B58" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C58" s="71" t="s">
+        <v>285</v>
+      </c>
+      <c r="C58" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="D58" s="77">
+      <c r="D58" s="75">
         <v>2.5</v>
       </c>
-      <c r="E58" s="73"/>
-      <c r="F58" s="73"/>
-      <c r="G58" s="73"/>
-      <c r="H58" s="73"/>
-      <c r="I58" s="73"/>
-      <c r="J58" s="98" t="s">
+      <c r="E58" s="71"/>
+      <c r="F58" s="71"/>
+      <c r="G58" s="71"/>
+      <c r="H58" s="71"/>
+      <c r="I58" s="71"/>
+      <c r="J58" s="96" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B59" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C59" s="71" t="s">
+        <v>287</v>
+      </c>
+      <c r="C59" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="D59" s="77">
+      <c r="D59" s="75">
         <v>20</v>
       </c>
-      <c r="E59" s="73"/>
-      <c r="F59" s="73"/>
-      <c r="G59" s="73"/>
-      <c r="H59" s="73"/>
-      <c r="I59" s="73"/>
-      <c r="J59" s="98" t="s">
+      <c r="E59" s="71"/>
+      <c r="F59" s="71"/>
+      <c r="G59" s="71"/>
+      <c r="H59" s="71"/>
+      <c r="I59" s="71"/>
+      <c r="J59" s="96" t="s">
         <v>69</v>
       </c>
     </row>
@@ -10053,25 +10638,25 @@
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
-      <c r="J60" s="102"/>
+      <c r="J60" s="100"/>
     </row>
     <row r="61" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B61" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C61" s="71" t="s">
+      <c r="C61" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="D61" s="78">
+      <c r="D61" s="76">
         <f>i_Historical!F51</f>
         <v>31223</v>
       </c>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="73"/>
-      <c r="J61" s="98" t="s">
+      <c r="E61" s="71"/>
+      <c r="F61" s="71"/>
+      <c r="G61" s="71"/>
+      <c r="H61" s="71"/>
+      <c r="I61" s="71"/>
+      <c r="J61" s="96" t="s">
         <v>70</v>
       </c>
     </row>
@@ -10079,18 +10664,18 @@
       <c r="B62" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C62" s="71" t="s">
+      <c r="C62" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D62" s="72">
+      <c r="D62" s="70">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E62" s="73"/>
-      <c r="F62" s="73"/>
-      <c r="G62" s="73"/>
-      <c r="H62" s="73"/>
-      <c r="I62" s="73"/>
-      <c r="J62" s="98" t="s">
+      <c r="E62" s="71"/>
+      <c r="F62" s="71"/>
+      <c r="G62" s="71"/>
+      <c r="H62" s="71"/>
+      <c r="I62" s="71"/>
+      <c r="J62" s="96" t="s">
         <v>72</v>
       </c>
     </row>
@@ -10098,18 +10683,18 @@
       <c r="B63" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C63" s="71" t="s">
+      <c r="C63" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="D63" s="79">
+      <c r="D63" s="77">
         <v>500000</v>
       </c>
-      <c r="E63" s="73"/>
-      <c r="F63" s="73"/>
-      <c r="G63" s="73"/>
-      <c r="H63" s="73"/>
-      <c r="I63" s="73"/>
-      <c r="J63" s="98" t="s">
+      <c r="E63" s="71"/>
+      <c r="F63" s="71"/>
+      <c r="G63" s="71"/>
+      <c r="H63" s="71"/>
+      <c r="I63" s="71"/>
+      <c r="J63" s="96" t="s">
         <v>74</v>
       </c>
     </row>
@@ -10122,46 +10707,46 @@
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
-      <c r="J64" s="102"/>
+      <c r="J64" s="100"/>
     </row>
     <row r="65" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B65" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C65" s="71" t="s">
-        <v>296</v>
-      </c>
-      <c r="D65" s="89" t="s">
-        <v>286</v>
-      </c>
-      <c r="E65" s="73"/>
-      <c r="F65" s="73"/>
-      <c r="G65" s="73"/>
-      <c r="H65" s="73"/>
-      <c r="I65" s="73"/>
-      <c r="J65" s="98" t="s">
-        <v>298</v>
+        <v>299</v>
+      </c>
+      <c r="C65" s="69" t="s">
+        <v>295</v>
+      </c>
+      <c r="D65" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="E65" s="71"/>
+      <c r="F65" s="71"/>
+      <c r="G65" s="71"/>
+      <c r="H65" s="71"/>
+      <c r="I65" s="71"/>
+      <c r="J65" s="96" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="66" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="J66" s="106"/>
+      <c r="J66" s="104"/>
     </row>
     <row r="67" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C67" s="71" t="s">
+      <c r="C67" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D67" s="72">
+      <c r="D67" s="70">
         <v>0.5</v>
       </c>
-      <c r="E67" s="73"/>
-      <c r="F67" s="73"/>
-      <c r="G67" s="73"/>
-      <c r="H67" s="73"/>
-      <c r="I67" s="73"/>
-      <c r="J67" s="98" t="s">
+      <c r="E67" s="71"/>
+      <c r="F67" s="71"/>
+      <c r="G67" s="71"/>
+      <c r="H67" s="71"/>
+      <c r="I67" s="71"/>
+      <c r="J67" s="96" t="s">
         <v>233</v>
       </c>
     </row>
@@ -10169,18 +10754,18 @@
       <c r="B68" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C68" s="71" t="s">
+      <c r="C68" s="69" t="s">
         <v>210</v>
       </c>
-      <c r="D68" s="80">
+      <c r="D68" s="78">
         <v>0.5</v>
       </c>
-      <c r="E68" s="73"/>
-      <c r="F68" s="73"/>
-      <c r="G68" s="73"/>
-      <c r="H68" s="73"/>
-      <c r="I68" s="73"/>
-      <c r="J68" s="98" t="s">
+      <c r="E68" s="71"/>
+      <c r="F68" s="71"/>
+      <c r="G68" s="71"/>
+      <c r="H68" s="71"/>
+      <c r="I68" s="71"/>
+      <c r="J68" s="96" t="s">
         <v>237</v>
       </c>
     </row>
@@ -10188,253 +10773,243 @@
       <c r="B69" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C69" s="71" t="s">
+      <c r="C69" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D69" s="72">
+      <c r="D69" s="70">
         <v>0.05</v>
       </c>
-      <c r="E69" s="73"/>
-      <c r="F69" s="73"/>
-      <c r="G69" s="73"/>
-      <c r="H69" s="73"/>
-      <c r="I69" s="73"/>
-      <c r="J69" s="98" t="s">
+      <c r="E69" s="71"/>
+      <c r="F69" s="71"/>
+      <c r="G69" s="71"/>
+      <c r="H69" s="71"/>
+      <c r="I69" s="71"/>
+      <c r="J69" s="96" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J70" s="99"/>
-    </row>
-    <row r="71" spans="1:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="90" t="s">
+      <c r="J70" s="97"/>
+    </row>
+    <row r="71" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B71" s="112" t="s">
-        <v>250</v>
-      </c>
-      <c r="J71" s="100"/>
+      <c r="B71" s="109" t="s">
+        <v>249</v>
+      </c>
+      <c r="J71" s="98"/>
     </row>
     <row r="72" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B72" s="2"/>
-      <c r="J72" s="104"/>
+      <c r="J72" s="102"/>
     </row>
     <row r="73" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B73" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C73" s="71" t="s">
+        <v>250</v>
+      </c>
+      <c r="C73" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D73" s="72">
+      <c r="D73" s="70">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="E73" s="73"/>
-      <c r="F73" s="73"/>
-      <c r="G73" s="73"/>
-      <c r="H73" s="73"/>
-      <c r="I73" s="73"/>
-      <c r="J73" s="105" t="s">
-        <v>261</v>
+      <c r="E73" s="71"/>
+      <c r="F73" s="71"/>
+      <c r="G73" s="71"/>
+      <c r="H73" s="71"/>
+      <c r="I73" s="71"/>
+      <c r="J73" s="103" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="74" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B74" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C74" s="71" t="s">
+        <v>251</v>
+      </c>
+      <c r="C74" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D74" s="72">
+      <c r="D74" s="70">
         <v>5.5E-2</v>
       </c>
-      <c r="E74" s="73"/>
-      <c r="F74" s="73"/>
-      <c r="G74" s="73"/>
-      <c r="H74" s="73"/>
-      <c r="I74" s="73"/>
-      <c r="J74" s="105" t="s">
-        <v>262</v>
+      <c r="E74" s="71"/>
+      <c r="F74" s="71"/>
+      <c r="G74" s="71"/>
+      <c r="H74" s="71"/>
+      <c r="I74" s="71"/>
+      <c r="J74" s="103" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="75" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B75" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C75" s="71" t="s">
+        <v>252</v>
+      </c>
+      <c r="C75" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D75" s="72">
+      <c r="D75" s="70">
         <v>0.01</v>
       </c>
-      <c r="E75" s="73"/>
-      <c r="F75" s="73"/>
-      <c r="G75" s="73"/>
-      <c r="H75" s="73"/>
-      <c r="I75" s="73"/>
-      <c r="J75" s="105" t="s">
-        <v>263</v>
+      <c r="E75" s="71"/>
+      <c r="F75" s="71"/>
+      <c r="G75" s="71"/>
+      <c r="H75" s="71"/>
+      <c r="I75" s="71"/>
+      <c r="J75" s="103" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="76" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B76" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C76" s="71" t="s">
+        <v>253</v>
+      </c>
+      <c r="C76" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="D76" s="74">
+      <c r="D76" s="72">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E76" s="73"/>
-      <c r="F76" s="73"/>
-      <c r="G76" s="73"/>
-      <c r="H76" s="73"/>
-      <c r="I76" s="73"/>
-      <c r="J76" s="105" t="s">
-        <v>264</v>
+      <c r="E76" s="71"/>
+      <c r="F76" s="71"/>
+      <c r="G76" s="71"/>
+      <c r="H76" s="71"/>
+      <c r="I76" s="71"/>
+      <c r="J76" s="103" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="77" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B77" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C77" s="71" t="s">
+        <v>254</v>
+      </c>
+      <c r="C77" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D77" s="72">
+      <c r="D77" s="70">
         <v>0.01</v>
       </c>
-      <c r="E77" s="73"/>
-      <c r="F77" s="73"/>
-      <c r="G77" s="73"/>
-      <c r="H77" s="73"/>
-      <c r="I77" s="73"/>
-      <c r="J77" s="105" t="s">
-        <v>265</v>
+      <c r="E77" s="71"/>
+      <c r="F77" s="71"/>
+      <c r="G77" s="71"/>
+      <c r="H77" s="71"/>
+      <c r="I77" s="71"/>
+      <c r="J77" s="103" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="78" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B78" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C78" s="71" t="s">
+        <v>255</v>
+      </c>
+      <c r="C78" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D78" s="75">
+      <c r="D78" s="73">
         <f>$D$35</f>
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="E78" s="73"/>
-      <c r="F78" s="73"/>
-      <c r="G78" s="73"/>
-      <c r="H78" s="73"/>
-      <c r="I78" s="73"/>
-      <c r="J78" s="105" t="s">
-        <v>266</v>
+      <c r="E78" s="71"/>
+      <c r="F78" s="71"/>
+      <c r="G78" s="71"/>
+      <c r="H78" s="71"/>
+      <c r="I78" s="71"/>
+      <c r="J78" s="103" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="79" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B79" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C79" s="71" t="s">
+        <v>256</v>
+      </c>
+      <c r="C79" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D79" s="75">
+      <c r="D79" s="73">
         <f>$D$49</f>
         <v>0.22</v>
       </c>
-      <c r="E79" s="73"/>
-      <c r="F79" s="73"/>
-      <c r="G79" s="73"/>
-      <c r="H79" s="73"/>
-      <c r="I79" s="73"/>
-      <c r="J79" s="105" t="s">
-        <v>267</v>
+      <c r="E79" s="71"/>
+      <c r="F79" s="71"/>
+      <c r="G79" s="71"/>
+      <c r="H79" s="71"/>
+      <c r="I79" s="71"/>
+      <c r="J79" s="103" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B80" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C80" s="71" t="s">
+        <v>257</v>
+      </c>
+      <c r="C80" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D80" s="72">
+      <c r="D80" s="70">
         <v>0.15</v>
       </c>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="73"/>
-      <c r="I80" s="73"/>
-      <c r="J80" s="105" t="s">
-        <v>268</v>
+      <c r="E80" s="71"/>
+      <c r="F80" s="71"/>
+      <c r="G80" s="71"/>
+      <c r="H80" s="71"/>
+      <c r="I80" s="71"/>
+      <c r="J80" s="103" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="81" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B81" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C81" s="71" t="s">
+        <v>258</v>
+      </c>
+      <c r="C81" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D81" s="75">
+      <c r="D81" s="73">
         <f>1-$D$80</f>
         <v>0.85</v>
       </c>
-      <c r="E81" s="73"/>
-      <c r="F81" s="73"/>
-      <c r="G81" s="73"/>
-      <c r="H81" s="73"/>
-      <c r="I81" s="73"/>
-      <c r="J81" s="105" t="s">
-        <v>269</v>
+      <c r="E81" s="71"/>
+      <c r="F81" s="71"/>
+      <c r="G81" s="71"/>
+      <c r="H81" s="71"/>
+      <c r="I81" s="71"/>
+      <c r="J81" s="103" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B82" s="2"/>
-      <c r="J82" s="104"/>
-    </row>
-    <row r="83" spans="1:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="90" t="s">
+      <c r="J82" s="102"/>
+    </row>
+    <row r="83" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B83" s="112" t="s">
+      <c r="B83" s="109" t="s">
         <v>118</v>
       </c>
-      <c r="J83" s="90"/>
+      <c r="J83" s="88"/>
     </row>
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <conditionalFormatting sqref="G8:H8">
-    <cfRule type="expression" dxfId="19" priority="11">
+  <conditionalFormatting sqref="G8:I10">
+    <cfRule type="expression" dxfId="16" priority="9">
       <formula>RIGHT(G$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G9:I10">
-    <cfRule type="expression" dxfId="18" priority="10">
-      <formula>RIGHT(G$4, 1)="A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I8">
-    <cfRule type="expression" dxfId="17" priority="9">
-      <formula>RIGHT(I$4, 1)="A"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G14:I14">
-    <cfRule type="expression" dxfId="16" priority="8">
+    <cfRule type="expression" dxfId="15" priority="8">
       <formula>RIGHT(G$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G16:I20">
-    <cfRule type="expression" dxfId="15" priority="7">
+    <cfRule type="expression" dxfId="14" priority="7">
       <formula>RIGHT(G$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G24:I25">
-    <cfRule type="expression" dxfId="14" priority="6">
+    <cfRule type="expression" dxfId="13" priority="6">
       <formula>RIGHT(G$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10505,91 +11080,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="199" t="str">
+      <c r="A1" s="193" t="str">
         <f>Contents!$A1</f>
         <v>Bolt Technology OÜ|Pre-IPO Equity Valuation Model</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="107" t="str">
+      <c r="A2" s="105" t="str">
         <f>Contents!$A2</f>
         <v>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E3" s="238">
+      <c r="E3" s="226">
         <f>C7</f>
         <v>45292</v>
       </c>
-      <c r="F3" s="238">
+      <c r="F3" s="226">
         <f>EDATE(E3,12)</f>
         <v>45658</v>
       </c>
-      <c r="G3" s="238">
+      <c r="G3" s="226">
         <f t="shared" ref="G3:I3" si="0">EDATE(F3,12)</f>
         <v>46023</v>
       </c>
-      <c r="H3" s="238">
+      <c r="H3" s="226">
         <f t="shared" si="0"/>
         <v>46388</v>
       </c>
-      <c r="I3" s="238">
+      <c r="I3" s="226">
         <f t="shared" si="0"/>
         <v>46753</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="70" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C4" s="70" t="s">
+    <row r="4" spans="1:13" s="68" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C4" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="237" t="str">
+      <c r="E4" s="68" t="str">
         <f>YEAR(E3)&amp;IF(E5="Actual", "A", IF(E5="Estimate","E",_xleta.NA))</f>
         <v>2024A</v>
       </c>
-      <c r="F4" s="237" t="str">
+      <c r="F4" s="68" t="str">
         <f t="shared" ref="F4:I4" si="1">YEAR(F3)&amp;IF(F5="Actual", "A", IF(F5="Estimate","E",_xleta.NA))</f>
         <v>2025A</v>
       </c>
-      <c r="G4" s="237" t="str">
+      <c r="G4" s="68" t="str">
         <f t="shared" si="1"/>
         <v>2026E</v>
       </c>
-      <c r="H4" s="237" t="str">
+      <c r="H4" s="68" t="str">
         <f t="shared" si="1"/>
         <v>2027E</v>
       </c>
-      <c r="I4" s="237" t="str">
+      <c r="I4" s="68" t="str">
         <f t="shared" si="1"/>
         <v>2028E</v>
       </c>
-      <c r="K4" s="70" t="s">
+      <c r="K4" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="L4" s="70" t="s">
+      <c r="L4" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="70" t="s">
+      <c r="M4" s="68" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="70" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E5" s="70" t="str">
+    <row r="5" spans="1:13" s="68" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="68" t="str">
         <f t="shared" ref="E5:I5" si="2">IF(E3&lt;$C$8, "Actual", "Estimate")</f>
         <v>Actual</v>
       </c>
-      <c r="F5" s="70" t="str">
+      <c r="F5" s="68" t="str">
         <f t="shared" si="2"/>
         <v>Actual</v>
       </c>
-      <c r="G5" s="70" t="str">
+      <c r="G5" s="68" t="str">
         <f t="shared" si="2"/>
         <v>Estimate</v>
       </c>
-      <c r="H5" s="70" t="str">
+      <c r="H5" s="68" t="str">
         <f t="shared" si="2"/>
         <v>Estimate</v>
       </c>
-      <c r="I5" s="70" t="str">
+      <c r="I5" s="68" t="str">
         <f t="shared" si="2"/>
         <v>Estimate</v>
       </c>
@@ -10600,42 +11175,42 @@
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:13" s="49" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="234"/>
-      <c r="B7" s="235" t="s">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="85"/>
+      <c r="B7" s="224" t="s">
+        <v>306</v>
+      </c>
+      <c r="C7" s="225">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="85"/>
+      <c r="B8" s="224" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="236">
-        <v>45292</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="49" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="234"/>
-      <c r="B8" s="235" t="s">
-        <v>308</v>
-      </c>
-      <c r="C8" s="236">
+      <c r="C8" s="225">
         <v>46023</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="108" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="108" t="s">
+    <row r="10" spans="1:13" s="106" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="106" t="s">
         <v>126</v>
       </c>
-      <c r="B10" s="109" t="s">
+      <c r="B10" s="107" t="s">
         <v>125</v>
       </c>
-      <c r="C10" s="110"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="110"/>
-      <c r="M10" s="110"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="108"/>
+      <c r="M10" s="108"/>
     </row>
     <row r="11" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" s="2"/>
@@ -11060,7 +11635,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="52" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" s="51" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B26" s="5" t="s">
         <v>28</v>
       </c>
@@ -11157,14 +11732,14 @@
       <c r="I29" s="31"/>
       <c r="J29" s="32"/>
     </row>
-    <row r="30" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="96" t="s">
+    <row r="30" spans="1:13" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="94" t="s">
         <v>126</v>
       </c>
-      <c r="B30" s="109" t="s">
+      <c r="B30" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="K30" s="97"/>
+      <c r="K30" s="95"/>
     </row>
     <row r="31" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B31" s="2"/>
@@ -11646,8 +12221,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:13" s="87" customFormat="1" ht="17" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="87" t="str">
+    <row r="47" spans="1:13" s="85" customFormat="1" ht="17" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="85" t="str">
         <f>IF(SUM(E47:I47)&lt;&gt;0,"Error","OK")</f>
         <v>OK</v>
       </c>
@@ -11788,18 +12363,18 @@
       </c>
     </row>
     <row r="52" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="53" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="96" t="s">
+    <row r="53" spans="1:13" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="94" t="s">
         <v>126</v>
       </c>
-      <c r="B53" s="109" t="s">
+      <c r="B53" s="107" t="s">
         <v>49</v>
       </c>
-      <c r="K53" s="97"/>
-    </row>
-    <row r="54" spans="1:13" s="49" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="111"/>
-      <c r="K54" s="50"/>
+      <c r="K53" s="95"/>
+    </row>
+    <row r="54" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="52"/>
+      <c r="K54" s="49"/>
     </row>
     <row r="55" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B55" s="3" t="s">
@@ -11848,7 +12423,7 @@
       <c r="G56" s="34"/>
       <c r="H56" s="34"/>
       <c r="I56" s="34"/>
-      <c r="J56" s="51"/>
+      <c r="J56" s="50"/>
       <c r="K56" s="17">
         <f>F56-E56</f>
         <v>-219</v>
@@ -11921,14 +12496,14 @@
         <v>55</v>
       </c>
     </row>
-    <row r="60" spans="1:13" s="96" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="90" t="s">
+    <row r="60" spans="1:13" s="94" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B60" s="112" t="s">
+      <c r="B60" s="109" t="s">
         <v>118</v>
       </c>
-      <c r="C60" s="112"/>
+      <c r="C60" s="109"/>
     </row>
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
@@ -11992,20 +12567,20 @@
   <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" style="187" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="187"/>
-    <col min="3" max="3" width="21" style="187" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="187"/>
+    <col min="1" max="1" width="3.83203125" style="182" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="182"/>
+    <col min="3" max="3" width="21" style="182" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="182"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="199" t="str">
+      <c r="A1" s="193" t="str">
         <f>Contents!$A1</f>
         <v>Bolt Technology OÜ|Pre-IPO Equity Valuation Model</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="107" t="str">
+      <c r="A2" s="105" t="str">
         <f>Contents!$A2</f>
         <v>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</v>
       </c>
@@ -12013,260 +12588,260 @@
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:12" s="189" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="188"/>
-    </row>
-    <row r="5" spans="1:12" s="69" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="69" t="s">
+    <row r="4" spans="1:12" s="184" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="183"/>
+    </row>
+    <row r="5" spans="1:12" s="67" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="B5" s="190" t="s">
-        <v>328</v>
+      <c r="B5" s="185" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="53"/>
+      <c r="B6" s="52"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B7" s="254" t="s">
-        <v>331</v>
-      </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
+      <c r="B7" s="239" t="s">
+        <v>330</v>
+      </c>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="54"/>
     </row>
     <row r="8" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="259" t="s">
+      <c r="B9" s="243" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="244" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="244" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="244" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="260" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="260" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="260" t="s">
-        <v>333</v>
-      </c>
-    </row>
     <row r="13" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="52"/>
-    </row>
-    <row r="14" spans="1:12" s="69" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="69" t="s">
+      <c r="B13" s="51"/>
+    </row>
+    <row r="14" spans="1:12" s="67" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="B14" s="190" t="s">
+      <c r="B14" s="185" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="53"/>
+      <c r="B15" s="52"/>
     </row>
     <row r="16" spans="1:12" s="1" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="191" t="s">
+      <c r="B16" s="186" t="s">
         <v>215</v>
       </c>
-      <c r="C16" s="192" t="s">
+      <c r="C16" s="187" t="s">
         <v>216</v>
       </c>
-      <c r="D16" s="193" t="s">
+      <c r="D16" s="188" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="194" t="s">
+      <c r="B17" s="189" t="s">
         <v>217</v>
       </c>
-      <c r="C17" s="192" t="s">
+      <c r="C17" s="187" t="s">
         <v>218</v>
       </c>
-      <c r="D17" s="193" t="s">
+      <c r="D17" s="188" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="200" t="s">
+      <c r="B18" s="194" t="s">
         <v>219</v>
       </c>
-      <c r="C18" s="192" t="s">
+      <c r="C18" s="187" t="s">
         <v>231</v>
       </c>
-      <c r="D18" s="193" t="s">
-        <v>290</v>
+      <c r="D18" s="188" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="53" t="s">
         <v>220</v>
       </c>
-      <c r="C19" s="192" t="s">
-        <v>302</v>
-      </c>
-      <c r="D19" s="193" t="s">
+      <c r="C19" s="187" t="s">
+        <v>301</v>
+      </c>
+      <c r="D19" s="188" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="54"/>
-      <c r="C20" s="192"/>
-      <c r="D20" s="193"/>
-    </row>
-    <row r="21" spans="1:12" s="69" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="69" t="s">
+      <c r="B20" s="53"/>
+      <c r="C20" s="187"/>
+      <c r="D20" s="188"/>
+    </row>
+    <row r="21" spans="1:12" s="67" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="B21" s="195" t="s">
-        <v>306</v>
+      <c r="B21" s="190" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="55" t="s">
-        <v>311</v>
-      </c>
-      <c r="C23" s="193"/>
-      <c r="D23" s="193"/>
+      <c r="B23" s="54" t="s">
+        <v>310</v>
+      </c>
+      <c r="C23" s="188"/>
+      <c r="D23" s="188"/>
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="56"/>
-      <c r="C24" s="192"/>
-      <c r="D24" s="193"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="187"/>
+      <c r="D24" s="188"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="254" t="s">
+      <c r="B25" s="239" t="s">
+        <v>318</v>
+      </c>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="54"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="54"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B26" s="240" t="s">
+        <v>317</v>
+      </c>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B27" s="54"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="54"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="54"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B28" s="239" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="55"/>
-      <c r="J25" s="55"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="55"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B26" s="255" t="s">
-        <v>318</v>
-      </c>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="55"/>
-      <c r="J26" s="55"/>
-      <c r="K26" s="55"/>
-      <c r="L26" s="55"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B27" s="55"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="55"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="55"/>
-      <c r="J27" s="55"/>
-      <c r="K27" s="55"/>
-      <c r="L27" s="55"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B28" s="254" t="s">
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="54"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="54"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B29" s="240" t="s">
         <v>320</v>
       </c>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="55"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="55"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B29" s="255" t="s">
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="54"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B30" s="54"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="54"/>
+      <c r="K30" s="54"/>
+      <c r="L30" s="54"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B31" s="239" t="s">
         <v>321</v>
       </c>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="55"/>
-      <c r="H29" s="55"/>
-      <c r="I29" s="55"/>
-      <c r="J29" s="55"/>
-      <c r="K29" s="55"/>
-      <c r="L29" s="55"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B30" s="55"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="55"/>
-      <c r="J30" s="55"/>
-      <c r="K30" s="55"/>
-      <c r="L30" s="55"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B31" s="254" t="s">
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="54"/>
+      <c r="L31" s="54"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B32" s="240" t="s">
         <v>322</v>
       </c>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="55"/>
-      <c r="K31" s="55"/>
-      <c r="L31" s="55"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B32" s="255" t="s">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B34" s="239" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B34" s="254" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B35" s="240" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B35" s="255" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" s="69" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="69" t="s">
+    <row r="37" spans="1:2" s="67" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="195" t="s">
+      <c r="B37" s="190" t="s">
         <v>118</v>
       </c>
     </row>
@@ -12311,540 +12886,540 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="199" t="str">
+      <c r="A1" s="193" t="str">
         <f>Contents!$A1</f>
         <v>Bolt Technology OÜ|Pre-IPO Equity Valuation Model</v>
       </c>
-      <c r="B1" s="155"/>
+      <c r="B1" s="152"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="113" t="str">
+      <c r="A2" s="110" t="str">
         <f>Contents!$A2</f>
         <v>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</v>
       </c>
-      <c r="B2" s="113"/>
+      <c r="B2" s="110"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="156"/>
-      <c r="F3" s="251" t="str">
+      <c r="A3" s="153"/>
+      <c r="F3" s="237" t="str">
         <f>i_Scenario_Manager!B6</f>
         <v>Selected Case</v>
       </c>
-      <c r="G3" s="252">
+      <c r="G3" s="229">
         <f>i_Scenario_Manager!C6</f>
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="49" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="201" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="195" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="90" t="s">
+    <row r="5" spans="1:7" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B5" s="112" t="s">
+      <c r="B5" s="109" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="8" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="87"/>
-      <c r="B6" s="53"/>
+      <c r="A6" s="85"/>
+      <c r="B6" s="52"/>
     </row>
     <row r="7" spans="1:7" ht="42" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="207" t="str">
+      <c r="B7" s="201" t="str">
         <f>o_Valuation!B81</f>
         <v>Target Price post IPO Discount</v>
       </c>
-      <c r="C7" s="157"/>
-      <c r="D7" s="158"/>
+      <c r="C7" s="154"/>
+      <c r="D7" s="155"/>
     </row>
     <row r="8" spans="1:7" ht="34" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="159">
+      <c r="B8" s="156">
         <f>o_Valuation!D81</f>
         <v>143.70014535289152</v>
       </c>
-      <c r="C8" s="160"/>
-      <c r="D8" s="161"/>
+      <c r="C8" s="157"/>
+      <c r="D8" s="158"/>
     </row>
     <row r="9" spans="1:7" ht="8" customHeight="1" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="206" t="str">
+      <c r="B10" s="200" t="str">
         <f>o_Valuation!B75</f>
         <v>Blended Target Pre-Money Equity Value</v>
       </c>
-      <c r="C10" s="162"/>
-      <c r="D10" s="162"/>
-      <c r="E10" s="162"/>
-      <c r="F10" s="162"/>
-      <c r="G10" s="163"/>
+      <c r="C10" s="159"/>
+      <c r="D10" s="159"/>
+      <c r="E10" s="159"/>
+      <c r="F10" s="159"/>
+      <c r="G10" s="160"/>
     </row>
     <row r="11" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="164">
+      <c r="B11" s="161">
         <f>o_Valuation!D75</f>
         <v>4824461.9767240128</v>
       </c>
-      <c r="C11" s="165"/>
-      <c r="D11" s="165"/>
-      <c r="E11" s="165"/>
-      <c r="F11" s="165"/>
-      <c r="G11" s="166"/>
+      <c r="C11" s="162"/>
+      <c r="D11" s="162"/>
+      <c r="E11" s="162"/>
+      <c r="F11" s="162"/>
+      <c r="G11" s="163"/>
     </row>
     <row r="12" spans="1:7" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:7" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="90" t="s">
+    <row r="13" spans="1:7" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="112" t="s">
+      <c r="B13" s="109" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="87"/>
-      <c r="B14" s="53"/>
+      <c r="A14" s="85"/>
+      <c r="B14" s="52"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="202" t="s">
+      <c r="B15" s="196" t="s">
         <v>214</v>
       </c>
-      <c r="C15" s="203" t="str">
+      <c r="C15" s="197" t="str">
         <f>o_FS!E4</f>
         <v>2024A</v>
       </c>
-      <c r="D15" s="203" t="str">
+      <c r="D15" s="197" t="str">
         <f>o_FS!F4</f>
         <v>2025A</v>
       </c>
-      <c r="E15" s="203" t="str">
+      <c r="E15" s="197" t="str">
         <f>o_FS!G4</f>
         <v>2026E</v>
       </c>
-      <c r="F15" s="203" t="str">
+      <c r="F15" s="197" t="str">
         <f>o_FS!H4</f>
         <v>2027E</v>
       </c>
-      <c r="G15" s="203" t="str">
+      <c r="G15" s="197" t="str">
         <f>o_FS!I4</f>
         <v>2028E</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="204"/>
-      <c r="C16" s="205" t="str">
+      <c r="B16" s="198"/>
+      <c r="C16" s="199" t="str">
         <f>o_FS!E5</f>
         <v>Actual</v>
       </c>
-      <c r="D16" s="205" t="str">
+      <c r="D16" s="199" t="str">
         <f>o_FS!F5</f>
         <v>Actual</v>
       </c>
-      <c r="E16" s="205" t="str">
+      <c r="E16" s="199" t="str">
         <f>o_FS!G5</f>
         <v>Estimate</v>
       </c>
-      <c r="F16" s="205" t="str">
+      <c r="F16" s="199" t="str">
         <f>o_FS!H5</f>
         <v>Estimate</v>
       </c>
-      <c r="G16" s="205" t="str">
+      <c r="G16" s="199" t="str">
         <f>o_FS!I5</f>
         <v>Estimate</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="167" t="str">
+      <c r="B17" s="164" t="str">
         <f>o_FS!B8</f>
         <v>Sales revenue</v>
       </c>
-      <c r="C17" s="168">
+      <c r="C17" s="165">
         <f>o_FS!E8</f>
         <v>1992054</v>
       </c>
-      <c r="D17" s="168">
+      <c r="D17" s="165">
         <f>o_FS!F8</f>
         <v>2270854</v>
       </c>
-      <c r="E17" s="209">
+      <c r="E17" s="203">
         <f>o_FS!G8</f>
         <v>2563281.25</v>
       </c>
-      <c r="F17" s="209">
+      <c r="F17" s="203">
         <f>o_FS!H8</f>
         <v>2867849.1805000002</v>
       </c>
-      <c r="G17" s="209">
+      <c r="G17" s="203">
         <f>o_FS!I8</f>
         <v>3172646.9490240002</v>
       </c>
     </row>
-    <row r="18" spans="2:7" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="169" t="str">
+    <row r="18" spans="2:7" s="51" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="166" t="str">
         <f>c_FS!B12</f>
         <v xml:space="preserve">  YoY revenue growth rate (%)</v>
       </c>
-      <c r="C18" s="170">
+      <c r="C18" s="167">
         <f>c_FS!E12</f>
         <v>0</v>
       </c>
-      <c r="D18" s="170">
+      <c r="D18" s="167">
         <f>c_FS!F12</f>
         <v>0.13995604536824802</v>
       </c>
-      <c r="E18" s="210">
+      <c r="E18" s="204">
         <f>c_FS!G12</f>
         <v>0.12877413078956201</v>
       </c>
-      <c r="F18" s="210">
+      <c r="F18" s="204">
         <f>c_FS!H12</f>
         <v>0.1188195522828408</v>
       </c>
-      <c r="G18" s="210">
+      <c r="G18" s="204">
         <f>c_FS!I12</f>
         <v>0.10628096156397571</v>
       </c>
     </row>
-    <row r="19" spans="2:7" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="169" t="str">
+    <row r="19" spans="2:7" s="51" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="166" t="str">
         <f>o_FS!B11</f>
         <v xml:space="preserve">  Gross Margin %</v>
       </c>
-      <c r="C19" s="170">
+      <c r="C19" s="167">
         <f>o_FS!E11</f>
         <v>0.56603736645693337</v>
       </c>
-      <c r="D19" s="170">
+      <c r="D19" s="167">
         <f>o_FS!F11</f>
         <v>0.63395268916451697</v>
       </c>
-      <c r="E19" s="210">
+      <c r="E19" s="204">
         <f>o_FS!G11</f>
         <v>0.64500000000000002</v>
       </c>
-      <c r="F19" s="210">
+      <c r="F19" s="204">
         <f>o_FS!H11</f>
         <v>0.65</v>
       </c>
-      <c r="G19" s="210">
+      <c r="G19" s="204">
         <f>o_FS!I11</f>
         <v>0.65500000000000003</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="171" t="str">
+      <c r="B20" s="168" t="str">
         <f>o_FS!B20</f>
         <v>EBITDA</v>
       </c>
-      <c r="C20" s="172">
+      <c r="C20" s="169">
         <f>o_FS!E20</f>
         <v>-30298</v>
       </c>
-      <c r="D20" s="172">
+      <c r="D20" s="169">
         <f>o_FS!F20</f>
         <v>76672</v>
       </c>
-      <c r="E20" s="211">
+      <c r="E20" s="205">
         <f>o_FS!G20</f>
         <v>92570.71875</v>
       </c>
-      <c r="F20" s="211">
+      <c r="F20" s="205">
         <f>o_FS!H20</f>
         <v>183438.2631225001</v>
       </c>
-      <c r="G20" s="211">
+      <c r="G20" s="205">
         <f>o_FS!I20</f>
         <v>292518.0561768004</v>
       </c>
     </row>
-    <row r="21" spans="2:7" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="169" t="str">
+    <row r="21" spans="2:7" s="51" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="166" t="str">
         <f>o_FS!B21</f>
         <v xml:space="preserve">  EBITDA Margin %</v>
       </c>
-      <c r="C21" s="170">
+      <c r="C21" s="167">
         <f>o_FS!E21</f>
         <v>-1.5209427053684287E-2</v>
       </c>
-      <c r="D21" s="170">
+      <c r="D21" s="167">
         <f>o_FS!F21</f>
         <v>3.3763509234851732E-2</v>
       </c>
-      <c r="E21" s="210">
+      <c r="E21" s="204">
         <f>o_FS!G21</f>
         <v>3.6114148125571476E-2</v>
       </c>
-      <c r="F21" s="210">
+      <c r="F21" s="204">
         <f>o_FS!H21</f>
         <v>6.3963706449346208E-2</v>
       </c>
-      <c r="G21" s="210">
+      <c r="G21" s="204">
         <f>o_FS!I21</f>
         <v>9.2200002356640276E-2</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="173" t="str">
+      <c r="B22" s="170" t="str">
         <f>o_FS!B17</f>
         <v>Operating Profit / (Loss) (EBIT)</v>
       </c>
-      <c r="C22" s="174">
+      <c r="C22" s="171">
         <f>o_FS!E17</f>
         <v>-87735</v>
       </c>
-      <c r="D22" s="174">
+      <c r="D22" s="171">
         <f>o_FS!F17</f>
         <v>19454</v>
       </c>
-      <c r="E22" s="212">
+      <c r="E22" s="206">
         <f>o_FS!G17</f>
         <v>38449.21875</v>
       </c>
-      <c r="F22" s="212">
+      <c r="F22" s="206">
         <f>o_FS!H17</f>
         <v>129053.21312250011</v>
       </c>
-      <c r="G22" s="212">
+      <c r="G22" s="206">
         <f>o_FS!I17</f>
         <v>237948.52117680036</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="173" t="str">
+      <c r="B23" s="170" t="str">
         <f>o_FS!B26</f>
         <v>Net Profit / (Loss) for the Period</v>
       </c>
-      <c r="C23" s="174">
+      <c r="C23" s="171">
         <f>o_FS!E26</f>
         <v>-102594</v>
       </c>
-      <c r="D23" s="174">
+      <c r="D23" s="171">
         <f>o_FS!F26</f>
         <v>920</v>
       </c>
-      <c r="E23" s="212">
+      <c r="E23" s="206">
         <f>o_FS!G26</f>
         <v>29347.712276999999</v>
       </c>
-      <c r="F23" s="212">
+      <c r="F23" s="206">
         <f>o_FS!H26</f>
         <v>101054.30998760104</v>
       </c>
-      <c r="G23" s="212">
+      <c r="G23" s="206">
         <f>o_FS!I26</f>
         <v>187892.75760187401</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="175" t="str">
+      <c r="B24" s="168" t="str">
         <f>o_FS!B35</f>
         <v>Free Cash Flow to Firm (FCFF)</v>
       </c>
-      <c r="C24" s="176">
+      <c r="C24" s="169">
         <f>o_FS!E35</f>
         <v>-34486.300000000003</v>
       </c>
-      <c r="D24" s="176">
+      <c r="D24" s="169">
         <f>o_FS!F35</f>
         <v>48622.119999999995</v>
       </c>
-      <c r="E24" s="211">
+      <c r="E24" s="205">
         <f>o_FS!G35</f>
         <v>39064.744648972614</v>
       </c>
-      <c r="F24" s="211">
+      <c r="F24" s="205">
         <f>o_FS!H35</f>
         <v>91447.670551303483</v>
       </c>
-      <c r="G24" s="211">
+      <c r="G24" s="205">
         <f>o_FS!I35</f>
         <v>188373.00718525331</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B25" s="173" t="str">
+      <c r="B25" s="170" t="str">
         <f>o_FS!B39</f>
         <v>Closing cash &amp; cash equivalents</v>
       </c>
-      <c r="C25" s="174">
+      <c r="C25" s="171">
         <f>o_FS!E39</f>
         <v>342247</v>
       </c>
-      <c r="D25" s="174">
+      <c r="D25" s="171">
         <f>o_FS!F39</f>
         <v>357038</v>
       </c>
-      <c r="E25" s="212">
+      <c r="E25" s="206">
         <f>o_FS!G39</f>
         <v>384660.83190148778</v>
       </c>
-      <c r="F25" s="212">
+      <c r="F25" s="206">
         <f>o_FS!H39</f>
         <v>465465.84478947567</v>
       </c>
-      <c r="G25" s="212">
+      <c r="G25" s="206">
         <f>o_FS!I39</f>
         <v>644276.36686017038</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B26" s="177" t="str">
+      <c r="B26" s="172" t="str">
         <f>o_FS!B42</f>
         <v>Net Cash / (Net Debt) Position</v>
       </c>
-      <c r="C26" s="178">
+      <c r="C26" s="173">
         <f>o_FS!E42</f>
         <v>104873</v>
       </c>
-      <c r="D26" s="178">
+      <c r="D26" s="173">
         <f>o_FS!F42</f>
         <v>249474</v>
       </c>
-      <c r="E26" s="213">
+      <c r="E26" s="207">
         <f>o_FS!G42</f>
         <v>287896.0663009726</v>
       </c>
-      <c r="F26" s="213">
+      <c r="F26" s="207">
         <f>o_FS!H42</f>
         <v>379736.54060432699</v>
       </c>
-      <c r="G26" s="213">
+      <c r="G26" s="207">
         <f>o_FS!I42</f>
         <v>570402.45887354994</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B28" s="208" t="s">
+      <c r="B28" s="202" t="s">
         <v>225</v>
       </c>
-      <c r="C28" s="208"/>
+      <c r="C28" s="202"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B29" s="179" t="str">
+      <c r="B29" s="174" t="str">
         <f>o_Valuation!B30</f>
         <v>Weighted Average Cost of Capital (WACC) - sensitized</v>
       </c>
-      <c r="C29" s="180">
+      <c r="C29" s="175">
         <f>o_Valuation!D30</f>
         <v>0.10201850000000001</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B30" s="181" t="str">
+      <c r="B30" s="176" t="str">
         <f>o_Valuation!B31</f>
         <v>Terminal Growth Rate (g) - sensitized</v>
       </c>
-      <c r="C30" s="180">
+      <c r="C30" s="175">
         <f>o_Valuation!D31</f>
         <v>0.04</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B31" s="181" t="str">
+      <c r="B31" s="176" t="str">
         <f>i_Inputs!B58</f>
         <v>Target EV / Sales Multiple</v>
       </c>
-      <c r="C31" s="182">
+      <c r="C31" s="177">
         <f>i_Inputs!D58</f>
         <v>2.5</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B32" s="181" t="str">
+      <c r="B32" s="176" t="str">
         <f>i_Inputs!B59</f>
         <v>Target EV / EBITDA Multiple</v>
       </c>
-      <c r="C32" s="182">
+      <c r="C32" s="177">
         <f>i_Inputs!D59</f>
         <v>20</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B33" s="181" t="str">
+      <c r="B33" s="176" t="str">
         <f>i_Inputs!B49</f>
         <v>Effective corporate tax rate</v>
       </c>
-      <c r="C33" s="180">
+      <c r="C33" s="175">
         <f>i_Inputs!D49</f>
         <v>0.22</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B34" s="183" t="str">
+      <c r="B34" s="178" t="str">
         <f>i_Inputs!B62</f>
         <v>IPO Underwriter Discount / Spread</v>
       </c>
-      <c r="C34" s="180">
+      <c r="C34" s="175">
         <f>i_Inputs!D62</f>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B35" s="181" t="str">
+      <c r="B35" s="176" t="str">
         <f>o_Valuation!B77</f>
         <v>Target Primary Capital Raised at IPO</v>
       </c>
-      <c r="C35" s="184">
+      <c r="C35" s="179">
         <f>o_Valuation!D77</f>
         <v>500000</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B37" s="208" t="s">
+      <c r="B37" s="202" t="s">
         <v>227</v>
       </c>
-      <c r="C37" s="208"/>
+      <c r="C37" s="202"/>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B38" s="181" t="str">
+      <c r="B38" s="176" t="str">
         <f>o_Valuation!B52</f>
         <v>Diluted Shares Outstanding</v>
       </c>
-      <c r="C38" s="185">
+      <c r="C38" s="180">
         <f>o_Valuation!D52</f>
         <v>31223</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B39" s="181" t="s">
+      <c r="B39" s="176" t="s">
         <v>228</v>
       </c>
-      <c r="C39" s="186">
+      <c r="C39" s="181">
         <f>o_FS!F39</f>
         <v>357038</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B40" s="181" t="s">
+      <c r="B40" s="176" t="s">
         <v>229</v>
       </c>
-      <c r="C40" s="185">
+      <c r="C40" s="180">
         <f>o_FS!F40</f>
         <v>-527</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B41" s="181" t="s">
+      <c r="B41" s="176" t="s">
         <v>230</v>
       </c>
-      <c r="C41" s="185">
+      <c r="C41" s="180">
         <f>o_FS!F41</f>
         <v>-107037</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B42" s="181" t="s">
+      <c r="B42" s="176" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="185">
+      <c r="C42" s="180">
         <f>i_Historical!F58</f>
         <v>220000</v>
       </c>
     </row>
-    <row r="64" spans="1:2" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="90" t="s">
+    <row r="64" spans="1:2" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B64" s="112" t="s">
+      <c r="B64" s="109" t="s">
         <v>118</v>
       </c>
     </row>
@@ -12870,51 +13445,51 @@
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="57.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="87" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="85" bestFit="1" customWidth="1"/>
     <col min="4" max="9" width="22.6640625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="199" t="str">
+      <c r="A1" s="193" t="str">
         <f>Contents!$A1</f>
         <v>Bolt Technology OÜ|Pre-IPO Equity Valuation Model</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="107" t="str">
+      <c r="A2" s="105" t="str">
         <f>Contents!$A2</f>
         <v>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="113"/>
-    </row>
-    <row r="4" spans="1:5" s="58" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C4" s="118"/>
-    </row>
-    <row r="5" spans="1:5" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="90" t="s">
+      <c r="A3" s="110"/>
+    </row>
+    <row r="4" spans="1:5" s="56" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C4" s="115"/>
+    </row>
+    <row r="5" spans="1:5" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B5" s="112" t="s">
-        <v>250</v>
-      </c>
-      <c r="C5" s="119"/>
-    </row>
-    <row r="6" spans="1:5" s="59" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="C6" s="120"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
+      <c r="B5" s="109" t="s">
+        <v>249</v>
+      </c>
+      <c r="C5" s="116"/>
+    </row>
+    <row r="6" spans="1:5" s="57" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="117"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
     </row>
     <row r="7" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C7" s="88" t="s">
+        <v>250</v>
+      </c>
+      <c r="C7" s="86" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="121">
+      <c r="D7" s="118">
         <f>i_Inputs!$D$73</f>
         <v>2.5000000000000001E-2</v>
       </c>
@@ -12922,12 +13497,12 @@
     </row>
     <row r="8" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C8" s="88" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="122">
+      <c r="D8" s="119">
         <f>i_Inputs!$D$76</f>
         <v>1.1000000000000001</v>
       </c>
@@ -12935,12 +13510,12 @@
     </row>
     <row r="9" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C9" s="88" t="s">
+        <v>271</v>
+      </c>
+      <c r="C9" s="86" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="121">
+      <c r="D9" s="118">
         <f>i_Inputs!$D$80</f>
         <v>0.15</v>
       </c>
@@ -12948,12 +13523,12 @@
     </row>
     <row r="10" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C10" s="88" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" s="86" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="121">
+      <c r="D10" s="118">
         <f>i_Inputs!$D$81</f>
         <v>0.85</v>
       </c>
@@ -12961,12 +13536,12 @@
     </row>
     <row r="11" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C11" s="88" t="s">
+        <v>272</v>
+      </c>
+      <c r="C11" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="123">
+      <c r="D11" s="120">
         <f>D9/D10</f>
         <v>0.17647058823529413</v>
       </c>
@@ -12974,12 +13549,12 @@
     </row>
     <row r="12" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C12" s="88" t="s">
+        <v>273</v>
+      </c>
+      <c r="C12" s="86" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="121">
+      <c r="D12" s="118">
         <f>i_Inputs!$D$79</f>
         <v>0.22</v>
       </c>
@@ -12987,18 +13562,18 @@
     </row>
     <row r="13" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3"/>
-      <c r="C13" s="88"/>
-      <c r="D13" s="124"/>
+      <c r="C13" s="86"/>
+      <c r="D13" s="121"/>
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C14" s="88" t="s">
+        <v>274</v>
+      </c>
+      <c r="C14" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="123">
+      <c r="D14" s="120">
         <f>D8*(1+(1-D12)*D11)</f>
         <v>1.2514117647058824</v>
       </c>
@@ -13006,12 +13581,12 @@
     </row>
     <row r="15" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C15" s="88" t="s">
+        <v>251</v>
+      </c>
+      <c r="C15" s="86" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="121">
+      <c r="D15" s="118">
         <f>i_Inputs!$D$74</f>
         <v>5.5E-2</v>
       </c>
@@ -13019,12 +13594,12 @@
     </row>
     <row r="16" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C16" s="88" t="s">
+        <v>252</v>
+      </c>
+      <c r="C16" s="86" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="121">
+      <c r="D16" s="118">
         <f>i_Inputs!$D$75</f>
         <v>0.01</v>
       </c>
@@ -13032,25 +13607,25 @@
     </row>
     <row r="17" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C17" s="88" t="s">
+        <v>275</v>
+      </c>
+      <c r="C17" s="86" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="121">
+      <c r="D17" s="118">
         <f>i_Inputs!$D$77</f>
         <v>0.01</v>
       </c>
       <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="125" t="s">
-        <v>277</v>
-      </c>
-      <c r="C18" s="126" t="s">
+      <c r="B18" s="122" t="s">
+        <v>276</v>
+      </c>
+      <c r="C18" s="123" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="127">
+      <c r="D18" s="124">
         <f>D7+D14*D15+D16+D17</f>
         <v>0.11382764705882353</v>
       </c>
@@ -13059,17 +13634,17 @@
     <row r="19" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B19" s="10"/>
       <c r="C19" s="43"/>
-      <c r="D19" s="128"/>
+      <c r="D19" s="125"/>
       <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B20" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C20" s="88" t="s">
+        <v>277</v>
+      </c>
+      <c r="C20" s="86" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="121">
+      <c r="D20" s="118">
         <f>i_Inputs!$D$78</f>
         <v>4.4999999999999998E-2</v>
       </c>
@@ -13077,25 +13652,25 @@
     </row>
     <row r="21" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C21" s="88" t="s">
+        <v>278</v>
+      </c>
+      <c r="C21" s="86" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="124">
+      <c r="D21" s="121">
         <f>D20*(1-D12)</f>
         <v>3.5099999999999999E-2</v>
       </c>
       <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="214" t="s">
-        <v>280</v>
-      </c>
-      <c r="C22" s="215" t="s">
+      <c r="B22" s="122" t="s">
+        <v>279</v>
+      </c>
+      <c r="C22" s="123" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="127">
+      <c r="D22" s="124">
         <f>D10*D18+D9*D21</f>
         <v>0.10201850000000001</v>
       </c>
@@ -13104,75 +13679,75 @@
     <row r="23" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B23" s="10"/>
       <c r="C23" s="43"/>
-      <c r="D23" s="128"/>
+      <c r="D23" s="125"/>
       <c r="E23" s="3"/>
     </row>
     <row r="24" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B24" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C24" s="88" t="s">
+        <v>280</v>
+      </c>
+      <c r="C24" s="86" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="121">
+      <c r="D24" s="118">
         <f>i_Inputs!$D$54</f>
         <v>0.105</v>
       </c>
       <c r="E24" s="3"/>
     </row>
     <row r="25" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="129" t="s">
-        <v>282</v>
-      </c>
-      <c r="C25" s="130" t="s">
+      <c r="B25" s="126" t="s">
+        <v>281</v>
+      </c>
+      <c r="C25" s="127" t="s">
         <v>244</v>
       </c>
-      <c r="D25" s="131">
+      <c r="D25" s="128">
         <f>i_Inputs!$D$55</f>
         <v>1</v>
       </c>
       <c r="E25" s="3"/>
     </row>
     <row r="26" spans="1:5" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="216" t="s">
-        <v>283</v>
-      </c>
-      <c r="C26" s="217" t="s">
+      <c r="B26" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="C26" s="137" t="s">
         <v>56</v>
       </c>
-      <c r="D26" s="218">
+      <c r="D26" s="208">
         <f>IF(D25=1,D22,D24)</f>
         <v>0.10201850000000001</v>
       </c>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" spans="1:5" s="59" customFormat="1" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="C27" s="120"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
-    </row>
-    <row r="28" spans="1:5" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="90" t="s">
+    <row r="27" spans="1:5" s="57" customFormat="1" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="C27" s="117"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+    </row>
+    <row r="28" spans="1:5" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B28" s="112" t="s">
+      <c r="B28" s="109" t="s">
         <v>121</v>
       </c>
-      <c r="C28" s="90"/>
-    </row>
-    <row r="29" spans="1:5" s="59" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="C29" s="120"/>
-      <c r="D29" s="60"/>
-      <c r="E29" s="60"/>
+      <c r="C28" s="88"/>
+    </row>
+    <row r="29" spans="1:5" s="57" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="C29" s="117"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
     </row>
     <row r="30" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B30" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C30" s="88" t="s">
+        <v>315</v>
+      </c>
+      <c r="C30" s="86" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="124">
+      <c r="D30" s="121">
         <f>$D$26*(1+i_Scenario_Manager!$D$26)</f>
         <v>0.10201850000000001</v>
       </c>
@@ -13180,12 +13755,12 @@
     </row>
     <row r="31" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B31" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C31" s="88" t="s">
+        <v>316</v>
+      </c>
+      <c r="C31" s="86" t="s">
         <v>56</v>
       </c>
-      <c r="D31" s="124">
+      <c r="D31" s="121">
         <f>i_Inputs!$D$57*(1+i_Scenario_Manager!$D$27)</f>
         <v>0.04</v>
       </c>
@@ -13195,10 +13770,10 @@
       <c r="B32" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C32" s="88" t="s">
+      <c r="C32" s="86" t="s">
         <v>210</v>
       </c>
-      <c r="D32" s="132">
+      <c r="D32" s="129">
         <f>i_Inputs!$D$68</f>
         <v>0.5</v>
       </c>
@@ -13206,42 +13781,42 @@
     </row>
     <row r="33" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B33" s="3"/>
-      <c r="C33" s="88"/>
-      <c r="D33" s="133"/>
+      <c r="C33" s="86"/>
+      <c r="D33" s="130"/>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="2:9" s="52" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="134" t="s">
-        <v>293</v>
-      </c>
-      <c r="C34" s="135"/>
-      <c r="D34" s="136"/>
-      <c r="E34" s="137" t="str">
+    <row r="34" spans="2:9" s="51" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="131" t="s">
+        <v>292</v>
+      </c>
+      <c r="C34" s="132"/>
+      <c r="D34" s="133"/>
+      <c r="E34" s="134" t="str">
         <f>o_FS!E4</f>
         <v>2024A</v>
       </c>
-      <c r="F34" s="137" t="str">
+      <c r="F34" s="134" t="str">
         <f>o_FS!F4</f>
         <v>2025A</v>
       </c>
-      <c r="G34" s="137" t="str">
+      <c r="G34" s="134" t="str">
         <f>o_FS!G4</f>
         <v>2026E</v>
       </c>
-      <c r="H34" s="137" t="str">
+      <c r="H34" s="134" t="str">
         <f>o_FS!H4</f>
         <v>2027E</v>
       </c>
-      <c r="I34" s="137" t="str">
+      <c r="I34" s="134" t="str">
         <f>o_FS!I4</f>
         <v>2028E</v>
       </c>
     </row>
     <row r="35" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="239" t="s">
+      <c r="B35" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C35" s="138" t="s">
+      <c r="C35" s="135" t="s">
         <v>244</v>
       </c>
       <c r="D35" s="18"/>
@@ -13270,27 +13845,27 @@
       <c r="B36" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C36" s="88" t="s">
+      <c r="C36" s="86" t="s">
         <v>210</v>
       </c>
       <c r="D36" s="18"/>
-      <c r="E36" s="139">
+      <c r="E36" s="136">
         <f>IF(E35=1,SUM($E35:E35)-$D$32,0)</f>
         <v>0</v>
       </c>
-      <c r="F36" s="139">
+      <c r="F36" s="136">
         <f>IF(F35=1,SUM($E35:F35)-$D$32,0)</f>
         <v>0</v>
       </c>
-      <c r="G36" s="139">
+      <c r="G36" s="136">
         <f>IF(G35=1,SUM($E35:G35)-$D$32,0)</f>
         <v>0.5</v>
       </c>
-      <c r="H36" s="139">
+      <c r="H36" s="136">
         <f>IF(H35=1,SUM($E35:H35)-$D$32,0)</f>
         <v>1.5</v>
       </c>
-      <c r="I36" s="139">
+      <c r="I36" s="136">
         <f>IF(I35=1,SUM($E35:I35)-$D$32,0)</f>
         <v>2.5</v>
       </c>
@@ -13299,7 +13874,7 @@
       <c r="B37" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C37" s="138" t="s">
+      <c r="C37" s="135" t="s">
         <v>244</v>
       </c>
       <c r="D37" s="18"/>
@@ -13326,7 +13901,7 @@
     </row>
     <row r="38" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B38" s="3"/>
-      <c r="C38" s="138"/>
+      <c r="C38" s="135"/>
       <c r="D38" s="18"/>
       <c r="E38" s="17"/>
       <c r="F38" s="17"/>
@@ -13338,7 +13913,7 @@
       <c r="B39" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C39" s="88" t="s">
+      <c r="C39" s="86" t="s">
         <v>6</v>
       </c>
       <c r="D39" s="18"/>
@@ -13367,39 +13942,39 @@
       <c r="B40" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C40" s="88" t="s">
+      <c r="C40" s="86" t="s">
         <v>67</v>
       </c>
       <c r="D40" s="18"/>
-      <c r="E40" s="139">
+      <c r="E40" s="136">
         <f>IF(E35=1,1/(1+$D$30)^E36,0)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="139">
+      <c r="F40" s="136">
         <f t="shared" ref="F40:I40" si="1">IF(F35=1,1/(1+$D$30)^F36,0)</f>
         <v>0</v>
       </c>
-      <c r="G40" s="139">
+      <c r="G40" s="136">
         <f t="shared" si="1"/>
         <v>0.9525889894280265</v>
       </c>
-      <c r="H40" s="139">
+      <c r="H40" s="136">
         <f t="shared" si="1"/>
         <v>0.86440380939886807</v>
       </c>
-      <c r="I40" s="139">
+      <c r="I40" s="136">
         <f t="shared" si="1"/>
         <v>0.78438230338135706</v>
       </c>
     </row>
-    <row r="41" spans="2:9" s="52" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" s="51" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B41" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="C41" s="140" t="s">
+        <v>288</v>
+      </c>
+      <c r="C41" s="137" t="s">
         <v>6</v>
       </c>
-      <c r="D41" s="141"/>
+      <c r="D41" s="138"/>
       <c r="E41" s="29">
         <f>E39*E40</f>
         <v>0</v>
@@ -13423,39 +13998,39 @@
     </row>
     <row r="42" spans="2:9" ht="17" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B42" s="3"/>
-      <c r="C42" s="88"/>
+      <c r="C42" s="86"/>
       <c r="D42" s="18"/>
-      <c r="E42" s="142"/>
-      <c r="F42" s="142"/>
-      <c r="G42" s="142"/>
-      <c r="H42" s="142"/>
-      <c r="I42" s="142"/>
+      <c r="E42" s="139"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="139"/>
+      <c r="H42" s="139"/>
+      <c r="I42" s="139"/>
     </row>
     <row r="43" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B43" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C43" s="88" t="s">
+      <c r="C43" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="D43" s="143">
+      <c r="D43" s="140">
         <f>SUM(E41:I41)</f>
         <v>264016.81368347007</v>
       </c>
-      <c r="E43" s="142"/>
-      <c r="F43" s="142"/>
-      <c r="G43" s="142"/>
-      <c r="H43" s="142"/>
-      <c r="I43" s="142"/>
+      <c r="E43" s="139"/>
+      <c r="F43" s="139"/>
+      <c r="G43" s="139"/>
+      <c r="H43" s="139"/>
+      <c r="I43" s="139"/>
     </row>
     <row r="44" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B44" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C44" s="88" t="s">
+      <c r="C44" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="D44" s="143">
+      <c r="D44" s="140">
         <f>SUMPRODUCT(E37:I37,E39:I39)</f>
         <v>188373.00718525331</v>
       </c>
@@ -13465,10 +14040,10 @@
       <c r="B45" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C45" s="88" t="s">
+      <c r="C45" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="D45" s="143">
+      <c r="D45" s="140">
         <f>D44*(1+D31)/(D30-D31)</f>
         <v>3158862.7179416372</v>
       </c>
@@ -13478,23 +14053,23 @@
       <c r="B46" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C46" s="88" t="s">
+      <c r="C46" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="D46" s="143">
+      <c r="D46" s="140">
         <f>D45*SUMPRODUCT(E37:I37,E40:I40)</f>
         <v>2477756.0147645553</v>
       </c>
       <c r="E46" s="3"/>
     </row>
     <row r="47" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="219" t="s">
+      <c r="B47" s="209" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="220" t="s">
+      <c r="C47" s="210" t="s">
         <v>6</v>
       </c>
-      <c r="D47" s="221">
+      <c r="D47" s="211">
         <f>D43+D46</f>
         <v>2741772.8284480255</v>
       </c>
@@ -13504,10 +14079,10 @@
       <c r="B48" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C48" s="88" t="s">
+      <c r="C48" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="D48" s="142">
+      <c r="D48" s="139">
         <f>i_Historical!F32</f>
         <v>357038</v>
       </c>
@@ -13517,10 +14092,10 @@
       <c r="B49" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="88" t="s">
+      <c r="C49" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="D49" s="142">
+      <c r="D49" s="139">
         <f>-i_Historical!F41</f>
         <v>-527</v>
       </c>
@@ -13530,23 +14105,23 @@
       <c r="B50" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="88" t="s">
+      <c r="C50" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="D50" s="142">
+      <c r="D50" s="139">
         <f>-i_Historical!F42</f>
         <v>-107037</v>
       </c>
       <c r="E50" s="3"/>
     </row>
     <row r="51" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="219" t="s">
+      <c r="B51" s="209" t="s">
         <v>100</v>
       </c>
-      <c r="C51" s="220" t="s">
+      <c r="C51" s="210" t="s">
         <v>6</v>
       </c>
-      <c r="D51" s="222">
+      <c r="D51" s="212">
         <f>D47+D48+D49+D50</f>
         <v>2991246.8284480255</v>
       </c>
@@ -13556,62 +14131,62 @@
       <c r="B52" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="88" t="s">
+      <c r="C52" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="D52" s="144">
+      <c r="D52" s="141">
         <f>i_Inputs!$D$61</f>
         <v>31223</v>
       </c>
       <c r="E52" s="3"/>
     </row>
     <row r="53" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="219" t="s">
+      <c r="B53" s="209" t="s">
         <v>102</v>
       </c>
-      <c r="C53" s="220" t="s">
+      <c r="C53" s="210" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="223">
+      <c r="D53" s="213">
         <f>D51/D52</f>
         <v>95.802672018961204</v>
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="55" spans="1:5" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="90" t="s">
+    <row r="55" spans="1:5" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B55" s="112" t="s">
+      <c r="B55" s="109" t="s">
         <v>122</v>
       </c>
-      <c r="C55" s="90"/>
+      <c r="C55" s="88"/>
     </row>
     <row r="56" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="87"/>
-      <c r="B56" s="53"/>
+      <c r="A56" s="85"/>
+      <c r="B56" s="52"/>
     </row>
     <row r="57" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B57" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C57" s="88" t="s">
+      <c r="C57" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="D57" s="142">
+      <c r="D57" s="139">
         <f>o_FS!G8</f>
         <v>2563281.25</v>
       </c>
       <c r="E57" s="3"/>
     </row>
     <row r="58" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="129" t="s">
+      <c r="B58" s="126" t="s">
         <v>104</v>
       </c>
-      <c r="C58" s="130" t="s">
+      <c r="C58" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="D58" s="145">
+      <c r="D58" s="142">
         <f>i_Inputs!$D$58</f>
         <v>2.5</v>
       </c>
@@ -13621,10 +14196,10 @@
       <c r="B59" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C59" s="146" t="s">
+      <c r="C59" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="D59" s="147">
+      <c r="D59" s="144">
         <f>D57*D58</f>
         <v>6408203.125</v>
       </c>
@@ -13634,23 +14209,23 @@
       <c r="B60" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C60" s="146" t="s">
+      <c r="C60" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="D60" s="147">
+      <c r="D60" s="144">
         <f>D59+D48+D49+D50</f>
         <v>6657677.125</v>
       </c>
       <c r="E60" s="3"/>
     </row>
     <row r="61" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="219" t="s">
+      <c r="B61" s="209" t="s">
         <v>107</v>
       </c>
-      <c r="C61" s="220" t="s">
+      <c r="C61" s="210" t="s">
         <v>103</v>
       </c>
-      <c r="D61" s="223">
+      <c r="D61" s="213">
         <f>D60/D52</f>
         <v>213.22989863241841</v>
       </c>
@@ -13666,23 +14241,23 @@
       <c r="B63" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C63" s="88" t="s">
+      <c r="C63" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="D63" s="142">
+      <c r="D63" s="139">
         <f>o_FS!G20</f>
         <v>92570.71875</v>
       </c>
       <c r="E63" s="3"/>
     </row>
     <row r="64" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="129" t="s">
+      <c r="B64" s="126" t="s">
         <v>108</v>
       </c>
-      <c r="C64" s="130" t="s">
+      <c r="C64" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="D64" s="145">
+      <c r="D64" s="142">
         <f>i_Inputs!$D$59</f>
         <v>20</v>
       </c>
@@ -13692,10 +14267,10 @@
       <c r="B65" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C65" s="146" t="s">
+      <c r="C65" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="D65" s="147">
+      <c r="D65" s="144">
         <f>D63*D64</f>
         <v>1851414.375</v>
       </c>
@@ -13705,94 +14280,94 @@
       <c r="B66" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C66" s="146" t="s">
+      <c r="C66" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="D66" s="147">
+      <c r="D66" s="144">
         <f>D65+D48+D49+D50</f>
         <v>2100888.375</v>
       </c>
       <c r="E66" s="3"/>
     </row>
     <row r="67" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="219" t="s">
+      <c r="B67" s="209" t="s">
         <v>111</v>
       </c>
-      <c r="C67" s="220" t="s">
+      <c r="C67" s="210" t="s">
         <v>103</v>
       </c>
-      <c r="D67" s="223">
+      <c r="D67" s="213">
         <f>D66/D52</f>
         <v>67.286563590942578</v>
       </c>
       <c r="E67" s="3"/>
     </row>
-    <row r="69" spans="1:5" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="90" t="s">
+    <row r="69" spans="1:5" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B69" s="112" t="s">
+      <c r="B69" s="109" t="s">
         <v>123</v>
       </c>
-      <c r="C69" s="90"/>
+      <c r="C69" s="88"/>
     </row>
     <row r="70" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="87"/>
-      <c r="B70" s="53"/>
+      <c r="A70" s="85"/>
+      <c r="B70" s="52"/>
     </row>
     <row r="71" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="87"/>
+      <c r="A71" s="85"/>
       <c r="B71" s="1" t="str">
         <f>i_Inputs!B67</f>
         <v>DCF Weight</v>
       </c>
-      <c r="C71" s="148" t="str">
+      <c r="C71" s="145" t="str">
         <f>i_Inputs!C67</f>
         <v>%</v>
       </c>
-      <c r="D71" s="149">
+      <c r="D71" s="146">
         <f>i_Inputs!D67</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="72" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="87"/>
+      <c r="A72" s="85"/>
       <c r="B72" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C72" s="148" t="s">
         <v>296</v>
       </c>
-      <c r="D72" s="62" t="str">
+      <c r="C72" s="145" t="s">
+        <v>295</v>
+      </c>
+      <c r="D72" s="60" t="str">
         <f>i_Inputs!D65</f>
         <v>Target EV / Sales Multiple</v>
       </c>
     </row>
     <row r="73" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="87"/>
-      <c r="B73" s="53"/>
+      <c r="A73" s="85"/>
+      <c r="B73" s="52"/>
     </row>
     <row r="74" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="224" t="s">
+      <c r="B74" s="214" t="s">
         <v>112</v>
       </c>
-      <c r="C74" s="225" t="s">
+      <c r="C74" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="D74" s="226">
+      <c r="D74" s="216">
         <f>D47*$D$71 + IF($D$72 = i_Inputs!$B$58, D59, IF($D$72 = i_Inputs!$B$59, D65, D47))*(1-$D$71)</f>
         <v>4574987.9767240128</v>
       </c>
       <c r="E74" s="10"/>
     </row>
     <row r="75" spans="1:5" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="227" t="s">
+      <c r="B75" s="217" t="s">
         <v>113</v>
       </c>
-      <c r="C75" s="228" t="s">
+      <c r="C75" s="218" t="s">
         <v>6</v>
       </c>
-      <c r="D75" s="229">
+      <c r="D75" s="219">
         <f>D74+D48+D49+D50</f>
         <v>4824461.9767240128</v>
       </c>
@@ -13805,26 +14380,26 @@
       <c r="E76" s="10"/>
     </row>
     <row r="77" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="239" t="s">
+      <c r="B77" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C77" s="88" t="s">
+      <c r="C77" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="D77" s="142">
+      <c r="D77" s="139">
         <f>i_Inputs!$D$63*(1+i_Scenario_Manager!$D$31)</f>
         <v>500000</v>
       </c>
       <c r="E77" s="10"/>
     </row>
     <row r="78" spans="1:5" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="230" t="s">
+      <c r="B78" s="220" t="s">
         <v>114</v>
       </c>
-      <c r="C78" s="231" t="s">
+      <c r="C78" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="D78" s="232">
+      <c r="D78" s="222">
         <f>D75+D77</f>
         <v>5324461.9767240128</v>
       </c>
@@ -13840,23 +14415,23 @@
       <c r="B80" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C80" s="88" t="s">
+      <c r="C80" s="86" t="s">
         <v>103</v>
       </c>
-      <c r="D80" s="150">
+      <c r="D80" s="147">
         <f>D75/D52</f>
         <v>154.51628532568981</v>
       </c>
       <c r="E80" s="10"/>
     </row>
     <row r="81" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="219" t="s">
-        <v>291</v>
-      </c>
-      <c r="C81" s="220" t="s">
+      <c r="B81" s="209" t="s">
+        <v>290</v>
+      </c>
+      <c r="C81" s="210" t="s">
         <v>103</v>
       </c>
-      <c r="D81" s="223">
+      <c r="D81" s="213">
         <f>D80*(1-i_Inputs!$D$62)</f>
         <v>143.70014535289152</v>
       </c>
@@ -13865,141 +14440,141 @@
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="E82" s="10"/>
     </row>
-    <row r="83" spans="1:8" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="90" t="s">
+    <row r="83" spans="1:8" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B83" s="112" t="s">
-        <v>327</v>
-      </c>
-      <c r="C83" s="90"/>
+      <c r="B83" s="109" t="s">
+        <v>326</v>
+      </c>
+      <c r="C83" s="88"/>
     </row>
     <row r="84" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="113" t="s">
-        <v>292</v>
+      <c r="B84" s="110" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="85" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
     <row r="86" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="84" t="s">
-        <v>326</v>
-      </c>
-      <c r="C86" s="85"/>
-      <c r="D86" s="233">
+      <c r="B86" s="82" t="s">
+        <v>325</v>
+      </c>
+      <c r="C86" s="83"/>
+      <c r="D86" s="223">
         <f>$F$86-1</f>
         <v>1.5</v>
       </c>
-      <c r="E86" s="233">
+      <c r="E86" s="223">
         <f>$F$86-0.5</f>
         <v>2</v>
       </c>
-      <c r="F86" s="233">
+      <c r="F86" s="223">
         <f>i_Inputs!$D$58</f>
         <v>2.5</v>
       </c>
-      <c r="G86" s="233">
+      <c r="G86" s="223">
         <f>$F$86+0.5</f>
         <v>3</v>
       </c>
-      <c r="H86" s="233">
+      <c r="H86" s="223">
         <f>F86+1</f>
         <v>3.5</v>
       </c>
     </row>
     <row r="87" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="151">
+      <c r="B87" s="148">
         <f>-i_Inputs!$D$69</f>
         <v>-0.05</v>
       </c>
-      <c r="C87" s="152" t="s">
+      <c r="C87" s="149" t="s">
         <v>103</v>
       </c>
-      <c r="D87" s="153">
+      <c r="D87" s="150">
         <f>(o_FS!$G$8*(1+$B87)*D$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>124.97677293181309</v>
       </c>
-      <c r="E87" s="153">
+      <c r="E87" s="150">
         <f>(o_FS!$G$8*(1+$B87)*E$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>163.972340101848</v>
       </c>
-      <c r="F87" s="153">
+      <c r="F87" s="150">
         <f>(o_FS!$G$8*(1+$B87)*F$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>202.96790727188289</v>
       </c>
-      <c r="G87" s="153">
+      <c r="G87" s="150">
         <f>(o_FS!$G$8*(1+$B87)*G$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>241.96347444191781</v>
       </c>
-      <c r="H87" s="153">
+      <c r="H87" s="150">
         <f>(o_FS!$G$8*(1+$B87)*H$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>280.95904161195273</v>
       </c>
     </row>
     <row r="88" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="151">
+      <c r="B88" s="148">
         <v>0</v>
       </c>
-      <c r="C88" s="152" t="s">
+      <c r="C88" s="149" t="s">
         <v>103</v>
       </c>
-      <c r="D88" s="153">
+      <c r="D88" s="150">
         <f>(o_FS!$G$8*(1+$B88)*D$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>131.13396774813438</v>
       </c>
-      <c r="E88" s="153">
+      <c r="E88" s="150">
         <f>(o_FS!$G$8*(1+$B88)*E$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>172.1819331902764</v>
       </c>
-      <c r="F88" s="154">
+      <c r="F88" s="151">
         <f>(o_FS!$G$8*(1+$B88)*F$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>213.22989863241841</v>
       </c>
-      <c r="G88" s="153">
+      <c r="G88" s="150">
         <f>(o_FS!$G$8*(1+$B88)*G$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>254.27786407456043</v>
       </c>
-      <c r="H88" s="153">
+      <c r="H88" s="150">
         <f>(o_FS!$G$8*(1+$B88)*H$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>295.32582951670241</v>
       </c>
     </row>
     <row r="89" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B89" s="151">
+      <c r="B89" s="148">
         <f>i_Inputs!$D$69</f>
         <v>0.05</v>
       </c>
-      <c r="C89" s="152" t="s">
+      <c r="C89" s="149" t="s">
         <v>103</v>
       </c>
-      <c r="D89" s="153">
+      <c r="D89" s="150">
         <f>(o_FS!$G$8*(1+$B89)*D$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>137.2911625644557</v>
       </c>
-      <c r="E89" s="153">
+      <c r="E89" s="150">
         <f>(o_FS!$G$8*(1+$B89)*E$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>180.39152627870479</v>
       </c>
-      <c r="F89" s="153">
+      <c r="F89" s="150">
         <f>(o_FS!$G$8*(1+$B89)*F$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>223.4918899929539</v>
       </c>
-      <c r="G89" s="153">
+      <c r="G89" s="150">
         <f>(o_FS!$G$8*(1+$B89)*G$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>266.59225370720304</v>
       </c>
-      <c r="H89" s="153">
+      <c r="H89" s="150">
         <f>(o_FS!$G$8*(1+$B89)*H$86+$D$48+$D$49+$D$50)/$D$52</f>
         <v>309.69261742145216</v>
       </c>
     </row>
-    <row r="91" spans="1:8" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="90" t="s">
+    <row r="91" spans="1:8" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B91" s="112" t="s">
+      <c r="B91" s="109" t="s">
         <v>118</v>
       </c>
-      <c r="C91" s="90"/>
+      <c r="C91" s="88"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="44Zk/J5ugrbWdiB86pV1kdYf2MNfYPRdhryQsIoCuTppH5QlUoj6eVbuH6wuxCMIgEZlAw25ch8OQDwwfWZJyw==" saltValue="q/OdvG72TQ8xMpYlkbUscg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -14025,70 +14600,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="199" t="str">
+      <c r="A1" s="193" t="str">
         <f>Contents!$A1</f>
         <v>Bolt Technology OÜ|Pre-IPO Equity Valuation Model</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="107" t="str">
+      <c r="A2" s="105" t="str">
         <f>Contents!$A2</f>
         <v>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="85" t="s">
+    <row r="4" spans="1:9" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="83" t="s">
         <v>224</v>
       </c>
-      <c r="C4" s="70"/>
-      <c r="E4" s="70" t="str">
+      <c r="C4" s="68"/>
+      <c r="E4" s="68" t="str">
         <f>c_FS!E4</f>
         <v>2024A</v>
       </c>
-      <c r="F4" s="70" t="str">
+      <c r="F4" s="68" t="str">
         <f>c_FS!F4</f>
         <v>2025A</v>
       </c>
-      <c r="G4" s="70" t="str">
+      <c r="G4" s="68" t="str">
         <f>c_FS!G4</f>
         <v>2026E</v>
       </c>
-      <c r="H4" s="70" t="str">
+      <c r="H4" s="68" t="str">
         <f>c_FS!H4</f>
         <v>2027E</v>
       </c>
-      <c r="I4" s="70" t="str">
+      <c r="I4" s="68" t="str">
         <f>c_FS!I4</f>
         <v>2028E</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="70" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E5" s="70" t="str">
+    <row r="5" spans="1:9" s="68" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="68" t="str">
         <f>c_FS!E5</f>
         <v>Actual</v>
       </c>
-      <c r="F5" s="70" t="str">
+      <c r="F5" s="68" t="str">
         <f>c_FS!F5</f>
         <v>Actual</v>
       </c>
-      <c r="G5" s="70" t="str">
+      <c r="G5" s="68" t="str">
         <f>c_FS!G5</f>
         <v>Estimate</v>
       </c>
-      <c r="H5" s="70" t="str">
+      <c r="H5" s="68" t="str">
         <f>c_FS!H5</f>
         <v>Estimate</v>
       </c>
-      <c r="I5" s="70" t="str">
+      <c r="I5" s="68" t="str">
         <f>c_FS!I5</f>
         <v>Estimate</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="90" t="s">
+    <row r="6" spans="1:9" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="112" t="s">
+      <c r="B6" s="109" t="s">
         <v>124</v>
       </c>
     </row>
@@ -14149,7 +14724,7 @@
       <c r="B10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="115"/>
+      <c r="C10" s="112"/>
       <c r="D10" s="5"/>
       <c r="E10" s="24">
         <f>SUM(E8:E9)</f>
@@ -14172,7 +14747,7 @@
         <v>2078083.7516107203</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="116" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" s="113" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
         <v>77</v>
       </c>
@@ -14333,7 +14908,7 @@
       <c r="B17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="115"/>
+      <c r="C17" s="112"/>
       <c r="D17" s="5"/>
       <c r="E17" s="24">
         <f>E10+SUM(E12:E16)</f>
@@ -14356,7 +14931,7 @@
         <v>237948.52117680036</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="87" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" s="85" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
         <v>79</v>
       </c>
@@ -14412,7 +14987,7 @@
       <c r="B20" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="115"/>
+      <c r="C20" s="112"/>
       <c r="D20" s="5"/>
       <c r="E20" s="24">
         <f>E17+E19</f>
@@ -14435,7 +15010,7 @@
         <v>292518.0561768004</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="87" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" s="85" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
         <v>81</v>
       </c>
@@ -14513,29 +15088,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="52" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" s="51" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B24" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="117"/>
+      <c r="C24" s="114"/>
       <c r="D24" s="5"/>
-      <c r="E24" s="63">
+      <c r="E24" s="61">
         <f>E17+SUM(E22:E23)</f>
         <v>-88000</v>
       </c>
-      <c r="F24" s="63">
+      <c r="F24" s="61">
         <f t="shared" ref="F24:I24" si="2">F17+SUM(F22:F23)</f>
         <v>14281</v>
       </c>
-      <c r="G24" s="63">
+      <c r="G24" s="61">
         <f t="shared" si="2"/>
         <v>37625.272149999997</v>
       </c>
-      <c r="H24" s="63">
+      <c r="H24" s="61">
         <f t="shared" si="2"/>
         <v>129556.80767641158</v>
       </c>
-      <c r="I24" s="63">
+      <c r="I24" s="61">
         <f t="shared" si="2"/>
         <v>240888.15077163334</v>
       </c>
@@ -14570,7 +15145,7 @@
       <c r="B26" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="91"/>
+      <c r="C26" s="89"/>
       <c r="D26" s="8"/>
       <c r="E26" s="41">
         <f>SUM(E24:E25)</f>
@@ -14593,7 +15168,7 @@
         <v>187892.75760187401</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="87" customFormat="1" ht="17" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" s="85" customFormat="1" ht="17" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
         <v>87</v>
       </c>
@@ -14619,11 +15194,11 @@
         <v>5.9222712334782587E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="90" t="s">
+    <row r="29" spans="1:9" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B29" s="112" t="s">
+      <c r="B29" s="109" t="s">
         <v>120</v>
       </c>
     </row>
@@ -14736,7 +15311,7 @@
       <c r="B35" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C35" s="91"/>
+      <c r="C35" s="89"/>
       <c r="D35" s="8"/>
       <c r="E35" s="41">
         <f>SUM(E31:E34)</f>
@@ -14762,11 +15337,11 @@
     <row r="36" spans="1:9" ht="17" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B36" s="10"/>
       <c r="D36" s="10"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="64"/>
-      <c r="G36" s="64"/>
-      <c r="H36" s="64"/>
-      <c r="I36" s="64"/>
+      <c r="E36" s="62"/>
+      <c r="F36" s="62"/>
+      <c r="G36" s="62"/>
+      <c r="H36" s="62"/>
+      <c r="I36" s="62"/>
     </row>
     <row r="37" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="3" t="s">
@@ -14820,32 +15395,32 @@
         <v>178810.52207069477</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="52" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" s="51" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B39" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C39" s="117"/>
-      <c r="D39" s="65">
+      <c r="C39" s="114"/>
+      <c r="D39" s="63">
         <f>i_Inputs!D47</f>
         <v>325013</v>
       </c>
-      <c r="E39" s="63">
+      <c r="E39" s="61">
         <f t="shared" ref="E39:F39" si="5">SUM(E37:E38)</f>
         <v>342247</v>
       </c>
-      <c r="F39" s="63">
+      <c r="F39" s="61">
         <f t="shared" si="5"/>
         <v>357038</v>
       </c>
-      <c r="G39" s="63">
+      <c r="G39" s="61">
         <f>SUM(G37:G38)</f>
         <v>384660.83190148778</v>
       </c>
-      <c r="H39" s="63">
+      <c r="H39" s="61">
         <f t="shared" ref="H39:I39" si="6">SUM(H37:H38)</f>
         <v>465465.84478947567</v>
       </c>
-      <c r="I39" s="63">
+      <c r="I39" s="61">
         <f t="shared" si="6"/>
         <v>644276.36686017038</v>
       </c>
@@ -14906,7 +15481,7 @@
       <c r="B42" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="91"/>
+      <c r="C42" s="89"/>
       <c r="D42" s="8"/>
       <c r="E42" s="41">
         <f>SUM(E39:E41)</f>
@@ -14930,11 +15505,11 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:9" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="90" t="s">
+    <row r="44" spans="1:9" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B44" s="112" t="s">
+      <c r="B44" s="109" t="s">
         <v>118</v>
       </c>
     </row>
@@ -14982,75 +15557,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="199" t="str">
+      <c r="A1" s="193" t="str">
         <f>Contents!$A1</f>
         <v>Bolt Technology OÜ|Pre-IPO Equity Valuation Model</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="107" t="str">
+      <c r="A2" s="105" t="str">
         <f>Contents!$A2</f>
         <v>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="85" t="s">
+    <row r="4" spans="1:9" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="83" t="s">
         <v>224</v>
       </c>
-      <c r="C4" s="70"/>
-      <c r="E4" s="70" t="str">
+      <c r="C4" s="68"/>
+      <c r="E4" s="68" t="str">
         <f>i_Inputs!E4</f>
         <v>2024A</v>
       </c>
-      <c r="F4" s="70" t="str">
+      <c r="F4" s="68" t="str">
         <f>i_Inputs!F4</f>
         <v>2025A</v>
       </c>
-      <c r="G4" s="70" t="str">
+      <c r="G4" s="68" t="str">
         <f>i_Inputs!G4</f>
         <v>2026E</v>
       </c>
-      <c r="H4" s="70" t="str">
+      <c r="H4" s="68" t="str">
         <f>i_Inputs!H4</f>
         <v>2027E</v>
       </c>
-      <c r="I4" s="70" t="str">
+      <c r="I4" s="68" t="str">
         <f>i_Inputs!I4</f>
         <v>2028E</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="70" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E5" s="70" t="str">
+    <row r="5" spans="1:9" s="68" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="68" t="str">
         <f>i_Inputs!E5</f>
         <v>Actual</v>
       </c>
-      <c r="F5" s="70" t="str">
+      <c r="F5" s="68" t="str">
         <f>i_Inputs!F5</f>
         <v>Actual</v>
       </c>
-      <c r="G5" s="70" t="str">
+      <c r="G5" s="68" t="str">
         <f>i_Inputs!G5</f>
         <v>Estimate</v>
       </c>
-      <c r="H5" s="70" t="str">
+      <c r="H5" s="68" t="str">
         <f>i_Inputs!H5</f>
         <v>Estimate</v>
       </c>
-      <c r="I5" s="70" t="str">
+      <c r="I5" s="68" t="str">
         <f>i_Inputs!I5</f>
         <v>Estimate</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="90" t="s">
+    <row r="6" spans="1:9" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="112" t="s">
+      <c r="B6" s="109" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="G7" s="250"/>
+      <c r="G7" s="236"/>
     </row>
     <row r="8" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
@@ -15137,7 +15712,7 @@
       <c r="B11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="91"/>
+      <c r="C11" s="89"/>
       <c r="D11" s="8"/>
       <c r="E11" s="41">
         <f>SUM(E8:E10)</f>
@@ -15160,62 +15735,62 @@
         <v>3172646.9490240002</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="87" customFormat="1" ht="17" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="66" t="s">
+    <row r="12" spans="1:9" s="85" customFormat="1" ht="17" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="64" t="s">
         <v>187</v>
       </c>
-      <c r="D12" s="66"/>
-      <c r="E12" s="92">
+      <c r="D12" s="64"/>
+      <c r="E12" s="90">
         <f>IF(D11=0, 0, E11/D11-1)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="92">
+      <c r="F12" s="90">
         <f t="shared" ref="F12:I12" si="0">IF(E11=0, 0, F11/E11-1)</f>
         <v>0.13995604536824802</v>
       </c>
-      <c r="G12" s="92">
+      <c r="G12" s="90">
         <f t="shared" si="0"/>
         <v>0.12877413078956201</v>
       </c>
-      <c r="H12" s="92">
+      <c r="H12" s="90">
         <f t="shared" si="0"/>
         <v>0.1188195522828408</v>
       </c>
-      <c r="I12" s="92">
+      <c r="I12" s="90">
         <f t="shared" si="0"/>
         <v>0.10628096156397571</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="90" t="s">
+    <row r="14" spans="1:9" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B14" s="112" t="s">
+      <c r="B14" s="109" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:9" s="52" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" s="51" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="E16" s="64">
+      <c r="E16" s="62">
         <f>IF(E$5="Actual",i_Historical!E16,-E$11*i_Inputs!E14+i_Scenario_Manager!$D16)</f>
         <v>-864477</v>
       </c>
-      <c r="F16" s="64">
+      <c r="F16" s="62">
         <f>IF(F$5="Actual",i_Historical!F16,-F$11*i_Inputs!F14+i_Scenario_Manager!$D16)</f>
         <v>-831240</v>
       </c>
-      <c r="G16" s="64">
+      <c r="G16" s="62">
         <f>IF(G$5="Actual",i_Historical!G16,-G$11*i_Inputs!G14+i_Scenario_Manager!$D16)</f>
         <v>-909964.84375</v>
       </c>
-      <c r="H16" s="64">
+      <c r="H16" s="62">
         <f>IF(H$5="Actual",i_Historical!H16,-H$11*i_Inputs!H14+i_Scenario_Manager!$D16)</f>
         <v>-1003747.213175</v>
       </c>
-      <c r="I16" s="64">
+      <c r="I16" s="62">
         <f>IF(I$5="Actual",i_Historical!I16,-I$11*i_Inputs!I14+i_Scenario_Manager!$D16)</f>
         <v>-1094563.1974132799</v>
       </c>
@@ -15350,7 +15925,7 @@
       <c r="B23" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="C23" s="91"/>
+      <c r="C23" s="89"/>
       <c r="D23" s="8"/>
       <c r="E23" s="41">
         <f>SUM(E18:E22)</f>
@@ -15373,37 +15948,37 @@
         <v>-1840135.2304339199</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="87" customFormat="1" ht="17" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="66" t="s">
+    <row r="24" spans="1:9" s="85" customFormat="1" ht="17" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="64" t="s">
         <v>194</v>
       </c>
-      <c r="D24" s="66"/>
-      <c r="E24" s="92">
+      <c r="D24" s="64"/>
+      <c r="E24" s="90">
         <f>-E23/E11</f>
         <v>0.61007984723305697</v>
       </c>
-      <c r="F24" s="92">
+      <c r="F24" s="90">
         <f t="shared" ref="F24:I24" si="2">-F23/F11</f>
         <v>0.62538586804787977</v>
       </c>
-      <c r="G24" s="92">
+      <c r="G24" s="90">
         <f t="shared" si="2"/>
         <v>0.63</v>
       </c>
-      <c r="H24" s="92">
+      <c r="H24" s="90">
         <f t="shared" si="2"/>
         <v>0.60499999999999998</v>
       </c>
-      <c r="I24" s="92">
+      <c r="I24" s="90">
         <f t="shared" si="2"/>
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="90" t="s">
+    <row r="26" spans="1:9" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B26" s="112" t="s">
+      <c r="B26" s="109" t="s">
         <v>139</v>
       </c>
     </row>
@@ -15460,12 +16035,12 @@
         <v>239904.26244674626</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="52" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" s="51" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B30" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C30" s="68"/>
-      <c r="D30" s="93">
+      <c r="C30" s="66"/>
+      <c r="D30" s="91">
         <f>i_Inputs!$D$26</f>
         <v>-34555</v>
       </c>
@@ -15525,11 +16100,11 @@
       <c r="H32" s="17"/>
       <c r="I32" s="17"/>
     </row>
-    <row r="33" spans="1:9" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="90" t="s">
+    <row r="33" spans="1:9" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="112" t="s">
+      <c r="B33" s="109" t="s">
         <v>147</v>
       </c>
     </row>
@@ -15638,12 +16213,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="52" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" s="51" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B39" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C39" s="68"/>
-      <c r="D39" s="94">
+      <c r="C39" s="66"/>
+      <c r="D39" s="92">
         <f>i_Inputs!D30</f>
         <v>209987</v>
       </c>
@@ -15669,17 +16244,17 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="E40" s="114"/>
-      <c r="F40" s="114"/>
-      <c r="G40" s="114"/>
-      <c r="H40" s="114"/>
-      <c r="I40" s="114"/>
-    </row>
-    <row r="41" spans="1:9" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="90" t="s">
+      <c r="E40" s="111"/>
+      <c r="F40" s="111"/>
+      <c r="G40" s="111"/>
+      <c r="H40" s="111"/>
+      <c r="I40" s="111"/>
+    </row>
+    <row r="41" spans="1:9" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B41" s="112" t="s">
+      <c r="B41" s="109" t="s">
         <v>160</v>
       </c>
     </row>
@@ -15760,12 +16335,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="52" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="68" t="s">
+    <row r="46" spans="1:9" s="51" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="66" t="s">
         <v>196</v>
       </c>
-      <c r="C46" s="68"/>
-      <c r="D46" s="94">
+      <c r="C46" s="66"/>
+      <c r="D46" s="92">
         <f>i_Inputs!D37</f>
         <v>139715</v>
       </c>
@@ -15892,12 +16467,12 @@
         <v>-18225.083499484805</v>
       </c>
     </row>
-    <row r="52" spans="1:9" s="52" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="68" t="s">
+    <row r="52" spans="1:9" s="51" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="66" t="s">
         <v>171</v>
       </c>
-      <c r="C52" s="68"/>
-      <c r="D52" s="94">
+      <c r="C52" s="66"/>
+      <c r="D52" s="92">
         <f>i_Inputs!D40</f>
         <v>96820</v>
       </c>
@@ -15973,17 +16548,17 @@
         <v>-6369.687300956547</v>
       </c>
     </row>
-    <row r="56" spans="1:9" s="52" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="68" t="s">
+    <row r="56" spans="1:9" s="51" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="66" t="s">
         <v>178</v>
       </c>
-      <c r="C56" s="68"/>
-      <c r="D56" s="68"/>
-      <c r="E56" s="94">
+      <c r="C56" s="66"/>
+      <c r="D56" s="66"/>
+      <c r="E56" s="92">
         <f>SUM(E54:E55)</f>
         <v>-13453.5185</v>
       </c>
-      <c r="F56" s="94">
+      <c r="F56" s="92">
         <f>SUM(F54:F55)</f>
         <v>-10474.549300000001</v>
       </c>
@@ -16001,36 +16576,36 @@
       </c>
     </row>
     <row r="57" spans="1:9" ht="17" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="58" spans="1:9" s="52" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" s="51" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B58" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E58" s="95">
+      <c r="E58" s="93">
         <f>IF(E$5="Actual",i_Historical!E24,E56+o_FS!E37*i_Inputs!$D$46)</f>
         <v>1686</v>
       </c>
-      <c r="F58" s="95">
+      <c r="F58" s="93">
         <f>IF(F$5="Actual",i_Historical!F24,F56+o_FS!F37*i_Inputs!$D$46)</f>
         <v>-1291</v>
       </c>
-      <c r="G58" s="95">
+      <c r="G58" s="93">
         <f>IF(G$5="Actual",i_Historical!G24,G56+o_FS!G37*i_Inputs!$D$46)</f>
         <v>-823.94660000000022</v>
       </c>
-      <c r="H58" s="95">
+      <c r="H58" s="93">
         <f>IF(H$5="Actual",i_Historical!H24,H56+o_FS!H37*i_Inputs!$D$46)</f>
         <v>503.59455391147549</v>
       </c>
-      <c r="I58" s="95">
+      <c r="I58" s="93">
         <f>IF(I$5="Actual",i_Historical!I24,I56+o_FS!I37*i_Inputs!$D$46)</f>
         <v>2939.6295948329671</v>
       </c>
     </row>
-    <row r="60" spans="1:9" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="90" t="s">
+    <row r="60" spans="1:9" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B60" s="112" t="s">
+      <c r="B60" s="109" t="s">
         <v>118</v>
       </c>
     </row>

--- a/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
+++ b/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
@@ -8,8 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarashan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF24F888-DFB9-1B42-BB49-DAB17E69E69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Z44C3UyMEVL96bB2AOb31YihuRAWn+WK0XNOKqNiH22qQvOGTrSBUlxcpAHwsliaRiFi7c92lVZkujb1M09ogg==" workbookSaltValue="3kyWm35AZS5dfiT25bcycw==" workbookSpinCount="100000" lockStructure="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B877CD6B-62CA-864F-BBAB-D5BDC746C533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="342">
   <si>
     <t>Source Note</t>
   </si>
@@ -1073,6 +1072,30 @@
   </si>
   <si>
     <t>Disclaimer: This model is a draft prepared for illustrative and analytical purposes only. Forward-looking figures (2026E-2028E), valuation multiples, and implied share prices are based on assumptions and estimates that are inherently uncertain and may differ materially from actual results. Historical figures are extracted from the Bolt Technology OÜ Consolidated Annual Reports 2024-25 and have not been independently verified. Nothing in this model constitutes investment, financial, legal or tax advice, an offer or solicitation to buy or sell any security, or a recommendation regarding any IPO. No output should be relied upon for any investment decision. The author accepts no liability for any loss arising from use of, or reliance on, this model.</t>
+  </si>
+  <si>
+    <t>Severe downside</t>
+  </si>
+  <si>
+    <t>Conservative</t>
+  </si>
+  <si>
+    <t>Base Case</t>
+  </si>
+  <si>
+    <t>Upside</t>
+  </si>
+  <si>
+    <t>Aggressive</t>
+  </si>
+  <si>
+    <t>Note: Insert additional scenario columns before Column J to preserve formula ranges.</t>
+  </si>
+  <si>
+    <t>Case Label</t>
+  </si>
+  <si>
+    <t>Active Scenario&gt;&gt;</t>
   </si>
 </sst>
 </file>
@@ -1096,7 +1119,7 @@
     <numFmt numFmtId="176" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="177" formatCode="&quot;Case&quot;\ General"/>
   </numFmts>
-  <fonts count="50" x14ac:knownFonts="1">
+  <fonts count="51" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1449,8 +1472,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1538,6 +1570,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.499984740745262"/>
         <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1835,7 +1873,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="246">
+  <cellXfs count="252">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2457,9 +2495,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2478,6 +2513,23 @@
     </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="16" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -9218,34 +9270,34 @@
       <c r="Q24"/>
     </row>
     <row r="25" spans="1:17" ht="71" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="245" t="s">
+      <c r="B25" s="244" t="s">
         <v>333</v>
       </c>
-      <c r="C25" s="245"/>
-      <c r="D25" s="245"/>
-      <c r="E25" s="245"/>
-      <c r="F25" s="245"/>
-      <c r="G25" s="245"/>
-      <c r="H25" s="245"/>
-      <c r="I25" s="245"/>
-      <c r="J25" s="245"/>
-      <c r="K25" s="245"/>
-      <c r="L25" s="245"/>
+      <c r="C25" s="244"/>
+      <c r="D25" s="244"/>
+      <c r="E25" s="244"/>
+      <c r="F25" s="244"/>
+      <c r="G25" s="244"/>
+      <c r="H25" s="244"/>
+      <c r="I25" s="244"/>
+      <c r="J25" s="244"/>
+      <c r="K25" s="244"/>
+      <c r="L25" s="244"/>
     </row>
     <row r="26" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="245" t="s">
+      <c r="B26" s="244" t="s">
         <v>293</v>
       </c>
-      <c r="C26" s="245"/>
-      <c r="D26" s="245"/>
-      <c r="E26" s="245"/>
-      <c r="F26" s="245"/>
-      <c r="G26" s="245"/>
-      <c r="H26" s="245"/>
-      <c r="I26" s="245"/>
-      <c r="J26" s="245"/>
-      <c r="K26" s="245"/>
-      <c r="L26" s="245"/>
+      <c r="C26" s="244"/>
+      <c r="D26" s="244"/>
+      <c r="E26" s="244"/>
+      <c r="F26" s="244"/>
+      <c r="G26" s="244"/>
+      <c r="H26" s="244"/>
+      <c r="I26" s="244"/>
+      <c r="J26" s="244"/>
+      <c r="K26" s="244"/>
+      <c r="L26" s="244"/>
     </row>
     <row r="28" spans="1:17" s="67" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="67" t="s">
@@ -9272,109 +9324,114 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5" style="182" customWidth="1"/>
     <col min="2" max="2" width="56.6640625" style="182" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" style="227" customWidth="1"/>
     <col min="4" max="4" width="16" style="182" customWidth="1"/>
-    <col min="5" max="9" width="14.33203125" style="182" customWidth="1"/>
+    <col min="5" max="9" width="17" style="182" customWidth="1"/>
     <col min="10" max="16384" width="10.83203125" style="182"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A1" s="193" t="str">
         <f>Contents!$A1</f>
         <v>Bolt Technology OÜ|Pre-IPO Equity Valuation Model</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="105" t="str">
         <f>Contents!$A2</f>
         <v>Source: Bolt Technology OÜ Consolidated Annual Report 2024-25 (AS PricewaterhouseCoopers audit)</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="110"/>
     </row>
-    <row r="4" spans="1:10" s="241" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:10" s="58" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="238"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" s="240" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B6" s="224" t="s">
         <v>314</v>
       </c>
-      <c r="C6" s="242">
+      <c r="C6" s="241">
         <v>3</v>
       </c>
-      <c r="E6" s="229">
+      <c r="D6" s="234"/>
+      <c r="E6" s="247">
         <f>D6+1</f>
         <v>1</v>
       </c>
-      <c r="F6" s="229">
+      <c r="F6" s="247">
         <f t="shared" ref="F6:I6" si="0">E6+1</f>
         <v>2</v>
       </c>
-      <c r="G6" s="229">
+      <c r="G6" s="247">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H6" s="229">
+      <c r="H6" s="247">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I6" s="229">
+      <c r="I6" s="247">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="J6" s="71"/>
-    </row>
-    <row r="7" spans="1:10" s="58" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="238"/>
-    </row>
-    <row r="8" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="88" t="s">
+      <c r="K6" s="246" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="58" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="224" t="s">
+        <v>340</v>
+      </c>
+      <c r="C7" s="245" t="str" cm="1">
+        <f t="array" ref="C7">INDEX(E7:J7,$C$6)</f>
+        <v>Base Case</v>
+      </c>
+      <c r="E7" s="247" t="s">
+        <v>334</v>
+      </c>
+      <c r="F7" s="247" t="s">
+        <v>335</v>
+      </c>
+      <c r="G7" s="247" t="s">
+        <v>336</v>
+      </c>
+      <c r="H7" s="247" t="s">
+        <v>337</v>
+      </c>
+      <c r="I7" s="247" t="s">
+        <v>338</v>
+      </c>
+      <c r="J7" s="71"/>
+    </row>
+    <row r="8" spans="1:11" s="248" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="249"/>
+      <c r="C8" s="250"/>
+      <c r="E8" s="251"/>
+      <c r="F8" s="251"/>
+      <c r="G8" s="251"/>
+      <c r="H8" s="251"/>
+      <c r="I8" s="251"/>
+      <c r="J8" s="251"/>
+    </row>
+    <row r="9" spans="1:11" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B8" s="109" t="s">
+      <c r="B9" s="109" t="s">
         <v>308</v>
       </c>
-      <c r="C8" s="230"/>
-    </row>
-    <row r="9" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="182" t="s">
+      <c r="C9" s="230"/>
+    </row>
+    <row r="10" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="182" t="s">
         <v>4</v>
-      </c>
-      <c r="C10" s="227" t="s">
-        <v>313</v>
-      </c>
-      <c r="D10" s="234" cm="1">
-        <f t="array" ref="D10">INDEX(E10:J10,$C$6)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="79">
-        <v>-0.05</v>
-      </c>
-      <c r="F10" s="79">
-        <v>-2.5000000000000001E-2</v>
-      </c>
-      <c r="G10" s="79">
-        <v>0</v>
-      </c>
-      <c r="H10" s="79">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="I10" s="79">
-        <v>0.05</v>
-      </c>
-      <c r="J10" s="71"/>
-    </row>
-    <row r="11" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="182" t="s">
-        <v>149</v>
       </c>
       <c r="C11" s="227" t="s">
         <v>313</v>
@@ -9400,9 +9457,9 @@
       </c>
       <c r="J11" s="71"/>
     </row>
-    <row r="12" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B12" s="182" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" s="227" t="s">
         <v>313</v>
@@ -9428,106 +9485,106 @@
       </c>
       <c r="J12" s="71"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="D13" s="234"/>
-      <c r="E13" s="232"/>
-      <c r="F13" s="232"/>
-      <c r="G13" s="232"/>
-      <c r="H13" s="232"/>
-      <c r="I13" s="232"/>
-    </row>
-    <row r="14" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="88" t="s">
+    <row r="13" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="182" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="227" t="s">
+        <v>313</v>
+      </c>
+      <c r="D13" s="234" cm="1">
+        <f t="array" ref="D13">INDEX(E13:J13,$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="79">
+        <v>-0.05</v>
+      </c>
+      <c r="F13" s="79">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="G13" s="79">
+        <v>0</v>
+      </c>
+      <c r="H13" s="79">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I13" s="79">
+        <v>0.05</v>
+      </c>
+      <c r="J13" s="71"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D14" s="234"/>
+      <c r="E14" s="232"/>
+      <c r="F14" s="232"/>
+      <c r="G14" s="232"/>
+      <c r="H14" s="232"/>
+      <c r="I14" s="232"/>
+    </row>
+    <row r="15" spans="1:11" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B14" s="109" t="s">
+      <c r="B15" s="109" t="s">
         <v>309</v>
       </c>
-      <c r="C14" s="230"/>
-      <c r="D14" s="235"/>
-      <c r="E14" s="233"/>
-      <c r="F14" s="233"/>
-      <c r="G14" s="233"/>
-      <c r="H14" s="233"/>
-      <c r="I14" s="233"/>
-    </row>
-    <row r="15" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="234"/>
-      <c r="E15" s="232"/>
-      <c r="F15" s="232"/>
-      <c r="G15" s="232"/>
-      <c r="H15" s="232"/>
-      <c r="I15" s="232"/>
-    </row>
-    <row r="16" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="182" t="s">
+      <c r="C15" s="230"/>
+      <c r="D15" s="235"/>
+      <c r="E15" s="233"/>
+      <c r="F15" s="233"/>
+      <c r="G15" s="233"/>
+      <c r="H15" s="233"/>
+      <c r="I15" s="233"/>
+    </row>
+    <row r="16" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="D16" s="234"/>
+      <c r="E16" s="232"/>
+      <c r="F16" s="232"/>
+      <c r="G16" s="232"/>
+      <c r="H16" s="232"/>
+      <c r="I16" s="232"/>
+    </row>
+    <row r="17" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="182" t="s">
         <v>161</v>
       </c>
-      <c r="C16" s="227" t="s">
+      <c r="C17" s="227" t="s">
         <v>313</v>
       </c>
-      <c r="D16" s="234" cm="1">
-        <f t="array" ref="D16">INDEX(E16:J16,$C$6)</f>
+      <c r="D17" s="234" cm="1">
+        <f t="array" ref="D17">INDEX(E17:J17,$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="79">
+      <c r="E17" s="79">
         <v>-0.05</v>
       </c>
-      <c r="F16" s="79">
+      <c r="F17" s="79">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="G16" s="79">
+      <c r="G17" s="79">
         <v>0</v>
       </c>
-      <c r="H16" s="79">
+      <c r="H17" s="79">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I16" s="79">
+      <c r="I17" s="79">
         <v>0.05</v>
       </c>
-      <c r="J16" s="71"/>
-    </row>
-    <row r="17" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="228"/>
-      <c r="C17" s="231"/>
-      <c r="D17" s="234"/>
-      <c r="E17" s="232"/>
-      <c r="F17" s="232"/>
-      <c r="G17" s="232"/>
-      <c r="H17" s="232"/>
-      <c r="I17" s="232"/>
+      <c r="J17" s="71"/>
     </row>
     <row r="18" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="182" t="s">
-        <v>153</v>
-      </c>
-      <c r="C18" s="227" t="s">
-        <v>313</v>
-      </c>
-      <c r="D18" s="234" cm="1">
-        <f t="array" ref="D18">INDEX(E18:J18,$C$6)</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="79">
-        <v>-0.05</v>
-      </c>
-      <c r="F18" s="79">
-        <v>-2.5000000000000001E-2</v>
-      </c>
-      <c r="G18" s="79">
-        <v>0</v>
-      </c>
-      <c r="H18" s="79">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="I18" s="79">
-        <v>0.05</v>
-      </c>
-      <c r="J18" s="71"/>
+      <c r="B18" s="228"/>
+      <c r="C18" s="231"/>
+      <c r="D18" s="234"/>
+      <c r="E18" s="232"/>
+      <c r="F18" s="232"/>
+      <c r="G18" s="232"/>
+      <c r="H18" s="232"/>
+      <c r="I18" s="232"/>
     </row>
     <row r="19" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B19" s="182" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C19" s="227" t="s">
         <v>313</v>
@@ -9555,7 +9612,7 @@
     </row>
     <row r="20" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B20" s="182" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="C20" s="227" t="s">
         <v>313</v>
@@ -9583,7 +9640,7 @@
     </row>
     <row r="21" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B21" s="182" t="s">
-        <v>21</v>
+        <v>128</v>
       </c>
       <c r="C21" s="227" t="s">
         <v>313</v>
@@ -9611,7 +9668,7 @@
     </row>
     <row r="22" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B22" s="182" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C22" s="227" t="s">
         <v>313</v>
@@ -9637,47 +9694,47 @@
       </c>
       <c r="J22" s="71"/>
     </row>
-    <row r="24" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="88" t="s">
+    <row r="23" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="182" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="227" t="s">
+        <v>313</v>
+      </c>
+      <c r="D23" s="234" cm="1">
+        <f t="array" ref="D23">INDEX(E23:J23,$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="79">
+        <v>-0.05</v>
+      </c>
+      <c r="F23" s="79">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="G23" s="79">
+        <v>0</v>
+      </c>
+      <c r="H23" s="79">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I23" s="79">
+        <v>0.05</v>
+      </c>
+      <c r="J23" s="71"/>
+    </row>
+    <row r="25" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="109" t="s">
+      <c r="B25" s="109" t="s">
         <v>311</v>
       </c>
-      <c r="C24" s="230"/>
-    </row>
-    <row r="25" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="227" t="s">
-        <v>313</v>
-      </c>
-      <c r="D26" s="234" cm="1">
-        <f t="array" ref="D26">INDEX(E26:J26,$C$6)</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="79">
-        <v>-0.05</v>
-      </c>
-      <c r="F26" s="79">
-        <v>-2.5000000000000001E-2</v>
-      </c>
-      <c r="G26" s="79">
-        <v>0</v>
-      </c>
-      <c r="H26" s="79">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="I26" s="79">
-        <v>0.05</v>
-      </c>
-      <c r="J26" s="71"/>
-    </row>
+      <c r="C25" s="230"/>
+    </row>
+    <row r="26" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B27" s="3" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="C27" s="227" t="s">
         <v>313</v>
@@ -9687,68 +9744,96 @@
         <v>0</v>
       </c>
       <c r="E27" s="79">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="F27" s="79">
-        <v>-2.5000000000000001E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G27" s="79">
         <v>0</v>
       </c>
       <c r="H27" s="79">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="I27" s="79">
+        <v>-0.05</v>
+      </c>
+      <c r="J27" s="71"/>
+    </row>
+    <row r="28" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="227" t="s">
+        <v>313</v>
+      </c>
+      <c r="D28" s="234" cm="1">
+        <f t="array" ref="D28">INDEX(E28:J28,$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="79">
+        <v>-0.05</v>
+      </c>
+      <c r="F28" s="79">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="G28" s="79">
+        <v>0</v>
+      </c>
+      <c r="H28" s="79">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I27" s="79">
+      <c r="I28" s="79">
         <v>0.05</v>
       </c>
-      <c r="J27" s="71"/>
-    </row>
-    <row r="29" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="88" t="s">
+      <c r="J28" s="71"/>
+    </row>
+    <row r="30" spans="1:10" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B29" s="109" t="s">
+      <c r="B30" s="109" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="230"/>
-    </row>
-    <row r="30" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="3" t="s">
+      <c r="C30" s="230"/>
+    </row>
+    <row r="31" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="227" t="s">
+      <c r="C32" s="227" t="s">
         <v>313</v>
       </c>
-      <c r="D31" s="234" cm="1">
-        <f t="array" ref="D31">INDEX(E31:J31,$C$6)</f>
+      <c r="D32" s="234" cm="1">
+        <f t="array" ref="D32">INDEX(E32:J32,$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E31" s="79">
+      <c r="E32" s="79">
         <v>-0.05</v>
       </c>
-      <c r="F31" s="79">
+      <c r="F32" s="79">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="G31" s="79">
+      <c r="G32" s="79">
         <v>0</v>
       </c>
-      <c r="H31" s="79">
+      <c r="H32" s="79">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I31" s="79">
+      <c r="I32" s="79">
         <v>0.05</v>
       </c>
-      <c r="J31" s="71"/>
-    </row>
-    <row r="33" spans="1:3" s="94" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="88" t="s">
+      <c r="J32" s="71"/>
+    </row>
+    <row r="34" spans="1:3" s="94" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="109" t="s">
+      <c r="B34" s="109" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="230"/>
+      <c r="C34" s="230"/>
     </row>
   </sheetData>
   <phoneticPr fontId="49" type="noConversion"/>
@@ -12603,7 +12688,7 @@
       <c r="B6" s="52"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B7" s="239" t="s">
+      <c r="B7" s="238" t="s">
         <v>330</v>
       </c>
       <c r="C7" s="54"/>
@@ -12619,22 +12704,22 @@
     </row>
     <row r="8" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="243" t="s">
+      <c r="B9" s="242" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="244" t="s">
+      <c r="B10" s="243" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="244" t="s">
+      <c r="B11" s="243" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="244" t="s">
+      <c r="B12" s="243" t="s">
         <v>332</v>
       </c>
     </row>
@@ -12722,7 +12807,7 @@
       <c r="D24" s="188"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="239" t="s">
+      <c r="B25" s="238" t="s">
         <v>318</v>
       </c>
       <c r="C25" s="54"/>
@@ -12737,7 +12822,7 @@
       <c r="L25" s="54"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B26" s="240" t="s">
+      <c r="B26" s="239" t="s">
         <v>317</v>
       </c>
       <c r="C26" s="54"/>
@@ -12765,7 +12850,7 @@
       <c r="L27" s="54"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B28" s="239" t="s">
+      <c r="B28" s="238" t="s">
         <v>319</v>
       </c>
       <c r="C28" s="54"/>
@@ -12780,7 +12865,7 @@
       <c r="L28" s="54"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B29" s="240" t="s">
+      <c r="B29" s="239" t="s">
         <v>320</v>
       </c>
       <c r="C29" s="54"/>
@@ -12808,7 +12893,7 @@
       <c r="L30" s="54"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B31" s="239" t="s">
+      <c r="B31" s="238" t="s">
         <v>321</v>
       </c>
       <c r="C31" s="54"/>
@@ -12823,17 +12908,17 @@
       <c r="L31" s="54"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B32" s="240" t="s">
+      <c r="B32" s="239" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B34" s="239" t="s">
+      <c r="B34" s="238" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B35" s="240" t="s">
+      <c r="B35" s="239" t="s">
         <v>324</v>
       </c>
     </row>
@@ -12901,13 +12986,12 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="153"/>
-      <c r="F3" s="237" t="str">
-        <f>i_Scenario_Manager!B6</f>
-        <v>Selected Case</v>
-      </c>
-      <c r="G3" s="229">
-        <f>i_Scenario_Manager!C6</f>
-        <v>3</v>
+      <c r="F3" s="237" t="s">
+        <v>341</v>
+      </c>
+      <c r="G3" s="229" t="str">
+        <f>i_Scenario_Manager!C6&amp;" - "&amp;i_Scenario_Manager!C7</f>
+        <v>3 - Base Case</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -13424,7 +13508,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="hvO+IBv/rr7y8NIjQKR2nkEPUnRfnOUfsl3qI1Mg+d9kxUDJDxelsSqA3Bl+vdvpfl9CQ5UT22+6etwQjFMMnQ==" saltValue="/ia3ch3I+79blbRzM/a1IQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" scale="56" orientation="landscape" errors="blank" horizontalDpi="0" verticalDpi="0"/>
@@ -13748,7 +13831,7 @@
         <v>56</v>
       </c>
       <c r="D30" s="121">
-        <f>$D$26*(1+i_Scenario_Manager!$D$26)</f>
+        <f>$D$26*(1+i_Scenario_Manager!$D$27)</f>
         <v>0.10201850000000001</v>
       </c>
       <c r="E30" s="3"/>
@@ -13761,7 +13844,7 @@
         <v>56</v>
       </c>
       <c r="D31" s="121">
-        <f>i_Inputs!$D$57*(1+i_Scenario_Manager!$D$27)</f>
+        <f>i_Inputs!$D$57*(1+i_Scenario_Manager!$D$28)</f>
         <v>0.04</v>
       </c>
       <c r="E31" s="3"/>
@@ -14387,7 +14470,7 @@
         <v>6</v>
       </c>
       <c r="D77" s="139">
-        <f>i_Inputs!$D$63*(1+i_Scenario_Manager!$D$31)</f>
+        <f>i_Inputs!$D$63*(1+i_Scenario_Manager!$D$32)</f>
         <v>500000</v>
       </c>
       <c r="E77" s="10"/>
@@ -15634,23 +15717,23 @@
       <c r="C8" s="14"/>
       <c r="D8" s="3"/>
       <c r="E8" s="17">
-        <f>IF(E$5="Actual",i_Historical!E12,D8*(1+i_Inputs!E8+i_Scenario_Manager!$D10))</f>
+        <f>IF(E$5="Actual",i_Historical!E12,D8*(1+i_Inputs!E8+i_Scenario_Manager!$D11))</f>
         <v>1633907</v>
       </c>
       <c r="F8" s="17">
-        <f>IF(F$5="Actual",i_Historical!F12,E8*(1+i_Inputs!F8+i_Scenario_Manager!$D10))</f>
+        <f>IF(F$5="Actual",i_Historical!F12,E8*(1+i_Inputs!F8+i_Scenario_Manager!$D11))</f>
         <v>1847432</v>
       </c>
       <c r="G8" s="17">
-        <f>IF(G$5="Actual",i_Historical!G12,F8*(1+i_Inputs!G8+i_Scenario_Manager!$D10))</f>
+        <f>IF(G$5="Actual",i_Historical!G12,F8*(1+i_Inputs!G8+i_Scenario_Manager!$D11))</f>
         <v>2069123.84</v>
       </c>
       <c r="H8" s="17">
-        <f>IF(H$5="Actual",i_Historical!H12,G8*(1+i_Inputs!H8+i_Scenario_Manager!$D10))</f>
+        <f>IF(H$5="Actual",i_Historical!H12,G8*(1+i_Inputs!H8+i_Scenario_Manager!$D11))</f>
         <v>2296727.4624000001</v>
       </c>
       <c r="I8" s="17">
-        <f>IF(I$5="Actual",i_Historical!I12,H8*(1+i_Inputs!I8+i_Scenario_Manager!$D10))</f>
+        <f>IF(I$5="Actual",i_Historical!I12,H8*(1+i_Inputs!I8+i_Scenario_Manager!$D11))</f>
         <v>2526400.2086400003</v>
       </c>
     </row>
@@ -15661,23 +15744,23 @@
       <c r="C9" s="14"/>
       <c r="D9" s="3"/>
       <c r="E9" s="17">
-        <f>IF(E$5="Actual",i_Historical!E13,D9*(1+i_Inputs!E9+i_Scenario_Manager!$D11))</f>
+        <f>IF(E$5="Actual",i_Historical!E13,D9*(1+i_Inputs!E9+i_Scenario_Manager!$D12))</f>
         <v>185469</v>
       </c>
       <c r="F9" s="17">
-        <f>IF(F$5="Actual",i_Historical!F13,E9*(1+i_Inputs!F9+i_Scenario_Manager!$D11))</f>
+        <f>IF(F$5="Actual",i_Historical!F13,E9*(1+i_Inputs!F9+i_Scenario_Manager!$D12))</f>
         <v>240737</v>
       </c>
       <c r="G9" s="17">
-        <f>IF(G$5="Actual",i_Historical!G13,F9*(1+i_Inputs!G9+i_Scenario_Manager!$D11))</f>
+        <f>IF(G$5="Actual",i_Historical!G13,F9*(1+i_Inputs!G9+i_Scenario_Manager!$D12))</f>
         <v>284069.65999999997</v>
       </c>
       <c r="H9" s="17">
-        <f>IF(H$5="Actual",i_Historical!H13,G9*(1+i_Inputs!H9+i_Scenario_Manager!$D11))</f>
+        <f>IF(H$5="Actual",i_Historical!H13,G9*(1+i_Inputs!H9+i_Scenario_Manager!$D12))</f>
         <v>329520.80559999996</v>
       </c>
       <c r="I9" s="17">
-        <f>IF(I$5="Actual",i_Historical!I13,H9*(1+i_Inputs!I9+i_Scenario_Manager!$D11))</f>
+        <f>IF(I$5="Actual",i_Historical!I13,H9*(1+i_Inputs!I9+i_Scenario_Manager!$D12))</f>
         <v>375653.71838400001</v>
       </c>
     </row>
@@ -15688,23 +15771,23 @@
       <c r="C10" s="14"/>
       <c r="D10" s="3"/>
       <c r="E10" s="17">
-        <f>IF(E$5="Actual",i_Historical!E14,D10*(1+i_Inputs!E10+i_Scenario_Manager!$D12))</f>
+        <f>IF(E$5="Actual",i_Historical!E14,D10*(1+i_Inputs!E10+i_Scenario_Manager!$D13))</f>
         <v>172678</v>
       </c>
       <c r="F10" s="17">
-        <f>IF(F$5="Actual",i_Historical!F14,E10*(1+i_Inputs!F10+i_Scenario_Manager!$D12))</f>
+        <f>IF(F$5="Actual",i_Historical!F14,E10*(1+i_Inputs!F10+i_Scenario_Manager!$D13))</f>
         <v>182685</v>
       </c>
       <c r="G10" s="17">
-        <f>IF(G$5="Actual",i_Historical!G14,F10*(1+i_Inputs!G10+i_Scenario_Manager!$D12))</f>
+        <f>IF(G$5="Actual",i_Historical!G14,F10*(1+i_Inputs!G10+i_Scenario_Manager!$D13))</f>
         <v>210087.74999999997</v>
       </c>
       <c r="H10" s="17">
-        <f>IF(H$5="Actual",i_Historical!H14,G10*(1+i_Inputs!H10+i_Scenario_Manager!$D12))</f>
+        <f>IF(H$5="Actual",i_Historical!H14,G10*(1+i_Inputs!H10+i_Scenario_Manager!$D13))</f>
         <v>241600.91249999995</v>
       </c>
       <c r="I10" s="17">
-        <f>IF(I$5="Actual",i_Historical!I14,H10*(1+i_Inputs!I10+i_Scenario_Manager!$D12))</f>
+        <f>IF(I$5="Actual",i_Historical!I14,H10*(1+i_Inputs!I10+i_Scenario_Manager!$D13))</f>
         <v>270593.02199999994</v>
       </c>
     </row>
@@ -15775,23 +15858,23 @@
         <v>131</v>
       </c>
       <c r="E16" s="62">
-        <f>IF(E$5="Actual",i_Historical!E16,-E$11*i_Inputs!E14+i_Scenario_Manager!$D16)</f>
+        <f>IF(E$5="Actual",i_Historical!E16,-E$11*i_Inputs!E14*(1+i_Scenario_Manager!$D17))</f>
         <v>-864477</v>
       </c>
       <c r="F16" s="62">
-        <f>IF(F$5="Actual",i_Historical!F16,-F$11*i_Inputs!F14+i_Scenario_Manager!$D16)</f>
+        <f>IF(F$5="Actual",i_Historical!F16,-F$11*i_Inputs!F14*(1+i_Scenario_Manager!$D17))</f>
         <v>-831240</v>
       </c>
       <c r="G16" s="62">
-        <f>IF(G$5="Actual",i_Historical!G16,-G$11*i_Inputs!G14+i_Scenario_Manager!$D16)</f>
+        <f>IF(G$5="Actual",i_Historical!G16,-G$11*i_Inputs!G14*(1+i_Scenario_Manager!$D17))</f>
         <v>-909964.84375</v>
       </c>
       <c r="H16" s="62">
-        <f>IF(H$5="Actual",i_Historical!H16,-H$11*i_Inputs!H14+i_Scenario_Manager!$D16)</f>
+        <f>IF(H$5="Actual",i_Historical!H16,-H$11*i_Inputs!H14*(1+i_Scenario_Manager!$D17))</f>
         <v>-1003747.213175</v>
       </c>
       <c r="I16" s="62">
-        <f>IF(I$5="Actual",i_Historical!I16,-I$11*i_Inputs!I14+i_Scenario_Manager!$D16)</f>
+        <f>IF(I$5="Actual",i_Historical!I16,-I$11*i_Inputs!I14*(1+i_Scenario_Manager!$D17))</f>
         <v>-1094563.1974132799</v>
       </c>
     </row>
@@ -15801,23 +15884,23 @@
         <v>17</v>
       </c>
       <c r="E18" s="17">
-        <f>IF(E$5="Actual",i_Historical!E18,-E$11*i_Inputs!E16+i_Scenario_Manager!$D18)</f>
+        <f>IF(E$5="Actual",i_Historical!E18,-E$11*i_Inputs!E16*(1+i_Scenario_Manager!$D19))</f>
         <v>-795513</v>
       </c>
       <c r="F18" s="17">
-        <f>IF(F$5="Actual",i_Historical!F18,-F$11*i_Inputs!F16+i_Scenario_Manager!$D18)</f>
+        <f>IF(F$5="Actual",i_Historical!F18,-F$11*i_Inputs!F16*(1+i_Scenario_Manager!$D19))</f>
         <v>-1048370</v>
       </c>
       <c r="G18" s="17">
-        <f>IF(G$5="Actual",i_Historical!G18,-G$11*i_Inputs!G16+i_Scenario_Manager!$D18)</f>
+        <f>IF(G$5="Actual",i_Historical!G18,-G$11*i_Inputs!G16*(1+i_Scenario_Manager!$D19))</f>
         <v>-1153476.5625</v>
       </c>
       <c r="H18" s="17">
-        <f>IF(H$5="Actual",i_Historical!H18,-H$11*i_Inputs!H16+i_Scenario_Manager!$D18)</f>
+        <f>IF(H$5="Actual",i_Historical!H18,-H$11*i_Inputs!H16*(1+i_Scenario_Manager!$D19))</f>
         <v>-1218835.9017125</v>
       </c>
       <c r="I18" s="17">
-        <f>IF(I$5="Actual",i_Historical!I18,-I$11*i_Inputs!I16+i_Scenario_Manager!$D18)</f>
+        <f>IF(I$5="Actual",i_Historical!I18,-I$11*i_Inputs!I16*(1+i_Scenario_Manager!$D19))</f>
         <v>-1269058.7796096001</v>
       </c>
     </row>
@@ -15826,23 +15909,23 @@
         <v>15</v>
       </c>
       <c r="E19" s="17">
-        <f>IF(E$5="Actual",i_Historical!E19,-E$11*i_Inputs!E17+i_Scenario_Manager!$D19)</f>
+        <f>IF(E$5="Actual",i_Historical!E19,-E$11*i_Inputs!E17*(1+i_Scenario_Manager!$D20))</f>
         <v>-107877</v>
       </c>
       <c r="F19" s="17">
-        <f>IF(F$5="Actual",i_Historical!F19,-F$11*i_Inputs!F17+i_Scenario_Manager!$D19)</f>
+        <f>IF(F$5="Actual",i_Historical!F19,-F$11*i_Inputs!F17*(1+i_Scenario_Manager!$D20))</f>
         <v>-127580</v>
       </c>
       <c r="G19" s="17">
-        <f>IF(G$5="Actual",i_Historical!G19,-G$11*i_Inputs!G17+i_Scenario_Manager!$D19)</f>
+        <f>IF(G$5="Actual",i_Historical!G19,-G$11*i_Inputs!G17*(1+i_Scenario_Manager!$D20))</f>
         <v>-128164.0625</v>
       </c>
       <c r="H19" s="17">
-        <f>IF(H$5="Actual",i_Historical!H19,-H$11*i_Inputs!H17+i_Scenario_Manager!$D19)</f>
+        <f>IF(H$5="Actual",i_Historical!H19,-H$11*i_Inputs!H17*(1+i_Scenario_Manager!$D20))</f>
         <v>-143392.45902500002</v>
       </c>
       <c r="I19" s="17">
-        <f>IF(I$5="Actual",i_Historical!I19,-I$11*i_Inputs!I17+i_Scenario_Manager!$D19)</f>
+        <f>IF(I$5="Actual",i_Historical!I19,-I$11*i_Inputs!I17*(1+i_Scenario_Manager!$D20))</f>
         <v>-158632.34745120001</v>
       </c>
     </row>
@@ -15851,23 +15934,23 @@
         <v>19</v>
       </c>
       <c r="E20" s="17">
-        <f>IF(E$5="Actual",i_Historical!E20,-E$11*i_Inputs!E18+i_Scenario_Manager!$D20)</f>
+        <f>IF(E$5="Actual",i_Historical!E20,-E$11*i_Inputs!E18*(1+i_Scenario_Manager!$D21))</f>
         <v>-319933</v>
       </c>
       <c r="F20" s="17">
-        <f>IF(F$5="Actual",i_Historical!F20,-F$11*i_Inputs!F18+i_Scenario_Manager!$D20)</f>
+        <f>IF(F$5="Actual",i_Historical!F20,-F$11*i_Inputs!F18*(1+i_Scenario_Manager!$D21))</f>
         <v>-253032</v>
       </c>
       <c r="G20" s="17">
-        <f>IF(G$5="Actual",i_Historical!G20,-G$11*i_Inputs!G18+i_Scenario_Manager!$D20)</f>
+        <f>IF(G$5="Actual",i_Historical!G20,-G$11*i_Inputs!G18*(1+i_Scenario_Manager!$D21))</f>
         <v>-307593.75</v>
       </c>
       <c r="H20" s="17">
-        <f>IF(H$5="Actual",i_Historical!H20,-H$11*i_Inputs!H18+i_Scenario_Manager!$D20)</f>
+        <f>IF(H$5="Actual",i_Historical!H20,-H$11*i_Inputs!H18*(1+i_Scenario_Manager!$D21))</f>
         <v>-344141.90166000003</v>
       </c>
       <c r="I20" s="17">
-        <f>IF(I$5="Actual",i_Historical!I20,-I$11*i_Inputs!I18+i_Scenario_Manager!$D20)</f>
+        <f>IF(I$5="Actual",i_Historical!I20,-I$11*i_Inputs!I18*(1+i_Scenario_Manager!$D21))</f>
         <v>-380717.63388288004</v>
       </c>
     </row>
@@ -15876,23 +15959,23 @@
         <v>21</v>
       </c>
       <c r="E21" s="17">
-        <f>IF(E$5="Actual",i_Historical!E21,-E$11*i_Inputs!E19+i_Scenario_Manager!$D21)</f>
+        <f>IF(E$5="Actual",i_Historical!E21,-E$11*i_Inputs!E19*(1+i_Scenario_Manager!$D22))</f>
         <v>-8913</v>
       </c>
       <c r="F21" s="17">
-        <f>IF(F$5="Actual",i_Historical!F21,-F$11*i_Inputs!F19+i_Scenario_Manager!$D21)</f>
+        <f>IF(F$5="Actual",i_Historical!F21,-F$11*i_Inputs!F19*(1+i_Scenario_Manager!$D22))</f>
         <v>-13131</v>
       </c>
       <c r="G21" s="17">
-        <f>IF(G$5="Actual",i_Historical!G21,-G$11*i_Inputs!G19+i_Scenario_Manager!$D21)</f>
+        <f>IF(G$5="Actual",i_Historical!G21,-G$11*i_Inputs!G19*(1+i_Scenario_Manager!$D22))</f>
         <v>-51265.625</v>
       </c>
       <c r="H21" s="17">
-        <f>IF(H$5="Actual",i_Historical!H21,-H$11*i_Inputs!H19+i_Scenario_Manager!$D21)</f>
+        <f>IF(H$5="Actual",i_Historical!H21,-H$11*i_Inputs!H19*(1+i_Scenario_Manager!$D22))</f>
         <v>-57356.983610000003</v>
       </c>
       <c r="I21" s="17">
-        <f>IF(I$5="Actual",i_Historical!I21,-I$11*i_Inputs!I19+i_Scenario_Manager!$D21)</f>
+        <f>IF(I$5="Actual",i_Historical!I21,-I$11*i_Inputs!I19*(1+i_Scenario_Manager!$D22))</f>
         <v>-63452.938980480008</v>
       </c>
     </row>
@@ -15901,23 +15984,23 @@
         <v>13</v>
       </c>
       <c r="E22" s="17">
-        <f>IF(E$5="Actual",i_Historical!E22,E$11*i_Inputs!E20+i_Scenario_Manager!$D22)</f>
+        <f>IF(E$5="Actual",i_Historical!E22,E$11*i_Inputs!E20*(1+i_Scenario_Manager!$D23))</f>
         <v>16924</v>
       </c>
       <c r="F22" s="17">
-        <f>IF(F$5="Actual",i_Historical!F22,F$11*i_Inputs!F20+i_Scenario_Manager!$D22)</f>
+        <f>IF(F$5="Actual",i_Historical!F22,F$11*i_Inputs!F20*(1+i_Scenario_Manager!$D23))</f>
         <v>21953</v>
       </c>
       <c r="G22" s="17">
-        <f>IF(G$5="Actual",i_Historical!G22,G$11*i_Inputs!G20+i_Scenario_Manager!$D22)</f>
+        <f>IF(G$5="Actual",i_Historical!G22,G$11*i_Inputs!G20*(1+i_Scenario_Manager!$D23))</f>
         <v>25632.8125</v>
       </c>
       <c r="H22" s="17">
-        <f>IF(H$5="Actual",i_Historical!H22,H$11*i_Inputs!H20+i_Scenario_Manager!$D22)</f>
+        <f>IF(H$5="Actual",i_Historical!H22,H$11*i_Inputs!H20*(1+i_Scenario_Manager!$D23))</f>
         <v>28678.491805000001</v>
       </c>
       <c r="I22" s="17">
-        <f>IF(I$5="Actual",i_Historical!I22,I$11*i_Inputs!I20+i_Scenario_Manager!$D22)</f>
+        <f>IF(I$5="Actual",i_Historical!I22,I$11*i_Inputs!I20*(1+i_Scenario_Manager!$D23))</f>
         <v>31726.469490240004</v>
       </c>
     </row>
@@ -16610,7 +16693,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1YzppcQclTwhD0zdOjzePjiOrRBEC6FW84s4fwhWXp4EX9vbTV/Ij8wVZVvzvYqFbTe3tUHhFTO89PJVWlzdJw==" saltValue="7h7fJ2DSeBCSBsr2H0pYSQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="qk/nGEuLWrNOjrqEvROkIhozMvWlrbfvgRIqNVUQGmiBHaCjvZkN3qHsrQQWaiccPi4Y81vbvFA/PzBTM3/GsQ==" saltValue="1hKaNdoWo7uv6UtA/h64zA==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>

--- a/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
+++ b/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
@@ -8,7 +8,8 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarashan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B877CD6B-62CA-864F-BBAB-D5BDC746C533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A90EFE-98A8-B644-9074-241849B74259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="P/esQtHEE/5gVcoDfqNzN/FNfIDAT72ni9Wg+cViuEL3wK4IUYTXUw/9dFsbAgcU4tB3RzJB7GnJZZs9jwYExA==" workbookSaltValue="k+aQesGtRPrMQlTqFr61vA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1873,7 +1874,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="252">
+  <cellXfs count="251">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2511,16 +2512,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2528,8 +2523,11 @@
     <xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -9270,34 +9268,34 @@
       <c r="Q24"/>
     </row>
     <row r="25" spans="1:17" ht="71" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="244" t="s">
+      <c r="B25" s="250" t="s">
         <v>333</v>
       </c>
-      <c r="C25" s="244"/>
-      <c r="D25" s="244"/>
-      <c r="E25" s="244"/>
-      <c r="F25" s="244"/>
-      <c r="G25" s="244"/>
-      <c r="H25" s="244"/>
-      <c r="I25" s="244"/>
-      <c r="J25" s="244"/>
-      <c r="K25" s="244"/>
-      <c r="L25" s="244"/>
+      <c r="C25" s="250"/>
+      <c r="D25" s="250"/>
+      <c r="E25" s="250"/>
+      <c r="F25" s="250"/>
+      <c r="G25" s="250"/>
+      <c r="H25" s="250"/>
+      <c r="I25" s="250"/>
+      <c r="J25" s="250"/>
+      <c r="K25" s="250"/>
+      <c r="L25" s="250"/>
     </row>
     <row r="26" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="244" t="s">
+      <c r="B26" s="250" t="s">
         <v>293</v>
       </c>
-      <c r="C26" s="244"/>
-      <c r="D26" s="244"/>
-      <c r="E26" s="244"/>
-      <c r="F26" s="244"/>
-      <c r="G26" s="244"/>
-      <c r="H26" s="244"/>
-      <c r="I26" s="244"/>
-      <c r="J26" s="244"/>
-      <c r="K26" s="244"/>
-      <c r="L26" s="244"/>
+      <c r="C26" s="250"/>
+      <c r="D26" s="250"/>
+      <c r="E26" s="250"/>
+      <c r="F26" s="250"/>
+      <c r="G26" s="250"/>
+      <c r="H26" s="250"/>
+      <c r="I26" s="250"/>
+      <c r="J26" s="250"/>
+      <c r="K26" s="250"/>
+      <c r="L26" s="250"/>
     </row>
     <row r="28" spans="1:17" s="67" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="67" t="s">
@@ -9359,28 +9357,28 @@
         <v>3</v>
       </c>
       <c r="D6" s="234"/>
-      <c r="E6" s="247">
+      <c r="E6" s="229">
         <f>D6+1</f>
         <v>1</v>
       </c>
-      <c r="F6" s="247">
+      <c r="F6" s="229">
         <f t="shared" ref="F6:I6" si="0">E6+1</f>
         <v>2</v>
       </c>
-      <c r="G6" s="247">
+      <c r="G6" s="229">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H6" s="247">
+      <c r="H6" s="229">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I6" s="247">
+      <c r="I6" s="229">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="J6" s="71"/>
-      <c r="K6" s="246" t="s">
+      <c r="K6" s="245" t="s">
         <v>339</v>
       </c>
     </row>
@@ -9388,36 +9386,36 @@
       <c r="B7" s="224" t="s">
         <v>340</v>
       </c>
-      <c r="C7" s="245" t="str" cm="1">
+      <c r="C7" s="244" t="str" cm="1">
         <f t="array" ref="C7">INDEX(E7:J7,$C$6)</f>
         <v>Base Case</v>
       </c>
-      <c r="E7" s="247" t="s">
+      <c r="E7" s="229" t="s">
         <v>334</v>
       </c>
-      <c r="F7" s="247" t="s">
+      <c r="F7" s="229" t="s">
         <v>335</v>
       </c>
-      <c r="G7" s="247" t="s">
+      <c r="G7" s="229" t="s">
         <v>336</v>
       </c>
-      <c r="H7" s="247" t="s">
+      <c r="H7" s="229" t="s">
         <v>337</v>
       </c>
-      <c r="I7" s="247" t="s">
+      <c r="I7" s="229" t="s">
         <v>338</v>
       </c>
       <c r="J7" s="71"/>
     </row>
-    <row r="8" spans="1:11" s="248" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="249"/>
-      <c r="C8" s="250"/>
-      <c r="E8" s="251"/>
-      <c r="F8" s="251"/>
-      <c r="G8" s="251"/>
-      <c r="H8" s="251"/>
-      <c r="I8" s="251"/>
-      <c r="J8" s="251"/>
+    <row r="8" spans="1:11" s="246" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="247"/>
+      <c r="C8" s="248"/>
+      <c r="E8" s="249"/>
+      <c r="F8" s="249"/>
+      <c r="G8" s="249"/>
+      <c r="H8" s="249"/>
+      <c r="I8" s="249"/>
+      <c r="J8" s="249"/>
     </row>
     <row r="9" spans="1:11" s="94" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="88" t="s">
@@ -13508,6 +13506,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="ObSXUAn6cBFGXtZqqgOBqYdRtUPo/54N+EbGIwaCosjfaPmWI2+a/DPk75WQM7dtdnlYk/v1NdIDynl16QC/lA==" saltValue="v0mh2dwqfjbNYL2m7FOjrQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" scale="56" orientation="landscape" errors="blank" horizontalDpi="0" verticalDpi="0"/>

--- a/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
+++ b/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarashan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A90EFE-98A8-B644-9074-241849B74259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBEDED2A-DBD8-1D4E-B407-7AB6DC6F5A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="P/esQtHEE/5gVcoDfqNzN/FNfIDAT72ni9Wg+cViuEL3wK4IUYTXUw/9dFsbAgcU4tB3RzJB7GnJZZs9jwYExA==" workbookSaltValue="k+aQesGtRPrMQlTqFr61vA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="344">
   <si>
     <t>Source Note</t>
   </si>
@@ -988,12 +988,6 @@
   </si>
   <si>
     <t>Model Roll-Forward and User Manual</t>
-  </si>
-  <si>
-    <t>Model Start Year</t>
-  </si>
-  <si>
-    <t>Forecast Start Year</t>
   </si>
   <si>
     <t>Revenue</t>
@@ -1097,6 +1091,18 @@
   </si>
   <si>
     <t>Active Scenario&gt;&gt;</t>
+  </si>
+  <si>
+    <t>Model Start Date</t>
+  </si>
+  <si>
+    <t>Forecast Start Date</t>
+  </si>
+  <si>
+    <t>Note: Input dates formatted as the first of the month.</t>
+  </si>
+  <si>
+    <t>Target Primary Capital Raised at IPO - sensitized</t>
   </si>
 </sst>
 </file>
@@ -1476,7 +1482,7 @@
     <font>
       <b/>
       <i/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1580,7 +1586,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1867,6 +1873,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1874,7 +1889,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="251">
+  <cellXfs count="253">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2515,7 +2530,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2528,6 +2542,13 @@
     </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2536,7 +2557,92 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="34">
+    <dxf>
+      <fill>
+        <patternFill patternType="lightDown"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightDown"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightDown"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightDown"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightDown"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightDown"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp"/>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="lightUp"/>
@@ -8940,7 +9046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7E54BF-0F64-6F44-99C9-3296C6C48469}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1:Q28"/>
@@ -9268,34 +9374,34 @@
       <c r="Q24"/>
     </row>
     <row r="25" spans="1:17" ht="71" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="250" t="s">
-        <v>333</v>
-      </c>
-      <c r="C25" s="250"/>
-      <c r="D25" s="250"/>
-      <c r="E25" s="250"/>
-      <c r="F25" s="250"/>
-      <c r="G25" s="250"/>
-      <c r="H25" s="250"/>
-      <c r="I25" s="250"/>
-      <c r="J25" s="250"/>
-      <c r="K25" s="250"/>
-      <c r="L25" s="250"/>
+      <c r="B25" s="249" t="s">
+        <v>331</v>
+      </c>
+      <c r="C25" s="249"/>
+      <c r="D25" s="249"/>
+      <c r="E25" s="249"/>
+      <c r="F25" s="249"/>
+      <c r="G25" s="249"/>
+      <c r="H25" s="249"/>
+      <c r="I25" s="249"/>
+      <c r="J25" s="249"/>
+      <c r="K25" s="249"/>
+      <c r="L25" s="249"/>
     </row>
     <row r="26" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="250" t="s">
+      <c r="B26" s="249" t="s">
         <v>293</v>
       </c>
-      <c r="C26" s="250"/>
-      <c r="D26" s="250"/>
-      <c r="E26" s="250"/>
-      <c r="F26" s="250"/>
-      <c r="G26" s="250"/>
-      <c r="H26" s="250"/>
-      <c r="I26" s="250"/>
-      <c r="J26" s="250"/>
-      <c r="K26" s="250"/>
-      <c r="L26" s="250"/>
+      <c r="C26" s="249"/>
+      <c r="D26" s="249"/>
+      <c r="E26" s="249"/>
+      <c r="F26" s="249"/>
+      <c r="G26" s="249"/>
+      <c r="H26" s="249"/>
+      <c r="I26" s="249"/>
+      <c r="J26" s="249"/>
+      <c r="K26" s="249"/>
+      <c r="L26" s="249"/>
     </row>
     <row r="28" spans="1:17" s="67" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="67" t="s">
@@ -9306,7 +9412,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="cjrqWurdRXbDN3J94aXSzH9Oradoec+3PtvkqHW2KkKP4Bn3okgq27BrS0M8dN1Y5oClnChMVNwuRYiGekM4ag==" saltValue="VxgFtFKQl2JXeM/oKegIgg==" spinCount="100000" sheet="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="lfJX6MJXpXKY6SqsJjdR4uYeKXWSpPFcPSOWtP7PlKaKZ8K7jbACw6PmBT6S7Trm0ptRWnGQvpY+q8bfGj4fIA==" saltValue="T+VUKaGRxenmv8RnXuGD/w==" spinCount="100000" sheet="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="B25:L25"/>
     <mergeCell ref="B26:L26"/>
@@ -9319,7 +9425,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49818518-BCDA-6746-98AC-1BB0D375A367}">
-  <sheetPr>
+  <sheetPr codeName="Sheet10">
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:K34"/>
@@ -9351,7 +9457,7 @@
     <row r="4" spans="1:11" s="240" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B6" s="224" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C6" s="241">
         <v>3</v>
@@ -9378,51 +9484,51 @@
         <v>5</v>
       </c>
       <c r="J6" s="71"/>
-      <c r="K6" s="245" t="s">
-        <v>339</v>
+      <c r="K6" s="250" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="58" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B7" s="224" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C7" s="244" t="str" cm="1">
         <f t="array" ref="C7">INDEX(E7:J7,$C$6)</f>
         <v>Base Case</v>
       </c>
-      <c r="E7" s="229" t="s">
+      <c r="E7" s="241" t="s">
+        <v>332</v>
+      </c>
+      <c r="F7" s="241" t="s">
+        <v>333</v>
+      </c>
+      <c r="G7" s="241" t="s">
         <v>334</v>
       </c>
-      <c r="F7" s="229" t="s">
+      <c r="H7" s="241" t="s">
         <v>335</v>
       </c>
-      <c r="G7" s="229" t="s">
+      <c r="I7" s="241" t="s">
         <v>336</v>
       </c>
-      <c r="H7" s="229" t="s">
-        <v>337</v>
-      </c>
-      <c r="I7" s="229" t="s">
-        <v>338</v>
-      </c>
       <c r="J7" s="71"/>
     </row>
-    <row r="8" spans="1:11" s="246" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="247"/>
-      <c r="C8" s="248"/>
-      <c r="E8" s="249"/>
-      <c r="F8" s="249"/>
-      <c r="G8" s="249"/>
-      <c r="H8" s="249"/>
-      <c r="I8" s="249"/>
-      <c r="J8" s="249"/>
+    <row r="8" spans="1:11" s="245" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="246"/>
+      <c r="C8" s="247"/>
+      <c r="E8" s="248"/>
+      <c r="F8" s="248"/>
+      <c r="G8" s="248"/>
+      <c r="H8" s="248"/>
+      <c r="I8" s="248"/>
+      <c r="J8" s="248"/>
     </row>
     <row r="9" spans="1:11" s="94" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="88" t="s">
         <v>126</v>
       </c>
       <c r="B9" s="109" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C9" s="230"/>
     </row>
@@ -9432,7 +9538,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="227" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D11" s="234" cm="1">
         <f t="array" ref="D11">INDEX(E11:J11,$C$6)</f>
@@ -9460,7 +9566,7 @@
         <v>149</v>
       </c>
       <c r="C12" s="227" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D12" s="234" cm="1">
         <f t="array" ref="D12">INDEX(E12:J12,$C$6)</f>
@@ -9488,7 +9594,7 @@
         <v>150</v>
       </c>
       <c r="C13" s="227" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D13" s="234" cm="1">
         <f t="array" ref="D13">INDEX(E13:J13,$C$6)</f>
@@ -9524,7 +9630,7 @@
         <v>126</v>
       </c>
       <c r="B15" s="109" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C15" s="230"/>
       <c r="D15" s="235"/>
@@ -9547,26 +9653,26 @@
         <v>161</v>
       </c>
       <c r="C17" s="227" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D17" s="234" cm="1">
         <f t="array" ref="D17">INDEX(E17:J17,$C$6)</f>
         <v>0</v>
       </c>
       <c r="E17" s="79">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="F17" s="79">
-        <v>-2.5000000000000001E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G17" s="79">
         <v>0</v>
       </c>
       <c r="H17" s="79">
-        <v>2.5000000000000001E-2</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="I17" s="79">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="J17" s="71"/>
     </row>
@@ -9585,26 +9691,26 @@
         <v>153</v>
       </c>
       <c r="C19" s="227" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D19" s="234" cm="1">
         <f t="array" ref="D19">INDEX(E19:J19,$C$6)</f>
         <v>0</v>
       </c>
       <c r="E19" s="79">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="F19" s="79">
-        <v>-2.5000000000000001E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G19" s="79">
         <v>0</v>
       </c>
       <c r="H19" s="79">
-        <v>2.5000000000000001E-2</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="I19" s="79">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="J19" s="71"/>
     </row>
@@ -9613,26 +9719,26 @@
         <v>154</v>
       </c>
       <c r="C20" s="227" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D20" s="234" cm="1">
         <f t="array" ref="D20">INDEX(E20:J20,$C$6)</f>
         <v>0</v>
       </c>
       <c r="E20" s="79">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="F20" s="79">
-        <v>-2.5000000000000001E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G20" s="79">
         <v>0</v>
       </c>
       <c r="H20" s="79">
-        <v>2.5000000000000001E-2</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="I20" s="79">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="J20" s="71"/>
     </row>
@@ -9641,26 +9747,26 @@
         <v>128</v>
       </c>
       <c r="C21" s="227" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D21" s="234" cm="1">
         <f t="array" ref="D21">INDEX(E21:J21,$C$6)</f>
         <v>0</v>
       </c>
       <c r="E21" s="79">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="F21" s="79">
-        <v>-2.5000000000000001E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G21" s="79">
         <v>0</v>
       </c>
       <c r="H21" s="79">
-        <v>2.5000000000000001E-2</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="I21" s="79">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="J21" s="71"/>
     </row>
@@ -9669,26 +9775,26 @@
         <v>21</v>
       </c>
       <c r="C22" s="227" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D22" s="234" cm="1">
         <f t="array" ref="D22">INDEX(E22:J22,$C$6)</f>
         <v>0</v>
       </c>
       <c r="E22" s="79">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="F22" s="79">
-        <v>-2.5000000000000001E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G22" s="79">
         <v>0</v>
       </c>
       <c r="H22" s="79">
-        <v>2.5000000000000001E-2</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="I22" s="79">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="J22" s="71"/>
     </row>
@@ -9697,26 +9803,26 @@
         <v>13</v>
       </c>
       <c r="C23" s="227" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D23" s="234" cm="1">
         <f t="array" ref="D23">INDEX(E23:J23,$C$6)</f>
         <v>0</v>
       </c>
       <c r="E23" s="79">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="F23" s="79">
-        <v>-2.5000000000000001E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G23" s="79">
         <v>0</v>
       </c>
       <c r="H23" s="79">
-        <v>2.5000000000000001E-2</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="I23" s="79">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="J23" s="71"/>
     </row>
@@ -9725,7 +9831,7 @@
         <v>126</v>
       </c>
       <c r="B25" s="109" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C25" s="230"/>
     </row>
@@ -9735,7 +9841,7 @@
         <v>66</v>
       </c>
       <c r="C27" s="227" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D27" s="234" cm="1">
         <f t="array" ref="D27">INDEX(E27:J27,$C$6)</f>
@@ -9763,26 +9869,26 @@
         <v>94</v>
       </c>
       <c r="C28" s="227" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D28" s="234" cm="1">
         <f t="array" ref="D28">INDEX(E28:J28,$C$6)</f>
         <v>0</v>
       </c>
       <c r="E28" s="79">
-        <v>-0.05</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="F28" s="79">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.01</v>
       </c>
       <c r="G28" s="79">
         <v>0</v>
       </c>
       <c r="H28" s="79">
+        <v>0.01</v>
+      </c>
+      <c r="I28" s="79">
         <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="I28" s="79">
-        <v>0.05</v>
       </c>
       <c r="J28" s="71"/>
     </row>
@@ -9791,7 +9897,7 @@
         <v>126</v>
       </c>
       <c r="B30" s="109" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C30" s="230"/>
     </row>
@@ -9801,7 +9907,7 @@
         <v>73</v>
       </c>
       <c r="C32" s="227" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D32" s="234" cm="1">
         <f t="array" ref="D32">INDEX(E32:J32,$C$6)</f>
@@ -9847,7 +9953,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet11">
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J83"/>
@@ -9947,8 +10053,8 @@
       <c r="C8" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="79"/>
       <c r="G8" s="79">
         <v>0.12</v>
       </c>
@@ -9969,8 +10075,8 @@
       <c r="C9" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="79"/>
       <c r="G9" s="79">
         <v>0.18</v>
       </c>
@@ -9991,8 +10097,8 @@
       <c r="C10" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="79"/>
       <c r="G10" s="79">
         <v>0.15</v>
       </c>
@@ -10030,8 +10136,8 @@
       <c r="C14" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="79"/>
       <c r="G14" s="79">
         <v>0.35499999999999998</v>
       </c>
@@ -10057,8 +10163,8 @@
       <c r="C16" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="79"/>
       <c r="G16" s="79">
         <v>0.45</v>
       </c>
@@ -10079,8 +10185,8 @@
       <c r="C17" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="79"/>
       <c r="G17" s="79">
         <v>0.05</v>
       </c>
@@ -10101,8 +10207,8 @@
       <c r="C18" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="79"/>
       <c r="G18" s="79">
         <v>0.12</v>
       </c>
@@ -10123,8 +10229,8 @@
       <c r="C19" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="79"/>
       <c r="G19" s="79">
         <v>0.02</v>
       </c>
@@ -10145,8 +10251,8 @@
       <c r="C20" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="79"/>
       <c r="G20" s="79">
         <v>0.01</v>
       </c>
@@ -10184,8 +10290,8 @@
       <c r="C24" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="81"/>
       <c r="G24" s="81">
         <v>20</v>
       </c>
@@ -10206,8 +10312,8 @@
       <c r="C25" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="81"/>
       <c r="G25" s="81">
         <v>85</v>
       </c>
@@ -10252,8 +10358,8 @@
       <c r="C28" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="71"/>
-      <c r="F28" s="71"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="81"/>
       <c r="G28" s="81">
         <v>55000</v>
       </c>
@@ -10313,8 +10419,8 @@
       <c r="C31" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="81"/>
       <c r="G31" s="81"/>
       <c r="H31" s="81"/>
       <c r="I31" s="81"/>
@@ -10366,8 +10472,8 @@
         <v>6</v>
       </c>
       <c r="D36" s="14"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="71"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
       <c r="G36" s="81">
         <v>-527</v>
       </c>
@@ -10454,8 +10560,8 @@
       <c r="C41" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E41" s="71"/>
-      <c r="F41" s="71"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
       <c r="G41" s="81">
         <f>PMT($D$39,$D$42,-c_FS!$F$52)</f>
         <v>18225.083499484805</v>
@@ -10576,8 +10682,8 @@
         <v>6</v>
       </c>
       <c r="D50" s="14"/>
-      <c r="E50" s="71"/>
-      <c r="F50" s="71"/>
+      <c r="E50" s="81"/>
+      <c r="F50" s="81"/>
       <c r="G50" s="81">
         <v>0</v>
       </c>
@@ -11077,48 +11183,68 @@
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <conditionalFormatting sqref="G8:I10">
-    <cfRule type="expression" dxfId="16" priority="9">
+    <cfRule type="expression" dxfId="33" priority="14">
       <formula>RIGHT(G$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14:I14">
-    <cfRule type="expression" dxfId="15" priority="8">
+    <cfRule type="expression" dxfId="32" priority="13">
       <formula>RIGHT(G$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G16:I20">
-    <cfRule type="expression" dxfId="14" priority="7">
+    <cfRule type="expression" dxfId="31" priority="12">
       <formula>RIGHT(G$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G24:I25">
-    <cfRule type="expression" dxfId="13" priority="6">
+    <cfRule type="expression" dxfId="30" priority="11">
       <formula>RIGHT(G$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G28:I28">
-    <cfRule type="expression" dxfId="12" priority="5">
-      <formula>RIGHT(G$4, 1)="A"</formula>
+  <conditionalFormatting sqref="E28:I28">
+    <cfRule type="expression" dxfId="29" priority="10">
+      <formula>RIGHT(E$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G31:I31">
-    <cfRule type="expression" dxfId="11" priority="4">
-      <formula>RIGHT(G$4, 1)="A"</formula>
+  <conditionalFormatting sqref="E31:I31">
+    <cfRule type="expression" dxfId="28" priority="9">
+      <formula>RIGHT(E$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36:I36">
-    <cfRule type="expression" dxfId="10" priority="3">
-      <formula>RIGHT(G$4, 1)="A"</formula>
+  <conditionalFormatting sqref="E36:I36">
+    <cfRule type="expression" dxfId="27" priority="8">
+      <formula>RIGHT(E$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G41:I41">
-    <cfRule type="expression" dxfId="9" priority="2">
-      <formula>RIGHT(G$4, 1)="A"</formula>
+  <conditionalFormatting sqref="E41:I41">
+    <cfRule type="expression" dxfId="26" priority="7">
+      <formula>RIGHT(E$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G50:I50">
-    <cfRule type="expression" dxfId="8" priority="1">
-      <formula>RIGHT(G$4, 1)="A"</formula>
+  <conditionalFormatting sqref="E50:I50">
+    <cfRule type="expression" dxfId="25" priority="6">
+      <formula>RIGHT(E$4, 1)="A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:F10">
+    <cfRule type="expression" dxfId="5" priority="5">
+      <formula>RIGHT(E$4, 1)="A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14:F14">
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>RIGHT(E$4, 1)="A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16:F20">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>RIGHT(E$4, 1)="A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E24:F25">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>RIGHT(E$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -11145,7 +11271,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet12">
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:M60"/>
@@ -11261,16 +11387,20 @@
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="85"/>
       <c r="B7" s="224" t="s">
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="C7" s="225">
         <v>45292</v>
       </c>
+      <c r="D7" s="250" t="s">
+        <v>342</v>
+      </c>
+      <c r="E7" s="250"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="85"/>
       <c r="B8" s="224" t="s">
-        <v>307</v>
+        <v>341</v>
       </c>
       <c r="C8" s="225">
         <v>46023</v>
@@ -11366,10 +11496,10 @@
         <v>6</v>
       </c>
       <c r="D14" s="14"/>
-      <c r="E14" s="15">
+      <c r="E14" s="251">
         <v>172678</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="251">
         <v>182685</v>
       </c>
       <c r="G14" s="15"/>
@@ -11396,10 +11526,10 @@
         <v>6</v>
       </c>
       <c r="D15" s="19"/>
-      <c r="E15" s="20">
+      <c r="E15" s="15">
         <v>1992054</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="15">
         <v>2270854</v>
       </c>
       <c r="G15" s="20"/>
@@ -11426,10 +11556,10 @@
         <v>6</v>
       </c>
       <c r="D16" s="14"/>
-      <c r="E16" s="15">
+      <c r="E16" s="251">
         <v>-864477</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="251">
         <v>-831240</v>
       </c>
       <c r="G16" s="15"/>
@@ -11456,10 +11586,10 @@
         <v>6</v>
       </c>
       <c r="D17" s="23"/>
-      <c r="E17" s="20">
+      <c r="E17" s="15">
         <v>1127577</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="15">
         <v>1439614</v>
       </c>
       <c r="G17" s="20"/>
@@ -11606,10 +11736,10 @@
         <v>6</v>
       </c>
       <c r="D22" s="26"/>
-      <c r="E22" s="15">
+      <c r="E22" s="251">
         <v>16924</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="251">
         <v>21953</v>
       </c>
       <c r="G22" s="15"/>
@@ -11636,10 +11766,10 @@
         <v>6</v>
       </c>
       <c r="D23" s="19"/>
-      <c r="E23" s="20">
+      <c r="E23" s="15">
         <v>-87735</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="15">
         <v>19454</v>
       </c>
       <c r="G23" s="20"/>
@@ -11696,10 +11826,10 @@
         <v>6</v>
       </c>
       <c r="D25" s="14"/>
-      <c r="E25" s="15">
+      <c r="E25" s="251">
         <v>-1951</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="251">
         <v>-3882</v>
       </c>
       <c r="G25" s="15"/>
@@ -11726,10 +11856,10 @@
         <v>6</v>
       </c>
       <c r="D26" s="23"/>
-      <c r="E26" s="20">
+      <c r="E26" s="15">
         <v>-88000</v>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="15">
         <v>14281</v>
       </c>
       <c r="G26" s="20"/>
@@ -11756,10 +11886,10 @@
         <v>6</v>
       </c>
       <c r="D27" s="14"/>
-      <c r="E27" s="15">
+      <c r="E27" s="251">
         <v>-14594</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="251">
         <v>-13361</v>
       </c>
       <c r="G27" s="15"/>
@@ -11895,11 +12025,11 @@
         <v>6</v>
       </c>
       <c r="D34" s="14"/>
-      <c r="E34" s="17">
+      <c r="E34" s="252">
         <f>E35-SUM(E32:E33)</f>
         <v>14105</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="252">
         <f>F35-SUM(F32:F33)</f>
         <v>16675</v>
       </c>
@@ -11934,10 +12064,10 @@
         <v>6</v>
       </c>
       <c r="D35" s="19"/>
-      <c r="E35" s="20">
+      <c r="E35" s="15">
         <v>457084</v>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="15">
         <v>501180</v>
       </c>
       <c r="G35" s="20"/>
@@ -11964,10 +12094,10 @@
         <v>6</v>
       </c>
       <c r="D36" s="14"/>
-      <c r="E36" s="34">
+      <c r="E36" s="15">
         <v>189638</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="15">
         <v>180405</v>
       </c>
       <c r="G36" s="15"/>
@@ -12282,10 +12412,10 @@
         <v>6</v>
       </c>
       <c r="D46" s="27"/>
-      <c r="E46" s="28">
+      <c r="E46" s="40">
         <v>201239</v>
       </c>
-      <c r="F46" s="28">
+      <c r="F46" s="40">
         <v>359984</v>
       </c>
       <c r="G46" s="28"/>
@@ -12591,43 +12721,98 @@
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <conditionalFormatting sqref="A47">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="Error">
+    <cfRule type="containsText" dxfId="24" priority="12" operator="containsText" text="Error">
       <formula>NOT(ISERROR(SEARCH("Error",A47)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G12:J28">
-    <cfRule type="expression" dxfId="6" priority="9">
+    <cfRule type="expression" dxfId="23" priority="20">
       <formula>RIGHT(G$4, 1)="E"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G32:J33">
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="22" priority="18">
       <formula>RIGHT(G$4, 1)="E"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:J36">
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="21" priority="17">
       <formula>RIGHT(G$4, 1)="E"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G38:J43">
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" dxfId="20" priority="16">
       <formula>RIGHT(G$4, 1)="E"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G45:J46">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="19" priority="15">
       <formula>RIGHT(G$4, 1)="E"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G49:J51">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="18" priority="14">
       <formula>RIGHT(G$4, 1)="E"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G55:J58">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="17" priority="13">
       <formula>RIGHT(G$4, 1)="E"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E12:F12">
+    <cfRule type="expression" dxfId="16" priority="11">
+      <formula>RIGHT(E$4, 1)="E"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:F14">
+    <cfRule type="expression" dxfId="15" priority="10">
+      <formula>RIGHT(E$4, 1)="E"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15:F16">
+    <cfRule type="expression" dxfId="14" priority="9">
+      <formula>RIGHT(E$4, 1)="E"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:F28">
+    <cfRule type="expression" dxfId="13" priority="8">
+      <formula>RIGHT(E$4, 1)="E"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E32:F33">
+    <cfRule type="expression" dxfId="12" priority="7">
+      <formula>RIGHT(E$4, 1)="E"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E35:F36">
+    <cfRule type="expression" dxfId="11" priority="6">
+      <formula>RIGHT(E$4, 1)="E"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E38:F43">
+    <cfRule type="expression" dxfId="10" priority="5">
+      <formula>RIGHT(E$4, 1)="E"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E45:F46">
+    <cfRule type="expression" dxfId="9" priority="4">
+      <formula>RIGHT(E$4, 1)="E"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E49:F51">
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>RIGHT(E$4, 1)="E"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E56:F58">
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>RIGHT(E$4, 1)="E"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E55:F55">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>RIGHT(E$4, 1)="E"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -12644,7 +12829,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDF72717-45DD-EB4F-94B9-710A0FEF5219}">
-  <sheetPr>
+  <sheetPr codeName="Sheet2">
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1:L37"/>
@@ -12679,7 +12864,7 @@
         <v>116</v>
       </c>
       <c r="B5" s="185" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -12687,7 +12872,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B7" s="238" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C7" s="54"/>
       <c r="D7" s="54"/>
@@ -12703,22 +12888,22 @@
     <row r="8" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B9" s="242" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="243" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B11" s="243" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="243" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -12794,7 +12979,7 @@
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="54" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C23" s="188"/>
       <c r="D23" s="188"/>
@@ -12806,7 +12991,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B25" s="238" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C25" s="54"/>
       <c r="D25" s="54"/>
@@ -12821,7 +13006,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B26" s="239" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C26" s="54"/>
       <c r="D26" s="54"/>
@@ -12849,7 +13034,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B28" s="238" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C28" s="54"/>
       <c r="D28" s="54"/>
@@ -12864,7 +13049,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B29" s="239" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C29" s="54"/>
       <c r="D29" s="54"/>
@@ -12892,7 +13077,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B31" s="238" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C31" s="54"/>
       <c r="D31" s="54"/>
@@ -12907,17 +13092,17 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B32" s="239" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B34" s="238" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B35" s="239" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" spans="1:2" s="67" customFormat="1" x14ac:dyDescent="0.2">
@@ -12929,7 +13114,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ssDXO1eLV3Snv1+p1o4QF5hediUTq0Nstcgb6Q2O7RWcY/Us3OJvLUFdmGKhV6sX9GVCyYhGQse6TPmLMrq6Nw==" saltValue="mwpxap7PSkG8EN7uya6cIQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="XWkWVnzYNOiVQhIXQbmCa4WXBNT9rP15NfxAusz7cTSv53wkZT+g9njGY88iu+xpLZgEWIg4ihe73xjwkfLpTw==" saltValue="dNWf03hhxK+uMNWG7eclxw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -12937,7 +13122,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5225210B-4F42-0B4C-B131-753C07A929A8}">
-  <sheetPr>
+  <sheetPr codeName="Sheet3">
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1"/>
@@ -12954,7 +13139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4599B56D-DC95-1D41-9245-8B9F23C86689}">
-  <sheetPr>
+  <sheetPr codeName="Sheet4">
     <tabColor theme="9"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -12985,7 +13170,7 @@
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="153"/>
       <c r="F3" s="237" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G3" s="229" t="str">
         <f>i_Scenario_Manager!C6&amp;" - "&amp;i_Scenario_Manager!C7</f>
@@ -13438,7 +13623,7 @@
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B35" s="176" t="str">
         <f>o_Valuation!B77</f>
-        <v>Target Primary Capital Raised at IPO</v>
+        <v>Target Primary Capital Raised at IPO - sensitized</v>
       </c>
       <c r="C35" s="179">
         <f>o_Valuation!D77</f>
@@ -13506,7 +13691,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ObSXUAn6cBFGXtZqqgOBqYdRtUPo/54N+EbGIwaCosjfaPmWI2+a/DPk75WQM7dtdnlYk/v1NdIDynl16QC/lA==" saltValue="v0mh2dwqfjbNYL2m7FOjrQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="xp2ucfzmtknv28xvzZHrljWM8K2ktGQMntVAoBTxqv00v6NPJJIF0Asg/orYfIM8Dne6HxpbP/vHCy/hvWDrUQ==" saltValue="0m4g1bsb4WwTiq7Dve/KoQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" scale="56" orientation="landscape" errors="blank" horizontalDpi="0" verticalDpi="0"/>
@@ -13519,7 +13704,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet5">
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:I91"/>
@@ -13824,26 +14009,26 @@
     </row>
     <row r="30" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B30" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C30" s="86" t="s">
         <v>56</v>
       </c>
       <c r="D30" s="121">
-        <f>$D$26*(1+i_Scenario_Manager!$D$27)</f>
+        <f>$D$26+i_Scenario_Manager!$D$27</f>
         <v>0.10201850000000001</v>
       </c>
       <c r="E30" s="3"/>
     </row>
     <row r="31" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B31" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C31" s="86" t="s">
         <v>56</v>
       </c>
       <c r="D31" s="121">
-        <f>i_Inputs!$D$57*(1+i_Scenario_Manager!$D$28)</f>
+        <f>i_Inputs!$D$57+i_Scenario_Manager!$D$28</f>
         <v>0.04</v>
       </c>
       <c r="E31" s="3"/>
@@ -14463,7 +14648,7 @@
     </row>
     <row r="77" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B77" s="3" t="s">
-        <v>73</v>
+        <v>343</v>
       </c>
       <c r="C77" s="86" t="s">
         <v>6</v>
@@ -14527,7 +14712,7 @@
         <v>126</v>
       </c>
       <c r="B83" s="109" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C83" s="88"/>
     </row>
@@ -14539,7 +14724,7 @@
     <row r="85" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
     <row r="86" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B86" s="82" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C86" s="83"/>
       <c r="D86" s="223">
@@ -14659,7 +14844,7 @@
       <c r="C91" s="88"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="44Zk/J5ugrbWdiB86pV1kdYf2MNfYPRdhryQsIoCuTppH5QlUoj6eVbuH6wuxCMIgEZlAw25ch8OQDwwfWZJyw==" saltValue="q/OdvG72TQ8xMpYlkbUscg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="38GG9/TD3dKD9ExeCki21sUWaKHV4oizaeJ+n99/YYH/ansDCJA8iZqyOBm2i9Ikg1JcUJw/yyKiwkHN9ydFaw==" saltValue="uU35BieSaMeYmtI5LYT8mQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
@@ -14668,7 +14853,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA95FAC-DE8E-B743-B567-AED2AAADD22F}">
-  <sheetPr>
+  <sheetPr codeName="Sheet6">
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:I44"/>
@@ -15596,7 +15781,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Dq/EFpxwssGtuYiwBYnBRBqDw7Q/VTM0d7gVW7r7d28gbtMji8OArZFK4foRB6NL8EvttoJ8vYtKZuFSOCTW0Q==" saltValue="lbRWn22udMPFCqFODDmSzQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="TWcAF9ZcqjR07lhaW80bKz0kQC/GhXW6K/3jztLsdM7uNCcmIbRuo0q112gR0RLZEG1UePIo4tsMp55/kmPLwQ==" saltValue="wXoSyfpxEwdcH+a1XUs55A==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
@@ -15605,7 +15790,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC13F75-15D2-A74D-A4CC-99A7F136F7C0}">
-  <sheetPr>
+  <sheetPr codeName="Sheet7">
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1"/>
@@ -15624,7 +15809,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet8">
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:I60"/>
@@ -16692,7 +16877,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="qk/nGEuLWrNOjrqEvROkIhozMvWlrbfvgRIqNVUQGmiBHaCjvZkN3qHsrQQWaiccPi4Y81vbvFA/PzBTM3/GsQ==" saltValue="1hKaNdoWo7uv6UtA/h64zA==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KT6ioIjE4SfXpzY+cOLKteIG75kd54MF9X14epyA51+ZZ4GnGJUTz+6jhZhAFKAkkMaRqITA+DZI8J8xqMsZDg==" saltValue="ZUYuNg6jFqvU4007FSOpxw==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
@@ -16701,7 +16886,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E0AC0BD-11EA-DB47-9896-C0E6F8C3E4F5}">
-  <sheetPr>
+  <sheetPr codeName="Sheet9">
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1"/>

--- a/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
+++ b/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarashan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBEDED2A-DBD8-1D4E-B407-7AB6DC6F5A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F09C0DD-4D90-0747-AFDF-A35C578C0D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="P/esQtHEE/5gVcoDfqNzN/FNfIDAT72ni9Wg+cViuEL3wK4IUYTXUw/9dFsbAgcU4tB3RzJB7GnJZZs9jwYExA==" workbookSaltValue="k+aQesGtRPrMQlTqFr61vA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -2540,15 +2540,15 @@
     <xf numFmtId="177" fontId="4" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="15" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2557,92 +2557,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="34">
-    <dxf>
-      <fill>
-        <patternFill patternType="lightDown"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightDown"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightDown"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightDown"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightDown"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightDown"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp"/>
-      </fill>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="lightUp"/>
@@ -9374,34 +9289,34 @@
       <c r="Q24"/>
     </row>
     <row r="25" spans="1:17" ht="71" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="249" t="s">
+      <c r="B25" s="252" t="s">
         <v>331</v>
       </c>
-      <c r="C25" s="249"/>
-      <c r="D25" s="249"/>
-      <c r="E25" s="249"/>
-      <c r="F25" s="249"/>
-      <c r="G25" s="249"/>
-      <c r="H25" s="249"/>
-      <c r="I25" s="249"/>
-      <c r="J25" s="249"/>
-      <c r="K25" s="249"/>
-      <c r="L25" s="249"/>
+      <c r="C25" s="252"/>
+      <c r="D25" s="252"/>
+      <c r="E25" s="252"/>
+      <c r="F25" s="252"/>
+      <c r="G25" s="252"/>
+      <c r="H25" s="252"/>
+      <c r="I25" s="252"/>
+      <c r="J25" s="252"/>
+      <c r="K25" s="252"/>
+      <c r="L25" s="252"/>
     </row>
     <row r="26" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="249" t="s">
+      <c r="B26" s="252" t="s">
         <v>293</v>
       </c>
-      <c r="C26" s="249"/>
-      <c r="D26" s="249"/>
-      <c r="E26" s="249"/>
-      <c r="F26" s="249"/>
-      <c r="G26" s="249"/>
-      <c r="H26" s="249"/>
-      <c r="I26" s="249"/>
-      <c r="J26" s="249"/>
-      <c r="K26" s="249"/>
-      <c r="L26" s="249"/>
+      <c r="C26" s="252"/>
+      <c r="D26" s="252"/>
+      <c r="E26" s="252"/>
+      <c r="F26" s="252"/>
+      <c r="G26" s="252"/>
+      <c r="H26" s="252"/>
+      <c r="I26" s="252"/>
+      <c r="J26" s="252"/>
+      <c r="K26" s="252"/>
+      <c r="L26" s="252"/>
     </row>
     <row r="28" spans="1:17" s="67" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="67" t="s">
@@ -9484,7 +9399,7 @@
         <v>5</v>
       </c>
       <c r="J6" s="71"/>
-      <c r="K6" s="250" t="s">
+      <c r="K6" s="249" t="s">
         <v>337</v>
       </c>
     </row>
@@ -9848,19 +9763,19 @@
         <v>0</v>
       </c>
       <c r="E27" s="79">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="F27" s="79">
-        <v>2.5000000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G27" s="79">
         <v>0</v>
       </c>
       <c r="H27" s="79">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.01</v>
       </c>
       <c r="I27" s="79">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="J27" s="71"/>
     </row>
@@ -9876,7 +9791,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="79">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.01</v>
       </c>
       <c r="F28" s="79">
         <v>-0.01</v>
@@ -9888,7 +9803,7 @@
         <v>0.01</v>
       </c>
       <c r="I28" s="79">
-        <v>2.5000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="J28" s="71"/>
     </row>
@@ -11182,68 +11097,48 @@
     </row>
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <conditionalFormatting sqref="G8:I10">
-    <cfRule type="expression" dxfId="33" priority="14">
-      <formula>RIGHT(G$4, 1)="A"</formula>
+  <conditionalFormatting sqref="E8:I10">
+    <cfRule type="expression" dxfId="16" priority="5">
+      <formula>RIGHT(E$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I14">
-    <cfRule type="expression" dxfId="32" priority="13">
-      <formula>RIGHT(G$4, 1)="A"</formula>
+  <conditionalFormatting sqref="E14:I14">
+    <cfRule type="expression" dxfId="15" priority="4">
+      <formula>RIGHT(E$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16:I20">
-    <cfRule type="expression" dxfId="31" priority="12">
-      <formula>RIGHT(G$4, 1)="A"</formula>
+  <conditionalFormatting sqref="E16:I20">
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>RIGHT(E$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G24:I25">
-    <cfRule type="expression" dxfId="30" priority="11">
-      <formula>RIGHT(G$4, 1)="A"</formula>
+  <conditionalFormatting sqref="E24:I25">
+    <cfRule type="expression" dxfId="13" priority="1">
+      <formula>RIGHT(E$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:I28">
-    <cfRule type="expression" dxfId="29" priority="10">
+    <cfRule type="expression" dxfId="12" priority="10">
       <formula>RIGHT(E$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:I31">
-    <cfRule type="expression" dxfId="28" priority="9">
+    <cfRule type="expression" dxfId="11" priority="9">
       <formula>RIGHT(E$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E36:I36">
-    <cfRule type="expression" dxfId="27" priority="8">
+    <cfRule type="expression" dxfId="10" priority="8">
       <formula>RIGHT(E$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41:I41">
-    <cfRule type="expression" dxfId="26" priority="7">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>RIGHT(E$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E50:I50">
-    <cfRule type="expression" dxfId="25" priority="6">
-      <formula>RIGHT(E$4, 1)="A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:F10">
-    <cfRule type="expression" dxfId="5" priority="5">
-      <formula>RIGHT(E$4, 1)="A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14:F14">
-    <cfRule type="expression" dxfId="4" priority="4">
-      <formula>RIGHT(E$4, 1)="A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16:F20">
-    <cfRule type="expression" dxfId="3" priority="3">
-      <formula>RIGHT(E$4, 1)="A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E24:F25">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="8" priority="6">
       <formula>RIGHT(E$4, 1)="A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11392,10 +11287,10 @@
       <c r="C7" s="225">
         <v>45292</v>
       </c>
-      <c r="D7" s="250" t="s">
+      <c r="D7" s="249" t="s">
         <v>342</v>
       </c>
-      <c r="E7" s="250"/>
+      <c r="E7" s="249"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="85"/>
@@ -11496,10 +11391,10 @@
         <v>6</v>
       </c>
       <c r="D14" s="14"/>
-      <c r="E14" s="251">
+      <c r="E14" s="250">
         <v>172678</v>
       </c>
-      <c r="F14" s="251">
+      <c r="F14" s="250">
         <v>182685</v>
       </c>
       <c r="G14" s="15"/>
@@ -11556,10 +11451,10 @@
         <v>6</v>
       </c>
       <c r="D16" s="14"/>
-      <c r="E16" s="251">
+      <c r="E16" s="250">
         <v>-864477</v>
       </c>
-      <c r="F16" s="251">
+      <c r="F16" s="250">
         <v>-831240</v>
       </c>
       <c r="G16" s="15"/>
@@ -11736,10 +11631,10 @@
         <v>6</v>
       </c>
       <c r="D22" s="26"/>
-      <c r="E22" s="251">
+      <c r="E22" s="250">
         <v>16924</v>
       </c>
-      <c r="F22" s="251">
+      <c r="F22" s="250">
         <v>21953</v>
       </c>
       <c r="G22" s="15"/>
@@ -11826,10 +11721,10 @@
         <v>6</v>
       </c>
       <c r="D25" s="14"/>
-      <c r="E25" s="251">
+      <c r="E25" s="250">
         <v>-1951</v>
       </c>
-      <c r="F25" s="251">
+      <c r="F25" s="250">
         <v>-3882</v>
       </c>
       <c r="G25" s="15"/>
@@ -11886,10 +11781,10 @@
         <v>6</v>
       </c>
       <c r="D27" s="14"/>
-      <c r="E27" s="251">
+      <c r="E27" s="250">
         <v>-14594</v>
       </c>
-      <c r="F27" s="251">
+      <c r="F27" s="250">
         <v>-13361</v>
       </c>
       <c r="G27" s="15"/>
@@ -12025,11 +11920,11 @@
         <v>6</v>
       </c>
       <c r="D34" s="14"/>
-      <c r="E34" s="252">
+      <c r="E34" s="251">
         <f>E35-SUM(E32:E33)</f>
         <v>14105</v>
       </c>
-      <c r="F34" s="252">
+      <c r="F34" s="251">
         <f>F35-SUM(F32:F33)</f>
         <v>16675</v>
       </c>
@@ -12721,97 +12616,42 @@
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <conditionalFormatting sqref="A47">
-    <cfRule type="containsText" dxfId="24" priority="12" operator="containsText" text="Error">
+    <cfRule type="containsText" dxfId="7" priority="12" operator="containsText" text="Error">
       <formula>NOT(ISERROR(SEARCH("Error",A47)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G12:J28">
-    <cfRule type="expression" dxfId="23" priority="20">
-      <formula>RIGHT(G$4, 1)="E"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G32:J33">
-    <cfRule type="expression" dxfId="22" priority="18">
-      <formula>RIGHT(G$4, 1)="E"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G35:J36">
-    <cfRule type="expression" dxfId="21" priority="17">
-      <formula>RIGHT(G$4, 1)="E"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G38:J43">
-    <cfRule type="expression" dxfId="20" priority="16">
-      <formula>RIGHT(G$4, 1)="E"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G45:J46">
-    <cfRule type="expression" dxfId="19" priority="15">
-      <formula>RIGHT(G$4, 1)="E"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G49:J51">
-    <cfRule type="expression" dxfId="18" priority="14">
-      <formula>RIGHT(G$4, 1)="E"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G55:J58">
-    <cfRule type="expression" dxfId="17" priority="13">
-      <formula>RIGHT(G$4, 1)="E"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E12:F12">
-    <cfRule type="expression" dxfId="16" priority="11">
+  <conditionalFormatting sqref="E12:J28">
+    <cfRule type="expression" dxfId="6" priority="8">
       <formula>RIGHT(E$4, 1)="E"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E13:F14">
-    <cfRule type="expression" dxfId="15" priority="10">
+  <conditionalFormatting sqref="E32:J33">
+    <cfRule type="expression" dxfId="5" priority="7">
       <formula>RIGHT(E$4, 1)="E"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E15:F16">
-    <cfRule type="expression" dxfId="14" priority="9">
+  <conditionalFormatting sqref="E35:J36">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>RIGHT(E$4, 1)="E"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E17:F28">
-    <cfRule type="expression" dxfId="13" priority="8">
+  <conditionalFormatting sqref="E38:J43">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>RIGHT(E$4, 1)="E"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E32:F33">
-    <cfRule type="expression" dxfId="12" priority="7">
+  <conditionalFormatting sqref="E45:J46">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>RIGHT(E$4, 1)="E"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E35:F36">
-    <cfRule type="expression" dxfId="11" priority="6">
+  <conditionalFormatting sqref="E49:J51">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>RIGHT(E$4, 1)="E"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E38:F43">
-    <cfRule type="expression" dxfId="10" priority="5">
-      <formula>RIGHT(E$4, 1)="E"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E45:F46">
-    <cfRule type="expression" dxfId="9" priority="4">
-      <formula>RIGHT(E$4, 1)="E"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E49:F51">
-    <cfRule type="expression" dxfId="8" priority="3">
-      <formula>RIGHT(E$4, 1)="E"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E56:F58">
-    <cfRule type="expression" dxfId="7" priority="2">
-      <formula>RIGHT(E$4, 1)="E"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E55:F55">
-    <cfRule type="expression" dxfId="6" priority="1">
+  <conditionalFormatting sqref="E55:J58">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>RIGHT(E$4, 1)="E"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
+++ b/models/Bolt OÜ_Dicounted Cashflow Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarashan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F09C0DD-4D90-0747-AFDF-A35C578C0D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467BBCA2-B214-2D4A-8D34-F6187A3B3787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="P/esQtHEE/5gVcoDfqNzN/FNfIDAT72ni9Wg+cViuEL3wK4IUYTXUw/9dFsbAgcU4tB3RzJB7GnJZZs9jwYExA==" workbookSaltValue="k+aQesGtRPrMQlTqFr61vA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -9775,7 +9775,7 @@
         <v>-0.01</v>
       </c>
       <c r="I27" s="79">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="J27" s="71"/>
     </row>
@@ -9800,10 +9800,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="79">
+        <v>0</v>
+      </c>
+      <c r="I28" s="79">
         <v>0.01</v>
-      </c>
-      <c r="I28" s="79">
-        <v>0</v>
       </c>
       <c r="J28" s="71"/>
     </row>
